--- a/data/50001501 - EQ MIN LA HACIENDA B.xlsx
+++ b/data/50001501 - EQ MIN LA HACIENDA B.xlsx
@@ -1939,13 +1939,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46073.60117046296</v>
+        <v>46073.76783712963</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.550945428244</v>
+        <v>46092.71761209491</v>
       </c>
       <c r="D4" s="5">
-        <v>46111.63901569444</v>
+        <v>46111.80568236111</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1988,13 +1988,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46073.601170821756</v>
+        <v>46073.76783748843</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.55091653935</v>
+        <v>46092.71758320602</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.550946504634</v>
+        <v>46092.71761317129</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -2051,13 +2051,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46073.60117112269</v>
+        <v>46073.76783778935</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.550917071756</v>
+        <v>46092.71758373843</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.55094635417</v>
+        <v>46092.71761302083</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -2114,13 +2114,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46073.601171435184</v>
+        <v>46073.76783810185</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.55091751157</v>
+        <v>46092.717584178245</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.5509459375</v>
+        <v>46092.71761260417</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -2177,13 +2177,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46073.60117173611</v>
+        <v>46073.76783840278</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.550917939814</v>
+        <v>46092.71758460648</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.614902395835</v>
+        <v>46100.7815690625</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -2240,13 +2240,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46073.60117203704</v>
+        <v>46073.7678387037</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.55091853009</v>
+        <v>46092.71758519676</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.55094583333</v>
+        <v>46092.7176125</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -2303,11 +2303,11 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46073.60117233796</v>
+        <v>46073.767839004635</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46114.35065797454</v>
+        <v>46114.5173246412</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -2350,13 +2350,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46073.60117267361</v>
+        <v>46073.767839340275</v>
       </c>
       <c r="C11" s="8">
-        <v>46114.35064819445</v>
+        <v>46114.51731486111</v>
       </c>
       <c r="D11" s="8">
-        <v>46114.350663425925</v>
+        <v>46114.517330092596</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -2415,11 +2415,11 @@
         <v>52</v>
       </c>
       <c r="B12" s="5">
-        <v>46073.601173020834</v>
+        <v>46073.7678396875</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46133.4083725463</v>
+        <v>46133.57503921296</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2478,13 +2478,13 @@
         <v>56</v>
       </c>
       <c r="B13" s="8">
-        <v>46073.60117333333</v>
+        <v>46073.76784</v>
       </c>
       <c r="C13" s="8">
-        <v>46114.35073248843</v>
+        <v>46114.51739915509</v>
       </c>
       <c r="D13" s="8">
-        <v>46114.35074378472</v>
+        <v>46114.517410451386</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>57</v>
@@ -2531,13 +2531,13 @@
         <v>59</v>
       </c>
       <c r="B14" s="5">
-        <v>46073.60117163195</v>
+        <v>46073.76783829861</v>
       </c>
       <c r="C14" s="5">
-        <v>46097.383173055554</v>
+        <v>46097.549839722225</v>
       </c>
       <c r="D14" s="5">
-        <v>46097.38319020833</v>
+        <v>46097.549856875004</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>60</v>
@@ -2596,13 +2596,13 @@
         <v>62</v>
       </c>
       <c r="B15" s="8">
-        <v>46073.60117232639</v>
+        <v>46073.76783899305</v>
       </c>
       <c r="C15" s="8">
-        <v>46114.35038931713</v>
+        <v>46114.5170559838</v>
       </c>
       <c r="D15" s="8">
-        <v>46114.35057649306</v>
+        <v>46114.517243159724</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>63</v>
@@ -2661,13 +2661,13 @@
         <v>65</v>
       </c>
       <c r="B16" s="5">
-        <v>46073.601172662035</v>
+        <v>46073.767839328706</v>
       </c>
       <c r="C16" s="5">
-        <v>46097.38345125</v>
+        <v>46097.55011791667</v>
       </c>
       <c r="D16" s="5">
-        <v>46097.38346895833</v>
+        <v>46097.550135625</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>66</v>
@@ -2726,13 +2726,13 @@
         <v>68</v>
       </c>
       <c r="B17" s="8">
-        <v>46073.601173020834</v>
+        <v>46073.7678396875</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.35071716435</v>
+        <v>46114.517383831015</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.350732708335</v>
+        <v>46114.517399375</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>69</v>
@@ -2791,13 +2791,13 @@
         <v>72</v>
       </c>
       <c r="B18" s="5">
-        <v>46073.60117332176</v>
+        <v>46073.767839988424</v>
       </c>
       <c r="C18" s="5">
-        <v>46122.491360092594</v>
+        <v>46122.65802675926</v>
       </c>
       <c r="D18" s="5">
-        <v>46146.33018775463</v>
+        <v>46146.4968544213</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>73</v>
@@ -2844,13 +2844,13 @@
         <v>75</v>
       </c>
       <c r="B19" s="8">
-        <v>46073.60117358796</v>
+        <v>46073.76784025463</v>
       </c>
       <c r="C19" s="8">
-        <v>46114.35083560185</v>
+        <v>46114.517502268514</v>
       </c>
       <c r="D19" s="8">
-        <v>46114.35085364583</v>
+        <v>46114.517520312496</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>76</v>
@@ -2909,13 +2909,13 @@
         <v>78</v>
       </c>
       <c r="B20" s="5">
-        <v>46073.60117390046</v>
+        <v>46073.76784056713</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.38322128472</v>
+        <v>46097.54988795139</v>
       </c>
       <c r="D20" s="5">
-        <v>46097.38323788195</v>
+        <v>46097.54990454861</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>79</v>
@@ -2974,13 +2974,13 @@
         <v>81</v>
       </c>
       <c r="B21" s="8">
-        <v>46073.60117421296</v>
+        <v>46073.767840879635</v>
       </c>
       <c r="C21" s="8">
-        <v>46114.35091847222</v>
+        <v>46114.51758513889</v>
       </c>
       <c r="D21" s="8">
-        <v>46114.350934409726</v>
+        <v>46114.51760107639</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>82</v>
@@ -3039,13 +3039,13 @@
         <v>84</v>
       </c>
       <c r="B22" s="5">
-        <v>46073.601174490745</v>
+        <v>46073.76784115741</v>
       </c>
       <c r="C22" s="5">
-        <v>46122.491342291665</v>
+        <v>46122.65800895833</v>
       </c>
       <c r="D22" s="5">
-        <v>46135.264657893524</v>
+        <v>46135.43132456018</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>85</v>
@@ -3104,13 +3104,13 @@
         <v>88</v>
       </c>
       <c r="B23" s="8">
-        <v>46073.601170995375</v>
+        <v>46073.76783766204</v>
       </c>
       <c r="C23" s="8">
-        <v>46097.383514236106</v>
+        <v>46097.55018090278</v>
       </c>
       <c r="D23" s="8">
-        <v>46100.615171006946</v>
+        <v>46100.78183767361</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>89</v>
@@ -3169,13 +3169,13 @@
         <v>93</v>
       </c>
       <c r="B24" s="5">
-        <v>46114.60800928241</v>
+        <v>46114.77467594907</v>
       </c>
       <c r="C24" s="5">
-        <v>46114.609259502315</v>
+        <v>46114.77592616898</v>
       </c>
       <c r="D24" s="5">
-        <v>46114.609272870366</v>
+        <v>46114.77593953704</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>94</v>
@@ -3224,11 +3224,11 @@
         <v>95</v>
       </c>
       <c r="B25" s="8">
-        <v>46073.6011713426</v>
+        <v>46073.767838009255</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="8">
-        <v>46122.491508113424</v>
+        <v>46122.658174780096</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>96</v>
@@ -3271,13 +3271,13 @@
         <v>98</v>
       </c>
       <c r="B26" s="5">
-        <v>46073.601171608796</v>
+        <v>46073.76783827547</v>
       </c>
       <c r="C26" s="5">
-        <v>46114.35120774306</v>
+        <v>46114.51787440972</v>
       </c>
       <c r="D26" s="5">
-        <v>46114.35129936342</v>
+        <v>46114.51796603009</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>99</v>
@@ -3336,13 +3336,13 @@
         <v>103</v>
       </c>
       <c r="B27" s="8">
-        <v>46073.601171863425</v>
+        <v>46073.7678385301</v>
       </c>
       <c r="C27" s="8">
-        <v>46114.35108994213</v>
+        <v>46114.517756608795</v>
       </c>
       <c r="D27" s="8">
-        <v>46114.35109119213</v>
+        <v>46114.5177578588</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>104</v>
@@ -3397,13 +3397,13 @@
         <v>107</v>
       </c>
       <c r="B28" s="5">
-        <v>46073.60117212963</v>
+        <v>46073.767838796295</v>
       </c>
       <c r="C28" s="5">
-        <v>46114.351128587965</v>
+        <v>46114.51779525463</v>
       </c>
       <c r="D28" s="5">
-        <v>46114.35112994213</v>
+        <v>46114.517796608794</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>108</v>
@@ -3458,11 +3458,11 @@
         <v>110</v>
       </c>
       <c r="B29" s="8">
-        <v>46073.6011724537</v>
+        <v>46073.767839120366</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="8">
-        <v>46169.67997875</v>
+        <v>46169.84664541666</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>111</v>
@@ -3521,13 +3521,13 @@
         <v>113</v>
       </c>
       <c r="B30" s="5">
-        <v>46073.60117271991</v>
+        <v>46073.76783938658</v>
       </c>
       <c r="C30" s="5">
-        <v>46114.609478032406</v>
+        <v>46114.77614469908</v>
       </c>
       <c r="D30" s="5">
-        <v>46169.68003099537</v>
+        <v>46169.84669766204</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>114</v>
@@ -3582,11 +3582,11 @@
         <v>116</v>
       </c>
       <c r="B31" s="8">
-        <v>46073.601173020834</v>
+        <v>46073.7678396875</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="8">
-        <v>46169.68005634259</v>
+        <v>46169.846723009265</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>117</v>
@@ -3641,13 +3641,13 @@
         <v>119</v>
       </c>
       <c r="B32" s="5">
-        <v>46073.60117363426</v>
+        <v>46073.76784030093</v>
       </c>
       <c r="C32" s="5">
-        <v>46122.49149890046</v>
+        <v>46122.65816556713</v>
       </c>
       <c r="D32" s="5">
-        <v>46122.49151211805</v>
+        <v>46122.658178784724</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>120</v>
@@ -3706,13 +3706,13 @@
         <v>122</v>
       </c>
       <c r="B33" s="8">
-        <v>46073.60117391204</v>
+        <v>46073.7678405787</v>
       </c>
       <c r="C33" s="8">
-        <v>46122.49144170139</v>
+        <v>46122.65810836805</v>
       </c>
       <c r="D33" s="8">
-        <v>46122.49144291667</v>
+        <v>46122.65810958333</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>123</v>
@@ -3767,13 +3767,13 @@
         <v>125</v>
       </c>
       <c r="B34" s="5">
-        <v>46073.60117013889</v>
+        <v>46073.76783680556</v>
       </c>
       <c r="C34" s="5">
-        <v>46122.491484467595</v>
+        <v>46122.65815113426</v>
       </c>
       <c r="D34" s="5">
-        <v>46122.49148599537</v>
+        <v>46122.658152662036</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>126</v>
@@ -3828,13 +3828,13 @@
         <v>128</v>
       </c>
       <c r="B35" s="8">
-        <v>46073.60117045139</v>
+        <v>46073.76783711805</v>
       </c>
       <c r="C35" s="8">
-        <v>46097.38336663194</v>
+        <v>46097.55003329861</v>
       </c>
       <c r="D35" s="8">
-        <v>46097.38337914352</v>
+        <v>46097.55004581019</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>129</v>
@@ -3893,13 +3893,13 @@
         <v>131</v>
       </c>
       <c r="B36" s="5">
-        <v>46073.60117072916</v>
+        <v>46073.76783739583</v>
       </c>
       <c r="C36" s="5">
-        <v>46097.383286516204</v>
+        <v>46097.54995318287</v>
       </c>
       <c r="D36" s="5">
-        <v>46097.38328805556</v>
+        <v>46097.54995472222</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>132</v>
@@ -3954,13 +3954,13 @@
         <v>134</v>
       </c>
       <c r="B37" s="8">
-        <v>46073.60117094907</v>
+        <v>46073.76783761574</v>
       </c>
       <c r="C37" s="8">
-        <v>46097.38332991899</v>
+        <v>46097.54999658564</v>
       </c>
       <c r="D37" s="8">
-        <v>46097.38333133102</v>
+        <v>46097.54999799769</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>135</v>
@@ -4015,13 +4015,13 @@
         <v>137</v>
       </c>
       <c r="B38" s="5">
-        <v>46073.60117116898</v>
+        <v>46073.76783783565</v>
       </c>
       <c r="C38" s="5">
-        <v>46097.38335193287</v>
+        <v>46097.55001859953</v>
       </c>
       <c r="D38" s="5">
-        <v>46097.38335341435</v>
+        <v>46097.55002008102</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>138</v>
@@ -4076,13 +4076,13 @@
         <v>140</v>
       </c>
       <c r="B39" s="8">
-        <v>46073.60117140046</v>
+        <v>46073.76783806713</v>
       </c>
       <c r="C39" s="8">
-        <v>46097.383667766204</v>
+        <v>46097.550334432875</v>
       </c>
       <c r="D39" s="8">
-        <v>46097.38368121527</v>
+        <v>46097.550347881945</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>141</v>
@@ -4141,13 +4141,13 @@
         <v>143</v>
       </c>
       <c r="B40" s="5">
-        <v>46073.60117163195</v>
+        <v>46073.76783829861</v>
       </c>
       <c r="C40" s="5">
-        <v>46097.38358700232</v>
+        <v>46097.55025366898</v>
       </c>
       <c r="D40" s="5">
-        <v>46097.383588530094</v>
+        <v>46097.55025519676</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>144</v>
@@ -4202,13 +4202,13 @@
         <v>146</v>
       </c>
       <c r="B41" s="8">
-        <v>46073.60117185186</v>
+        <v>46073.76783851851</v>
       </c>
       <c r="C41" s="8">
-        <v>46097.383653310186</v>
+        <v>46097.55031997686</v>
       </c>
       <c r="D41" s="8">
-        <v>46097.3836547338</v>
+        <v>46097.550321400464</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>147</v>
@@ -4263,11 +4263,11 @@
         <v>149</v>
       </c>
       <c r="B42" s="5">
-        <v>46073.60117207176</v>
+        <v>46073.76783873842</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46142.48291041667</v>
+        <v>46142.64957708333</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>150</v>
@@ -4310,13 +4310,13 @@
         <v>152</v>
       </c>
       <c r="B43" s="8">
-        <v>46073.60117230324</v>
+        <v>46073.76783896991</v>
       </c>
       <c r="C43" s="8">
-        <v>46097.64822350694</v>
+        <v>46097.81489017361</v>
       </c>
       <c r="D43" s="8">
-        <v>46097.64824458333</v>
+        <v>46097.814911249996</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>153</v>
@@ -4375,13 +4375,13 @@
         <v>157</v>
       </c>
       <c r="B44" s="5">
-        <v>46073.60117072916</v>
+        <v>46073.76783739583</v>
       </c>
       <c r="C44" s="5">
-        <v>46097.64833244213</v>
+        <v>46097.8149991088</v>
       </c>
       <c r="D44" s="5">
-        <v>46097.64834734953</v>
+        <v>46097.8150140162</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>158</v>
@@ -4440,13 +4440,13 @@
         <v>161</v>
       </c>
       <c r="B45" s="8">
-        <v>46090.32726181713</v>
+        <v>46090.4939284838</v>
       </c>
       <c r="C45" s="8">
-        <v>46097.648378032405</v>
+        <v>46097.81504469908</v>
       </c>
       <c r="D45" s="8">
-        <v>46097.64839695602</v>
+        <v>46097.815063622686</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>162</v>
@@ -4503,11 +4503,11 @@
         <v>164</v>
       </c>
       <c r="B46" s="5">
-        <v>46090.327324224534</v>
+        <v>46090.493990891206</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46129.51230702546</v>
+        <v>46129.678973692135</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>165</v>
@@ -4564,11 +4564,11 @@
         <v>169</v>
       </c>
       <c r="B47" s="8">
-        <v>46128.40007857639</v>
+        <v>46128.56674524306</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="8">
-        <v>46129.51497804398</v>
+        <v>46129.68164471065</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>170</v>
@@ -4615,11 +4615,11 @@
         <v>172</v>
       </c>
       <c r="B48" s="5">
-        <v>46128.400088888884</v>
+        <v>46128.566755555556</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46129.51496973379</v>
+        <v>46129.68163640046</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>170</v>
@@ -4666,11 +4666,11 @@
         <v>173</v>
       </c>
       <c r="B49" s="8">
-        <v>46128.400095439814</v>
+        <v>46128.56676210648</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46129.51497234954</v>
+        <v>46129.6816390162</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>170</v>
@@ -4717,11 +4717,11 @@
         <v>174</v>
       </c>
       <c r="B50" s="5">
-        <v>46128.40010180556</v>
+        <v>46128.56676847222</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46129.51497373843</v>
+        <v>46129.68164040509</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>175</v>
@@ -4768,11 +4768,11 @@
         <v>176</v>
       </c>
       <c r="B51" s="8">
-        <v>46128.40010745371</v>
+        <v>46128.566774120365</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="8">
-        <v>46129.51496721065</v>
+        <v>46129.68163387731</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>170</v>
@@ -4819,11 +4819,11 @@
         <v>177</v>
       </c>
       <c r="B52" s="5">
-        <v>46128.40011346065</v>
+        <v>46128.566780127316</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46129.514971006945</v>
+        <v>46129.68163767361</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>170</v>
@@ -4870,11 +4870,11 @@
         <v>178</v>
       </c>
       <c r="B53" s="8">
-        <v>46128.400119467595</v>
+        <v>46128.56678613426</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46129.51497646991</v>
+        <v>46129.68164313657</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>170</v>
@@ -4921,11 +4921,11 @@
         <v>179</v>
       </c>
       <c r="B54" s="5">
-        <v>46128.4001240162</v>
+        <v>46128.566790682875</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46129.51497949074</v>
+        <v>46129.681646157405</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>170</v>
@@ -4972,11 +4972,11 @@
         <v>180</v>
       </c>
       <c r="B55" s="8">
-        <v>46128.40013016204</v>
+        <v>46128.5667968287</v>
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="8">
-        <v>46129.514975046295</v>
+        <v>46129.68164171296</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>170</v>
@@ -5023,11 +5023,11 @@
         <v>181</v>
       </c>
       <c r="B56" s="5">
-        <v>46128.400135</v>
+        <v>46128.56680166667</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46129.51498076389</v>
+        <v>46129.68164743055</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>170</v>
@@ -5074,11 +5074,11 @@
         <v>182</v>
       </c>
       <c r="B57" s="8">
-        <v>46128.40014059028</v>
+        <v>46128.566807256946</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46129.51498231481</v>
+        <v>46129.68164898148</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>170</v>
@@ -5125,11 +5125,11 @@
         <v>183</v>
       </c>
       <c r="B58" s="5">
-        <v>46128.400144687505</v>
+        <v>46128.56681135416</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46129.514968449075</v>
+        <v>46129.68163511574</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>170</v>
@@ -5176,13 +5176,13 @@
         <v>184</v>
       </c>
       <c r="B59" s="8">
-        <v>46073.60117112269</v>
+        <v>46073.76783778935</v>
       </c>
       <c r="C59" s="8">
-        <v>46097.648960810184</v>
+        <v>46097.815627476855</v>
       </c>
       <c r="D59" s="8">
-        <v>46097.64899113426</v>
+        <v>46097.81565780092</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>185</v>
@@ -5229,13 +5229,13 @@
         <v>187</v>
       </c>
       <c r="B60" s="5">
-        <v>46073.60117141204</v>
+        <v>46073.767838078704</v>
       </c>
       <c r="C60" s="5">
-        <v>46097.64860516204</v>
+        <v>46097.8152718287</v>
       </c>
       <c r="D60" s="5">
-        <v>46097.648623437504</v>
+        <v>46097.81529010416</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>188</v>
@@ -5294,13 +5294,13 @@
         <v>192</v>
       </c>
       <c r="B61" s="8">
-        <v>46073.60117172454</v>
+        <v>46073.7678383912</v>
       </c>
       <c r="C61" s="8">
-        <v>46097.648944976856</v>
+        <v>46097.81561164352</v>
       </c>
       <c r="D61" s="8">
-        <v>46097.64896204861</v>
+        <v>46097.81562871528</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>193</v>
@@ -5359,11 +5359,11 @@
         <v>197</v>
       </c>
       <c r="B62" s="5">
-        <v>46073.601172002316</v>
+        <v>46073.76783866898</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46150.61716299769</v>
+        <v>46150.78382966435</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>198</v>
@@ -5406,13 +5406,13 @@
         <v>200</v>
       </c>
       <c r="B63" s="8">
-        <v>46073.60117226852</v>
+        <v>46073.767838935186</v>
       </c>
       <c r="C63" s="8">
-        <v>46111.63961503472</v>
+        <v>46111.806281701385</v>
       </c>
       <c r="D63" s="8">
-        <v>46128.4155549537</v>
+        <v>46128.58222162037</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>201</v>
@@ -5471,13 +5471,13 @@
         <v>205</v>
       </c>
       <c r="B64" s="5">
-        <v>46073.601172546296</v>
+        <v>46073.76783921296</v>
       </c>
       <c r="C64" s="5">
-        <v>46146.72889909722</v>
+        <v>46146.89556576389</v>
       </c>
       <c r="D64" s="5">
-        <v>46158.804498240745</v>
+        <v>46158.97116490741</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>206</v>
@@ -5536,13 +5536,13 @@
         <v>209</v>
       </c>
       <c r="B65" s="8">
-        <v>46128.397901006945</v>
+        <v>46128.56456767361</v>
       </c>
       <c r="C65" s="8">
-        <v>46129.517537175925</v>
+        <v>46129.6842038426</v>
       </c>
       <c r="D65" s="8">
-        <v>46129.51753832176</v>
+        <v>46129.68420498843</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>170</v>
@@ -5591,13 +5591,13 @@
         <v>212</v>
       </c>
       <c r="B66" s="5">
-        <v>46128.39791799769</v>
+        <v>46128.56458466435</v>
       </c>
       <c r="C66" s="5">
-        <v>46129.51754765047</v>
+        <v>46129.68421431713</v>
       </c>
       <c r="D66" s="5">
-        <v>46129.51754883102</v>
+        <v>46129.684215497684</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>170</v>
@@ -5646,13 +5646,13 @@
         <v>213</v>
       </c>
       <c r="B67" s="8">
-        <v>46128.39793015046</v>
+        <v>46128.56459681713</v>
       </c>
       <c r="C67" s="8">
-        <v>46129.517607870366</v>
+        <v>46129.68427453704</v>
       </c>
       <c r="D67" s="8">
-        <v>46129.5176090625</v>
+        <v>46129.68427572917</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>170</v>
@@ -5701,13 +5701,13 @@
         <v>214</v>
       </c>
       <c r="B68" s="5">
-        <v>46128.397935</v>
+        <v>46128.564601666665</v>
       </c>
       <c r="C68" s="5">
-        <v>46129.517560011576</v>
+        <v>46129.68422667824</v>
       </c>
       <c r="D68" s="5">
-        <v>46129.51756115741</v>
+        <v>46129.68422782407</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>170</v>
@@ -5756,13 +5756,13 @@
         <v>215</v>
       </c>
       <c r="B69" s="8">
-        <v>46128.39796590278</v>
+        <v>46128.56463256944</v>
       </c>
       <c r="C69" s="8">
-        <v>46129.51762571759</v>
+        <v>46129.68429238426</v>
       </c>
       <c r="D69" s="8">
-        <v>46129.51762711805</v>
+        <v>46129.684293784725</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>170</v>
@@ -5811,13 +5811,13 @@
         <v>216</v>
       </c>
       <c r="B70" s="5">
-        <v>46128.397977789355</v>
+        <v>46128.56464445602</v>
       </c>
       <c r="C70" s="5">
-        <v>46129.51763667824</v>
+        <v>46129.68430334491</v>
       </c>
       <c r="D70" s="5">
-        <v>46129.517637881945</v>
+        <v>46129.68430454861</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>170</v>
@@ -5866,13 +5866,13 @@
         <v>217</v>
       </c>
       <c r="B71" s="8">
-        <v>46128.39798949074</v>
+        <v>46128.56465615741</v>
       </c>
       <c r="C71" s="8">
-        <v>46146.728493518516</v>
+        <v>46146.89516018519</v>
       </c>
       <c r="D71" s="8">
-        <v>46146.728494849536</v>
+        <v>46146.89516151621</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>170</v>
@@ -5921,13 +5921,13 @@
         <v>219</v>
       </c>
       <c r="B72" s="5">
-        <v>46128.39800064814</v>
+        <v>46128.564667314815</v>
       </c>
       <c r="C72" s="5">
-        <v>46146.72850666667</v>
+        <v>46146.89517333334</v>
       </c>
       <c r="D72" s="5">
-        <v>46146.72850829861</v>
+        <v>46146.89517496528</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>170</v>
@@ -5976,13 +5976,13 @@
         <v>220</v>
       </c>
       <c r="B73" s="8">
-        <v>46128.3980118287</v>
+        <v>46128.56467849537</v>
       </c>
       <c r="C73" s="8">
-        <v>46146.728561689815</v>
+        <v>46146.89522835649</v>
       </c>
       <c r="D73" s="8">
-        <v>46146.72856307871</v>
+        <v>46146.895229745365</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>170</v>
@@ -6031,13 +6031,13 @@
         <v>221</v>
       </c>
       <c r="B74" s="5">
-        <v>46128.398024953705</v>
+        <v>46128.56469162037</v>
       </c>
       <c r="C74" s="5">
-        <v>46146.7285277662</v>
+        <v>46146.89519443287</v>
       </c>
       <c r="D74" s="5">
-        <v>46146.72852917824</v>
+        <v>46146.8951958449</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>170</v>
@@ -6086,13 +6086,13 @@
         <v>222</v>
       </c>
       <c r="B75" s="8">
-        <v>46128.39803494213</v>
+        <v>46128.5647016088</v>
       </c>
       <c r="C75" s="8">
-        <v>46146.728646284726</v>
+        <v>46146.89531295139</v>
       </c>
       <c r="D75" s="8">
-        <v>46146.728647615746</v>
+        <v>46146.8953142824</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>170</v>
@@ -6141,13 +6141,13 @@
         <v>223</v>
       </c>
       <c r="B76" s="5">
-        <v>46128.398046435184</v>
+        <v>46128.56471310185</v>
       </c>
       <c r="C76" s="5">
-        <v>46146.7286625</v>
+        <v>46146.89532916667</v>
       </c>
       <c r="D76" s="5">
-        <v>46146.72866381945</v>
+        <v>46146.895330486106</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>170</v>
@@ -6196,13 +6196,13 @@
         <v>224</v>
       </c>
       <c r="B77" s="8">
-        <v>46073.60117282407</v>
+        <v>46073.76783949074</v>
       </c>
       <c r="C77" s="8">
-        <v>46150.61715427083</v>
+        <v>46150.783820937504</v>
       </c>
       <c r="D77" s="8">
-        <v>46158.80526421296</v>
+        <v>46158.971930879634</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>225</v>
@@ -6259,13 +6259,13 @@
         <v>227</v>
       </c>
       <c r="B78" s="5">
-        <v>46128.398986064814</v>
+        <v>46128.565652731486</v>
       </c>
       <c r="C78" s="5">
-        <v>46129.51917438657</v>
+        <v>46129.685841053244</v>
       </c>
       <c r="D78" s="5">
-        <v>46129.519175567126</v>
+        <v>46129.6858422338</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>170</v>
@@ -6312,13 +6312,13 @@
         <v>229</v>
       </c>
       <c r="B79" s="8">
-        <v>46128.399004363426</v>
+        <v>46128.5656710301</v>
       </c>
       <c r="C79" s="8">
-        <v>46129.519186631944</v>
+        <v>46129.68585329861</v>
       </c>
       <c r="D79" s="8">
-        <v>46129.519187997685</v>
+        <v>46129.68585466435</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>170</v>
@@ -6365,13 +6365,13 @@
         <v>230</v>
       </c>
       <c r="B80" s="5">
-        <v>46128.39901228009</v>
+        <v>46128.56567894676</v>
       </c>
       <c r="C80" s="5">
-        <v>46129.519228634264</v>
+        <v>46129.68589530092</v>
       </c>
       <c r="D80" s="5">
-        <v>46129.51922981482</v>
+        <v>46129.68589648148</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>170</v>
@@ -6418,13 +6418,13 @@
         <v>231</v>
       </c>
       <c r="B81" s="8">
-        <v>46128.39901900463</v>
+        <v>46128.565685671296</v>
       </c>
       <c r="C81" s="8">
-        <v>46129.51924313657</v>
+        <v>46129.685909803244</v>
       </c>
       <c r="D81" s="8">
-        <v>46129.519244282405</v>
+        <v>46129.685910949076</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>170</v>
@@ -6471,13 +6471,13 @@
         <v>232</v>
       </c>
       <c r="B82" s="5">
-        <v>46128.39902619213</v>
+        <v>46128.5656928588</v>
       </c>
       <c r="C82" s="5">
-        <v>46129.51925791666</v>
+        <v>46129.68592458333</v>
       </c>
       <c r="D82" s="5">
-        <v>46129.51925914352</v>
+        <v>46129.68592581019</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>170</v>
@@ -6524,13 +6524,13 @@
         <v>233</v>
       </c>
       <c r="B83" s="8">
-        <v>46128.3990324537</v>
+        <v>46128.56569912037</v>
       </c>
       <c r="C83" s="8">
-        <v>46129.519289918986</v>
+        <v>46129.68595658564</v>
       </c>
       <c r="D83" s="8">
-        <v>46129.51929111111</v>
+        <v>46129.68595777778</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>170</v>
@@ -6577,13 +6577,13 @@
         <v>234</v>
       </c>
       <c r="B84" s="5">
-        <v>46128.39903893518</v>
+        <v>46128.56570560185</v>
       </c>
       <c r="C84" s="5">
-        <v>46146.73072116898</v>
+        <v>46146.89738783565</v>
       </c>
       <c r="D84" s="5">
-        <v>46146.73072283565</v>
+        <v>46146.897389502315</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>170</v>
@@ -6630,13 +6630,13 @@
         <v>235</v>
       </c>
       <c r="B85" s="8">
-        <v>46128.39904510417</v>
+        <v>46128.56571177083</v>
       </c>
       <c r="C85" s="8">
-        <v>46146.73072903935</v>
+        <v>46146.89739570602</v>
       </c>
       <c r="D85" s="8">
-        <v>46146.7307305787</v>
+        <v>46146.89739724537</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>170</v>
@@ -6683,13 +6683,13 @@
         <v>236</v>
       </c>
       <c r="B86" s="5">
-        <v>46128.399051608794</v>
+        <v>46128.565718275466</v>
       </c>
       <c r="C86" s="5">
-        <v>46146.73073826389</v>
+        <v>46146.897404930554</v>
       </c>
       <c r="D86" s="5">
-        <v>46146.7307399537</v>
+        <v>46146.89740662037</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>170</v>
@@ -6736,13 +6736,13 @@
         <v>237</v>
       </c>
       <c r="B87" s="8">
-        <v>46128.399058599534</v>
+        <v>46128.565725266206</v>
       </c>
       <c r="C87" s="8">
-        <v>46158.80521825231</v>
+        <v>46158.97188491898</v>
       </c>
       <c r="D87" s="8">
-        <v>46158.8052196875</v>
+        <v>46158.971886354164</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>170</v>
@@ -6789,13 +6789,13 @@
         <v>238</v>
       </c>
       <c r="B88" s="5">
-        <v>46128.39906481482</v>
+        <v>46128.56573148148</v>
       </c>
       <c r="C88" s="5">
-        <v>46158.80524590278</v>
+        <v>46158.97191256944</v>
       </c>
       <c r="D88" s="5">
-        <v>46158.8052469213</v>
+        <v>46158.971913587964</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>170</v>
@@ -6842,13 +6842,13 @@
         <v>239</v>
       </c>
       <c r="B89" s="8">
-        <v>46128.399071168984</v>
+        <v>46128.56573783565</v>
       </c>
       <c r="C89" s="8">
-        <v>46158.80525888889</v>
+        <v>46158.971925555554</v>
       </c>
       <c r="D89" s="8">
-        <v>46158.805260243054</v>
+        <v>46158.971926909726</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>170</v>
@@ -6895,11 +6895,11 @@
         <v>240</v>
       </c>
       <c r="B90" s="5">
-        <v>46073.60117311343</v>
+        <v>46073.76783978009</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46157.33266760416</v>
+        <v>46157.49933427083</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>185</v>
@@ -6942,13 +6942,13 @@
         <v>242</v>
       </c>
       <c r="B91" s="8">
-        <v>46073.601173414354</v>
+        <v>46073.76784008102</v>
       </c>
       <c r="C91" s="8">
-        <v>46157.3326624537</v>
+        <v>46157.49932912037</v>
       </c>
       <c r="D91" s="8">
-        <v>46157.33266392361</v>
+        <v>46157.499330590275</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>243</v>
@@ -7005,11 +7005,11 @@
         <v>244</v>
       </c>
       <c r="B92" s="5">
-        <v>46073.60117087963</v>
+        <v>46073.7678375463</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46090.67454670139</v>
+        <v>46090.841213368054</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>54</v>
@@ -7068,13 +7068,13 @@
         <v>246</v>
       </c>
       <c r="B93" s="8">
-        <v>46073.60117122685</v>
+        <v>46073.76783789352</v>
       </c>
       <c r="C93" s="8">
-        <v>46157.33251503472</v>
+        <v>46157.499181701394</v>
       </c>
       <c r="D93" s="8">
-        <v>46157.33251638889</v>
+        <v>46157.49918305555</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>247</v>
@@ -7131,13 +7131,13 @@
         <v>248</v>
       </c>
       <c r="B94" s="5">
-        <v>46073.60117150463</v>
+        <v>46073.7678381713</v>
       </c>
       <c r="C94" s="5">
-        <v>46122.49179760416</v>
+        <v>46122.65846427083</v>
       </c>
       <c r="D94" s="5">
-        <v>46122.49181190973</v>
+        <v>46122.658478576384</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>249</v>
@@ -7194,11 +7194,11 @@
         <v>251</v>
       </c>
       <c r="B95" s="8">
-        <v>46073.60117177083</v>
+        <v>46073.7678384375</v>
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="8">
-        <v>46157.33062565972</v>
+        <v>46157.497292326385</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>252</v>
@@ -7241,11 +7241,11 @@
         <v>254</v>
       </c>
       <c r="B96" s="5">
-        <v>46073.60117204861</v>
+        <v>46073.76783871528</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46158.80858324074</v>
+        <v>46158.97524990741</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>255</v>
@@ -7304,13 +7304,13 @@
         <v>257</v>
       </c>
       <c r="B97" s="8">
-        <v>46128.399159085646</v>
+        <v>46128.56582575232</v>
       </c>
       <c r="C97" s="8">
-        <v>46129.5219956713</v>
+        <v>46129.68866233796</v>
       </c>
       <c r="D97" s="8">
-        <v>46129.52199671297</v>
+        <v>46129.68866337963</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>170</v>
@@ -7359,13 +7359,13 @@
         <v>259</v>
       </c>
       <c r="B98" s="5">
-        <v>46128.39916721065</v>
+        <v>46128.565833877314</v>
       </c>
       <c r="C98" s="5">
-        <v>46129.52200336805</v>
+        <v>46129.688670034724</v>
       </c>
       <c r="D98" s="5">
-        <v>46129.52200449074</v>
+        <v>46129.688671157404</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>170</v>
@@ -7414,13 +7414,13 @@
         <v>260</v>
       </c>
       <c r="B99" s="8">
-        <v>46128.3991728588</v>
+        <v>46128.56583952546</v>
       </c>
       <c r="C99" s="8">
-        <v>46129.522014675924</v>
+        <v>46129.688681342595</v>
       </c>
       <c r="D99" s="8">
-        <v>46129.522015787035</v>
+        <v>46129.68868245371</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>170</v>
@@ -7469,13 +7469,13 @@
         <v>261</v>
       </c>
       <c r="B100" s="5">
-        <v>46128.3991812037</v>
+        <v>46128.56584787037</v>
       </c>
       <c r="C100" s="5">
-        <v>46129.52202533565</v>
+        <v>46129.68869200231</v>
       </c>
       <c r="D100" s="5">
-        <v>46129.52202650463</v>
+        <v>46129.688693171294</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>170</v>
@@ -7524,13 +7524,13 @@
         <v>262</v>
       </c>
       <c r="B101" s="8">
-        <v>46128.3991874537</v>
+        <v>46128.565854120374</v>
       </c>
       <c r="C101" s="8">
-        <v>46129.52203578704</v>
+        <v>46129.6887024537</v>
       </c>
       <c r="D101" s="8">
-        <v>46129.522037083334</v>
+        <v>46129.68870375</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>170</v>
@@ -7579,13 +7579,13 @@
         <v>263</v>
       </c>
       <c r="B102" s="5">
-        <v>46128.39919340277</v>
+        <v>46128.565860069444</v>
       </c>
       <c r="C102" s="5">
-        <v>46158.80824061343</v>
+        <v>46158.97490728009</v>
       </c>
       <c r="D102" s="5">
-        <v>46158.808242071755</v>
+        <v>46158.974908738426</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>170</v>
@@ -7634,13 +7634,13 @@
         <v>264</v>
       </c>
       <c r="B103" s="8">
-        <v>46128.39919943287</v>
+        <v>46128.56586609954</v>
       </c>
       <c r="C103" s="8">
-        <v>46158.80844273148</v>
+        <v>46158.97510939815</v>
       </c>
       <c r="D103" s="8">
-        <v>46158.80844368055</v>
+        <v>46158.97511034722</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>170</v>
@@ -7689,13 +7689,13 @@
         <v>265</v>
       </c>
       <c r="B104" s="5">
-        <v>46128.39920584491</v>
+        <v>46128.56587251158</v>
       </c>
       <c r="C104" s="5">
-        <v>46158.80851631945</v>
+        <v>46158.97518298611</v>
       </c>
       <c r="D104" s="5">
-        <v>46158.80851797454</v>
+        <v>46158.975184641204</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>170</v>
@@ -7744,11 +7744,11 @@
         <v>266</v>
       </c>
       <c r="B105" s="8">
-        <v>46128.399212766206</v>
+        <v>46128.56587943287</v>
       </c>
       <c r="C105" s="9"/>
       <c r="D105" s="8">
-        <v>46158.80816123843</v>
+        <v>46158.97482790509</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>170</v>
@@ -7797,11 +7797,11 @@
         <v>267</v>
       </c>
       <c r="B106" s="5">
-        <v>46128.39921895834</v>
+        <v>46128.565885625</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46158.80815347222</v>
+        <v>46158.97482013889</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>170</v>
@@ -7850,11 +7850,11 @@
         <v>268</v>
       </c>
       <c r="B107" s="8">
-        <v>46128.39922582176</v>
+        <v>46128.56589248843</v>
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="8">
-        <v>46158.80814390046</v>
+        <v>46158.97481056713</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>170</v>
@@ -7903,11 +7903,11 @@
         <v>269</v>
       </c>
       <c r="B108" s="5">
-        <v>46128.39923224537</v>
+        <v>46128.56589891204</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46158.80813484953</v>
+        <v>46158.974801516204</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>170</v>
@@ -7956,11 +7956,11 @@
         <v>270</v>
       </c>
       <c r="B109" s="8">
-        <v>46073.60117258102</v>
+        <v>46073.76783924768</v>
       </c>
       <c r="C109" s="9"/>
       <c r="D109" s="8">
-        <v>46158.806923067124</v>
+        <v>46158.973589733796</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>271</v>
@@ -8017,13 +8017,13 @@
         <v>272</v>
       </c>
       <c r="B110" s="5">
-        <v>46128.39928989584</v>
+        <v>46128.565956562496</v>
       </c>
       <c r="C110" s="5">
-        <v>46157.33211148148</v>
+        <v>46157.49877814815</v>
       </c>
       <c r="D110" s="5">
-        <v>46157.332113321754</v>
+        <v>46157.498779988426</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>170</v>
@@ -8070,13 +8070,13 @@
         <v>274</v>
       </c>
       <c r="B111" s="8">
-        <v>46128.3993015625</v>
+        <v>46128.565968229166</v>
       </c>
       <c r="C111" s="8">
-        <v>46157.33211565972</v>
+        <v>46157.49878232639</v>
       </c>
       <c r="D111" s="8">
-        <v>46157.33211701389</v>
+        <v>46157.49878368055</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>170</v>
@@ -8123,13 +8123,13 @@
         <v>275</v>
       </c>
       <c r="B112" s="5">
-        <v>46128.39930916666</v>
+        <v>46128.565975833335</v>
       </c>
       <c r="C112" s="5">
-        <v>46157.33212039352</v>
+        <v>46157.49878706018</v>
       </c>
       <c r="D112" s="5">
-        <v>46157.33212157407</v>
+        <v>46157.498788240744</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>170</v>
@@ -8176,13 +8176,13 @@
         <v>276</v>
       </c>
       <c r="B113" s="8">
-        <v>46128.399315138886</v>
+        <v>46128.56598180556</v>
       </c>
       <c r="C113" s="8">
-        <v>46157.3321268287</v>
+        <v>46157.49879349537</v>
       </c>
       <c r="D113" s="8">
-        <v>46157.332128078706</v>
+        <v>46157.49879474537</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>170</v>
@@ -8229,13 +8229,13 @@
         <v>277</v>
       </c>
       <c r="B114" s="5">
-        <v>46128.39932268519</v>
+        <v>46128.56598935185</v>
       </c>
       <c r="C114" s="5">
-        <v>46157.33217627315</v>
+        <v>46157.498842939814</v>
       </c>
       <c r="D114" s="5">
-        <v>46157.332177766206</v>
+        <v>46157.49884443287</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>170</v>
@@ -8282,13 +8282,13 @@
         <v>278</v>
       </c>
       <c r="B115" s="8">
-        <v>46128.39932975694</v>
+        <v>46128.56599642361</v>
       </c>
       <c r="C115" s="8">
-        <v>46157.33213247685</v>
+        <v>46157.49879914352</v>
       </c>
       <c r="D115" s="8">
-        <v>46158.808245636574</v>
+        <v>46158.97491230324</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>170</v>
@@ -8335,13 +8335,13 @@
         <v>279</v>
       </c>
       <c r="B116" s="5">
-        <v>46128.3993362037</v>
+        <v>46128.56600287037</v>
       </c>
       <c r="C116" s="5">
-        <v>46157.33226005787</v>
+        <v>46157.49892672454</v>
       </c>
       <c r="D116" s="5">
-        <v>46158.80844748842</v>
+        <v>46158.975114155095</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>170</v>
@@ -8388,13 +8388,13 @@
         <v>280</v>
       </c>
       <c r="B117" s="8">
-        <v>46128.39934241898</v>
+        <v>46128.56600908565</v>
       </c>
       <c r="C117" s="8">
-        <v>46157.33232371528</v>
+        <v>46157.498990381944</v>
       </c>
       <c r="D117" s="8">
-        <v>46158.80852190973</v>
+        <v>46158.97518857638</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>170</v>
@@ -8441,11 +8441,11 @@
         <v>281</v>
       </c>
       <c r="B118" s="5">
-        <v>46128.399349444444</v>
+        <v>46128.566016111115</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46158.80816429398</v>
+        <v>46158.97483096065</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>170</v>
@@ -8492,11 +8492,11 @@
         <v>282</v>
       </c>
       <c r="B119" s="8">
-        <v>46128.3993559375</v>
+        <v>46128.566022604165</v>
       </c>
       <c r="C119" s="9"/>
       <c r="D119" s="8">
-        <v>46158.80815788194</v>
+        <v>46158.97482454861</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>170</v>
@@ -8543,11 +8543,11 @@
         <v>283</v>
       </c>
       <c r="B120" s="5">
-        <v>46128.39936300926</v>
+        <v>46128.56602967593</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46158.808147662035</v>
+        <v>46158.9748143287</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>170</v>
@@ -8594,11 +8594,11 @@
         <v>284</v>
       </c>
       <c r="B121" s="8">
-        <v>46128.399369074075</v>
+        <v>46128.56603574074</v>
       </c>
       <c r="C121" s="9"/>
       <c r="D121" s="8">
-        <v>46158.808138865745</v>
+        <v>46158.97480553241</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>170</v>
@@ -8645,11 +8645,11 @@
         <v>285</v>
       </c>
       <c r="B122" s="5">
-        <v>46073.601172951385</v>
+        <v>46073.767839618056</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46158.80862689815</v>
+        <v>46158.975293564814</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>286</v>
@@ -8708,13 +8708,13 @@
         <v>287</v>
       </c>
       <c r="B123" s="8">
-        <v>46128.39941763889</v>
+        <v>46128.56608430555</v>
       </c>
       <c r="C123" s="8">
-        <v>46157.33103008102</v>
+        <v>46157.49769674768</v>
       </c>
       <c r="D123" s="8">
-        <v>46157.332119212966</v>
+        <v>46157.49878587963</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>170</v>
@@ -8763,13 +8763,13 @@
         <v>289</v>
       </c>
       <c r="B124" s="5">
-        <v>46128.39942972222</v>
+        <v>46128.56609638889</v>
       </c>
       <c r="C124" s="5">
-        <v>46157.33110560185</v>
+        <v>46157.497772268514</v>
       </c>
       <c r="D124" s="5">
-        <v>46157.33212230324</v>
+        <v>46157.49878896991</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>170</v>
@@ -8818,13 +8818,13 @@
         <v>290</v>
       </c>
       <c r="B125" s="8">
-        <v>46128.3994374537</v>
+        <v>46128.56610412037</v>
       </c>
       <c r="C125" s="8">
-        <v>46157.331169756944</v>
+        <v>46157.497836423616</v>
       </c>
       <c r="D125" s="8">
-        <v>46157.33212627315</v>
+        <v>46157.49879293982</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>170</v>
@@ -8873,13 +8873,13 @@
         <v>291</v>
       </c>
       <c r="B126" s="5">
-        <v>46128.399444270835</v>
+        <v>46128.5661109375</v>
       </c>
       <c r="C126" s="5">
-        <v>46157.33122826389</v>
+        <v>46157.49789493055</v>
       </c>
       <c r="D126" s="5">
-        <v>46157.33213289352</v>
+        <v>46157.498799560184</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>170</v>
@@ -8928,13 +8928,13 @@
         <v>292</v>
       </c>
       <c r="B127" s="8">
-        <v>46128.39945019676</v>
+        <v>46128.566116863425</v>
       </c>
       <c r="C127" s="8">
-        <v>46157.33127819444</v>
+        <v>46157.49794486111</v>
       </c>
       <c r="D127" s="8">
-        <v>46157.332183391205</v>
+        <v>46157.49885005787</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>170</v>
@@ -8983,13 +8983,13 @@
         <v>293</v>
       </c>
       <c r="B128" s="5">
-        <v>46128.399457141204</v>
+        <v>46128.566123807876</v>
       </c>
       <c r="C128" s="5">
-        <v>46157.33142364583</v>
+        <v>46157.498090312496</v>
       </c>
       <c r="D128" s="5">
-        <v>46157.33213891204</v>
+        <v>46157.4988055787</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>170</v>
@@ -9038,13 +9038,13 @@
         <v>294</v>
       </c>
       <c r="B129" s="8">
-        <v>46128.399463622685</v>
+        <v>46128.56613028936</v>
       </c>
       <c r="C129" s="8">
-        <v>46157.33150461805</v>
+        <v>46157.49817128472</v>
       </c>
       <c r="D129" s="8">
-        <v>46157.332266875004</v>
+        <v>46157.49893354166</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>170</v>
@@ -9093,13 +9093,13 @@
         <v>295</v>
       </c>
       <c r="B130" s="5">
-        <v>46128.39947015046</v>
+        <v>46128.56613681713</v>
       </c>
       <c r="C130" s="5">
-        <v>46157.33161864583</v>
+        <v>46157.4982853125</v>
       </c>
       <c r="D130" s="5">
-        <v>46157.33233341435</v>
+        <v>46157.49900008102</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>170</v>
@@ -9148,11 +9148,11 @@
         <v>296</v>
       </c>
       <c r="B131" s="8">
-        <v>46128.39947685185</v>
+        <v>46128.56614351852</v>
       </c>
       <c r="C131" s="9"/>
       <c r="D131" s="8">
-        <v>46129.514448587965</v>
+        <v>46129.68111525463</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>170</v>
@@ -9201,11 +9201,11 @@
         <v>297</v>
       </c>
       <c r="B132" s="5">
-        <v>46128.399482673616</v>
+        <v>46128.56614934027</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46129.51444940972</v>
+        <v>46129.68111607639</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>170</v>
@@ -9254,11 +9254,11 @@
         <v>298</v>
       </c>
       <c r="B133" s="8">
-        <v>46128.39948821759</v>
+        <v>46128.56615488426</v>
       </c>
       <c r="C133" s="9"/>
       <c r="D133" s="8">
-        <v>46129.51445018519</v>
+        <v>46129.68111685185</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>170</v>
@@ -9307,11 +9307,11 @@
         <v>299</v>
       </c>
       <c r="B134" s="5">
-        <v>46128.39949541667</v>
+        <v>46128.566162083334</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46129.51445138889</v>
+        <v>46129.68111805555</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>170</v>
@@ -9360,13 +9360,13 @@
         <v>300</v>
       </c>
       <c r="B135" s="8">
-        <v>46073.60117232639</v>
+        <v>46073.76783899305</v>
       </c>
       <c r="C135" s="8">
-        <v>46157.33062064815</v>
+        <v>46157.497287314814</v>
       </c>
       <c r="D135" s="8">
-        <v>46158.80870234953</v>
+        <v>46158.9753690162</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>301</v>
@@ -9423,13 +9423,13 @@
         <v>303</v>
       </c>
       <c r="B136" s="5">
-        <v>46128.39956262731</v>
+        <v>46128.56622929398</v>
       </c>
       <c r="C136" s="5">
-        <v>46129.52221115741</v>
+        <v>46129.688877824075</v>
       </c>
       <c r="D136" s="5">
-        <v>46157.3313462963</v>
+        <v>46157.49801296296</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>170</v>
@@ -9478,13 +9478,13 @@
         <v>305</v>
       </c>
       <c r="B137" s="8">
-        <v>46128.39957309028</v>
+        <v>46128.56623975694</v>
       </c>
       <c r="C137" s="8">
-        <v>46129.52250082176</v>
+        <v>46129.689167488425</v>
       </c>
       <c r="D137" s="8">
-        <v>46157.331359502314</v>
+        <v>46157.49802616898</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>170</v>
@@ -9533,13 +9533,13 @@
         <v>306</v>
       </c>
       <c r="B138" s="5">
-        <v>46128.39958064815</v>
+        <v>46128.56624731481</v>
       </c>
       <c r="C138" s="5">
-        <v>46129.52259707176</v>
+        <v>46129.68926373843</v>
       </c>
       <c r="D138" s="5">
-        <v>46157.331367928244</v>
+        <v>46157.49803459491</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>170</v>
@@ -9588,13 +9588,13 @@
         <v>307</v>
       </c>
       <c r="B139" s="8">
-        <v>46128.39958712963</v>
+        <v>46128.56625379629</v>
       </c>
       <c r="C139" s="8">
-        <v>46129.52268012732</v>
+        <v>46129.68934679398</v>
       </c>
       <c r="D139" s="8">
-        <v>46157.33137369213</v>
+        <v>46157.4980403588</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>170</v>
@@ -9643,13 +9643,13 @@
         <v>308</v>
       </c>
       <c r="B140" s="5">
-        <v>46128.39959421296</v>
+        <v>46128.56626087963</v>
       </c>
       <c r="C140" s="5">
-        <v>46129.52279594907</v>
+        <v>46129.689462615745</v>
       </c>
       <c r="D140" s="5">
-        <v>46157.33137880787</v>
+        <v>46157.49804547454</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>170</v>
@@ -9698,13 +9698,13 @@
         <v>309</v>
       </c>
       <c r="B141" s="8">
-        <v>46128.39960163194</v>
+        <v>46128.566268298615</v>
       </c>
       <c r="C141" s="8">
-        <v>46157.330259803246</v>
+        <v>46157.4969264699</v>
       </c>
       <c r="D141" s="8">
-        <v>46157.331430185186</v>
+        <v>46157.49809685185</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>170</v>
@@ -9753,13 +9753,13 @@
         <v>310</v>
       </c>
       <c r="B142" s="5">
-        <v>46128.399608657404</v>
+        <v>46128.566275324076</v>
       </c>
       <c r="C142" s="5">
-        <v>46157.33040572917</v>
+        <v>46157.49707239583</v>
       </c>
       <c r="D142" s="5">
-        <v>46157.33150975694</v>
+        <v>46157.498176423614</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>170</v>
@@ -9808,13 +9808,13 @@
         <v>311</v>
       </c>
       <c r="B143" s="8">
-        <v>46128.39961503472</v>
+        <v>46128.56628170139</v>
       </c>
       <c r="C143" s="8">
-        <v>46157.32987297454</v>
+        <v>46157.4965396412</v>
       </c>
       <c r="D143" s="8">
-        <v>46157.331626238425</v>
+        <v>46157.49829290509</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>170</v>
@@ -9863,13 +9863,13 @@
         <v>312</v>
       </c>
       <c r="B144" s="5">
-        <v>46128.39962135417</v>
+        <v>46128.56628802083</v>
       </c>
       <c r="C144" s="5">
-        <v>46157.33055591435</v>
+        <v>46157.49722258102</v>
       </c>
       <c r="D144" s="5">
-        <v>46157.33055709491</v>
+        <v>46157.49722376157</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>170</v>
@@ -9918,13 +9918,13 @@
         <v>313</v>
       </c>
       <c r="B145" s="8">
-        <v>46128.39962813657</v>
+        <v>46128.56629480324</v>
       </c>
       <c r="C145" s="8">
-        <v>46157.33069737269</v>
+        <v>46157.49736403935</v>
       </c>
       <c r="D145" s="8">
-        <v>46157.33069858796</v>
+        <v>46157.49736525463</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>170</v>
@@ -9973,13 +9973,13 @@
         <v>314</v>
       </c>
       <c r="B146" s="5">
-        <v>46128.39963672454</v>
+        <v>46128.5663033912</v>
       </c>
       <c r="C146" s="5">
-        <v>46157.33075273148</v>
+        <v>46157.49741939815</v>
       </c>
       <c r="D146" s="5">
-        <v>46157.330754490744</v>
+        <v>46157.49742115741</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>170</v>
@@ -10028,13 +10028,13 @@
         <v>315</v>
       </c>
       <c r="B147" s="8">
-        <v>46128.39964325231</v>
+        <v>46128.566309918984</v>
       </c>
       <c r="C147" s="8">
-        <v>46157.33081483796</v>
+        <v>46157.49748150463</v>
       </c>
       <c r="D147" s="8">
-        <v>46157.330816354166</v>
+        <v>46157.49748302084</v>
       </c>
       <c r="E147" s="9" t="s">
         <v>170</v>
@@ -10083,11 +10083,11 @@
         <v>316</v>
       </c>
       <c r="B148" s="5">
-        <v>46073.60117333333</v>
+        <v>46073.76784</v>
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46129.51496700232</v>
+        <v>46129.68163366898</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>317</v>
@@ -10144,11 +10144,11 @@
         <v>318</v>
       </c>
       <c r="B149" s="8">
-        <v>46128.39970388889</v>
+        <v>46128.566370555556</v>
       </c>
       <c r="C149" s="9"/>
       <c r="D149" s="8">
-        <v>46129.5222168287</v>
+        <v>46129.68888349537</v>
       </c>
       <c r="E149" s="9" t="s">
         <v>170</v>
@@ -10195,11 +10195,11 @@
         <v>320</v>
       </c>
       <c r="B150" s="5">
-        <v>46128.399718148146</v>
+        <v>46128.56638481481</v>
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46129.52250760417</v>
+        <v>46129.68917427083</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>170</v>
@@ -10246,11 +10246,11 @@
         <v>321</v>
       </c>
       <c r="B151" s="8">
-        <v>46128.39972476852</v>
+        <v>46128.56639143519</v>
       </c>
       <c r="C151" s="9"/>
       <c r="D151" s="8">
-        <v>46129.522602916666</v>
+        <v>46129.68926958334</v>
       </c>
       <c r="E151" s="9" t="s">
         <v>170</v>
@@ -10297,11 +10297,11 @@
         <v>322</v>
       </c>
       <c r="B152" s="5">
-        <v>46128.39973149306</v>
+        <v>46128.56639815972</v>
       </c>
       <c r="C152" s="6"/>
       <c r="D152" s="5">
-        <v>46129.52268592593</v>
+        <v>46129.68935259259</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>170</v>
@@ -10348,11 +10348,11 @@
         <v>324</v>
       </c>
       <c r="B153" s="8">
-        <v>46128.3997390625</v>
+        <v>46128.566405729165</v>
       </c>
       <c r="C153" s="9"/>
       <c r="D153" s="8">
-        <v>46129.522802638894</v>
+        <v>46129.68946930555</v>
       </c>
       <c r="E153" s="9" t="s">
         <v>170</v>
@@ -10399,11 +10399,11 @@
         <v>325</v>
       </c>
       <c r="B154" s="5">
-        <v>46128.39974591435</v>
+        <v>46128.566412581014</v>
       </c>
       <c r="C154" s="6"/>
       <c r="D154" s="5">
-        <v>46157.33026533565</v>
+        <v>46157.496932002316</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>170</v>
@@ -10450,11 +10450,11 @@
         <v>326</v>
       </c>
       <c r="B155" s="8">
-        <v>46128.39975251157</v>
+        <v>46128.56641917824</v>
       </c>
       <c r="C155" s="9"/>
       <c r="D155" s="8">
-        <v>46157.330412337964</v>
+        <v>46157.49707900463</v>
       </c>
       <c r="E155" s="9" t="s">
         <v>170</v>
@@ -10501,11 +10501,11 @@
         <v>327</v>
       </c>
       <c r="B156" s="5">
-        <v>46128.399760671295</v>
+        <v>46128.566427337966</v>
       </c>
       <c r="C156" s="6"/>
       <c r="D156" s="5">
-        <v>46157.32987826389</v>
+        <v>46157.49654493056</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>170</v>
@@ -10552,11 +10552,11 @@
         <v>328</v>
       </c>
       <c r="B157" s="8">
-        <v>46128.3997670949</v>
+        <v>46128.566433761574</v>
       </c>
       <c r="C157" s="9"/>
       <c r="D157" s="8">
-        <v>46157.33056203704</v>
+        <v>46157.49722870371</v>
       </c>
       <c r="E157" s="9" t="s">
         <v>170</v>
@@ -10603,11 +10603,11 @@
         <v>329</v>
       </c>
       <c r="B158" s="5">
-        <v>46128.399773310186</v>
+        <v>46128.56643997685</v>
       </c>
       <c r="C158" s="6"/>
       <c r="D158" s="5">
-        <v>46157.330703541666</v>
+        <v>46157.49737020834</v>
       </c>
       <c r="E158" s="6" t="s">
         <v>170</v>
@@ -10654,11 +10654,11 @@
         <v>330</v>
       </c>
       <c r="B159" s="8">
-        <v>46128.39977965278</v>
+        <v>46128.56644631944</v>
       </c>
       <c r="C159" s="9"/>
       <c r="D159" s="8">
-        <v>46157.33075887732</v>
+        <v>46157.49742554398</v>
       </c>
       <c r="E159" s="9" t="s">
         <v>170</v>
@@ -10705,11 +10705,11 @@
         <v>331</v>
       </c>
       <c r="B160" s="5">
-        <v>46128.39978715278</v>
+        <v>46128.56645381944</v>
       </c>
       <c r="C160" s="6"/>
       <c r="D160" s="5">
-        <v>46157.33082280093</v>
+        <v>46157.4974894676</v>
       </c>
       <c r="E160" s="6" t="s">
         <v>170</v>
@@ -10756,11 +10756,11 @@
         <v>332</v>
       </c>
       <c r="B161" s="8">
-        <v>46073.60117362269</v>
+        <v>46073.76784028935</v>
       </c>
       <c r="C161" s="9"/>
       <c r="D161" s="8">
-        <v>46129.51526989583</v>
+        <v>46129.6819365625</v>
       </c>
       <c r="E161" s="9" t="s">
         <v>333</v>
@@ -10817,11 +10817,11 @@
         <v>335</v>
       </c>
       <c r="B162" s="5">
-        <v>46128.399858958335</v>
+        <v>46128.566525625</v>
       </c>
       <c r="C162" s="6"/>
       <c r="D162" s="5">
-        <v>46129.51527005787</v>
+        <v>46129.68193672453</v>
       </c>
       <c r="E162" s="6" t="s">
         <v>170</v>
@@ -10868,11 +10868,11 @@
         <v>337</v>
       </c>
       <c r="B163" s="8">
-        <v>46128.39986534722</v>
+        <v>46128.566532013894</v>
       </c>
       <c r="C163" s="9"/>
       <c r="D163" s="8">
-        <v>46129.51527077546</v>
+        <v>46129.68193744213</v>
       </c>
       <c r="E163" s="9" t="s">
         <v>170</v>
@@ -10919,11 +10919,11 @@
         <v>338</v>
       </c>
       <c r="B164" s="5">
-        <v>46128.39987255787</v>
+        <v>46128.566539224536</v>
       </c>
       <c r="C164" s="6"/>
       <c r="D164" s="5">
-        <v>46129.51527153935</v>
+        <v>46129.68193820602</v>
       </c>
       <c r="E164" s="6" t="s">
         <v>170</v>
@@ -10970,11 +10970,11 @@
         <v>339</v>
       </c>
       <c r="B165" s="8">
-        <v>46128.39987865741</v>
+        <v>46128.56654532407</v>
       </c>
       <c r="C165" s="9"/>
       <c r="D165" s="8">
-        <v>46129.51527222223</v>
+        <v>46129.68193888888</v>
       </c>
       <c r="E165" s="9" t="s">
         <v>170</v>
@@ -11021,11 +11021,11 @@
         <v>340</v>
       </c>
       <c r="B166" s="5">
-        <v>46128.399885023144</v>
+        <v>46128.566551689815</v>
       </c>
       <c r="C166" s="6"/>
       <c r="D166" s="5">
-        <v>46129.51527293981</v>
+        <v>46129.68193960648</v>
       </c>
       <c r="E166" s="6" t="s">
         <v>170</v>
@@ -11072,11 +11072,11 @@
         <v>341</v>
       </c>
       <c r="B167" s="8">
-        <v>46128.399891863424</v>
+        <v>46128.56655853009</v>
       </c>
       <c r="C167" s="9"/>
       <c r="D167" s="8">
-        <v>46129.51527365741</v>
+        <v>46129.68194032407</v>
       </c>
       <c r="E167" s="9" t="s">
         <v>170</v>
@@ -11123,11 +11123,11 @@
         <v>342</v>
       </c>
       <c r="B168" s="5">
-        <v>46128.399897650466</v>
+        <v>46128.56656431713</v>
       </c>
       <c r="C168" s="6"/>
       <c r="D168" s="5">
-        <v>46129.515274375</v>
+        <v>46129.681941041665</v>
       </c>
       <c r="E168" s="6" t="s">
         <v>170</v>
@@ -11174,11 +11174,11 @@
         <v>343</v>
       </c>
       <c r="B169" s="8">
-        <v>46128.399904143516</v>
+        <v>46128.56657081019</v>
       </c>
       <c r="C169" s="9"/>
       <c r="D169" s="8">
-        <v>46129.51527506944</v>
+        <v>46129.68194173611</v>
       </c>
       <c r="E169" s="9" t="s">
         <v>170</v>
@@ -11225,11 +11225,11 @@
         <v>344</v>
       </c>
       <c r="B170" s="5">
-        <v>46128.39991079862</v>
+        <v>46128.56657746527</v>
       </c>
       <c r="C170" s="6"/>
       <c r="D170" s="5">
-        <v>46129.51527574074</v>
+        <v>46129.681942407406</v>
       </c>
       <c r="E170" s="6" t="s">
         <v>170</v>
@@ -11276,11 +11276,11 @@
         <v>345</v>
       </c>
       <c r="B171" s="8">
-        <v>46128.39991644676</v>
+        <v>46128.566583113425</v>
       </c>
       <c r="C171" s="9"/>
       <c r="D171" s="8">
-        <v>46129.515276481485</v>
+        <v>46129.68194314815</v>
       </c>
       <c r="E171" s="9" t="s">
         <v>170</v>
@@ -11327,11 +11327,11 @@
         <v>346</v>
       </c>
       <c r="B172" s="5">
-        <v>46128.39992402778</v>
+        <v>46128.56659069445</v>
       </c>
       <c r="C172" s="6"/>
       <c r="D172" s="5">
-        <v>46129.5152771875</v>
+        <v>46129.68194385417</v>
       </c>
       <c r="E172" s="6" t="s">
         <v>170</v>
@@ -11378,11 +11378,11 @@
         <v>347</v>
       </c>
       <c r="B173" s="8">
-        <v>46128.39993115741</v>
+        <v>46128.56659782407</v>
       </c>
       <c r="C173" s="9"/>
       <c r="D173" s="8">
-        <v>46129.51527791667</v>
+        <v>46129.68194458333</v>
       </c>
       <c r="E173" s="9" t="s">
         <v>170</v>
@@ -11429,11 +11429,11 @@
         <v>348</v>
       </c>
       <c r="B174" s="5">
-        <v>46073.60117105324</v>
+        <v>46073.767837719904</v>
       </c>
       <c r="C174" s="6"/>
       <c r="D174" s="5">
-        <v>46090.469636967595</v>
+        <v>46090.63630363426</v>
       </c>
       <c r="E174" s="6" t="s">
         <v>349</v>
@@ -11476,11 +11476,11 @@
         <v>351</v>
       </c>
       <c r="B175" s="8">
-        <v>46073.601171435184</v>
+        <v>46073.76783810185</v>
       </c>
       <c r="C175" s="9"/>
       <c r="D175" s="8">
-        <v>46129.51625891204</v>
+        <v>46129.6829255787</v>
       </c>
       <c r="E175" s="9" t="s">
         <v>352</v>
@@ -11539,11 +11539,11 @@
         <v>356</v>
       </c>
       <c r="B176" s="5">
-        <v>46128.40037993055</v>
+        <v>46128.56704659722</v>
       </c>
       <c r="C176" s="6"/>
       <c r="D176" s="5">
-        <v>46129.516259861106</v>
+        <v>46129.68292652778</v>
       </c>
       <c r="E176" s="6" t="s">
         <v>170</v>
@@ -11590,11 +11590,11 @@
         <v>358</v>
       </c>
       <c r="B177" s="8">
-        <v>46128.400386388894</v>
+        <v>46128.56705305555</v>
       </c>
       <c r="C177" s="9"/>
       <c r="D177" s="8">
-        <v>46129.516260613425</v>
+        <v>46129.6829272801</v>
       </c>
       <c r="E177" s="9" t="s">
         <v>170</v>
@@ -11641,11 +11641,11 @@
         <v>359</v>
       </c>
       <c r="B178" s="5">
-        <v>46128.400393460644</v>
+        <v>46128.567060127316</v>
       </c>
       <c r="C178" s="6"/>
       <c r="D178" s="5">
-        <v>46129.516261377314</v>
+        <v>46129.682928043985</v>
       </c>
       <c r="E178" s="6" t="s">
         <v>170</v>
@@ -11692,11 +11692,11 @@
         <v>360</v>
       </c>
       <c r="B179" s="8">
-        <v>46128.400399351856</v>
+        <v>46128.56706601851</v>
       </c>
       <c r="C179" s="9"/>
       <c r="D179" s="8">
-        <v>46129.51626211806</v>
+        <v>46129.68292878472</v>
       </c>
       <c r="E179" s="9" t="s">
         <v>170</v>
@@ -11743,11 +11743,11 @@
         <v>361</v>
       </c>
       <c r="B180" s="5">
-        <v>46128.400406354165</v>
+        <v>46128.56707302084</v>
       </c>
       <c r="C180" s="6"/>
       <c r="D180" s="5">
-        <v>46129.5162628588</v>
+        <v>46129.682929525465</v>
       </c>
       <c r="E180" s="6" t="s">
         <v>170</v>
@@ -11794,11 +11794,11 @@
         <v>362</v>
       </c>
       <c r="B181" s="8">
-        <v>46128.400413634256</v>
+        <v>46128.56708030093</v>
       </c>
       <c r="C181" s="9"/>
       <c r="D181" s="8">
-        <v>46129.51626359954</v>
+        <v>46129.68293026621</v>
       </c>
       <c r="E181" s="9" t="s">
         <v>170</v>
@@ -11845,11 +11845,11 @@
         <v>363</v>
       </c>
       <c r="B182" s="5">
-        <v>46128.40042064815</v>
+        <v>46128.56708731482</v>
       </c>
       <c r="C182" s="6"/>
       <c r="D182" s="5">
-        <v>46129.51626445602</v>
+        <v>46129.68293112269</v>
       </c>
       <c r="E182" s="6" t="s">
         <v>170</v>
@@ -11896,11 +11896,11 @@
         <v>364</v>
       </c>
       <c r="B183" s="8">
-        <v>46128.4004277662</v>
+        <v>46128.567094432874</v>
       </c>
       <c r="C183" s="9"/>
       <c r="D183" s="8">
-        <v>46129.51626521991</v>
+        <v>46129.68293188658</v>
       </c>
       <c r="E183" s="9" t="s">
         <v>170</v>
@@ -11947,11 +11947,11 @@
         <v>366</v>
       </c>
       <c r="B184" s="5">
-        <v>46128.40043542824</v>
+        <v>46128.56710209491</v>
       </c>
       <c r="C184" s="6"/>
       <c r="D184" s="5">
-        <v>46129.51626603009</v>
+        <v>46129.682932696756</v>
       </c>
       <c r="E184" s="6" t="s">
         <v>170</v>
@@ -11998,11 +11998,11 @@
         <v>367</v>
       </c>
       <c r="B185" s="8">
-        <v>46128.40044216435</v>
+        <v>46128.56710883102</v>
       </c>
       <c r="C185" s="9"/>
       <c r="D185" s="8">
-        <v>46129.51626689815</v>
+        <v>46129.682933564814</v>
       </c>
       <c r="E185" s="9" t="s">
         <v>170</v>
@@ -12049,11 +12049,11 @@
         <v>368</v>
       </c>
       <c r="B186" s="5">
-        <v>46128.40044966435</v>
+        <v>46128.56711633102</v>
       </c>
       <c r="C186" s="6"/>
       <c r="D186" s="5">
-        <v>46129.51626783564</v>
+        <v>46129.682934502314</v>
       </c>
       <c r="E186" s="6" t="s">
         <v>170</v>
@@ -12100,11 +12100,11 @@
         <v>369</v>
       </c>
       <c r="B187" s="8">
-        <v>46128.40045667824</v>
+        <v>46128.56712334491</v>
       </c>
       <c r="C187" s="9"/>
       <c r="D187" s="8">
-        <v>46129.516268761574</v>
+        <v>46129.68293542824</v>
       </c>
       <c r="E187" s="9" t="s">
         <v>170</v>
@@ -12151,11 +12151,11 @@
         <v>370</v>
       </c>
       <c r="B188" s="5">
-        <v>46073.60117172454</v>
+        <v>46073.7678383912</v>
       </c>
       <c r="C188" s="6"/>
       <c r="D188" s="5">
-        <v>46129.51652914352</v>
+        <v>46129.68319581018</v>
       </c>
       <c r="E188" s="6" t="s">
         <v>371</v>
@@ -12214,11 +12214,11 @@
         <v>372</v>
       </c>
       <c r="B189" s="8">
-        <v>46128.4005152662</v>
+        <v>46128.56718193287</v>
       </c>
       <c r="C189" s="9"/>
       <c r="D189" s="8">
-        <v>46129.51652921297</v>
+        <v>46129.683195879625</v>
       </c>
       <c r="E189" s="9" t="s">
         <v>170</v>
@@ -12267,11 +12267,11 @@
         <v>374</v>
       </c>
       <c r="B190" s="5">
-        <v>46128.400523425924</v>
+        <v>46128.567190092595</v>
       </c>
       <c r="C190" s="6"/>
       <c r="D190" s="5">
-        <v>46129.51652993055</v>
+        <v>46129.68319659722</v>
       </c>
       <c r="E190" s="6" t="s">
         <v>170</v>
@@ -12320,11 +12320,11 @@
         <v>375</v>
       </c>
       <c r="B191" s="8">
-        <v>46128.40052988426</v>
+        <v>46128.567196550925</v>
       </c>
       <c r="C191" s="9"/>
       <c r="D191" s="8">
-        <v>46129.51653064815</v>
+        <v>46129.683197314815</v>
       </c>
       <c r="E191" s="9" t="s">
         <v>170</v>
@@ -12373,11 +12373,11 @@
         <v>376</v>
       </c>
       <c r="B192" s="5">
-        <v>46128.4005380787</v>
+        <v>46128.56720474537</v>
       </c>
       <c r="C192" s="6"/>
       <c r="D192" s="5">
-        <v>46129.516531354166</v>
+        <v>46129.68319802084</v>
       </c>
       <c r="E192" s="6" t="s">
         <v>170</v>
@@ -12426,11 +12426,11 @@
         <v>377</v>
       </c>
       <c r="B193" s="8">
-        <v>46128.40054480324</v>
+        <v>46128.56721146991</v>
       </c>
       <c r="C193" s="9"/>
       <c r="D193" s="8">
-        <v>46129.516532106485</v>
+        <v>46129.68319877315</v>
       </c>
       <c r="E193" s="9" t="s">
         <v>170</v>
@@ -12479,11 +12479,11 @@
         <v>378</v>
       </c>
       <c r="B194" s="5">
-        <v>46128.40055128472</v>
+        <v>46128.56721795139</v>
       </c>
       <c r="C194" s="6"/>
       <c r="D194" s="5">
-        <v>46129.51653284722</v>
+        <v>46129.68319951389</v>
       </c>
       <c r="E194" s="6" t="s">
         <v>170</v>
@@ -12532,11 +12532,11 @@
         <v>379</v>
       </c>
       <c r="B195" s="8">
-        <v>46128.40055881944</v>
+        <v>46128.56722548611</v>
       </c>
       <c r="C195" s="9"/>
       <c r="D195" s="8">
-        <v>46129.51653361111</v>
+        <v>46129.68320027778</v>
       </c>
       <c r="E195" s="9" t="s">
         <v>170</v>
@@ -12585,11 +12585,11 @@
         <v>380</v>
       </c>
       <c r="B196" s="5">
-        <v>46128.40056666666</v>
+        <v>46128.567233333335</v>
       </c>
       <c r="C196" s="6"/>
       <c r="D196" s="5">
-        <v>46129.51653434028</v>
+        <v>46129.68320100695</v>
       </c>
       <c r="E196" s="6" t="s">
         <v>170</v>
@@ -12638,11 +12638,11 @@
         <v>381</v>
       </c>
       <c r="B197" s="8">
-        <v>46128.400573437495</v>
+        <v>46128.56724010417</v>
       </c>
       <c r="C197" s="9"/>
       <c r="D197" s="8">
-        <v>46129.51653508102</v>
+        <v>46129.683201747685</v>
       </c>
       <c r="E197" s="9" t="s">
         <v>170</v>
@@ -12691,11 +12691,11 @@
         <v>382</v>
       </c>
       <c r="B198" s="5">
-        <v>46128.40057939815</v>
+        <v>46128.56724606482</v>
       </c>
       <c r="C198" s="6"/>
       <c r="D198" s="5">
-        <v>46129.51653583333</v>
+        <v>46129.683202500004</v>
       </c>
       <c r="E198" s="6" t="s">
         <v>170</v>
@@ -12744,11 +12744,11 @@
         <v>383</v>
       </c>
       <c r="B199" s="8">
-        <v>46128.40058570602</v>
+        <v>46128.56725237268</v>
       </c>
       <c r="C199" s="9"/>
       <c r="D199" s="8">
-        <v>46129.51653658565</v>
+        <v>46129.683203252316</v>
       </c>
       <c r="E199" s="9" t="s">
         <v>170</v>
@@ -12797,11 +12797,11 @@
         <v>384</v>
       </c>
       <c r="B200" s="5">
-        <v>46128.400592777776</v>
+        <v>46128.56725944445</v>
       </c>
       <c r="C200" s="6"/>
       <c r="D200" s="5">
-        <v>46129.51653731482</v>
+        <v>46129.683203981476</v>
       </c>
       <c r="E200" s="6" t="s">
         <v>170</v>
@@ -12850,11 +12850,11 @@
         <v>385</v>
       </c>
       <c r="B201" s="8">
-        <v>46073.60117201389</v>
+        <v>46073.76783868056</v>
       </c>
       <c r="C201" s="9"/>
       <c r="D201" s="8">
-        <v>46129.516863240744</v>
+        <v>46129.68352990741</v>
       </c>
       <c r="E201" s="9" t="s">
         <v>386</v>
@@ -12911,11 +12911,11 @@
         <v>387</v>
       </c>
       <c r="B202" s="5">
-        <v>46128.40064677084</v>
+        <v>46128.567313437496</v>
       </c>
       <c r="C202" s="6"/>
       <c r="D202" s="5">
-        <v>46129.51685976852</v>
+        <v>46129.68352643518</v>
       </c>
       <c r="E202" s="6" t="s">
         <v>170</v>
@@ -12962,11 +12962,11 @@
         <v>389</v>
       </c>
       <c r="B203" s="8">
-        <v>46128.40065387731</v>
+        <v>46128.56732054398</v>
       </c>
       <c r="C203" s="9"/>
       <c r="D203" s="8">
-        <v>46129.51686050926</v>
+        <v>46129.68352717593</v>
       </c>
       <c r="E203" s="9" t="s">
         <v>170</v>
@@ -13013,11 +13013,11 @@
         <v>390</v>
       </c>
       <c r="B204" s="5">
-        <v>46128.40065994213</v>
+        <v>46128.5673266088</v>
       </c>
       <c r="C204" s="6"/>
       <c r="D204" s="5">
-        <v>46129.51686125</v>
+        <v>46129.68352791667</v>
       </c>
       <c r="E204" s="6" t="s">
         <v>170</v>
@@ -13064,11 +13064,11 @@
         <v>391</v>
       </c>
       <c r="B205" s="8">
-        <v>46128.400666284724</v>
+        <v>46128.56733295139</v>
       </c>
       <c r="C205" s="9"/>
       <c r="D205" s="8">
-        <v>46129.51686199074</v>
+        <v>46129.683528657406</v>
       </c>
       <c r="E205" s="9" t="s">
         <v>170</v>
@@ -13115,11 +13115,11 @@
         <v>392</v>
       </c>
       <c r="B206" s="5">
-        <v>46128.400671875</v>
+        <v>46128.56733854167</v>
       </c>
       <c r="C206" s="6"/>
       <c r="D206" s="5">
-        <v>46129.516862766206</v>
+        <v>46129.68352943287</v>
       </c>
       <c r="E206" s="6" t="s">
         <v>170</v>
@@ -13166,11 +13166,11 @@
         <v>393</v>
       </c>
       <c r="B207" s="8">
-        <v>46128.40067851852</v>
+        <v>46128.56734518518</v>
       </c>
       <c r="C207" s="9"/>
       <c r="D207" s="8">
-        <v>46129.516863530094</v>
+        <v>46129.68353019676</v>
       </c>
       <c r="E207" s="9" t="s">
         <v>170</v>
@@ -13217,11 +13217,11 @@
         <v>394</v>
       </c>
       <c r="B208" s="5">
-        <v>46128.40068510416</v>
+        <v>46128.567351770835</v>
       </c>
       <c r="C208" s="6"/>
       <c r="D208" s="5">
-        <v>46129.51686422454</v>
+        <v>46129.683530891205</v>
       </c>
       <c r="E208" s="6" t="s">
         <v>170</v>
@@ -13268,11 +13268,11 @@
         <v>396</v>
       </c>
       <c r="B209" s="8">
-        <v>46128.40069071759</v>
+        <v>46128.56735738426</v>
       </c>
       <c r="C209" s="9"/>
       <c r="D209" s="8">
-        <v>46129.516864930556</v>
+        <v>46129.68353159723</v>
       </c>
       <c r="E209" s="9" t="s">
         <v>170</v>
@@ -13319,11 +13319,11 @@
         <v>397</v>
       </c>
       <c r="B210" s="5">
-        <v>46128.400695902776</v>
+        <v>46128.56736256945</v>
       </c>
       <c r="C210" s="6"/>
       <c r="D210" s="5">
-        <v>46129.51686565972</v>
+        <v>46129.68353232639</v>
       </c>
       <c r="E210" s="6" t="s">
         <v>170</v>
@@ -13370,11 +13370,11 @@
         <v>398</v>
       </c>
       <c r="B211" s="8">
-        <v>46128.40070153935</v>
+        <v>46128.567368206015</v>
       </c>
       <c r="C211" s="9"/>
       <c r="D211" s="8">
-        <v>46129.51686645833</v>
+        <v>46129.683533125004</v>
       </c>
       <c r="E211" s="9" t="s">
         <v>170</v>
@@ -13421,11 +13421,11 @@
         <v>399</v>
       </c>
       <c r="B212" s="5">
-        <v>46128.400707002314</v>
+        <v>46128.56737366898</v>
       </c>
       <c r="C212" s="6"/>
       <c r="D212" s="5">
-        <v>46129.5168671875</v>
+        <v>46129.68353385417</v>
       </c>
       <c r="E212" s="6" t="s">
         <v>170</v>
@@ -13472,11 +13472,11 @@
         <v>400</v>
       </c>
       <c r="B213" s="8">
-        <v>46128.400711863425</v>
+        <v>46128.56737853009</v>
       </c>
       <c r="C213" s="9"/>
       <c r="D213" s="8">
-        <v>46129.516867928236</v>
+        <v>46129.68353459491</v>
       </c>
       <c r="E213" s="9" t="s">
         <v>170</v>
@@ -13523,11 +13523,11 @@
         <v>401</v>
       </c>
       <c r="B214" s="5">
-        <v>46073.60117229167</v>
+        <v>46073.76783895833</v>
       </c>
       <c r="C214" s="6"/>
       <c r="D214" s="5">
-        <v>46129.51723466435</v>
+        <v>46129.683901331024</v>
       </c>
       <c r="E214" s="6" t="s">
         <v>402</v>
@@ -13584,11 +13584,11 @@
         <v>404</v>
       </c>
       <c r="B215" s="8">
-        <v>46128.400799525465</v>
+        <v>46128.56746619213</v>
       </c>
       <c r="C215" s="9"/>
       <c r="D215" s="8">
-        <v>46129.527850150465</v>
+        <v>46129.69451681713</v>
       </c>
       <c r="E215" s="9" t="s">
         <v>170</v>
@@ -13635,11 +13635,11 @@
         <v>405</v>
       </c>
       <c r="B216" s="5">
-        <v>46128.40080708334</v>
+        <v>46128.56747375</v>
       </c>
       <c r="C216" s="6"/>
       <c r="D216" s="5">
-        <v>46129.5278769213</v>
+        <v>46129.69454358796</v>
       </c>
       <c r="E216" s="6" t="s">
         <v>170</v>
@@ -13686,11 +13686,11 @@
         <v>406</v>
       </c>
       <c r="B217" s="8">
-        <v>46128.40081416667</v>
+        <v>46128.567480833335</v>
       </c>
       <c r="C217" s="9"/>
       <c r="D217" s="8">
-        <v>46129.52789783565</v>
+        <v>46129.694564502315</v>
       </c>
       <c r="E217" s="9" t="s">
         <v>170</v>
@@ -13737,11 +13737,11 @@
         <v>407</v>
       </c>
       <c r="B218" s="5">
-        <v>46128.40082196759</v>
+        <v>46128.56748863426</v>
       </c>
       <c r="C218" s="6"/>
       <c r="D218" s="5">
-        <v>46129.52791761574</v>
+        <v>46129.694584282406</v>
       </c>
       <c r="E218" s="6" t="s">
         <v>170</v>
@@ -13788,11 +13788,11 @@
         <v>408</v>
       </c>
       <c r="B219" s="8">
-        <v>46128.40082953704</v>
+        <v>46128.5674962037</v>
       </c>
       <c r="C219" s="9"/>
       <c r="D219" s="8">
-        <v>46129.527940266205</v>
+        <v>46129.69460693287</v>
       </c>
       <c r="E219" s="9" t="s">
         <v>170</v>
@@ -13839,11 +13839,11 @@
         <v>409</v>
       </c>
       <c r="B220" s="5">
-        <v>46128.400837407404</v>
+        <v>46128.567504074075</v>
       </c>
       <c r="C220" s="6"/>
       <c r="D220" s="5">
-        <v>46129.52795960648</v>
+        <v>46129.69462627315</v>
       </c>
       <c r="E220" s="6" t="s">
         <v>170</v>
@@ -13890,11 +13890,11 @@
         <v>410</v>
       </c>
       <c r="B221" s="8">
-        <v>46128.40084611111</v>
+        <v>46128.56751277778</v>
       </c>
       <c r="C221" s="9"/>
       <c r="D221" s="8">
-        <v>46129.52798398148</v>
+        <v>46129.69465064815</v>
       </c>
       <c r="E221" s="9" t="s">
         <v>170</v>
@@ -13941,11 +13941,11 @@
         <v>411</v>
       </c>
       <c r="B222" s="5">
-        <v>46128.40085472222</v>
+        <v>46128.56752138889</v>
       </c>
       <c r="C222" s="6"/>
       <c r="D222" s="5">
-        <v>46129.528004907406</v>
+        <v>46129.69467157408</v>
       </c>
       <c r="E222" s="6" t="s">
         <v>170</v>
@@ -13992,11 +13992,11 @@
         <v>412</v>
       </c>
       <c r="B223" s="8">
-        <v>46128.40086168981</v>
+        <v>46128.56752835648</v>
       </c>
       <c r="C223" s="9"/>
       <c r="D223" s="8">
-        <v>46129.528025590276</v>
+        <v>46129.69469225695</v>
       </c>
       <c r="E223" s="9" t="s">
         <v>170</v>
@@ -14043,11 +14043,11 @@
         <v>413</v>
       </c>
       <c r="B224" s="5">
-        <v>46128.40086961805</v>
+        <v>46128.567536284725</v>
       </c>
       <c r="C224" s="6"/>
       <c r="D224" s="5">
-        <v>46129.52804671296</v>
+        <v>46129.694713379635</v>
       </c>
       <c r="E224" s="6" t="s">
         <v>170</v>
@@ -14094,11 +14094,11 @@
         <v>414</v>
       </c>
       <c r="B225" s="8">
-        <v>46128.40087725694</v>
+        <v>46128.56754392361</v>
       </c>
       <c r="C225" s="9"/>
       <c r="D225" s="8">
-        <v>46129.5280690162</v>
+        <v>46129.694735682875</v>
       </c>
       <c r="E225" s="9" t="s">
         <v>170</v>
@@ -14145,11 +14145,11 @@
         <v>415</v>
       </c>
       <c r="B226" s="5">
-        <v>46128.40088428241</v>
+        <v>46128.567550949076</v>
       </c>
       <c r="C226" s="6"/>
       <c r="D226" s="5">
-        <v>46129.52810822916</v>
+        <v>46129.694774895834</v>
       </c>
       <c r="E226" s="6" t="s">
         <v>170</v>
@@ -14196,11 +14196,11 @@
         <v>416</v>
       </c>
       <c r="B227" s="8">
-        <v>46073.601172905095</v>
+        <v>46073.76783957176</v>
       </c>
       <c r="C227" s="9"/>
       <c r="D227" s="8">
-        <v>46076.668122187504</v>
+        <v>46076.83478885417</v>
       </c>
       <c r="E227" s="9" t="s">
         <v>417</v>
@@ -14243,11 +14243,11 @@
         <v>419</v>
       </c>
       <c r="B228" s="5">
-        <v>46073.601173194445</v>
+        <v>46073.76783986111</v>
       </c>
       <c r="C228" s="6"/>
       <c r="D228" s="5">
-        <v>46090.67485423612</v>
+        <v>46090.84152090277</v>
       </c>
       <c r="E228" s="6" t="s">
         <v>420</v>
@@ -14306,11 +14306,11 @@
         <v>423</v>
       </c>
       <c r="B229" s="8">
-        <v>46073.60117346064</v>
+        <v>46073.767840127315</v>
       </c>
       <c r="C229" s="9"/>
       <c r="D229" s="8">
-        <v>46114.350726516204</v>
+        <v>46114.517393182876</v>
       </c>
       <c r="E229" s="9" t="s">
         <v>424</v>
@@ -14369,11 +14369,11 @@
         <v>426</v>
       </c>
       <c r="B230" s="5">
-        <v>46090.4717330787</v>
+        <v>46090.63839974537</v>
       </c>
       <c r="C230" s="6"/>
       <c r="D230" s="5">
-        <v>46091.69625637731</v>
+        <v>46091.862923043984</v>
       </c>
       <c r="E230" s="6" t="s">
         <v>427</v>
@@ -14418,11 +14418,11 @@
         <v>429</v>
       </c>
       <c r="B231" s="8">
-        <v>46090.47183018518</v>
+        <v>46090.638496851854</v>
       </c>
       <c r="C231" s="9"/>
       <c r="D231" s="8">
-        <v>46090.96268834491</v>
+        <v>46091.12935501157</v>
       </c>
       <c r="E231" s="9" t="s">
         <v>430</v>
@@ -14481,11 +14481,11 @@
         <v>432</v>
       </c>
       <c r="B232" s="5">
-        <v>46090.472055763894</v>
+        <v>46090.63872243055</v>
       </c>
       <c r="C232" s="6"/>
       <c r="D232" s="5">
-        <v>46099.96883761574</v>
+        <v>46100.13550428241</v>
       </c>
       <c r="E232" s="6" t="s">
         <v>433</v>

--- a/data/50001501 - EQ MIN LA HACIENDA B.xlsx
+++ b/data/50001501 - EQ MIN LA HACIENDA B.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2651" uniqueCount="434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2652" uniqueCount="434">
   <si>
     <t>50001501 - EQ. MIN. LA HACIENDA</t>
   </si>
@@ -5361,9 +5361,11 @@
       <c r="B62" s="5">
         <v>46073.76783866898</v>
       </c>
-      <c r="C62" s="6"/>
+      <c r="C62" s="5">
+        <v>46191.772903206016</v>
+      </c>
       <c r="D62" s="5">
-        <v>46150.78382966435</v>
+        <v>46191.77291996528</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>198</v>
@@ -5398,8 +5400,12 @@
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
       <c r="S62" s="6"/>
-      <c r="T62" s="6"/>
-      <c r="U62" s="6"/>
+      <c r="T62" s="6">
+        <v>1</v>
+      </c>
+      <c r="U62" s="11" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">

--- a/data/50001501 - EQ MIN LA HACIENDA B.xlsx
+++ b/data/50001501 - EQ MIN LA HACIENDA B.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2652" uniqueCount="434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2655" uniqueCount="434">
   <si>
     <t>50001501 - EQ. MIN. LA HACIENDA</t>
   </si>
@@ -178,162 +178,165 @@
     <t>Recepcion Tableros</t>
   </si>
   <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
+    <t>1213330953387467</t>
+  </si>
+  <si>
+    <t>Ingenieria Jefe de proyecto:</t>
+  </si>
+  <si>
+    <t>Ingenieria Detalle,Ingenieria basica Rodete,Ingenieria Basica Motor,Analisis de costeo</t>
+  </si>
+  <si>
+    <t>1213330953387468</t>
+  </si>
+  <si>
+    <t>Ingenieria Basica Motor</t>
+  </si>
+  <si>
+    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,propuesta motor</t>
+  </si>
+  <si>
+    <t>1213330953387470</t>
+  </si>
+  <si>
+    <t>Ingenieria basica Rodete</t>
+  </si>
+  <si>
+    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,propuesta nucleo rodete,propuesta alabes</t>
+  </si>
+  <si>
+    <t>1213330953387471</t>
+  </si>
+  <si>
+    <t>Ingenieria Detalle</t>
+  </si>
+  <si>
+    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,propuesta compras a codigo // aprovisionamiento,Planos preliminar</t>
+  </si>
+  <si>
+    <t>1213330953387472</t>
+  </si>
+  <si>
+    <t>Analisis de costeo</t>
+  </si>
+  <si>
+    <t>Ingenieria Detalle,Ingenieria basica Rodete,Ingenieria Basica Motor</t>
+  </si>
+  <si>
+    <t>Ingenieria Jefe de proyecto:,Costos</t>
+  </si>
+  <si>
+    <t>1213330953387473</t>
+  </si>
+  <si>
+    <t>Propuesta compras:</t>
+  </si>
+  <si>
+    <t>propuesta tableros,propuesta nucleo rodete,propuesta alabes,propuesta motor,propuesta compras a codigo // aprovisionamiento</t>
+  </si>
+  <si>
+    <t>1213330953387474</t>
+  </si>
+  <si>
+    <t>propuesta alabes</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC Alabe</t>
+  </si>
+  <si>
+    <t>1213330953387475</t>
+  </si>
+  <si>
+    <t>propuesta motor</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC motor</t>
+  </si>
+  <si>
+    <t>1213330953387476</t>
+  </si>
+  <si>
+    <t>propuesta tableros</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC Tableros ot 4215</t>
+  </si>
+  <si>
+    <t>1213330953387477</t>
+  </si>
+  <si>
+    <t>propuesta nucleo rodete</t>
+  </si>
+  <si>
+    <t>benjamin.bustos@zitron.com</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC Rodete</t>
+  </si>
+  <si>
+    <t>1213330953387478</t>
+  </si>
+  <si>
+    <t>propuesta compras a codigo // aprovisionamiento</t>
+  </si>
+  <si>
+    <t>hugo isla martinez</t>
+  </si>
+  <si>
+    <t>hugo.isla@zitron.com</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC materiales</t>
+  </si>
+  <si>
+    <t>1213910573903699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Propuesta fabricación exterma </t>
+  </si>
+  <si>
+    <t>1213330953387479</t>
+  </si>
+  <si>
+    <t>Compras:</t>
+  </si>
+  <si>
+    <t>Alabe,Tablero ot 4215,rodete,Motor,Materiales a codigo // compras locales aprovisionamientomiento:</t>
+  </si>
+  <si>
+    <t>1213330953387480</t>
+  </si>
+  <si>
+    <t>Alabe</t>
+  </si>
+  <si>
+    <t>Eliana</t>
+  </si>
+  <si>
+    <t>ecarico@zitron.com</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe,Fabricación Alabe</t>
+  </si>
+  <si>
+    <t>1213330953387481</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe</t>
+  </si>
+  <si>
+    <t>Fabricación Alabe,Alabe</t>
+  </si>
+  <si>
+    <t>Baja</t>
+  </si>
+  <si>
     <t>Tarea sin iniciar</t>
   </si>
   <si>
-    <t>1213330953387467</t>
-  </si>
-  <si>
-    <t>Ingenieria Jefe de proyecto:</t>
-  </si>
-  <si>
-    <t>Ingenieria Detalle,Ingenieria basica Rodete,Ingenieria Basica Motor,Analisis de costeo</t>
-  </si>
-  <si>
-    <t>1213330953387468</t>
-  </si>
-  <si>
-    <t>Ingenieria Basica Motor</t>
-  </si>
-  <si>
-    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,propuesta motor</t>
-  </si>
-  <si>
-    <t>1213330953387470</t>
-  </si>
-  <si>
-    <t>Ingenieria basica Rodete</t>
-  </si>
-  <si>
-    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,propuesta nucleo rodete,propuesta alabes</t>
-  </si>
-  <si>
-    <t>1213330953387471</t>
-  </si>
-  <si>
-    <t>Ingenieria Detalle</t>
-  </si>
-  <si>
-    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,propuesta compras a codigo // aprovisionamiento,Planos preliminar</t>
-  </si>
-  <si>
-    <t>1213330953387472</t>
-  </si>
-  <si>
-    <t>Analisis de costeo</t>
-  </si>
-  <si>
-    <t>Ingenieria Detalle,Ingenieria basica Rodete,Ingenieria Basica Motor</t>
-  </si>
-  <si>
-    <t>Ingenieria Jefe de proyecto:,Costos</t>
-  </si>
-  <si>
-    <t>1213330953387473</t>
-  </si>
-  <si>
-    <t>Propuesta compras:</t>
-  </si>
-  <si>
-    <t>propuesta tableros,propuesta nucleo rodete,propuesta alabes,propuesta motor,propuesta compras a codigo // aprovisionamiento</t>
-  </si>
-  <si>
-    <t>1213330953387474</t>
-  </si>
-  <si>
-    <t>propuesta alabes</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC Alabe</t>
-  </si>
-  <si>
-    <t>1213330953387475</t>
-  </si>
-  <si>
-    <t>propuesta motor</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC motor</t>
-  </si>
-  <si>
-    <t>1213330953387476</t>
-  </si>
-  <si>
-    <t>propuesta tableros</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC Tableros ot 4215</t>
-  </si>
-  <si>
-    <t>1213330953387477</t>
-  </si>
-  <si>
-    <t>propuesta nucleo rodete</t>
-  </si>
-  <si>
-    <t>benjamin.bustos@zitron.com</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC Rodete</t>
-  </si>
-  <si>
-    <t>1213330953387478</t>
-  </si>
-  <si>
-    <t>propuesta compras a codigo // aprovisionamiento</t>
-  </si>
-  <si>
-    <t>hugo isla martinez</t>
-  </si>
-  <si>
-    <t>hugo.isla@zitron.com</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC materiales</t>
-  </si>
-  <si>
-    <t>1213910573903699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Propuesta fabricación exterma </t>
-  </si>
-  <si>
-    <t>1213330953387479</t>
-  </si>
-  <si>
-    <t>Compras:</t>
-  </si>
-  <si>
-    <t>Alabe,Tablero ot 4215,rodete,Motor,Materiales a codigo // compras locales aprovisionamientomiento:</t>
-  </si>
-  <si>
-    <t>1213330953387480</t>
-  </si>
-  <si>
-    <t>Alabe</t>
-  </si>
-  <si>
-    <t>Eliana</t>
-  </si>
-  <si>
-    <t>ecarico@zitron.com</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe,Fabricación Alabe</t>
-  </si>
-  <si>
-    <t>1213330953387481</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe</t>
-  </si>
-  <si>
-    <t>Fabricación Alabe,Alabe</t>
-  </si>
-  <si>
-    <t>Baja</t>
-  </si>
-  <si>
     <t>1213330953387482</t>
   </si>
   <si>
@@ -635,9 +638,6 @@
   </si>
   <si>
     <t>Preparación1 Materiales,Check Planos,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1214075676500706</t>
@@ -2419,7 +2419,7 @@
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46133.57503921296</v>
+        <v>46191.7935575463</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2469,7 +2469,7 @@
       <c r="T12" s="6">
         <v>0</v>
       </c>
-      <c r="U12" s="10" t="s">
+      <c r="U12" s="12" t="s">
         <v>55</v>
       </c>
     </row>
@@ -3228,7 +3228,7 @@
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="8">
-        <v>46122.658174780096</v>
+        <v>46191.79346162037</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>96</v>
@@ -3264,7 +3264,9 @@
       <c r="R25" s="9"/>
       <c r="S25" s="9"/>
       <c r="T25" s="9"/>
-      <c r="U25" s="9"/>
+      <c r="U25" s="12" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
@@ -3389,12 +3391,12 @@
         <v>0</v>
       </c>
       <c r="U27" s="10" t="s">
-        <v>55</v>
+        <v>107</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B28" s="5">
         <v>46073.767838796295</v>
@@ -3406,7 +3408,7 @@
         <v>46114.517796608794</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
@@ -3439,7 +3441,7 @@
         <v>104</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3450,22 +3452,24 @@
         <v>0</v>
       </c>
       <c r="U28" s="10" t="s">
-        <v>55</v>
+        <v>107</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B29" s="8">
         <v>46073.767839120366</v>
       </c>
-      <c r="C29" s="9"/>
+      <c r="C29" s="8">
+        <v>46191.79343924769</v>
+      </c>
       <c r="D29" s="8">
-        <v>46169.84664541666</v>
+        <v>46191.793455046296</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
@@ -3495,7 +3499,7 @@
         <v>96</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P29" s="9" t="s">
         <v>96</v>
@@ -3510,15 +3514,15 @@
         <v>31</v>
       </c>
       <c r="T29" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="U29" s="10" t="s">
-        <v>55</v>
+        <v>1</v>
+      </c>
+      <c r="U29" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B30" s="5">
         <v>46073.76783938658</v>
@@ -3530,7 +3534,7 @@
         <v>46169.84669766204</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
@@ -3557,13 +3561,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>82</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3574,22 +3578,24 @@
         <v>0</v>
       </c>
       <c r="U30" s="10" t="s">
-        <v>55</v>
+        <v>107</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B31" s="8">
         <v>46073.7678396875</v>
       </c>
-      <c r="C31" s="9"/>
+      <c r="C31" s="8">
+        <v>46191.79342321759</v>
+      </c>
       <c r="D31" s="8">
-        <v>46169.846723009265</v>
+        <v>46191.79342476852</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
@@ -3616,13 +3622,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -3633,12 +3639,12 @@
         <v>0</v>
       </c>
       <c r="U31" s="10" t="s">
-        <v>55</v>
+        <v>107</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B32" s="5">
         <v>46073.76784030093</v>
@@ -3650,7 +3656,7 @@
         <v>46122.658178784724</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
@@ -3680,7 +3686,7 @@
         <v>96</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>96</v>
@@ -3703,7 +3709,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B33" s="8">
         <v>46073.7678405787</v>
@@ -3715,7 +3721,7 @@
         <v>46122.65810958333</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
@@ -3742,13 +3748,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O33" s="9" t="s">
         <v>85</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
@@ -3759,12 +3765,12 @@
         <v>0</v>
       </c>
       <c r="U33" s="10" t="s">
-        <v>55</v>
+        <v>107</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B34" s="5">
         <v>46073.76783680556</v>
@@ -3776,7 +3782,7 @@
         <v>46122.658152662036</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
@@ -3803,13 +3809,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3820,12 +3826,12 @@
         <v>0</v>
       </c>
       <c r="U34" s="10" t="s">
-        <v>55</v>
+        <v>107</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B35" s="8">
         <v>46073.76783711805</v>
@@ -3837,7 +3843,7 @@
         <v>46097.55004581019</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
@@ -3867,7 +3873,7 @@
         <v>96</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P35" s="9" t="s">
         <v>96</v>
@@ -3890,7 +3896,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B36" s="5">
         <v>46073.76783739583</v>
@@ -3902,7 +3908,7 @@
         <v>46097.54995472222</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
@@ -3929,13 +3935,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>79</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3946,12 +3952,12 @@
         <v>0</v>
       </c>
       <c r="U36" s="10" t="s">
-        <v>55</v>
+        <v>107</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B37" s="8">
         <v>46073.76783761574</v>
@@ -3963,7 +3969,7 @@
         <v>46097.54999799769</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
@@ -3990,13 +3996,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -4007,12 +4013,12 @@
         <v>0</v>
       </c>
       <c r="U37" s="10" t="s">
-        <v>55</v>
+        <v>107</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B38" s="5">
         <v>46073.76783783565</v>
@@ -4024,7 +4030,7 @@
         <v>46097.55002008102</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
@@ -4051,13 +4057,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -4068,12 +4074,12 @@
         <v>0</v>
       </c>
       <c r="U38" s="10" t="s">
-        <v>55</v>
+        <v>107</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B39" s="8">
         <v>46073.76783806713</v>
@@ -4085,7 +4091,7 @@
         <v>46097.550347881945</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
@@ -4115,7 +4121,7 @@
         <v>96</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P39" s="9" t="s">
         <v>96</v>
@@ -4138,7 +4144,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B40" s="5">
         <v>46073.76783829861</v>
@@ -4150,7 +4156,7 @@
         <v>46097.55025519676</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
@@ -4177,13 +4183,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>89</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4194,12 +4200,12 @@
         <v>0</v>
       </c>
       <c r="U40" s="10" t="s">
-        <v>55</v>
+        <v>107</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B41" s="8">
         <v>46073.76783851851</v>
@@ -4211,7 +4217,7 @@
         <v>46097.550321400464</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
@@ -4238,13 +4244,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
@@ -4255,12 +4261,12 @@
         <v>0</v>
       </c>
       <c r="U41" s="10" t="s">
-        <v>55</v>
+        <v>107</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B42" s="5">
         <v>46073.76783873842</v>
@@ -4270,7 +4276,7 @@
         <v>46142.64957708333</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>25</v>
@@ -4294,7 +4300,7 @@
         <v>26</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4307,7 +4313,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B43" s="8">
         <v>46073.76783896991</v>
@@ -4319,16 +4325,16 @@
         <v>46097.814911249996</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I43" s="8">
         <v>46007</v>
@@ -4346,13 +4352,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O43" s="9" t="s">
         <v>66</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q43" s="8">
         <v>46007</v>
@@ -4372,7 +4378,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B44" s="5">
         <v>46073.76783739583</v>
@@ -4384,16 +4390,16 @@
         <v>46097.8150140162</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I44" s="5">
         <v>46028</v>
@@ -4411,13 +4417,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q44" s="5">
         <v>46028</v>
@@ -4437,7 +4443,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B45" s="8">
         <v>46090.4939284838</v>
@@ -4449,16 +4455,16 @@
         <v>46097.815063622686</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I45" s="9"/>
       <c r="J45" s="8">
@@ -4474,13 +4480,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q45" s="8">
         <v>46035</v>
@@ -4500,7 +4506,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B46" s="5">
         <v>46090.493990891206</v>
@@ -4510,16 +4516,16 @@
         <v>46129.678973692135</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I46" s="6"/>
       <c r="J46" s="5">
@@ -4535,10 +4541,10 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4556,31 +4562,31 @@
         <v>0</v>
       </c>
       <c r="U46" s="10" t="s">
-        <v>55</v>
+        <v>107</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B47" s="8">
         <v>46128.56674524306</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="8">
-        <v>46129.68164471065</v>
+        <v>46191.79533020833</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I47" s="9"/>
       <c r="J47" s="8">
@@ -4596,13 +4602,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q47" s="9"/>
       <c r="R47" s="9"/>
@@ -4612,26 +4618,26 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B48" s="5">
         <v>46128.566755555556</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46129.68163640046</v>
+        <v>46191.795324189814</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I48" s="6"/>
       <c r="J48" s="5">
@@ -4647,13 +4653,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4663,26 +4669,26 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B49" s="8">
         <v>46128.56676210648</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46129.6816390162</v>
+        <v>46191.79531811342</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I49" s="9"/>
       <c r="J49" s="8">
@@ -4698,13 +4704,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q49" s="9"/>
       <c r="R49" s="9"/>
@@ -4714,26 +4720,26 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B50" s="5">
         <v>46128.56676847222</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46129.68164040509</v>
+        <v>46191.79531166666</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I50" s="6"/>
       <c r="J50" s="5">
@@ -4749,13 +4755,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4765,26 +4771,26 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B51" s="8">
         <v>46128.566774120365</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="8">
-        <v>46129.68163387731</v>
+        <v>46191.795306423606</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I51" s="9"/>
       <c r="J51" s="8">
@@ -4800,13 +4806,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -4816,26 +4822,26 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B52" s="5">
         <v>46128.566780127316</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46129.68163767361</v>
+        <v>46191.7952890625</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -4851,13 +4857,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4867,26 +4873,26 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B53" s="8">
         <v>46128.56678613426</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46129.68164313657</v>
+        <v>46191.79528329861</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I53" s="9"/>
       <c r="J53" s="8">
@@ -4902,13 +4908,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -4918,26 +4924,26 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B54" s="5">
         <v>46128.566790682875</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46129.681646157405</v>
+        <v>46191.79527969907</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I54" s="6"/>
       <c r="J54" s="5">
@@ -4953,13 +4959,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4969,26 +4975,26 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B55" s="8">
         <v>46128.5667968287</v>
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="8">
-        <v>46129.68164171296</v>
+        <v>46191.795272557865</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I55" s="9"/>
       <c r="J55" s="8">
@@ -5004,13 +5010,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q55" s="9"/>
       <c r="R55" s="9"/>
@@ -5020,26 +5026,26 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B56" s="5">
         <v>46128.56680166667</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46129.68164743055</v>
+        <v>46191.795269375</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I56" s="6"/>
       <c r="J56" s="5">
@@ -5055,13 +5061,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -5071,26 +5077,26 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B57" s="8">
         <v>46128.566807256946</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46129.68164898148</v>
+        <v>46191.7952605787</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I57" s="9"/>
       <c r="J57" s="8">
@@ -5106,13 +5112,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q57" s="9"/>
       <c r="R57" s="9"/>
@@ -5122,26 +5128,26 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B58" s="5">
         <v>46128.56681135416</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46129.68163511574</v>
+        <v>46191.79525575231</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I58" s="6"/>
       <c r="J58" s="5">
@@ -5157,13 +5163,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -5173,7 +5179,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B59" s="8">
         <v>46073.76783778935</v>
@@ -5185,7 +5191,7 @@
         <v>46097.81565780092</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>25</v>
@@ -5209,7 +5215,7 @@
         <v>26</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P59" s="9" t="s">
         <v>26</v>
@@ -5226,7 +5232,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B60" s="5">
         <v>46073.767838078704</v>
@@ -5238,16 +5244,16 @@
         <v>46097.81529010416</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I60" s="5">
         <v>46041</v>
@@ -5265,13 +5271,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q60" s="5">
         <v>46041</v>
@@ -5291,7 +5297,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B61" s="8">
         <v>46073.7678383912</v>
@@ -5303,16 +5309,16 @@
         <v>46097.81562871528</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I61" s="8">
         <v>46043</v>
@@ -5330,13 +5336,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q61" s="8">
         <v>46043</v>
@@ -5356,7 +5362,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B62" s="5">
         <v>46073.76783866898</v>
@@ -5368,7 +5374,7 @@
         <v>46191.77291996528</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>25</v>
@@ -5392,7 +5398,7 @@
         <v>26</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>26</v>
@@ -5409,7 +5415,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B63" s="8">
         <v>46073.767838935186</v>
@@ -5421,16 +5427,16 @@
         <v>46128.58222162037</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I63" s="8">
         <v>46045</v>
@@ -5448,13 +5454,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q63" s="8">
         <v>46045</v>
@@ -5474,7 +5480,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B64" s="5">
         <v>46073.76783921296</v>
@@ -5486,16 +5492,16 @@
         <v>46158.97116490741</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I64" s="5">
         <v>46050</v>
@@ -5513,13 +5519,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q64" s="5">
         <v>46050</v>
@@ -5534,7 +5540,7 @@
         <v>1</v>
       </c>
       <c r="U64" s="12" t="s">
-        <v>208</v>
+        <v>55</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
@@ -5551,16 +5557,16 @@
         <v>46129.68420498843</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I65" s="8">
         <v>46050</v>
@@ -5578,7 +5584,7 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O65" s="9" t="s">
         <v>210</v>
@@ -5606,16 +5612,16 @@
         <v>46129.684215497684</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I66" s="5">
         <v>46050</v>
@@ -5633,10 +5639,10 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>211</v>
@@ -5661,16 +5667,16 @@
         <v>46129.68427572917</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I67" s="8">
         <v>46050</v>
@@ -5688,10 +5694,10 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="P67" s="9" t="s">
         <v>211</v>
@@ -5716,16 +5722,16 @@
         <v>46129.68422782407</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I68" s="5">
         <v>46050</v>
@@ -5743,10 +5749,10 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>211</v>
@@ -5771,16 +5777,16 @@
         <v>46129.684293784725</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I69" s="8">
         <v>46050</v>
@@ -5798,10 +5804,10 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="P69" s="9" t="s">
         <v>211</v>
@@ -5826,16 +5832,16 @@
         <v>46129.68430454861</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I70" s="5">
         <v>46050</v>
@@ -5853,7 +5859,7 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>26</v>
@@ -5881,16 +5887,16 @@
         <v>46146.89516151621</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I71" s="8">
         <v>46050</v>
@@ -5908,7 +5914,7 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O71" s="9" t="s">
         <v>218</v>
@@ -5936,16 +5942,16 @@
         <v>46146.89517496528</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I72" s="5">
         <v>46050</v>
@@ -5963,10 +5969,10 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>211</v>
@@ -5991,16 +5997,16 @@
         <v>46146.895229745365</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I73" s="8">
         <v>46050</v>
@@ -6018,10 +6024,10 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="P73" s="9" t="s">
         <v>211</v>
@@ -6046,16 +6052,16 @@
         <v>46146.8951958449</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I74" s="5">
         <v>46050</v>
@@ -6073,10 +6079,10 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>211</v>
@@ -6101,16 +6107,16 @@
         <v>46146.8953142824</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I75" s="8">
         <v>46050</v>
@@ -6128,10 +6134,10 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="P75" s="9" t="s">
         <v>211</v>
@@ -6156,16 +6162,16 @@
         <v>46146.895330486106</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I76" s="5">
         <v>46050</v>
@@ -6183,10 +6189,10 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>211</v>
@@ -6217,10 +6223,10 @@
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I77" s="9"/>
       <c r="J77" s="8">
@@ -6236,13 +6242,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O77" s="9" t="s">
         <v>226</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q77" s="8">
         <v>46055</v>
@@ -6257,7 +6263,7 @@
         <v>1</v>
       </c>
       <c r="U77" s="10" t="s">
-        <v>55</v>
+        <v>107</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
@@ -6274,16 +6280,16 @@
         <v>46129.6858422338</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I78" s="6"/>
       <c r="J78" s="5">
@@ -6302,7 +6308,7 @@
         <v>225</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>228</v>
@@ -6327,16 +6333,16 @@
         <v>46129.68585466435</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I79" s="9"/>
       <c r="J79" s="8">
@@ -6355,7 +6361,7 @@
         <v>225</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P79" s="9" t="s">
         <v>228</v>
@@ -6380,16 +6386,16 @@
         <v>46129.68589648148</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I80" s="6"/>
       <c r="J80" s="5">
@@ -6408,7 +6414,7 @@
         <v>225</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>228</v>
@@ -6433,16 +6439,16 @@
         <v>46129.685910949076</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I81" s="9"/>
       <c r="J81" s="8">
@@ -6461,7 +6467,7 @@
         <v>225</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P81" s="9" t="s">
         <v>228</v>
@@ -6486,16 +6492,16 @@
         <v>46129.68592581019</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I82" s="6"/>
       <c r="J82" s="5">
@@ -6514,7 +6520,7 @@
         <v>225</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>228</v>
@@ -6539,16 +6545,16 @@
         <v>46129.68595777778</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I83" s="9"/>
       <c r="J83" s="8">
@@ -6567,7 +6573,7 @@
         <v>225</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P83" s="9" t="s">
         <v>228</v>
@@ -6592,16 +6598,16 @@
         <v>46146.897389502315</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I84" s="6"/>
       <c r="J84" s="5">
@@ -6620,7 +6626,7 @@
         <v>225</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>228</v>
@@ -6645,16 +6651,16 @@
         <v>46146.89739724537</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I85" s="9"/>
       <c r="J85" s="8">
@@ -6673,7 +6679,7 @@
         <v>225</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P85" s="9" t="s">
         <v>228</v>
@@ -6698,16 +6704,16 @@
         <v>46146.89740662037</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I86" s="6"/>
       <c r="J86" s="5">
@@ -6726,7 +6732,7 @@
         <v>225</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>228</v>
@@ -6751,16 +6757,16 @@
         <v>46158.971886354164</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I87" s="9"/>
       <c r="J87" s="8">
@@ -6779,7 +6785,7 @@
         <v>225</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P87" s="9" t="s">
         <v>228</v>
@@ -6804,16 +6810,16 @@
         <v>46158.971913587964</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I88" s="6"/>
       <c r="J88" s="5">
@@ -6832,7 +6838,7 @@
         <v>225</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>228</v>
@@ -6857,16 +6863,16 @@
         <v>46158.971926909726</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I89" s="9"/>
       <c r="J89" s="8">
@@ -6885,7 +6891,7 @@
         <v>225</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P89" s="9" t="s">
         <v>228</v>
@@ -6903,12 +6909,14 @@
       <c r="B90" s="5">
         <v>46073.76783978009</v>
       </c>
-      <c r="C90" s="6"/>
+      <c r="C90" s="5">
+        <v>46191.79355605324</v>
+      </c>
       <c r="D90" s="5">
-        <v>46157.49933427083</v>
+        <v>46191.79356716435</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>25</v>
@@ -6940,8 +6948,12 @@
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
       <c r="S90" s="6"/>
-      <c r="T90" s="6"/>
-      <c r="U90" s="6"/>
+      <c r="T90" s="6">
+        <v>1</v>
+      </c>
+      <c r="U90" s="11" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
@@ -6963,10 +6975,10 @@
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I91" s="9"/>
       <c r="J91" s="8">
@@ -6982,13 +6994,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q91" s="8">
         <v>46030</v>
@@ -7003,7 +7015,7 @@
         <v>0.2</v>
       </c>
       <c r="U91" s="12" t="s">
-        <v>208</v>
+        <v>55</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
@@ -7013,9 +7025,11 @@
       <c r="B92" s="5">
         <v>46073.7678375463</v>
       </c>
-      <c r="C92" s="6"/>
+      <c r="C92" s="5">
+        <v>46191.79353944444</v>
+      </c>
       <c r="D92" s="5">
-        <v>46090.841213368054</v>
+        <v>46191.79355703703</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>54</v>
@@ -7024,10 +7038,10 @@
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I92" s="5">
         <v>46069</v>
@@ -7045,10 +7059,10 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>245</v>
@@ -7063,10 +7077,10 @@
         <v>31</v>
       </c>
       <c r="T92" s="6">
-        <v>0</v>
-      </c>
-      <c r="U92" s="10" t="s">
-        <v>55</v>
+        <v>1</v>
+      </c>
+      <c r="U92" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
@@ -7089,10 +7103,10 @@
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H93" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I93" s="9"/>
       <c r="J93" s="8">
@@ -7108,13 +7122,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q93" s="8">
         <v>46014</v>
@@ -7129,7 +7143,7 @@
         <v>0</v>
       </c>
       <c r="U93" s="12" t="s">
-        <v>208</v>
+        <v>55</v>
       </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
@@ -7152,10 +7166,10 @@
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I94" s="6"/>
       <c r="J94" s="5">
@@ -7171,10 +7185,10 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>250</v>
@@ -7202,9 +7216,11 @@
       <c r="B95" s="8">
         <v>46073.7678384375</v>
       </c>
-      <c r="C95" s="9"/>
+      <c r="C95" s="8">
+        <v>46191.795435520835</v>
+      </c>
       <c r="D95" s="8">
-        <v>46157.497292326385</v>
+        <v>46191.79544686343</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>252</v>
@@ -7239,8 +7255,12 @@
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
       <c r="S95" s="9"/>
-      <c r="T95" s="9"/>
-      <c r="U95" s="9"/>
+      <c r="T95" s="9">
+        <v>1</v>
+      </c>
+      <c r="U95" s="11" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
@@ -7249,9 +7269,11 @@
       <c r="B96" s="5">
         <v>46073.76783871528</v>
       </c>
-      <c r="C96" s="6"/>
+      <c r="C96" s="5">
+        <v>46191.794743819446</v>
+      </c>
       <c r="D96" s="5">
-        <v>46158.97524990741</v>
+        <v>46191.79475693287</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>255</v>
@@ -7299,10 +7321,10 @@
         <v>31</v>
       </c>
       <c r="T96" s="6">
-        <v>0.66</v>
-      </c>
-      <c r="U96" s="10" t="s">
-        <v>55</v>
+        <v>1</v>
+      </c>
+      <c r="U96" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
@@ -7319,7 +7341,7 @@
         <v>46129.68866337963</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
@@ -7349,7 +7371,7 @@
         <v>255</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P97" s="9" t="s">
         <v>258</v>
@@ -7374,7 +7396,7 @@
         <v>46129.688671157404</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7404,7 +7426,7 @@
         <v>255</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P98" s="6" t="s">
         <v>258</v>
@@ -7429,7 +7451,7 @@
         <v>46129.68868245371</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
@@ -7459,7 +7481,7 @@
         <v>255</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P99" s="9" t="s">
         <v>258</v>
@@ -7484,7 +7506,7 @@
         <v>46129.688693171294</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7514,7 +7536,7 @@
         <v>255</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P100" s="6" t="s">
         <v>258</v>
@@ -7539,7 +7561,7 @@
         <v>46129.68870375</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
@@ -7569,7 +7591,7 @@
         <v>255</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P101" s="9" t="s">
         <v>258</v>
@@ -7594,7 +7616,7 @@
         <v>46158.974908738426</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7624,7 +7646,7 @@
         <v>255</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>258</v>
@@ -7649,7 +7671,7 @@
         <v>46158.97511034722</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
@@ -7679,7 +7701,7 @@
         <v>255</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P103" s="9" t="s">
         <v>258</v>
@@ -7704,7 +7726,7 @@
         <v>46158.975184641204</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7734,7 +7756,7 @@
         <v>255</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P104" s="6" t="s">
         <v>258</v>
@@ -7752,12 +7774,14 @@
       <c r="B105" s="8">
         <v>46128.56587943287</v>
       </c>
-      <c r="C105" s="9"/>
+      <c r="C105" s="8">
+        <v>46191.794653784724</v>
+      </c>
       <c r="D105" s="8">
-        <v>46158.97482790509</v>
+        <v>46191.79465511574</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
@@ -7787,7 +7811,7 @@
         <v>255</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P105" s="9" t="s">
         <v>258</v>
@@ -7805,12 +7829,14 @@
       <c r="B106" s="5">
         <v>46128.565885625</v>
       </c>
-      <c r="C106" s="6"/>
+      <c r="C106" s="5">
+        <v>46191.7946603125</v>
+      </c>
       <c r="D106" s="5">
-        <v>46158.97482013889</v>
+        <v>46191.79466190972</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7840,7 +7866,7 @@
         <v>255</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P106" s="6" t="s">
         <v>258</v>
@@ -7858,12 +7884,14 @@
       <c r="B107" s="8">
         <v>46128.56589248843</v>
       </c>
-      <c r="C107" s="9"/>
+      <c r="C107" s="8">
+        <v>46191.79466587963</v>
+      </c>
       <c r="D107" s="8">
-        <v>46158.97481056713</v>
+        <v>46191.79466734953</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
@@ -7893,7 +7921,7 @@
         <v>255</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P107" s="9" t="s">
         <v>258</v>
@@ -7911,12 +7939,14 @@
       <c r="B108" s="5">
         <v>46128.56589891204</v>
       </c>
-      <c r="C108" s="6"/>
+      <c r="C108" s="5">
+        <v>46191.79472609954</v>
+      </c>
       <c r="D108" s="5">
-        <v>46158.974801516204</v>
+        <v>46191.79473116898</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7946,7 +7976,7 @@
         <v>255</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P108" s="6" t="s">
         <v>258</v>
@@ -7964,9 +7994,11 @@
       <c r="B109" s="8">
         <v>46073.76783924768</v>
       </c>
-      <c r="C109" s="9"/>
+      <c r="C109" s="8">
+        <v>46191.794535196765</v>
+      </c>
       <c r="D109" s="8">
-        <v>46158.973589733796</v>
+        <v>46191.79454671296</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>271</v>
@@ -8012,10 +8044,10 @@
         <v>31</v>
       </c>
       <c r="T109" s="9">
-        <v>0.66</v>
-      </c>
-      <c r="U109" s="10" t="s">
-        <v>55</v>
+        <v>1</v>
+      </c>
+      <c r="U109" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
@@ -8032,7 +8064,7 @@
         <v>46157.498779988426</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -8060,7 +8092,7 @@
         <v>271</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>273</v>
@@ -8085,7 +8117,7 @@
         <v>46157.49878368055</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
@@ -8113,7 +8145,7 @@
         <v>271</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P111" s="9" t="s">
         <v>273</v>
@@ -8138,7 +8170,7 @@
         <v>46157.498788240744</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8166,7 +8198,7 @@
         <v>271</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P112" s="6" t="s">
         <v>273</v>
@@ -8191,7 +8223,7 @@
         <v>46157.49879474537</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
@@ -8219,7 +8251,7 @@
         <v>271</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P113" s="9" t="s">
         <v>273</v>
@@ -8244,7 +8276,7 @@
         <v>46157.49884443287</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -8272,7 +8304,7 @@
         <v>271</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>273</v>
@@ -8297,7 +8329,7 @@
         <v>46158.97491230324</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
@@ -8325,7 +8357,7 @@
         <v>271</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P115" s="9" t="s">
         <v>273</v>
@@ -8350,7 +8382,7 @@
         <v>46158.975114155095</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8378,7 +8410,7 @@
         <v>271</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P116" s="6" t="s">
         <v>273</v>
@@ -8403,7 +8435,7 @@
         <v>46158.97518857638</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
@@ -8431,7 +8463,7 @@
         <v>271</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P117" s="9" t="s">
         <v>273</v>
@@ -8449,12 +8481,14 @@
       <c r="B118" s="5">
         <v>46128.566016111115</v>
       </c>
-      <c r="C118" s="6"/>
+      <c r="C118" s="5">
+        <v>46191.79378611111</v>
+      </c>
       <c r="D118" s="5">
-        <v>46158.97483096065</v>
+        <v>46191.794660555555</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8482,7 +8516,7 @@
         <v>271</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P118" s="6" t="s">
         <v>273</v>
@@ -8500,12 +8534,14 @@
       <c r="B119" s="8">
         <v>46128.566022604165</v>
       </c>
-      <c r="C119" s="9"/>
+      <c r="C119" s="8">
+        <v>46191.794240787036</v>
+      </c>
       <c r="D119" s="8">
-        <v>46158.97482454861</v>
+        <v>46191.79466525463</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
@@ -8533,7 +8569,7 @@
         <v>271</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P119" s="9" t="s">
         <v>273</v>
@@ -8551,12 +8587,14 @@
       <c r="B120" s="5">
         <v>46128.56602967593</v>
       </c>
-      <c r="C120" s="6"/>
+      <c r="C120" s="5">
+        <v>46191.794392662036</v>
+      </c>
       <c r="D120" s="5">
-        <v>46158.9748143287</v>
+        <v>46191.794671875</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8584,7 +8622,7 @@
         <v>271</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P120" s="6" t="s">
         <v>273</v>
@@ -8602,12 +8640,14 @@
       <c r="B121" s="8">
         <v>46128.56603574074</v>
       </c>
-      <c r="C121" s="9"/>
+      <c r="C121" s="8">
+        <v>46191.794520763884</v>
+      </c>
       <c r="D121" s="8">
-        <v>46158.97480553241</v>
+        <v>46191.79473787037</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
@@ -8635,7 +8675,7 @@
         <v>271</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P121" s="9" t="s">
         <v>273</v>
@@ -8653,9 +8693,11 @@
       <c r="B122" s="5">
         <v>46073.767839618056</v>
       </c>
-      <c r="C122" s="6"/>
+      <c r="C122" s="5">
+        <v>46191.793681041665</v>
+      </c>
       <c r="D122" s="5">
-        <v>46158.975293564814</v>
+        <v>46191.79368314815</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>286</v>
@@ -8703,10 +8745,10 @@
         <v>31</v>
       </c>
       <c r="T122" s="6">
-        <v>0.66</v>
-      </c>
-      <c r="U122" s="10" t="s">
-        <v>55</v>
+        <v>1</v>
+      </c>
+      <c r="U122" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
@@ -8723,7 +8765,7 @@
         <v>46157.49878587963</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>26</v>
@@ -8753,7 +8795,7 @@
         <v>286</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P123" s="9" t="s">
         <v>288</v>
@@ -8778,7 +8820,7 @@
         <v>46157.49878896991</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -8808,7 +8850,7 @@
         <v>286</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P124" s="6" t="s">
         <v>288</v>
@@ -8833,7 +8875,7 @@
         <v>46157.49879293982</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
@@ -8863,7 +8905,7 @@
         <v>286</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P125" s="9" t="s">
         <v>288</v>
@@ -8888,7 +8930,7 @@
         <v>46157.498799560184</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -8918,7 +8960,7 @@
         <v>286</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P126" s="6" t="s">
         <v>288</v>
@@ -8943,7 +8985,7 @@
         <v>46157.49885005787</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>26</v>
@@ -8973,7 +9015,7 @@
         <v>286</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P127" s="9" t="s">
         <v>288</v>
@@ -8998,7 +9040,7 @@
         <v>46157.4988055787</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -9028,7 +9070,7 @@
         <v>286</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P128" s="6" t="s">
         <v>288</v>
@@ -9053,7 +9095,7 @@
         <v>46157.49893354166</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>26</v>
@@ -9083,7 +9125,7 @@
         <v>286</v>
       </c>
       <c r="O129" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P129" s="9" t="s">
         <v>288</v>
@@ -9108,7 +9150,7 @@
         <v>46157.49900008102</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -9138,7 +9180,7 @@
         <v>286</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P130" s="6" t="s">
         <v>288</v>
@@ -9156,12 +9198,14 @@
       <c r="B131" s="8">
         <v>46128.56614351852</v>
       </c>
-      <c r="C131" s="9"/>
+      <c r="C131" s="8">
+        <v>46191.79334379629</v>
+      </c>
       <c r="D131" s="8">
-        <v>46129.68111525463</v>
+        <v>46191.7937930787</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>26</v>
@@ -9191,7 +9235,7 @@
         <v>286</v>
       </c>
       <c r="O131" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P131" s="9" t="s">
         <v>288</v>
@@ -9209,12 +9253,14 @@
       <c r="B132" s="5">
         <v>46128.56614934027</v>
       </c>
-      <c r="C132" s="6"/>
+      <c r="C132" s="5">
+        <v>46191.793437546294</v>
+      </c>
       <c r="D132" s="5">
-        <v>46129.68111607639</v>
+        <v>46191.79424862268</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
@@ -9244,7 +9290,7 @@
         <v>286</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P132" s="6" t="s">
         <v>288</v>
@@ -9262,12 +9308,14 @@
       <c r="B133" s="8">
         <v>46128.56615488426</v>
       </c>
-      <c r="C133" s="9"/>
+      <c r="C133" s="8">
+        <v>46191.793505208334</v>
+      </c>
       <c r="D133" s="8">
-        <v>46129.68111685185</v>
+        <v>46191.79439909723</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>26</v>
@@ -9297,7 +9345,7 @@
         <v>286</v>
       </c>
       <c r="O133" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P133" s="9" t="s">
         <v>288</v>
@@ -9315,12 +9363,14 @@
       <c r="B134" s="5">
         <v>46128.566162083334</v>
       </c>
-      <c r="C134" s="6"/>
+      <c r="C134" s="5">
+        <v>46191.79358293982</v>
+      </c>
       <c r="D134" s="5">
-        <v>46129.68111805555</v>
+        <v>46191.79452946759</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
@@ -9350,7 +9400,7 @@
         <v>286</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P134" s="6" t="s">
         <v>288</v>
@@ -9421,7 +9471,7 @@
         <v>1</v>
       </c>
       <c r="U135" s="10" t="s">
-        <v>55</v>
+        <v>107</v>
       </c>
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
@@ -9438,7 +9488,7 @@
         <v>46157.49801296296</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9468,7 +9518,7 @@
         <v>301</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P136" s="6" t="s">
         <v>304</v>
@@ -9493,7 +9543,7 @@
         <v>46157.49802616898</v>
       </c>
       <c r="E137" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>26</v>
@@ -9523,7 +9573,7 @@
         <v>301</v>
       </c>
       <c r="O137" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P137" s="9" t="s">
         <v>304</v>
@@ -9548,7 +9598,7 @@
         <v>46157.49803459491</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
@@ -9578,7 +9628,7 @@
         <v>301</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P138" s="6" t="s">
         <v>304</v>
@@ -9603,7 +9653,7 @@
         <v>46157.4980403588</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
@@ -9633,7 +9683,7 @@
         <v>301</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P139" s="9" t="s">
         <v>304</v>
@@ -9658,7 +9708,7 @@
         <v>46157.49804547454</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
@@ -9688,7 +9738,7 @@
         <v>301</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P140" s="6" t="s">
         <v>304</v>
@@ -9713,7 +9763,7 @@
         <v>46157.49809685185</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>26</v>
@@ -9743,7 +9793,7 @@
         <v>301</v>
       </c>
       <c r="O141" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P141" s="9" t="s">
         <v>304</v>
@@ -9768,7 +9818,7 @@
         <v>46157.498176423614</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
@@ -9798,7 +9848,7 @@
         <v>301</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P142" s="6" t="s">
         <v>304</v>
@@ -9823,7 +9873,7 @@
         <v>46157.49829290509</v>
       </c>
       <c r="E143" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F143" s="9" t="s">
         <v>26</v>
@@ -9853,7 +9903,7 @@
         <v>301</v>
       </c>
       <c r="O143" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P143" s="9" t="s">
         <v>304</v>
@@ -9875,10 +9925,10 @@
         <v>46157.49722258102</v>
       </c>
       <c r="D144" s="5">
-        <v>46157.49722376157</v>
+        <v>46191.793351631946</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
@@ -9908,7 +9958,7 @@
         <v>301</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P144" s="6" t="s">
         <v>304</v>
@@ -9930,10 +9980,10 @@
         <v>46157.49736403935</v>
       </c>
       <c r="D145" s="8">
-        <v>46157.49736525463</v>
+        <v>46191.79344340278</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>26</v>
@@ -9963,7 +10013,7 @@
         <v>301</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P145" s="9" t="s">
         <v>304</v>
@@ -9985,10 +10035,10 @@
         <v>46157.49741939815</v>
       </c>
       <c r="D146" s="5">
-        <v>46157.49742115741</v>
+        <v>46191.79351224537</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
@@ -10018,7 +10068,7 @@
         <v>301</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P146" s="6" t="s">
         <v>304</v>
@@ -10040,10 +10090,10 @@
         <v>46157.49748150463</v>
       </c>
       <c r="D147" s="8">
-        <v>46157.49748302084</v>
+        <v>46191.7935915625</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>26</v>
@@ -10073,7 +10123,7 @@
         <v>301</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P147" s="9" t="s">
         <v>304</v>
@@ -10091,9 +10141,11 @@
       <c r="B148" s="5">
         <v>46073.76784</v>
       </c>
-      <c r="C148" s="6"/>
+      <c r="C148" s="5">
+        <v>46191.795175555555</v>
+      </c>
       <c r="D148" s="5">
-        <v>46129.68163366898</v>
+        <v>46191.79533850694</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>317</v>
@@ -10139,9 +10191,9 @@
         <v>31</v>
       </c>
       <c r="T148" s="6">
-        <v>0</v>
-      </c>
-      <c r="U148" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="U148" s="12" t="s">
         <v>55</v>
       </c>
     </row>
@@ -10152,12 +10204,14 @@
       <c r="B149" s="8">
         <v>46128.566370555556</v>
       </c>
-      <c r="C149" s="9"/>
+      <c r="C149" s="8">
+        <v>46191.79532146991</v>
+      </c>
       <c r="D149" s="8">
-        <v>46129.68888349537</v>
+        <v>46191.79532310185</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>26</v>
@@ -10185,7 +10239,7 @@
         <v>317</v>
       </c>
       <c r="O149" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P149" s="9" t="s">
         <v>319</v>
@@ -10203,12 +10257,14 @@
       <c r="B150" s="5">
         <v>46128.56638481481</v>
       </c>
-      <c r="C150" s="6"/>
+      <c r="C150" s="5">
+        <v>46191.79531609954</v>
+      </c>
       <c r="D150" s="5">
-        <v>46129.68917427083</v>
+        <v>46191.7953178125</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
@@ -10236,7 +10292,7 @@
         <v>317</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P150" s="6" t="s">
         <v>319</v>
@@ -10254,12 +10310,14 @@
       <c r="B151" s="8">
         <v>46128.56639143519</v>
       </c>
-      <c r="C151" s="9"/>
+      <c r="C151" s="8">
+        <v>46191.79531059028</v>
+      </c>
       <c r="D151" s="8">
-        <v>46129.68926958334</v>
+        <v>46191.79531292824</v>
       </c>
       <c r="E151" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F151" s="9" t="s">
         <v>26</v>
@@ -10287,7 +10345,7 @@
         <v>317</v>
       </c>
       <c r="O151" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P151" s="9" t="s">
         <v>319</v>
@@ -10305,12 +10363,14 @@
       <c r="B152" s="5">
         <v>46128.56639815972</v>
       </c>
-      <c r="C152" s="6"/>
+      <c r="C152" s="5">
+        <v>46191.795305625</v>
+      </c>
       <c r="D152" s="5">
-        <v>46129.68935259259</v>
+        <v>46191.79530751157</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
@@ -10338,7 +10398,7 @@
         <v>317</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P152" s="6" t="s">
         <v>323</v>
@@ -10356,12 +10416,14 @@
       <c r="B153" s="8">
         <v>46128.566405729165</v>
       </c>
-      <c r="C153" s="9"/>
+      <c r="C153" s="8">
+        <v>46191.79529790509</v>
+      </c>
       <c r="D153" s="8">
-        <v>46129.68946930555</v>
+        <v>46191.79530002315</v>
       </c>
       <c r="E153" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F153" s="9" t="s">
         <v>26</v>
@@ -10389,7 +10451,7 @@
         <v>317</v>
       </c>
       <c r="O153" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P153" s="9" t="s">
         <v>319</v>
@@ -10407,12 +10469,14 @@
       <c r="B154" s="5">
         <v>46128.566412581014</v>
       </c>
-      <c r="C154" s="6"/>
+      <c r="C154" s="5">
+        <v>46191.795281377315</v>
+      </c>
       <c r="D154" s="5">
-        <v>46157.496932002316</v>
+        <v>46191.79528344907</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>26</v>
@@ -10440,7 +10504,7 @@
         <v>317</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P154" s="6" t="s">
         <v>319</v>
@@ -10458,12 +10522,14 @@
       <c r="B155" s="8">
         <v>46128.56641917824</v>
       </c>
-      <c r="C155" s="9"/>
+      <c r="C155" s="8">
+        <v>46191.79527634259</v>
+      </c>
       <c r="D155" s="8">
-        <v>46157.49707900463</v>
+        <v>46191.79527836805</v>
       </c>
       <c r="E155" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F155" s="9" t="s">
         <v>26</v>
@@ -10491,7 +10557,7 @@
         <v>317</v>
       </c>
       <c r="O155" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P155" s="9" t="s">
         <v>319</v>
@@ -10509,12 +10575,14 @@
       <c r="B156" s="5">
         <v>46128.566427337966</v>
       </c>
-      <c r="C156" s="6"/>
+      <c r="C156" s="5">
+        <v>46191.795271967596</v>
+      </c>
       <c r="D156" s="5">
-        <v>46157.49654493056</v>
+        <v>46191.79527357639</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
@@ -10542,7 +10610,7 @@
         <v>317</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P156" s="6" t="s">
         <v>319</v>
@@ -10560,12 +10628,14 @@
       <c r="B157" s="8">
         <v>46128.566433761574</v>
       </c>
-      <c r="C157" s="9"/>
+      <c r="C157" s="8">
+        <v>46191.79526633101</v>
+      </c>
       <c r="D157" s="8">
-        <v>46157.49722870371</v>
+        <v>46191.795267951384</v>
       </c>
       <c r="E157" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F157" s="9" t="s">
         <v>26</v>
@@ -10593,7 +10663,7 @@
         <v>317</v>
       </c>
       <c r="O157" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P157" s="9" t="s">
         <v>319</v>
@@ -10611,12 +10681,14 @@
       <c r="B158" s="5">
         <v>46128.56643997685</v>
       </c>
-      <c r="C158" s="6"/>
+      <c r="C158" s="5">
+        <v>46191.79526179398</v>
+      </c>
       <c r="D158" s="5">
-        <v>46157.49737020834</v>
+        <v>46191.79526363426</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
@@ -10644,7 +10716,7 @@
         <v>317</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P158" s="6" t="s">
         <v>319</v>
@@ -10662,12 +10734,14 @@
       <c r="B159" s="8">
         <v>46128.56644631944</v>
       </c>
-      <c r="C159" s="9"/>
+      <c r="C159" s="8">
+        <v>46191.795253749995</v>
+      </c>
       <c r="D159" s="8">
-        <v>46157.49742554398</v>
+        <v>46191.79525519676</v>
       </c>
       <c r="E159" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F159" s="9" t="s">
         <v>26</v>
@@ -10695,7 +10769,7 @@
         <v>317</v>
       </c>
       <c r="O159" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P159" s="9" t="s">
         <v>319</v>
@@ -10713,12 +10787,14 @@
       <c r="B160" s="5">
         <v>46128.56645381944</v>
       </c>
-      <c r="C160" s="6"/>
+      <c r="C160" s="5">
+        <v>46191.79524839121</v>
+      </c>
       <c r="D160" s="5">
-        <v>46157.4974894676</v>
+        <v>46191.795250173614</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>26</v>
@@ -10746,7 +10822,7 @@
         <v>317</v>
       </c>
       <c r="O160" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P160" s="6" t="s">
         <v>319</v>
@@ -10764,9 +10840,11 @@
       <c r="B161" s="8">
         <v>46073.76784028935</v>
       </c>
-      <c r="C161" s="9"/>
+      <c r="C161" s="8">
+        <v>46191.7954187963</v>
+      </c>
       <c r="D161" s="8">
-        <v>46129.6819365625</v>
+        <v>46191.796637673615</v>
       </c>
       <c r="E161" s="9" t="s">
         <v>333</v>
@@ -10812,9 +10890,9 @@
         <v>31</v>
       </c>
       <c r="T161" s="9">
-        <v>0</v>
-      </c>
-      <c r="U161" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="U161" s="12" t="s">
         <v>55</v>
       </c>
     </row>
@@ -10825,12 +10903,14 @@
       <c r="B162" s="5">
         <v>46128.566525625</v>
       </c>
-      <c r="C162" s="6"/>
+      <c r="C162" s="5">
+        <v>46191.79662097222</v>
+      </c>
       <c r="D162" s="5">
-        <v>46129.68193672453</v>
+        <v>46191.796622511574</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F162" s="6" t="s">
         <v>26</v>
@@ -10858,7 +10938,7 @@
         <v>333</v>
       </c>
       <c r="O162" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P162" s="6" t="s">
         <v>336</v>
@@ -10876,12 +10956,14 @@
       <c r="B163" s="8">
         <v>46128.566532013894</v>
       </c>
-      <c r="C163" s="9"/>
+      <c r="C163" s="8">
+        <v>46191.796464733794</v>
+      </c>
       <c r="D163" s="8">
-        <v>46129.68193744213</v>
+        <v>46191.796466134256</v>
       </c>
       <c r="E163" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F163" s="9" t="s">
         <v>26</v>
@@ -10909,7 +10991,7 @@
         <v>333</v>
       </c>
       <c r="O163" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P163" s="9" t="s">
         <v>336</v>
@@ -10927,12 +11009,14 @@
       <c r="B164" s="5">
         <v>46128.566539224536</v>
       </c>
-      <c r="C164" s="6"/>
+      <c r="C164" s="5">
+        <v>46191.79639053241</v>
+      </c>
       <c r="D164" s="5">
-        <v>46129.68193820602</v>
+        <v>46191.79639206019</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>26</v>
@@ -10960,7 +11044,7 @@
         <v>333</v>
       </c>
       <c r="O164" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P164" s="6" t="s">
         <v>336</v>
@@ -10978,12 +11062,14 @@
       <c r="B165" s="8">
         <v>46128.56654532407</v>
       </c>
-      <c r="C165" s="9"/>
+      <c r="C165" s="8">
+        <v>46191.79629663195</v>
+      </c>
       <c r="D165" s="8">
-        <v>46129.68193888888</v>
+        <v>46191.796298194444</v>
       </c>
       <c r="E165" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F165" s="9" t="s">
         <v>26</v>
@@ -11011,7 +11097,7 @@
         <v>333</v>
       </c>
       <c r="O165" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P165" s="9" t="s">
         <v>336</v>
@@ -11029,12 +11115,14 @@
       <c r="B166" s="5">
         <v>46128.566551689815</v>
       </c>
-      <c r="C166" s="6"/>
+      <c r="C166" s="5">
+        <v>46191.79617204861</v>
+      </c>
       <c r="D166" s="5">
-        <v>46129.68193960648</v>
+        <v>46191.79617392361</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>26</v>
@@ -11062,7 +11150,7 @@
         <v>333</v>
       </c>
       <c r="O166" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P166" s="6" t="s">
         <v>336</v>
@@ -11080,12 +11168,14 @@
       <c r="B167" s="8">
         <v>46128.56655853009</v>
       </c>
-      <c r="C167" s="9"/>
+      <c r="C167" s="8">
+        <v>46191.79610912037</v>
+      </c>
       <c r="D167" s="8">
-        <v>46129.68194032407</v>
+        <v>46191.796110972224</v>
       </c>
       <c r="E167" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F167" s="9" t="s">
         <v>26</v>
@@ -11113,7 +11203,7 @@
         <v>333</v>
       </c>
       <c r="O167" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P167" s="9" t="s">
         <v>336</v>
@@ -11131,12 +11221,14 @@
       <c r="B168" s="5">
         <v>46128.56656431713</v>
       </c>
-      <c r="C168" s="6"/>
+      <c r="C168" s="5">
+        <v>46191.796043587965</v>
+      </c>
       <c r="D168" s="5">
-        <v>46129.681941041665</v>
+        <v>46191.7960453125</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>26</v>
@@ -11164,7 +11256,7 @@
         <v>333</v>
       </c>
       <c r="O168" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P168" s="6" t="s">
         <v>336</v>
@@ -11182,12 +11274,14 @@
       <c r="B169" s="8">
         <v>46128.56657081019</v>
       </c>
-      <c r="C169" s="9"/>
+      <c r="C169" s="8">
+        <v>46191.795971342595</v>
+      </c>
       <c r="D169" s="8">
-        <v>46129.68194173611</v>
+        <v>46191.79597306713</v>
       </c>
       <c r="E169" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F169" s="9" t="s">
         <v>26</v>
@@ -11215,7 +11309,7 @@
         <v>333</v>
       </c>
       <c r="O169" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P169" s="9" t="s">
         <v>336</v>
@@ -11233,12 +11327,14 @@
       <c r="B170" s="5">
         <v>46128.56657746527</v>
       </c>
-      <c r="C170" s="6"/>
+      <c r="C170" s="5">
+        <v>46191.79585572917</v>
+      </c>
       <c r="D170" s="5">
-        <v>46129.681942407406</v>
+        <v>46191.79585737269</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>26</v>
@@ -11266,7 +11362,7 @@
         <v>333</v>
       </c>
       <c r="O170" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P170" s="6" t="s">
         <v>336</v>
@@ -11284,12 +11380,14 @@
       <c r="B171" s="8">
         <v>46128.566583113425</v>
       </c>
-      <c r="C171" s="9"/>
+      <c r="C171" s="8">
+        <v>46191.795773958336</v>
+      </c>
       <c r="D171" s="8">
-        <v>46129.68194314815</v>
+        <v>46191.79577540509</v>
       </c>
       <c r="E171" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F171" s="9" t="s">
         <v>26</v>
@@ -11317,7 +11415,7 @@
         <v>333</v>
       </c>
       <c r="O171" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P171" s="9" t="s">
         <v>336</v>
@@ -11335,12 +11433,14 @@
       <c r="B172" s="5">
         <v>46128.56659069445</v>
       </c>
-      <c r="C172" s="6"/>
+      <c r="C172" s="5">
+        <v>46191.79563440972</v>
+      </c>
       <c r="D172" s="5">
-        <v>46129.68194385417</v>
+        <v>46191.795636319446</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F172" s="6" t="s">
         <v>26</v>
@@ -11368,7 +11468,7 @@
         <v>333</v>
       </c>
       <c r="O172" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P172" s="6" t="s">
         <v>336</v>
@@ -11386,12 +11486,14 @@
       <c r="B173" s="8">
         <v>46128.56659782407</v>
       </c>
-      <c r="C173" s="9"/>
+      <c r="C173" s="8">
+        <v>46191.79554900463</v>
+      </c>
       <c r="D173" s="8">
-        <v>46129.68194458333</v>
+        <v>46191.79555090278</v>
       </c>
       <c r="E173" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F173" s="9" t="s">
         <v>26</v>
@@ -11419,7 +11521,7 @@
         <v>333</v>
       </c>
       <c r="O173" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P173" s="9" t="s">
         <v>336</v>
@@ -11439,7 +11541,7 @@
       </c>
       <c r="C174" s="6"/>
       <c r="D174" s="5">
-        <v>46090.63630363426</v>
+        <v>46191.79694226852</v>
       </c>
       <c r="E174" s="6" t="s">
         <v>349</v>
@@ -11486,7 +11588,7 @@
       </c>
       <c r="C175" s="9"/>
       <c r="D175" s="8">
-        <v>46129.6829255787</v>
+        <v>46191.795426412034</v>
       </c>
       <c r="E175" s="9" t="s">
         <v>352</v>
@@ -11537,7 +11639,7 @@
         <v>0</v>
       </c>
       <c r="U175" s="10" t="s">
-        <v>55</v>
+        <v>107</v>
       </c>
     </row>
     <row r="176" spans="1:21" x14ac:dyDescent="0.25">
@@ -11549,10 +11651,10 @@
       </c>
       <c r="C176" s="6"/>
       <c r="D176" s="5">
-        <v>46129.68292652778</v>
+        <v>46191.79663023148</v>
       </c>
       <c r="E176" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F176" s="6" t="s">
         <v>26</v>
@@ -11580,7 +11682,7 @@
         <v>352</v>
       </c>
       <c r="O176" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P176" s="6" t="s">
         <v>357</v>
@@ -11600,10 +11702,10 @@
       </c>
       <c r="C177" s="9"/>
       <c r="D177" s="8">
-        <v>46129.6829272801</v>
+        <v>46191.79647164352</v>
       </c>
       <c r="E177" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F177" s="9" t="s">
         <v>26</v>
@@ -11631,7 +11733,7 @@
         <v>352</v>
       </c>
       <c r="O177" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P177" s="9" t="s">
         <v>357</v>
@@ -11651,10 +11753,10 @@
       </c>
       <c r="C178" s="6"/>
       <c r="D178" s="5">
-        <v>46129.682928043985</v>
+        <v>46191.796397881946</v>
       </c>
       <c r="E178" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F178" s="6" t="s">
         <v>26</v>
@@ -11682,7 +11784,7 @@
         <v>352</v>
       </c>
       <c r="O178" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P178" s="6" t="s">
         <v>357</v>
@@ -11702,10 +11804,10 @@
       </c>
       <c r="C179" s="9"/>
       <c r="D179" s="8">
-        <v>46129.68292878472</v>
+        <v>46191.796304710646</v>
       </c>
       <c r="E179" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F179" s="9" t="s">
         <v>26</v>
@@ -11733,7 +11835,7 @@
         <v>352</v>
       </c>
       <c r="O179" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P179" s="9" t="s">
         <v>357</v>
@@ -11753,10 +11855,10 @@
       </c>
       <c r="C180" s="6"/>
       <c r="D180" s="5">
-        <v>46129.682929525465</v>
+        <v>46191.79617898148</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F180" s="6" t="s">
         <v>26</v>
@@ -11784,7 +11886,7 @@
         <v>352</v>
       </c>
       <c r="O180" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P180" s="6" t="s">
         <v>357</v>
@@ -11804,10 +11906,10 @@
       </c>
       <c r="C181" s="9"/>
       <c r="D181" s="8">
-        <v>46129.68293026621</v>
+        <v>46191.79611597222</v>
       </c>
       <c r="E181" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F181" s="9" t="s">
         <v>26</v>
@@ -11835,7 +11937,7 @@
         <v>352</v>
       </c>
       <c r="O181" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P181" s="9" t="s">
         <v>357</v>
@@ -11855,10 +11957,10 @@
       </c>
       <c r="C182" s="6"/>
       <c r="D182" s="5">
-        <v>46129.68293112269</v>
+        <v>46191.796051701385</v>
       </c>
       <c r="E182" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F182" s="6" t="s">
         <v>26</v>
@@ -11886,7 +11988,7 @@
         <v>352</v>
       </c>
       <c r="O182" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P182" s="6" t="s">
         <v>357</v>
@@ -11906,10 +12008,10 @@
       </c>
       <c r="C183" s="9"/>
       <c r="D183" s="8">
-        <v>46129.68293188658</v>
+        <v>46191.795977581016</v>
       </c>
       <c r="E183" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F183" s="9" t="s">
         <v>26</v>
@@ -11937,7 +12039,7 @@
         <v>352</v>
       </c>
       <c r="O183" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P183" s="9" t="s">
         <v>365</v>
@@ -11957,10 +12059,10 @@
       </c>
       <c r="C184" s="6"/>
       <c r="D184" s="5">
-        <v>46129.682932696756</v>
+        <v>46191.795861736115</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F184" s="6" t="s">
         <v>26</v>
@@ -11988,7 +12090,7 @@
         <v>352</v>
       </c>
       <c r="O184" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P184" s="6" t="s">
         <v>357</v>
@@ -12008,10 +12110,10 @@
       </c>
       <c r="C185" s="9"/>
       <c r="D185" s="8">
-        <v>46129.682933564814</v>
+        <v>46191.795781168985</v>
       </c>
       <c r="E185" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F185" s="9" t="s">
         <v>26</v>
@@ -12039,7 +12141,7 @@
         <v>352</v>
       </c>
       <c r="O185" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P185" s="9" t="s">
         <v>357</v>
@@ -12059,10 +12161,10 @@
       </c>
       <c r="C186" s="6"/>
       <c r="D186" s="5">
-        <v>46129.682934502314</v>
+        <v>46191.795643460646</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F186" s="6" t="s">
         <v>26</v>
@@ -12090,7 +12192,7 @@
         <v>352</v>
       </c>
       <c r="O186" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P186" s="6" t="s">
         <v>357</v>
@@ -12110,10 +12212,10 @@
       </c>
       <c r="C187" s="9"/>
       <c r="D187" s="8">
-        <v>46129.68293542824</v>
+        <v>46191.795556990735</v>
       </c>
       <c r="E187" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F187" s="9" t="s">
         <v>26</v>
@@ -12141,7 +12243,7 @@
         <v>352</v>
       </c>
       <c r="O187" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P187" s="9" t="s">
         <v>357</v>
@@ -12159,9 +12261,11 @@
       <c r="B188" s="5">
         <v>46073.7678383912</v>
       </c>
-      <c r="C188" s="6"/>
+      <c r="C188" s="5">
+        <v>46191.796778240736</v>
+      </c>
       <c r="D188" s="5">
-        <v>46129.68319581018</v>
+        <v>46191.79679478009</v>
       </c>
       <c r="E188" s="6" t="s">
         <v>371</v>
@@ -12209,10 +12313,10 @@
         <v>31</v>
       </c>
       <c r="T188" s="6">
-        <v>0</v>
-      </c>
-      <c r="U188" s="10" t="s">
-        <v>55</v>
+        <v>1</v>
+      </c>
+      <c r="U188" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="189" spans="1:21" x14ac:dyDescent="0.25">
@@ -12227,7 +12331,7 @@
         <v>46129.683195879625</v>
       </c>
       <c r="E189" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F189" s="9" t="s">
         <v>26</v>
@@ -12257,7 +12361,7 @@
         <v>371</v>
       </c>
       <c r="O189" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P189" s="9" t="s">
         <v>373</v>
@@ -12280,7 +12384,7 @@
         <v>46129.68319659722</v>
       </c>
       <c r="E190" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F190" s="6" t="s">
         <v>26</v>
@@ -12310,7 +12414,7 @@
         <v>371</v>
       </c>
       <c r="O190" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P190" s="6" t="s">
         <v>373</v>
@@ -12333,7 +12437,7 @@
         <v>46129.683197314815</v>
       </c>
       <c r="E191" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F191" s="9" t="s">
         <v>26</v>
@@ -12363,7 +12467,7 @@
         <v>371</v>
       </c>
       <c r="O191" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P191" s="9" t="s">
         <v>373</v>
@@ -12386,7 +12490,7 @@
         <v>46129.68319802084</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F192" s="6" t="s">
         <v>26</v>
@@ -12416,7 +12520,7 @@
         <v>371</v>
       </c>
       <c r="O192" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P192" s="6" t="s">
         <v>373</v>
@@ -12439,7 +12543,7 @@
         <v>46129.68319877315</v>
       </c>
       <c r="E193" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F193" s="9" t="s">
         <v>26</v>
@@ -12469,7 +12573,7 @@
         <v>371</v>
       </c>
       <c r="O193" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P193" s="9" t="s">
         <v>373</v>
@@ -12492,7 +12596,7 @@
         <v>46129.68319951389</v>
       </c>
       <c r="E194" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F194" s="6" t="s">
         <v>26</v>
@@ -12522,7 +12626,7 @@
         <v>371</v>
       </c>
       <c r="O194" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P194" s="6" t="s">
         <v>373</v>
@@ -12545,7 +12649,7 @@
         <v>46129.68320027778</v>
       </c>
       <c r="E195" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F195" s="9" t="s">
         <v>26</v>
@@ -12575,7 +12679,7 @@
         <v>371</v>
       </c>
       <c r="O195" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P195" s="9" t="s">
         <v>373</v>
@@ -12598,7 +12702,7 @@
         <v>46129.68320100695</v>
       </c>
       <c r="E196" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F196" s="6" t="s">
         <v>26</v>
@@ -12628,7 +12732,7 @@
         <v>371</v>
       </c>
       <c r="O196" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P196" s="6" t="s">
         <v>373</v>
@@ -12651,7 +12755,7 @@
         <v>46129.683201747685</v>
       </c>
       <c r="E197" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F197" s="9" t="s">
         <v>26</v>
@@ -12681,7 +12785,7 @@
         <v>371</v>
       </c>
       <c r="O197" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P197" s="9" t="s">
         <v>26</v>
@@ -12704,7 +12808,7 @@
         <v>46129.683202500004</v>
       </c>
       <c r="E198" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F198" s="6" t="s">
         <v>26</v>
@@ -12734,7 +12838,7 @@
         <v>371</v>
       </c>
       <c r="O198" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P198" s="6" t="s">
         <v>373</v>
@@ -12757,7 +12861,7 @@
         <v>46129.683203252316</v>
       </c>
       <c r="E199" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F199" s="9" t="s">
         <v>26</v>
@@ -12787,7 +12891,7 @@
         <v>371</v>
       </c>
       <c r="O199" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P199" s="9" t="s">
         <v>373</v>
@@ -12810,7 +12914,7 @@
         <v>46129.683203981476</v>
       </c>
       <c r="E200" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F200" s="6" t="s">
         <v>26</v>
@@ -12840,7 +12944,7 @@
         <v>371</v>
       </c>
       <c r="O200" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P200" s="6" t="s">
         <v>373</v>
@@ -12858,9 +12962,11 @@
       <c r="B201" s="8">
         <v>46073.76783868056</v>
       </c>
-      <c r="C201" s="9"/>
+      <c r="C201" s="8">
+        <v>46191.79687179398</v>
+      </c>
       <c r="D201" s="8">
-        <v>46129.68352990741</v>
+        <v>46191.7968871875</v>
       </c>
       <c r="E201" s="9" t="s">
         <v>386</v>
@@ -12869,10 +12975,10 @@
         <v>26</v>
       </c>
       <c r="G201" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H201" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I201" s="9"/>
       <c r="J201" s="8">
@@ -12906,10 +13012,10 @@
         <v>31</v>
       </c>
       <c r="T201" s="9">
-        <v>0</v>
-      </c>
-      <c r="U201" s="10" t="s">
-        <v>55</v>
+        <v>1</v>
+      </c>
+      <c r="U201" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="202" spans="1:21" x14ac:dyDescent="0.25">
@@ -12924,16 +13030,16 @@
         <v>46129.68352643518</v>
       </c>
       <c r="E202" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F202" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G202" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H202" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I202" s="6"/>
       <c r="J202" s="5">
@@ -12952,7 +13058,7 @@
         <v>386</v>
       </c>
       <c r="O202" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P202" s="6" t="s">
         <v>388</v>
@@ -12975,16 +13081,16 @@
         <v>46129.68352717593</v>
       </c>
       <c r="E203" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F203" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G203" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H203" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I203" s="9"/>
       <c r="J203" s="8">
@@ -13003,7 +13109,7 @@
         <v>386</v>
       </c>
       <c r="O203" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P203" s="9" t="s">
         <v>388</v>
@@ -13026,16 +13132,16 @@
         <v>46129.68352791667</v>
       </c>
       <c r="E204" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F204" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G204" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H204" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I204" s="6"/>
       <c r="J204" s="5">
@@ -13054,7 +13160,7 @@
         <v>386</v>
       </c>
       <c r="O204" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P204" s="6" t="s">
         <v>388</v>
@@ -13077,16 +13183,16 @@
         <v>46129.683528657406</v>
       </c>
       <c r="E205" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F205" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G205" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H205" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I205" s="9"/>
       <c r="J205" s="8">
@@ -13105,7 +13211,7 @@
         <v>386</v>
       </c>
       <c r="O205" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P205" s="9" t="s">
         <v>388</v>
@@ -13128,16 +13234,16 @@
         <v>46129.68352943287</v>
       </c>
       <c r="E206" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F206" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G206" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H206" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I206" s="6"/>
       <c r="J206" s="5">
@@ -13156,7 +13262,7 @@
         <v>386</v>
       </c>
       <c r="O206" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P206" s="6" t="s">
         <v>388</v>
@@ -13179,16 +13285,16 @@
         <v>46129.68353019676</v>
       </c>
       <c r="E207" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F207" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G207" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H207" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I207" s="9"/>
       <c r="J207" s="8">
@@ -13207,7 +13313,7 @@
         <v>386</v>
       </c>
       <c r="O207" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P207" s="9" t="s">
         <v>388</v>
@@ -13230,16 +13336,16 @@
         <v>46129.683530891205</v>
       </c>
       <c r="E208" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F208" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G208" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H208" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I208" s="6"/>
       <c r="J208" s="5">
@@ -13258,7 +13364,7 @@
         <v>386</v>
       </c>
       <c r="O208" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P208" s="6" t="s">
         <v>395</v>
@@ -13281,16 +13387,16 @@
         <v>46129.68353159723</v>
       </c>
       <c r="E209" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F209" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G209" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H209" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I209" s="9"/>
       <c r="J209" s="8">
@@ -13309,7 +13415,7 @@
         <v>386</v>
       </c>
       <c r="O209" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P209" s="9" t="s">
         <v>395</v>
@@ -13332,16 +13438,16 @@
         <v>46129.68353232639</v>
       </c>
       <c r="E210" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F210" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G210" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H210" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I210" s="6"/>
       <c r="J210" s="5">
@@ -13360,7 +13466,7 @@
         <v>386</v>
       </c>
       <c r="O210" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P210" s="6" t="s">
         <v>395</v>
@@ -13383,16 +13489,16 @@
         <v>46129.683533125004</v>
       </c>
       <c r="E211" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F211" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G211" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H211" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I211" s="9"/>
       <c r="J211" s="8">
@@ -13411,7 +13517,7 @@
         <v>386</v>
       </c>
       <c r="O211" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P211" s="9" t="s">
         <v>395</v>
@@ -13434,16 +13540,16 @@
         <v>46129.68353385417</v>
       </c>
       <c r="E212" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F212" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G212" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H212" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I212" s="6"/>
       <c r="J212" s="5">
@@ -13462,7 +13568,7 @@
         <v>386</v>
       </c>
       <c r="O212" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P212" s="6" t="s">
         <v>395</v>
@@ -13485,16 +13591,16 @@
         <v>46129.68353459491</v>
       </c>
       <c r="E213" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F213" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G213" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H213" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I213" s="9"/>
       <c r="J213" s="8">
@@ -13513,7 +13619,7 @@
         <v>386</v>
       </c>
       <c r="O213" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P213" s="9" t="s">
         <v>395</v>
@@ -13531,9 +13637,11 @@
       <c r="B214" s="5">
         <v>46073.76783895833</v>
       </c>
-      <c r="C214" s="6"/>
+      <c r="C214" s="5">
+        <v>46191.79693015046</v>
+      </c>
       <c r="D214" s="5">
-        <v>46129.683901331024</v>
+        <v>46191.79694662037</v>
       </c>
       <c r="E214" s="6" t="s">
         <v>402</v>
@@ -13542,10 +13650,10 @@
         <v>26</v>
       </c>
       <c r="G214" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H214" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I214" s="6"/>
       <c r="J214" s="5">
@@ -13579,10 +13687,10 @@
         <v>31</v>
       </c>
       <c r="T214" s="6">
-        <v>0</v>
-      </c>
-      <c r="U214" s="10" t="s">
-        <v>55</v>
+        <v>1</v>
+      </c>
+      <c r="U214" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="215" spans="1:21" x14ac:dyDescent="0.25">
@@ -13597,16 +13705,16 @@
         <v>46129.69451681713</v>
       </c>
       <c r="E215" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F215" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G215" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H215" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I215" s="9"/>
       <c r="J215" s="8">
@@ -13625,7 +13733,7 @@
         <v>402</v>
       </c>
       <c r="O215" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P215" s="9" t="s">
         <v>402</v>
@@ -13648,16 +13756,16 @@
         <v>46129.69454358796</v>
       </c>
       <c r="E216" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F216" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G216" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H216" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I216" s="6"/>
       <c r="J216" s="5">
@@ -13676,7 +13784,7 @@
         <v>402</v>
       </c>
       <c r="O216" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P216" s="6" t="s">
         <v>402</v>
@@ -13699,16 +13807,16 @@
         <v>46129.694564502315</v>
       </c>
       <c r="E217" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F217" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G217" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H217" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I217" s="9"/>
       <c r="J217" s="8">
@@ -13727,7 +13835,7 @@
         <v>402</v>
       </c>
       <c r="O217" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P217" s="9" t="s">
         <v>402</v>
@@ -13750,16 +13858,16 @@
         <v>46129.694584282406</v>
       </c>
       <c r="E218" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F218" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G218" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H218" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I218" s="6"/>
       <c r="J218" s="5">
@@ -13778,7 +13886,7 @@
         <v>402</v>
       </c>
       <c r="O218" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P218" s="6" t="s">
         <v>402</v>
@@ -13801,16 +13909,16 @@
         <v>46129.69460693287</v>
       </c>
       <c r="E219" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F219" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G219" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H219" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I219" s="9"/>
       <c r="J219" s="8">
@@ -13829,7 +13937,7 @@
         <v>402</v>
       </c>
       <c r="O219" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P219" s="9" t="s">
         <v>402</v>
@@ -13852,16 +13960,16 @@
         <v>46129.69462627315</v>
       </c>
       <c r="E220" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F220" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G220" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H220" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I220" s="6"/>
       <c r="J220" s="5">
@@ -13880,7 +13988,7 @@
         <v>402</v>
       </c>
       <c r="O220" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P220" s="6" t="s">
         <v>402</v>
@@ -13903,16 +14011,16 @@
         <v>46129.69465064815</v>
       </c>
       <c r="E221" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F221" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G221" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H221" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I221" s="9"/>
       <c r="J221" s="8">
@@ -13931,7 +14039,7 @@
         <v>402</v>
       </c>
       <c r="O221" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P221" s="9" t="s">
         <v>402</v>
@@ -13954,16 +14062,16 @@
         <v>46129.69467157408</v>
       </c>
       <c r="E222" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F222" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G222" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H222" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I222" s="6"/>
       <c r="J222" s="5">
@@ -13982,7 +14090,7 @@
         <v>402</v>
       </c>
       <c r="O222" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P222" s="6" t="s">
         <v>402</v>
@@ -14005,16 +14113,16 @@
         <v>46129.69469225695</v>
       </c>
       <c r="E223" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F223" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G223" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H223" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I223" s="9"/>
       <c r="J223" s="8">
@@ -14033,7 +14141,7 @@
         <v>402</v>
       </c>
       <c r="O223" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P223" s="9" t="s">
         <v>402</v>
@@ -14056,16 +14164,16 @@
         <v>46129.694713379635</v>
       </c>
       <c r="E224" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F224" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G224" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H224" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I224" s="6"/>
       <c r="J224" s="5">
@@ -14084,7 +14192,7 @@
         <v>402</v>
       </c>
       <c r="O224" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P224" s="6" t="s">
         <v>402</v>
@@ -14107,16 +14215,16 @@
         <v>46129.694735682875</v>
       </c>
       <c r="E225" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F225" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G225" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H225" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I225" s="9"/>
       <c r="J225" s="8">
@@ -14135,7 +14243,7 @@
         <v>402</v>
       </c>
       <c r="O225" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P225" s="9" t="s">
         <v>402</v>
@@ -14158,16 +14266,16 @@
         <v>46129.694774895834</v>
       </c>
       <c r="E226" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F226" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G226" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H226" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I226" s="6"/>
       <c r="J226" s="5">
@@ -14186,7 +14294,7 @@
         <v>402</v>
       </c>
       <c r="O226" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P226" s="6" t="s">
         <v>402</v>
@@ -14253,7 +14361,7 @@
       </c>
       <c r="C228" s="6"/>
       <c r="D228" s="5">
-        <v>46090.84152090277</v>
+        <v>46191.79694986111</v>
       </c>
       <c r="E228" s="6" t="s">
         <v>420</v>
@@ -14303,7 +14411,7 @@
       <c r="T228" s="6">
         <v>0</v>
       </c>
-      <c r="U228" s="10" t="s">
+      <c r="U228" s="12" t="s">
         <v>55</v>
       </c>
     </row>
@@ -14316,7 +14424,7 @@
       </c>
       <c r="C229" s="9"/>
       <c r="D229" s="8">
-        <v>46114.517393182876</v>
+        <v>46191.79695027778</v>
       </c>
       <c r="E229" s="9" t="s">
         <v>424</v>
@@ -14366,7 +14474,7 @@
       <c r="T229" s="9">
         <v>0</v>
       </c>
-      <c r="U229" s="10" t="s">
+      <c r="U229" s="12" t="s">
         <v>55</v>
       </c>
     </row>
@@ -14428,7 +14536,7 @@
       </c>
       <c r="C231" s="9"/>
       <c r="D231" s="8">
-        <v>46091.12935501157</v>
+        <v>46191.79695047454</v>
       </c>
       <c r="E231" s="9" t="s">
         <v>430</v>
@@ -14478,7 +14586,7 @@
       <c r="T231" s="9">
         <v>0</v>
       </c>
-      <c r="U231" s="10" t="s">
+      <c r="U231" s="12" t="s">
         <v>55</v>
       </c>
     </row>
@@ -14542,7 +14650,7 @@
         <v>0</v>
       </c>
       <c r="U232" s="10" t="s">
-        <v>55</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001501 - EQ MIN LA HACIENDA B.xlsx
+++ b/data/50001501 - EQ MIN LA HACIENDA B.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2655" uniqueCount="434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2667" uniqueCount="436">
   <si>
     <t>50001501 - EQ. MIN. LA HACIENDA</t>
   </si>
@@ -178,468 +178,468 @@
     <t>Recepcion Tableros</t>
   </si>
   <si>
+    <t>1213330953387467</t>
+  </si>
+  <si>
+    <t>Ingenieria Jefe de proyecto:</t>
+  </si>
+  <si>
+    <t>Ingenieria Detalle,Ingenieria basica Rodete,Ingenieria Basica Motor,Analisis de costeo</t>
+  </si>
+  <si>
+    <t>1213330953387468</t>
+  </si>
+  <si>
+    <t>Ingenieria Basica Motor</t>
+  </si>
+  <si>
+    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,propuesta motor</t>
+  </si>
+  <si>
+    <t>1213330953387470</t>
+  </si>
+  <si>
+    <t>Ingenieria basica Rodete</t>
+  </si>
+  <si>
+    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,propuesta nucleo rodete,propuesta alabes</t>
+  </si>
+  <si>
+    <t>1213330953387471</t>
+  </si>
+  <si>
+    <t>Ingenieria Detalle</t>
+  </si>
+  <si>
+    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,propuesta compras a codigo // aprovisionamiento,Planos preliminar</t>
+  </si>
+  <si>
+    <t>1213330953387472</t>
+  </si>
+  <si>
+    <t>Analisis de costeo</t>
+  </si>
+  <si>
+    <t>Ingenieria Detalle,Ingenieria basica Rodete,Ingenieria Basica Motor</t>
+  </si>
+  <si>
+    <t>Ingenieria Jefe de proyecto:,Costos</t>
+  </si>
+  <si>
+    <t>1213330953387473</t>
+  </si>
+  <si>
+    <t>Propuesta compras:</t>
+  </si>
+  <si>
+    <t>propuesta tableros,propuesta nucleo rodete,propuesta alabes,propuesta motor,propuesta compras a codigo // aprovisionamiento</t>
+  </si>
+  <si>
+    <t>1213330953387474</t>
+  </si>
+  <si>
+    <t>propuesta alabes</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC Alabe</t>
+  </si>
+  <si>
+    <t>1213330953387475</t>
+  </si>
+  <si>
+    <t>propuesta motor</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC motor</t>
+  </si>
+  <si>
+    <t>1213330953387476</t>
+  </si>
+  <si>
+    <t>propuesta tableros</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC Tableros ot 4215</t>
+  </si>
+  <si>
+    <t>1213330953387477</t>
+  </si>
+  <si>
+    <t>propuesta nucleo rodete</t>
+  </si>
+  <si>
+    <t>benjamin.bustos@zitron.com</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC Rodete</t>
+  </si>
+  <si>
+    <t>1213330953387478</t>
+  </si>
+  <si>
+    <t>propuesta compras a codigo // aprovisionamiento</t>
+  </si>
+  <si>
+    <t>hugo isla martinez</t>
+  </si>
+  <si>
+    <t>hugo.isla@zitron.com</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC materiales</t>
+  </si>
+  <si>
+    <t>1213910573903699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Propuesta fabricación exterma </t>
+  </si>
+  <si>
+    <t>1213330953387479</t>
+  </si>
+  <si>
+    <t>Compras:</t>
+  </si>
+  <si>
+    <t>Alabe,Tablero ot 4215,rodete,Motor,Materiales a codigo // compras locales aprovisionamientomiento:</t>
+  </si>
+  <si>
+    <t>1213330953387480</t>
+  </si>
+  <si>
+    <t>Alabe</t>
+  </si>
+  <si>
+    <t>Eliana</t>
+  </si>
+  <si>
+    <t>ecarico@zitron.com</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe,Fabricación Alabe</t>
+  </si>
+  <si>
+    <t>1213330953387481</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe</t>
+  </si>
+  <si>
+    <t>Fabricación Alabe,Alabe</t>
+  </si>
+  <si>
+    <t>Baja</t>
+  </si>
+  <si>
+    <t>Tarea sin iniciar</t>
+  </si>
+  <si>
+    <t>1213330953387482</t>
+  </si>
+  <si>
+    <t>Fabricación Alabe</t>
+  </si>
+  <si>
+    <t>Alabe,Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>1213330953387483</t>
+  </si>
+  <si>
+    <t>Tablero ot 4215</t>
+  </si>
+  <si>
+    <t>Generación OC Tableros ot 4215,Fabricación Tablero ot 4215</t>
+  </si>
+  <si>
+    <t>1213330953387484</t>
+  </si>
+  <si>
+    <t>Generación OC Tableros ot 4215</t>
+  </si>
+  <si>
+    <t>Fabricación Tablero ot 4215,Tablero ot 4215</t>
+  </si>
+  <si>
+    <t>1213330953387485</t>
+  </si>
+  <si>
+    <t>Fabricación Tablero ot 4215</t>
+  </si>
+  <si>
+    <t>Tablero ot 4215,Recepcion Tableros</t>
+  </si>
+  <si>
+    <t>1213330953387486</t>
+  </si>
+  <si>
+    <t>rodete</t>
+  </si>
+  <si>
+    <t>Generación OC Rodete,Fabricación Rodete</t>
+  </si>
+  <si>
+    <t>1213330953387487</t>
+  </si>
+  <si>
+    <t>Generación OC Rodete</t>
+  </si>
+  <si>
+    <t>Fabricación Rodete,rodete</t>
+  </si>
+  <si>
+    <t>1213330953387488</t>
+  </si>
+  <si>
+    <t>Fabricación Rodete</t>
+  </si>
+  <si>
+    <t>rodete,Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>1213330953387489</t>
+  </si>
+  <si>
+    <t>Motor</t>
+  </si>
+  <si>
+    <t>Generación OC motor,Fabricación motor,Planos motor proveedor</t>
+  </si>
+  <si>
+    <t>1213333324436206</t>
+  </si>
+  <si>
+    <t>Generación OC motor</t>
+  </si>
+  <si>
+    <t>Fabricación motor,Planos motor proveedor,Motor</t>
+  </si>
+  <si>
+    <t>1213333324436207</t>
+  </si>
+  <si>
+    <t>Fabricación motor</t>
+  </si>
+  <si>
+    <t>Motor,Recepcion motor</t>
+  </si>
+  <si>
+    <t>1213333324436208</t>
+  </si>
+  <si>
+    <t>Planos motor proveedor</t>
+  </si>
+  <si>
+    <t>Motor,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1213333324436209</t>
+  </si>
+  <si>
+    <t>Materiales a codigo // compras locales aprovisionamientomiento:</t>
+  </si>
+  <si>
+    <t>Generación OC materiales,Fabricacion a codigo y compras locales</t>
+  </si>
+  <si>
+    <t>1213333324436210</t>
+  </si>
+  <si>
+    <t>Generación OC materiales</t>
+  </si>
+  <si>
+    <t>Fabricacion a codigo y compras locales,Materiales a codigo // compras locales aprovisionamientomiento:</t>
+  </si>
+  <si>
+    <t>1213333324436211</t>
+  </si>
+  <si>
+    <t>Fabricacion a codigo y compras locales</t>
+  </si>
+  <si>
+    <t>Materiales a codigo // compras locales aprovisionamientomiento:,Recepcion materiales a codigos // compras locales aprovisionamiento</t>
+  </si>
+  <si>
+    <t>1213333324436212</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseño:</t>
+  </si>
+  <si>
+    <t>Planos preliminar,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1213333324436213</t>
+  </si>
+  <si>
+    <t>Planos preliminar</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseño:,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1213333324436214</t>
+  </si>
+  <si>
+    <t>Planos definitivos</t>
+  </si>
+  <si>
+    <t>Planos motor proveedor,Planos preliminar</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseño:,Ingenieria y diseño:,Check Planos</t>
+  </si>
+  <si>
+    <t>1213575386155777</t>
+  </si>
+  <si>
+    <t>Check Planos</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado,Montaje Alabe,Montaje motor,Montaje Rodete,Armado</t>
+  </si>
+  <si>
+    <t>1213575386155778</t>
+  </si>
+  <si>
+    <t>Check pruebas Fat</t>
+  </si>
+  <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2 ,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2</t>
+  </si>
+  <si>
+    <t>1214075676500814</t>
+  </si>
+  <si>
+    <t>OT 4213 ZVN 1-9-86/2</t>
+  </si>
+  <si>
+    <t>Check pruebas Fat,OT 4213 ZVN 1-9-86/2</t>
+  </si>
+  <si>
+    <t>1214075676500815</t>
+  </si>
+  <si>
+    <t>1214075676500816</t>
+  </si>
+  <si>
+    <t>1214075676500817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4213 ZVN 1-9-86/2 </t>
+  </si>
+  <si>
+    <t>1214075676500818</t>
+  </si>
+  <si>
+    <t>1214075676500819</t>
+  </si>
+  <si>
+    <t>1214075676500820</t>
+  </si>
+  <si>
+    <t>1214075676500821</t>
+  </si>
+  <si>
+    <t>1214075676500822</t>
+  </si>
+  <si>
+    <t>1214075676500823</t>
+  </si>
+  <si>
+    <t>1214075676500824</t>
+  </si>
+  <si>
+    <t>1214075676500825</t>
+  </si>
+  <si>
+    <t>1213333324436215</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamiento,Recepcion materiales a codigos // compras locales aprovisionamiento</t>
+  </si>
+  <si>
+    <t>1213333324436216</t>
+  </si>
+  <si>
+    <t>Recepcion materiales a codigos // compras locales aprovisionamiento</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamiento,Bodega:</t>
+  </si>
+  <si>
+    <t>1213333324436217</t>
+  </si>
+  <si>
+    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamiento</t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>Bodega:,Preparación1 Materiales</t>
+  </si>
+  <si>
+    <t>1213333324436218</t>
+  </si>
+  <si>
+    <t>Caldereria:</t>
+  </si>
+  <si>
+    <t>Preparación1 Materiales,Armado,Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1213333324436219</t>
+  </si>
+  <si>
+    <t>Preparación1 Materiales</t>
+  </si>
+  <si>
+    <t>Nicolás Mol</t>
+  </si>
+  <si>
+    <t>nicolas.mol@zitron.com</t>
+  </si>
+  <si>
+    <t>Caldereria:,Armado,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2</t>
+  </si>
+  <si>
+    <t>1213333324436220</t>
+  </si>
+  <si>
+    <t>Armado</t>
+  </si>
+  <si>
+    <t>Preparación1 Materiales,Check Planos,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2</t>
+  </si>
+  <si>
     <t>Tarea en curso</t>
   </si>
   <si>
-    <t>1213330953387467</t>
-  </si>
-  <si>
-    <t>Ingenieria Jefe de proyecto:</t>
-  </si>
-  <si>
-    <t>Ingenieria Detalle,Ingenieria basica Rodete,Ingenieria Basica Motor,Analisis de costeo</t>
-  </si>
-  <si>
-    <t>1213330953387468</t>
-  </si>
-  <si>
-    <t>Ingenieria Basica Motor</t>
-  </si>
-  <si>
-    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,propuesta motor</t>
-  </si>
-  <si>
-    <t>1213330953387470</t>
-  </si>
-  <si>
-    <t>Ingenieria basica Rodete</t>
-  </si>
-  <si>
-    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,propuesta nucleo rodete,propuesta alabes</t>
-  </si>
-  <si>
-    <t>1213330953387471</t>
-  </si>
-  <si>
-    <t>Ingenieria Detalle</t>
-  </si>
-  <si>
-    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,propuesta compras a codigo // aprovisionamiento,Planos preliminar</t>
-  </si>
-  <si>
-    <t>1213330953387472</t>
-  </si>
-  <si>
-    <t>Analisis de costeo</t>
-  </si>
-  <si>
-    <t>Ingenieria Detalle,Ingenieria basica Rodete,Ingenieria Basica Motor</t>
-  </si>
-  <si>
-    <t>Ingenieria Jefe de proyecto:,Costos</t>
-  </si>
-  <si>
-    <t>1213330953387473</t>
-  </si>
-  <si>
-    <t>Propuesta compras:</t>
-  </si>
-  <si>
-    <t>propuesta tableros,propuesta nucleo rodete,propuesta alabes,propuesta motor,propuesta compras a codigo // aprovisionamiento</t>
-  </si>
-  <si>
-    <t>1213330953387474</t>
-  </si>
-  <si>
-    <t>propuesta alabes</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC Alabe</t>
-  </si>
-  <si>
-    <t>1213330953387475</t>
-  </si>
-  <si>
-    <t>propuesta motor</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC motor</t>
-  </si>
-  <si>
-    <t>1213330953387476</t>
-  </si>
-  <si>
-    <t>propuesta tableros</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC Tableros ot 4215</t>
-  </si>
-  <si>
-    <t>1213330953387477</t>
-  </si>
-  <si>
-    <t>propuesta nucleo rodete</t>
-  </si>
-  <si>
-    <t>benjamin.bustos@zitron.com</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC Rodete</t>
-  </si>
-  <si>
-    <t>1213330953387478</t>
-  </si>
-  <si>
-    <t>propuesta compras a codigo // aprovisionamiento</t>
-  </si>
-  <si>
-    <t>hugo isla martinez</t>
-  </si>
-  <si>
-    <t>hugo.isla@zitron.com</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC materiales</t>
-  </si>
-  <si>
-    <t>1213910573903699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Propuesta fabricación exterma </t>
-  </si>
-  <si>
-    <t>1213330953387479</t>
-  </si>
-  <si>
-    <t>Compras:</t>
-  </si>
-  <si>
-    <t>Alabe,Tablero ot 4215,rodete,Motor,Materiales a codigo // compras locales aprovisionamientomiento:</t>
-  </si>
-  <si>
-    <t>1213330953387480</t>
-  </si>
-  <si>
-    <t>Alabe</t>
-  </si>
-  <si>
-    <t>Eliana</t>
-  </si>
-  <si>
-    <t>ecarico@zitron.com</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe,Fabricación Alabe</t>
-  </si>
-  <si>
-    <t>1213330953387481</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe</t>
-  </si>
-  <si>
-    <t>Fabricación Alabe,Alabe</t>
-  </si>
-  <si>
-    <t>Baja</t>
-  </si>
-  <si>
-    <t>Tarea sin iniciar</t>
-  </si>
-  <si>
-    <t>1213330953387482</t>
-  </si>
-  <si>
-    <t>Fabricación Alabe</t>
-  </si>
-  <si>
-    <t>Alabe,Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>1213330953387483</t>
-  </si>
-  <si>
-    <t>Tablero ot 4215</t>
-  </si>
-  <si>
-    <t>Generación OC Tableros ot 4215,Fabricación Tablero ot 4215</t>
-  </si>
-  <si>
-    <t>1213330953387484</t>
-  </si>
-  <si>
-    <t>Generación OC Tableros ot 4215</t>
-  </si>
-  <si>
-    <t>Fabricación Tablero ot 4215,Tablero ot 4215</t>
-  </si>
-  <si>
-    <t>1213330953387485</t>
-  </si>
-  <si>
-    <t>Fabricación Tablero ot 4215</t>
-  </si>
-  <si>
-    <t>Tablero ot 4215,Recepcion Tableros</t>
-  </si>
-  <si>
-    <t>1213330953387486</t>
-  </si>
-  <si>
-    <t>rodete</t>
-  </si>
-  <si>
-    <t>Generación OC Rodete,Fabricación Rodete</t>
-  </si>
-  <si>
-    <t>1213330953387487</t>
-  </si>
-  <si>
-    <t>Generación OC Rodete</t>
-  </si>
-  <si>
-    <t>Fabricación Rodete,rodete</t>
-  </si>
-  <si>
-    <t>1213330953387488</t>
-  </si>
-  <si>
-    <t>Fabricación Rodete</t>
-  </si>
-  <si>
-    <t>rodete,Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>1213330953387489</t>
-  </si>
-  <si>
-    <t>Motor</t>
-  </si>
-  <si>
-    <t>Generación OC motor,Fabricación motor,Planos motor proveedor</t>
-  </si>
-  <si>
-    <t>1213333324436206</t>
-  </si>
-  <si>
-    <t>Generación OC motor</t>
-  </si>
-  <si>
-    <t>Fabricación motor,Planos motor proveedor,Motor</t>
-  </si>
-  <si>
-    <t>1213333324436207</t>
-  </si>
-  <si>
-    <t>Fabricación motor</t>
-  </si>
-  <si>
-    <t>Motor,Recepcion motor</t>
-  </si>
-  <si>
-    <t>1213333324436208</t>
-  </si>
-  <si>
-    <t>Planos motor proveedor</t>
-  </si>
-  <si>
-    <t>Motor,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1213333324436209</t>
-  </si>
-  <si>
-    <t>Materiales a codigo // compras locales aprovisionamientomiento:</t>
-  </si>
-  <si>
-    <t>Generación OC materiales,Fabricacion a codigo y compras locales</t>
-  </si>
-  <si>
-    <t>1213333324436210</t>
-  </si>
-  <si>
-    <t>Generación OC materiales</t>
-  </si>
-  <si>
-    <t>Fabricacion a codigo y compras locales,Materiales a codigo // compras locales aprovisionamientomiento:</t>
-  </si>
-  <si>
-    <t>1213333324436211</t>
-  </si>
-  <si>
-    <t>Fabricacion a codigo y compras locales</t>
-  </si>
-  <si>
-    <t>Materiales a codigo // compras locales aprovisionamientomiento:,Recepcion materiales a codigos // compras locales aprovisionamiento</t>
-  </si>
-  <si>
-    <t>1213333324436212</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseño:</t>
-  </si>
-  <si>
-    <t>Planos preliminar,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1213333324436213</t>
-  </si>
-  <si>
-    <t>Planos preliminar</t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseño:,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1213333324436214</t>
-  </si>
-  <si>
-    <t>Planos definitivos</t>
-  </si>
-  <si>
-    <t>Planos motor proveedor,Planos preliminar</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseño:,Ingenieria y diseño:,Check Planos</t>
-  </si>
-  <si>
-    <t>1213575386155777</t>
-  </si>
-  <si>
-    <t>Check Planos</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado,Montaje Alabe,Montaje motor,Montaje Rodete,Armado</t>
-  </si>
-  <si>
-    <t>1213575386155778</t>
-  </si>
-  <si>
-    <t>Check pruebas Fat</t>
-  </si>
-  <si>
-    <t>Francisca González Cornejo</t>
-  </si>
-  <si>
-    <t>francisca.gonzalez@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2 ,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t>1214075676500814</t>
-  </si>
-  <si>
-    <t>OT 4213 ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t>Check pruebas Fat,OT 4213 ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t>1214075676500815</t>
-  </si>
-  <si>
-    <t>1214075676500816</t>
-  </si>
-  <si>
-    <t>1214075676500817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4213 ZVN 1-9-86/2 </t>
-  </si>
-  <si>
-    <t>1214075676500818</t>
-  </si>
-  <si>
-    <t>1214075676500819</t>
-  </si>
-  <si>
-    <t>1214075676500820</t>
-  </si>
-  <si>
-    <t>1214075676500821</t>
-  </si>
-  <si>
-    <t>1214075676500822</t>
-  </si>
-  <si>
-    <t>1214075676500823</t>
-  </si>
-  <si>
-    <t>1214075676500824</t>
-  </si>
-  <si>
-    <t>1214075676500825</t>
-  </si>
-  <si>
-    <t>1213333324436215</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamiento,Recepcion materiales a codigos // compras locales aprovisionamiento</t>
-  </si>
-  <si>
-    <t>1213333324436216</t>
-  </si>
-  <si>
-    <t>Recepcion materiales a codigos // compras locales aprovisionamiento</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamiento,Bodega:</t>
-  </si>
-  <si>
-    <t>1213333324436217</t>
-  </si>
-  <si>
-    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamiento</t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>Bodega:,Preparación1 Materiales</t>
-  </si>
-  <si>
-    <t>1213333324436218</t>
-  </si>
-  <si>
-    <t>Caldereria:</t>
-  </si>
-  <si>
-    <t>Preparación1 Materiales,Armado,Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1213333324436219</t>
-  </si>
-  <si>
-    <t>Preparación1 Materiales</t>
-  </si>
-  <si>
-    <t>Nicolás Mol</t>
-  </si>
-  <si>
-    <t>nicolas.mol@zitron.com</t>
-  </si>
-  <si>
-    <t>Caldereria:,Armado,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t>1213333324436220</t>
-  </si>
-  <si>
-    <t>Armado</t>
-  </si>
-  <si>
-    <t>Preparación1 Materiales,Check Planos,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2</t>
-  </si>
-  <si>
     <t>1214075676500706</t>
   </si>
   <si>
@@ -1121,6 +1121,12 @@
   </si>
   <si>
     <t>1214075676500838</t>
+  </si>
+  <si>
+    <t>1215845094807099</t>
+  </si>
+  <si>
+    <t>OT 4215 tABLERO DE FUERZA SS</t>
   </si>
   <si>
     <t>1213333324436236</t>
@@ -1836,7 +1842,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U232"/>
+  <dimension ref="A1:U233"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10.4" customWidth="1"/>
@@ -2305,9 +2311,11 @@
       <c r="B10" s="5">
         <v>46073.767839004635</v>
       </c>
-      <c r="C10" s="6"/>
+      <c r="C10" s="5">
+        <v>46191.89493512732</v>
+      </c>
       <c r="D10" s="5">
-        <v>46114.5173246412</v>
+        <v>46191.89494637732</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -2342,8 +2350,12 @@
       <c r="Q10" s="6"/>
       <c r="R10" s="6"/>
       <c r="S10" s="6"/>
-      <c r="T10" s="6"/>
-      <c r="U10" s="6"/>
+      <c r="T10" s="6">
+        <v>1</v>
+      </c>
+      <c r="U10" s="11" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
@@ -2417,9 +2429,11 @@
       <c r="B12" s="5">
         <v>46073.7678396875</v>
       </c>
-      <c r="C12" s="6"/>
+      <c r="C12" s="5">
+        <v>46191.89490662037</v>
+      </c>
       <c r="D12" s="5">
-        <v>46191.7935575463</v>
+        <v>46191.894935613425</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2467,15 +2481,15 @@
         <v>31</v>
       </c>
       <c r="T12" s="6">
-        <v>0</v>
-      </c>
-      <c r="U12" s="12" t="s">
-        <v>55</v>
+        <v>1</v>
+      </c>
+      <c r="U12" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B13" s="8">
         <v>46073.76784</v>
@@ -2487,7 +2501,7 @@
         <v>46114.517410451386</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>25</v>
@@ -2511,7 +2525,7 @@
         <v>26</v>
       </c>
       <c r="O13" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P13" s="9" t="s">
         <v>26</v>
@@ -2528,7 +2542,7 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B14" s="5">
         <v>46073.76783829861</v>
@@ -2540,7 +2554,7 @@
         <v>46097.549856875004</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>26</v>
@@ -2567,13 +2581,13 @@
         <v>26</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>40</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q14" s="5">
         <v>46002</v>
@@ -2593,7 +2607,7 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B15" s="8">
         <v>46073.76783899305</v>
@@ -2605,7 +2619,7 @@
         <v>46114.517243159724</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>26</v>
@@ -2632,13 +2646,13 @@
         <v>26</v>
       </c>
       <c r="N15" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="O15" s="9" t="s">
         <v>40</v>
       </c>
       <c r="P15" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="Q15" s="8">
         <v>46002</v>
@@ -2658,7 +2672,7 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B16" s="5">
         <v>46073.767839328706</v>
@@ -2670,7 +2684,7 @@
         <v>46097.550135625</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
@@ -2697,13 +2711,13 @@
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>40</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q16" s="5">
         <v>46002</v>
@@ -2723,7 +2737,7 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B17" s="8">
         <v>46073.7678396875</v>
@@ -2735,7 +2749,7 @@
         <v>46114.517399375</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>26</v>
@@ -2762,13 +2776,13 @@
         <v>26</v>
       </c>
       <c r="N17" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="O17" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="P17" s="9" t="s">
         <v>70</v>
-      </c>
-      <c r="P17" s="9" t="s">
-        <v>71</v>
       </c>
       <c r="Q17" s="8">
         <v>46002</v>
@@ -2788,7 +2802,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B18" s="5">
         <v>46073.767839988424</v>
@@ -2800,7 +2814,7 @@
         <v>46146.4968544213</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>25</v>
@@ -2824,7 +2838,7 @@
         <v>26</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P18" s="6" t="s">
         <v>26</v>
@@ -2841,7 +2855,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B19" s="8">
         <v>46073.76784025463</v>
@@ -2853,7 +2867,7 @@
         <v>46114.517520312496</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>26</v>
@@ -2880,13 +2894,13 @@
         <v>26</v>
       </c>
       <c r="N19" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O19" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q19" s="8">
         <v>46006</v>
@@ -2906,7 +2920,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B20" s="5">
         <v>46073.76784056713</v>
@@ -2918,7 +2932,7 @@
         <v>46097.54990454861</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -2945,13 +2959,13 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q20" s="5">
         <v>46006</v>
@@ -2971,7 +2985,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B21" s="8">
         <v>46073.767840879635</v>
@@ -2983,7 +2997,7 @@
         <v>46114.51760107639</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>26</v>
@@ -3010,13 +3024,13 @@
         <v>26</v>
       </c>
       <c r="N21" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O21" s="9" t="s">
         <v>48</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q21" s="8">
         <v>46007</v>
@@ -3036,7 +3050,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B22" s="5">
         <v>46073.76784115741</v>
@@ -3048,16 +3062,16 @@
         <v>46135.43132456018</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I22" s="5">
         <v>46006</v>
@@ -3075,13 +3089,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Q22" s="5">
         <v>46006</v>
@@ -3101,7 +3115,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B23" s="8">
         <v>46073.76783766204</v>
@@ -3113,16 +3127,16 @@
         <v>46100.78183767361</v>
       </c>
       <c r="E23" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G23" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="F23" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G23" s="9" t="s">
+      <c r="H23" s="9" t="s">
         <v>90</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>91</v>
       </c>
       <c r="I23" s="8">
         <v>46008</v>
@@ -3140,13 +3154,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q23" s="8">
         <v>46008</v>
@@ -3166,7 +3180,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B24" s="5">
         <v>46114.77467594907</v>
@@ -3178,16 +3192,16 @@
         <v>46114.77593953704</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="H24" s="6" t="s">
         <v>90</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>91</v>
       </c>
       <c r="I24" s="6"/>
       <c r="J24" s="6"/>
@@ -3201,7 +3215,7 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>26</v>
@@ -3221,17 +3235,19 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B25" s="8">
         <v>46073.767838009255</v>
       </c>
-      <c r="C25" s="9"/>
+      <c r="C25" s="8">
+        <v>46191.89589885417</v>
+      </c>
       <c r="D25" s="8">
-        <v>46191.79346162037</v>
+        <v>46191.89593702546</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>25</v>
@@ -3255,7 +3271,7 @@
         <v>26</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="P25" s="9" t="s">
         <v>26</v>
@@ -3263,14 +3279,16 @@
       <c r="Q25" s="9"/>
       <c r="R25" s="9"/>
       <c r="S25" s="9"/>
-      <c r="T25" s="9"/>
-      <c r="U25" s="12" t="s">
-        <v>55</v>
+      <c r="T25" s="9">
+        <v>1</v>
+      </c>
+      <c r="U25" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B26" s="5">
         <v>46073.76783827547</v>
@@ -3282,16 +3300,16 @@
         <v>46114.51796603009</v>
       </c>
       <c r="E26" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G26" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="F26" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G26" s="6" t="s">
+      <c r="H26" s="6" t="s">
         <v>100</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>101</v>
       </c>
       <c r="I26" s="5">
         <v>46008</v>
@@ -3309,13 +3327,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Q26" s="5">
         <v>46008</v>
@@ -3335,7 +3353,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B27" s="8">
         <v>46073.7678385301</v>
@@ -3347,16 +3365,16 @@
         <v>46114.5177578588</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="H27" s="9" t="s">
         <v>100</v>
-      </c>
-      <c r="H27" s="9" t="s">
-        <v>101</v>
       </c>
       <c r="I27" s="8">
         <v>46008</v>
@@ -3374,29 +3392,29 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
       <c r="S27" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T27" s="9">
         <v>0</v>
       </c>
       <c r="U27" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B28" s="5">
         <v>46073.767838796295</v>
@@ -3408,16 +3426,16 @@
         <v>46114.517796608794</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="H28" s="6" t="s">
         <v>100</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>101</v>
       </c>
       <c r="I28" s="5">
         <v>46010</v>
@@ -3435,29 +3453,29 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
       <c r="S28" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B29" s="8">
         <v>46073.767839120366</v>
@@ -3469,16 +3487,16 @@
         <v>46191.793455046296</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="H29" s="9" t="s">
         <v>100</v>
-      </c>
-      <c r="H29" s="9" t="s">
-        <v>101</v>
       </c>
       <c r="I29" s="8">
         <v>46009</v>
@@ -3496,13 +3514,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Q29" s="8">
         <v>46009</v>
@@ -3522,7 +3540,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B30" s="5">
         <v>46073.76783938658</v>
@@ -3534,16 +3552,16 @@
         <v>46169.84669766204</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>100</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>101</v>
       </c>
       <c r="I30" s="5">
         <v>46009</v>
@@ -3561,29 +3579,29 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
       <c r="S30" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
       </c>
       <c r="U30" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B31" s="8">
         <v>46073.7678396875</v>
@@ -3595,16 +3613,16 @@
         <v>46191.79342476852</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="H31" s="9" t="s">
         <v>100</v>
-      </c>
-      <c r="H31" s="9" t="s">
-        <v>101</v>
       </c>
       <c r="I31" s="8">
         <v>46020</v>
@@ -3622,29 +3640,29 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
       <c r="S31" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T31" s="9">
         <v>0</v>
       </c>
       <c r="U31" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B32" s="5">
         <v>46073.76784030093</v>
@@ -3656,16 +3674,16 @@
         <v>46122.658178784724</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="H32" s="6" t="s">
         <v>100</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>101</v>
       </c>
       <c r="I32" s="5">
         <v>46008</v>
@@ -3683,13 +3701,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Q32" s="5">
         <v>46008</v>
@@ -3709,7 +3727,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B33" s="8">
         <v>46073.7678405787</v>
@@ -3721,16 +3739,16 @@
         <v>46122.65810958333</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="H33" s="9" t="s">
         <v>100</v>
-      </c>
-      <c r="H33" s="9" t="s">
-        <v>101</v>
       </c>
       <c r="I33" s="8">
         <v>46008</v>
@@ -3748,29 +3766,29 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
       <c r="S33" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T33" s="9">
         <v>0</v>
       </c>
       <c r="U33" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B34" s="5">
         <v>46073.76783680556</v>
@@ -3782,16 +3800,16 @@
         <v>46122.658152662036</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="H34" s="6" t="s">
         <v>100</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>101</v>
       </c>
       <c r="I34" s="5">
         <v>46010</v>
@@ -3809,29 +3827,29 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
       <c r="S34" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T34" s="6">
         <v>0</v>
       </c>
       <c r="U34" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B35" s="8">
         <v>46073.76783711805</v>
@@ -3843,16 +3861,16 @@
         <v>46097.55004581019</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="H35" s="9" t="s">
         <v>100</v>
-      </c>
-      <c r="H35" s="9" t="s">
-        <v>101</v>
       </c>
       <c r="I35" s="8">
         <v>46008</v>
@@ -3870,13 +3888,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Q35" s="8">
         <v>46008</v>
@@ -3896,7 +3914,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B36" s="5">
         <v>46073.76783739583</v>
@@ -3908,16 +3926,16 @@
         <v>46097.54995472222</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>100</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>101</v>
       </c>
       <c r="I36" s="5">
         <v>46008</v>
@@ -3935,29 +3953,29 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
       <c r="S36" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T36" s="6">
         <v>0</v>
       </c>
       <c r="U36" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B37" s="8">
         <v>46073.76783761574</v>
@@ -3969,16 +3987,16 @@
         <v>46097.54999799769</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="H37" s="9" t="s">
         <v>100</v>
-      </c>
-      <c r="H37" s="9" t="s">
-        <v>101</v>
       </c>
       <c r="I37" s="8">
         <v>46017</v>
@@ -3996,29 +4014,29 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
       <c r="S37" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T37" s="9">
         <v>0</v>
       </c>
       <c r="U37" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B38" s="5">
         <v>46073.76783783565</v>
@@ -4030,16 +4048,16 @@
         <v>46097.55002008102</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>100</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>101</v>
       </c>
       <c r="I38" s="5">
         <v>46017</v>
@@ -4057,29 +4075,29 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
       <c r="S38" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T38" s="6">
         <v>0</v>
       </c>
       <c r="U38" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B39" s="8">
         <v>46073.76783806713</v>
@@ -4091,16 +4109,16 @@
         <v>46097.550347881945</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="H39" s="9" t="s">
         <v>100</v>
-      </c>
-      <c r="H39" s="9" t="s">
-        <v>101</v>
       </c>
       <c r="I39" s="8">
         <v>46010</v>
@@ -4118,13 +4136,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Q39" s="8">
         <v>46010</v>
@@ -4144,7 +4162,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B40" s="5">
         <v>46073.76783829861</v>
@@ -4156,16 +4174,16 @@
         <v>46097.55025519676</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>100</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>101</v>
       </c>
       <c r="I40" s="5">
         <v>46010</v>
@@ -4183,29 +4201,29 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
       <c r="S40" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T40" s="6">
         <v>0</v>
       </c>
       <c r="U40" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B41" s="8">
         <v>46073.76783851851</v>
@@ -4217,16 +4235,16 @@
         <v>46097.550321400464</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="H41" s="9" t="s">
         <v>100</v>
-      </c>
-      <c r="H41" s="9" t="s">
-        <v>101</v>
       </c>
       <c r="I41" s="8">
         <v>46021</v>
@@ -4244,29 +4262,29 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
       <c r="S41" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T41" s="9">
         <v>0</v>
       </c>
       <c r="U41" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B42" s="5">
         <v>46073.76783873842</v>
@@ -4276,7 +4294,7 @@
         <v>46142.64957708333</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>25</v>
@@ -4300,7 +4318,7 @@
         <v>26</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4313,7 +4331,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B43" s="8">
         <v>46073.76783896991</v>
@@ -4325,16 +4343,16 @@
         <v>46097.814911249996</v>
       </c>
       <c r="E43" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="F43" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G43" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="F43" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G43" s="9" t="s">
+      <c r="H43" s="9" t="s">
         <v>155</v>
-      </c>
-      <c r="H43" s="9" t="s">
-        <v>156</v>
       </c>
       <c r="I43" s="8">
         <v>46007</v>
@@ -4352,13 +4370,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Q43" s="8">
         <v>46007</v>
@@ -4378,7 +4396,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B44" s="5">
         <v>46073.76783739583</v>
@@ -4390,16 +4408,16 @@
         <v>46097.8150140162</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>155</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>156</v>
       </c>
       <c r="I44" s="5">
         <v>46028</v>
@@ -4417,13 +4435,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O44" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="P44" s="6" t="s">
         <v>160</v>
-      </c>
-      <c r="P44" s="6" t="s">
-        <v>161</v>
       </c>
       <c r="Q44" s="5">
         <v>46028</v>
@@ -4443,7 +4461,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B45" s="8">
         <v>46090.4939284838</v>
@@ -4455,16 +4473,16 @@
         <v>46097.815063622686</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="H45" s="9" t="s">
         <v>155</v>
-      </c>
-      <c r="H45" s="9" t="s">
-        <v>156</v>
       </c>
       <c r="I45" s="9"/>
       <c r="J45" s="8">
@@ -4480,13 +4498,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q45" s="8">
         <v>46035</v>
@@ -4506,7 +4524,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B46" s="5">
         <v>46090.493990891206</v>
@@ -4516,16 +4534,16 @@
         <v>46129.678973692135</v>
       </c>
       <c r="E46" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G46" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="F46" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G46" s="6" t="s">
+      <c r="H46" s="6" t="s">
         <v>167</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>168</v>
       </c>
       <c r="I46" s="6"/>
       <c r="J46" s="5">
@@ -4541,10 +4559,10 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4562,12 +4580,12 @@
         <v>0</v>
       </c>
       <c r="U46" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B47" s="8">
         <v>46128.56674524306</v>
@@ -4577,16 +4595,16 @@
         <v>46191.79533020833</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="H47" s="9" t="s">
         <v>167</v>
-      </c>
-      <c r="H47" s="9" t="s">
-        <v>168</v>
       </c>
       <c r="I47" s="9"/>
       <c r="J47" s="8">
@@ -4602,13 +4620,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O47" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="P47" s="9" t="s">
         <v>171</v>
-      </c>
-      <c r="P47" s="9" t="s">
-        <v>172</v>
       </c>
       <c r="Q47" s="9"/>
       <c r="R47" s="9"/>
@@ -4618,7 +4636,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B48" s="5">
         <v>46128.566755555556</v>
@@ -4628,16 +4646,16 @@
         <v>46191.795324189814</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>167</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>168</v>
       </c>
       <c r="I48" s="6"/>
       <c r="J48" s="5">
@@ -4653,13 +4671,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O48" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="P48" s="6" t="s">
         <v>171</v>
-      </c>
-      <c r="P48" s="6" t="s">
-        <v>172</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4669,7 +4687,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B49" s="8">
         <v>46128.56676210648</v>
@@ -4679,16 +4697,16 @@
         <v>46191.79531811342</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="H49" s="9" t="s">
         <v>167</v>
-      </c>
-      <c r="H49" s="9" t="s">
-        <v>168</v>
       </c>
       <c r="I49" s="9"/>
       <c r="J49" s="8">
@@ -4704,13 +4722,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O49" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="P49" s="9" t="s">
         <v>171</v>
-      </c>
-      <c r="P49" s="9" t="s">
-        <v>172</v>
       </c>
       <c r="Q49" s="9"/>
       <c r="R49" s="9"/>
@@ -4720,7 +4738,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B50" s="5">
         <v>46128.56676847222</v>
@@ -4730,16 +4748,16 @@
         <v>46191.79531166666</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="H50" s="6" t="s">
         <v>167</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>168</v>
       </c>
       <c r="I50" s="6"/>
       <c r="J50" s="5">
@@ -4755,13 +4773,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O50" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="P50" s="6" t="s">
         <v>171</v>
-      </c>
-      <c r="P50" s="6" t="s">
-        <v>172</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4771,7 +4789,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B51" s="8">
         <v>46128.566774120365</v>
@@ -4781,16 +4799,16 @@
         <v>46191.795306423606</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="H51" s="9" t="s">
         <v>167</v>
-      </c>
-      <c r="H51" s="9" t="s">
-        <v>168</v>
       </c>
       <c r="I51" s="9"/>
       <c r="J51" s="8">
@@ -4806,13 +4824,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O51" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="P51" s="9" t="s">
         <v>171</v>
-      </c>
-      <c r="P51" s="9" t="s">
-        <v>172</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -4822,7 +4840,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B52" s="5">
         <v>46128.566780127316</v>
@@ -4832,16 +4850,16 @@
         <v>46191.7952890625</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>167</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>168</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -4857,13 +4875,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O52" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="P52" s="6" t="s">
         <v>171</v>
-      </c>
-      <c r="P52" s="6" t="s">
-        <v>172</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4873,7 +4891,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B53" s="8">
         <v>46128.56678613426</v>
@@ -4883,16 +4901,16 @@
         <v>46191.79528329861</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="H53" s="9" t="s">
         <v>167</v>
-      </c>
-      <c r="H53" s="9" t="s">
-        <v>168</v>
       </c>
       <c r="I53" s="9"/>
       <c r="J53" s="8">
@@ -4908,13 +4926,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O53" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="P53" s="9" t="s">
         <v>171</v>
-      </c>
-      <c r="P53" s="9" t="s">
-        <v>172</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -4924,7 +4942,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B54" s="5">
         <v>46128.566790682875</v>
@@ -4934,16 +4952,16 @@
         <v>46191.79527969907</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>167</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>168</v>
       </c>
       <c r="I54" s="6"/>
       <c r="J54" s="5">
@@ -4959,13 +4977,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O54" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="P54" s="6" t="s">
         <v>171</v>
-      </c>
-      <c r="P54" s="6" t="s">
-        <v>172</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4975,7 +4993,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B55" s="8">
         <v>46128.5667968287</v>
@@ -4985,16 +5003,16 @@
         <v>46191.795272557865</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="H55" s="9" t="s">
         <v>167</v>
-      </c>
-      <c r="H55" s="9" t="s">
-        <v>168</v>
       </c>
       <c r="I55" s="9"/>
       <c r="J55" s="8">
@@ -5010,13 +5028,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O55" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="P55" s="9" t="s">
         <v>171</v>
-      </c>
-      <c r="P55" s="9" t="s">
-        <v>172</v>
       </c>
       <c r="Q55" s="9"/>
       <c r="R55" s="9"/>
@@ -5026,7 +5044,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B56" s="5">
         <v>46128.56680166667</v>
@@ -5036,16 +5054,16 @@
         <v>46191.795269375</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>167</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>168</v>
       </c>
       <c r="I56" s="6"/>
       <c r="J56" s="5">
@@ -5061,13 +5079,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O56" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="P56" s="6" t="s">
         <v>171</v>
-      </c>
-      <c r="P56" s="6" t="s">
-        <v>172</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -5077,7 +5095,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B57" s="8">
         <v>46128.566807256946</v>
@@ -5087,16 +5105,16 @@
         <v>46191.7952605787</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="H57" s="9" t="s">
         <v>167</v>
-      </c>
-      <c r="H57" s="9" t="s">
-        <v>168</v>
       </c>
       <c r="I57" s="9"/>
       <c r="J57" s="8">
@@ -5112,13 +5130,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O57" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="P57" s="9" t="s">
         <v>171</v>
-      </c>
-      <c r="P57" s="9" t="s">
-        <v>172</v>
       </c>
       <c r="Q57" s="9"/>
       <c r="R57" s="9"/>
@@ -5128,7 +5146,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B58" s="5">
         <v>46128.56681135416</v>
@@ -5138,16 +5156,16 @@
         <v>46191.79525575231</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>167</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>168</v>
       </c>
       <c r="I58" s="6"/>
       <c r="J58" s="5">
@@ -5163,13 +5181,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O58" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="P58" s="6" t="s">
         <v>171</v>
-      </c>
-      <c r="P58" s="6" t="s">
-        <v>172</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -5179,7 +5197,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B59" s="8">
         <v>46073.76783778935</v>
@@ -5191,7 +5209,7 @@
         <v>46097.81565780092</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>25</v>
@@ -5215,7 +5233,7 @@
         <v>26</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P59" s="9" t="s">
         <v>26</v>
@@ -5232,7 +5250,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B60" s="5">
         <v>46073.767838078704</v>
@@ -5244,16 +5262,16 @@
         <v>46097.81529010416</v>
       </c>
       <c r="E60" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G60" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="F60" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G60" s="6" t="s">
+      <c r="H60" s="6" t="s">
         <v>190</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>191</v>
       </c>
       <c r="I60" s="5">
         <v>46041</v>
@@ -5271,13 +5289,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Q60" s="5">
         <v>46041</v>
@@ -5297,7 +5315,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B61" s="8">
         <v>46073.7678383912</v>
@@ -5309,16 +5327,16 @@
         <v>46097.81562871528</v>
       </c>
       <c r="E61" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="F61" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G61" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="F61" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G61" s="9" t="s">
+      <c r="H61" s="9" t="s">
         <v>195</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>196</v>
       </c>
       <c r="I61" s="8">
         <v>46043</v>
@@ -5336,13 +5354,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q61" s="8">
         <v>46043</v>
@@ -5362,7 +5380,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B62" s="5">
         <v>46073.76783866898</v>
@@ -5374,7 +5392,7 @@
         <v>46191.77291996528</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>25</v>
@@ -5398,7 +5416,7 @@
         <v>26</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>26</v>
@@ -5415,7 +5433,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B63" s="8">
         <v>46073.767838935186</v>
@@ -5427,16 +5445,16 @@
         <v>46128.58222162037</v>
       </c>
       <c r="E63" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="F63" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G63" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="F63" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G63" s="9" t="s">
+      <c r="H63" s="9" t="s">
         <v>203</v>
-      </c>
-      <c r="H63" s="9" t="s">
-        <v>204</v>
       </c>
       <c r="I63" s="8">
         <v>46045</v>
@@ -5454,13 +5472,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q63" s="8">
         <v>46045</v>
@@ -5480,7 +5498,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B64" s="5">
         <v>46073.76783921296</v>
@@ -5492,16 +5510,16 @@
         <v>46158.97116490741</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>203</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>204</v>
       </c>
       <c r="I64" s="5">
         <v>46050</v>
@@ -5519,13 +5537,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q64" s="5">
         <v>46050</v>
@@ -5540,7 +5558,7 @@
         <v>1</v>
       </c>
       <c r="U64" s="12" t="s">
-        <v>55</v>
+        <v>208</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
@@ -5557,16 +5575,16 @@
         <v>46129.68420498843</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="H65" s="9" t="s">
         <v>203</v>
-      </c>
-      <c r="H65" s="9" t="s">
-        <v>204</v>
       </c>
       <c r="I65" s="8">
         <v>46050</v>
@@ -5584,7 +5602,7 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="O65" s="9" t="s">
         <v>210</v>
@@ -5612,16 +5630,16 @@
         <v>46129.684215497684</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="H66" s="6" t="s">
         <v>203</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>204</v>
       </c>
       <c r="I66" s="5">
         <v>46050</v>
@@ -5639,10 +5657,10 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>211</v>
@@ -5667,16 +5685,16 @@
         <v>46129.68427572917</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="H67" s="9" t="s">
         <v>203</v>
-      </c>
-      <c r="H67" s="9" t="s">
-        <v>204</v>
       </c>
       <c r="I67" s="8">
         <v>46050</v>
@@ -5694,10 +5712,10 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="P67" s="9" t="s">
         <v>211</v>
@@ -5722,16 +5740,16 @@
         <v>46129.68422782407</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>203</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>204</v>
       </c>
       <c r="I68" s="5">
         <v>46050</v>
@@ -5749,10 +5767,10 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>211</v>
@@ -5777,16 +5795,16 @@
         <v>46129.684293784725</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="H69" s="9" t="s">
         <v>203</v>
-      </c>
-      <c r="H69" s="9" t="s">
-        <v>204</v>
       </c>
       <c r="I69" s="8">
         <v>46050</v>
@@ -5804,10 +5822,10 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="P69" s="9" t="s">
         <v>211</v>
@@ -5832,16 +5850,16 @@
         <v>46129.68430454861</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>203</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>204</v>
       </c>
       <c r="I70" s="5">
         <v>46050</v>
@@ -5859,7 +5877,7 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>26</v>
@@ -5887,16 +5905,16 @@
         <v>46146.89516151621</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="H71" s="9" t="s">
         <v>203</v>
-      </c>
-      <c r="H71" s="9" t="s">
-        <v>204</v>
       </c>
       <c r="I71" s="8">
         <v>46050</v>
@@ -5914,7 +5932,7 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="O71" s="9" t="s">
         <v>218</v>
@@ -5942,16 +5960,16 @@
         <v>46146.89517496528</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>203</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>204</v>
       </c>
       <c r="I72" s="5">
         <v>46050</v>
@@ -5969,10 +5987,10 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>211</v>
@@ -5997,16 +6015,16 @@
         <v>46146.895229745365</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="H73" s="9" t="s">
         <v>203</v>
-      </c>
-      <c r="H73" s="9" t="s">
-        <v>204</v>
       </c>
       <c r="I73" s="8">
         <v>46050</v>
@@ -6024,10 +6042,10 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="P73" s="9" t="s">
         <v>211</v>
@@ -6052,16 +6070,16 @@
         <v>46146.8951958449</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>203</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>204</v>
       </c>
       <c r="I74" s="5">
         <v>46050</v>
@@ -6079,10 +6097,10 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>211</v>
@@ -6107,16 +6125,16 @@
         <v>46146.8953142824</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="H75" s="9" t="s">
         <v>203</v>
-      </c>
-      <c r="H75" s="9" t="s">
-        <v>204</v>
       </c>
       <c r="I75" s="8">
         <v>46050</v>
@@ -6134,10 +6152,10 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="P75" s="9" t="s">
         <v>211</v>
@@ -6162,16 +6180,16 @@
         <v>46146.895330486106</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="H76" s="6" t="s">
         <v>203</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>204</v>
       </c>
       <c r="I76" s="5">
         <v>46050</v>
@@ -6189,10 +6207,10 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>211</v>
@@ -6223,10 +6241,10 @@
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="H77" s="9" t="s">
         <v>195</v>
-      </c>
-      <c r="H77" s="9" t="s">
-        <v>196</v>
       </c>
       <c r="I77" s="9"/>
       <c r="J77" s="8">
@@ -6242,13 +6260,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O77" s="9" t="s">
         <v>226</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q77" s="8">
         <v>46055</v>
@@ -6263,7 +6281,7 @@
         <v>1</v>
       </c>
       <c r="U77" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
@@ -6280,16 +6298,16 @@
         <v>46129.6858422338</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="H78" s="6" t="s">
         <v>195</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>196</v>
       </c>
       <c r="I78" s="6"/>
       <c r="J78" s="5">
@@ -6308,7 +6326,7 @@
         <v>225</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>228</v>
@@ -6333,16 +6351,16 @@
         <v>46129.68585466435</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="H79" s="9" t="s">
         <v>195</v>
-      </c>
-      <c r="H79" s="9" t="s">
-        <v>196</v>
       </c>
       <c r="I79" s="9"/>
       <c r="J79" s="8">
@@ -6361,7 +6379,7 @@
         <v>225</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P79" s="9" t="s">
         <v>228</v>
@@ -6386,16 +6404,16 @@
         <v>46129.68589648148</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="H80" s="6" t="s">
         <v>195</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>196</v>
       </c>
       <c r="I80" s="6"/>
       <c r="J80" s="5">
@@ -6414,7 +6432,7 @@
         <v>225</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>228</v>
@@ -6439,16 +6457,16 @@
         <v>46129.685910949076</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="H81" s="9" t="s">
         <v>195</v>
-      </c>
-      <c r="H81" s="9" t="s">
-        <v>196</v>
       </c>
       <c r="I81" s="9"/>
       <c r="J81" s="8">
@@ -6467,7 +6485,7 @@
         <v>225</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P81" s="9" t="s">
         <v>228</v>
@@ -6492,16 +6510,16 @@
         <v>46129.68592581019</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="H82" s="6" t="s">
         <v>195</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>196</v>
       </c>
       <c r="I82" s="6"/>
       <c r="J82" s="5">
@@ -6520,7 +6538,7 @@
         <v>225</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>228</v>
@@ -6545,16 +6563,16 @@
         <v>46129.68595777778</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="H83" s="9" t="s">
         <v>195</v>
-      </c>
-      <c r="H83" s="9" t="s">
-        <v>196</v>
       </c>
       <c r="I83" s="9"/>
       <c r="J83" s="8">
@@ -6573,7 +6591,7 @@
         <v>225</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P83" s="9" t="s">
         <v>228</v>
@@ -6598,16 +6616,16 @@
         <v>46146.897389502315</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="H84" s="6" t="s">
         <v>195</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>196</v>
       </c>
       <c r="I84" s="6"/>
       <c r="J84" s="5">
@@ -6626,7 +6644,7 @@
         <v>225</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>228</v>
@@ -6651,16 +6669,16 @@
         <v>46146.89739724537</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="H85" s="9" t="s">
         <v>195</v>
-      </c>
-      <c r="H85" s="9" t="s">
-        <v>196</v>
       </c>
       <c r="I85" s="9"/>
       <c r="J85" s="8">
@@ -6679,7 +6697,7 @@
         <v>225</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P85" s="9" t="s">
         <v>228</v>
@@ -6704,16 +6722,16 @@
         <v>46146.89740662037</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="H86" s="6" t="s">
         <v>195</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>196</v>
       </c>
       <c r="I86" s="6"/>
       <c r="J86" s="5">
@@ -6732,7 +6750,7 @@
         <v>225</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>228</v>
@@ -6757,16 +6775,16 @@
         <v>46158.971886354164</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="H87" s="9" t="s">
         <v>195</v>
-      </c>
-      <c r="H87" s="9" t="s">
-        <v>196</v>
       </c>
       <c r="I87" s="9"/>
       <c r="J87" s="8">
@@ -6785,7 +6803,7 @@
         <v>225</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P87" s="9" t="s">
         <v>228</v>
@@ -6810,16 +6828,16 @@
         <v>46158.971913587964</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="H88" s="6" t="s">
         <v>195</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>196</v>
       </c>
       <c r="I88" s="6"/>
       <c r="J88" s="5">
@@ -6838,7 +6856,7 @@
         <v>225</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>228</v>
@@ -6863,16 +6881,16 @@
         <v>46158.971926909726</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="H89" s="9" t="s">
         <v>195</v>
-      </c>
-      <c r="H89" s="9" t="s">
-        <v>196</v>
       </c>
       <c r="I89" s="9"/>
       <c r="J89" s="8">
@@ -6891,7 +6909,7 @@
         <v>225</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P89" s="9" t="s">
         <v>228</v>
@@ -6916,7 +6934,7 @@
         <v>46191.79356716435</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>25</v>
@@ -6975,10 +6993,10 @@
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="H91" s="9" t="s">
         <v>190</v>
-      </c>
-      <c r="H91" s="9" t="s">
-        <v>191</v>
       </c>
       <c r="I91" s="9"/>
       <c r="J91" s="8">
@@ -6994,13 +7012,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q91" s="8">
         <v>46030</v>
@@ -7015,7 +7033,7 @@
         <v>0.2</v>
       </c>
       <c r="U91" s="12" t="s">
-        <v>55</v>
+        <v>208</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
@@ -7038,10 +7056,10 @@
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="H92" s="6" t="s">
         <v>190</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>191</v>
       </c>
       <c r="I92" s="5">
         <v>46069</v>
@@ -7059,10 +7077,10 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>245</v>
@@ -7103,10 +7121,10 @@
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="H93" s="9" t="s">
         <v>190</v>
-      </c>
-      <c r="H93" s="9" t="s">
-        <v>191</v>
       </c>
       <c r="I93" s="9"/>
       <c r="J93" s="8">
@@ -7122,13 +7140,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q93" s="8">
         <v>46014</v>
@@ -7143,7 +7161,7 @@
         <v>0</v>
       </c>
       <c r="U93" s="12" t="s">
-        <v>55</v>
+        <v>208</v>
       </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
@@ -7166,10 +7184,10 @@
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="H94" s="6" t="s">
         <v>190</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>191</v>
       </c>
       <c r="I94" s="6"/>
       <c r="J94" s="5">
@@ -7185,10 +7203,10 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>250</v>
@@ -7282,10 +7300,10 @@
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I96" s="5">
         <v>46056</v>
@@ -7341,16 +7359,16 @@
         <v>46129.68866337963</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I97" s="8">
         <v>46056</v>
@@ -7371,7 +7389,7 @@
         <v>255</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P97" s="9" t="s">
         <v>258</v>
@@ -7396,16 +7414,16 @@
         <v>46129.688671157404</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I98" s="5">
         <v>46056</v>
@@ -7426,7 +7444,7 @@
         <v>255</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P98" s="6" t="s">
         <v>258</v>
@@ -7451,16 +7469,16 @@
         <v>46129.68868245371</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H99" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I99" s="8">
         <v>46056</v>
@@ -7481,7 +7499,7 @@
         <v>255</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P99" s="9" t="s">
         <v>258</v>
@@ -7506,16 +7524,16 @@
         <v>46129.688693171294</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I100" s="5">
         <v>46056</v>
@@ -7536,7 +7554,7 @@
         <v>255</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P100" s="6" t="s">
         <v>258</v>
@@ -7561,16 +7579,16 @@
         <v>46129.68870375</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H101" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I101" s="8">
         <v>46056</v>
@@ -7591,7 +7609,7 @@
         <v>255</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P101" s="9" t="s">
         <v>258</v>
@@ -7616,16 +7634,16 @@
         <v>46158.974908738426</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I102" s="5">
         <v>46056</v>
@@ -7646,7 +7664,7 @@
         <v>255</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>258</v>
@@ -7671,16 +7689,16 @@
         <v>46158.97511034722</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H103" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I103" s="8">
         <v>46056</v>
@@ -7701,7 +7719,7 @@
         <v>255</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P103" s="9" t="s">
         <v>258</v>
@@ -7726,16 +7744,16 @@
         <v>46158.975184641204</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I104" s="5">
         <v>46056</v>
@@ -7756,7 +7774,7 @@
         <v>255</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P104" s="6" t="s">
         <v>258</v>
@@ -7781,16 +7799,16 @@
         <v>46191.79465511574</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H105" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I105" s="8">
         <v>46056</v>
@@ -7811,7 +7829,7 @@
         <v>255</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P105" s="9" t="s">
         <v>258</v>
@@ -7836,16 +7854,16 @@
         <v>46191.79466190972</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I106" s="5">
         <v>46056</v>
@@ -7866,7 +7884,7 @@
         <v>255</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P106" s="6" t="s">
         <v>258</v>
@@ -7891,16 +7909,16 @@
         <v>46191.79466734953</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H107" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I107" s="8">
         <v>46056</v>
@@ -7921,7 +7939,7 @@
         <v>255</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P107" s="9" t="s">
         <v>258</v>
@@ -7946,16 +7964,16 @@
         <v>46191.79473116898</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I108" s="5">
         <v>46056</v>
@@ -7976,7 +7994,7 @@
         <v>255</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P108" s="6" t="s">
         <v>258</v>
@@ -8007,10 +8025,10 @@
         <v>26</v>
       </c>
       <c r="G109" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H109" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I109" s="9"/>
       <c r="J109" s="8">
@@ -8064,16 +8082,16 @@
         <v>46157.498779988426</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I110" s="6"/>
       <c r="J110" s="5">
@@ -8092,7 +8110,7 @@
         <v>271</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>273</v>
@@ -8117,16 +8135,16 @@
         <v>46157.49878368055</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H111" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I111" s="9"/>
       <c r="J111" s="8">
@@ -8145,7 +8163,7 @@
         <v>271</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P111" s="9" t="s">
         <v>273</v>
@@ -8170,16 +8188,16 @@
         <v>46157.498788240744</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I112" s="6"/>
       <c r="J112" s="5">
@@ -8198,7 +8216,7 @@
         <v>271</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P112" s="6" t="s">
         <v>273</v>
@@ -8223,16 +8241,16 @@
         <v>46157.49879474537</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H113" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I113" s="9"/>
       <c r="J113" s="8">
@@ -8251,7 +8269,7 @@
         <v>271</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P113" s="9" t="s">
         <v>273</v>
@@ -8276,16 +8294,16 @@
         <v>46157.49884443287</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I114" s="6"/>
       <c r="J114" s="5">
@@ -8304,7 +8322,7 @@
         <v>271</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>273</v>
@@ -8329,16 +8347,16 @@
         <v>46158.97491230324</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H115" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I115" s="9"/>
       <c r="J115" s="8">
@@ -8357,7 +8375,7 @@
         <v>271</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P115" s="9" t="s">
         <v>273</v>
@@ -8382,16 +8400,16 @@
         <v>46158.975114155095</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I116" s="6"/>
       <c r="J116" s="5">
@@ -8410,7 +8428,7 @@
         <v>271</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P116" s="6" t="s">
         <v>273</v>
@@ -8435,16 +8453,16 @@
         <v>46158.97518857638</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H117" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I117" s="9"/>
       <c r="J117" s="8">
@@ -8463,7 +8481,7 @@
         <v>271</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P117" s="9" t="s">
         <v>273</v>
@@ -8488,16 +8506,16 @@
         <v>46191.794660555555</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I118" s="6"/>
       <c r="J118" s="5">
@@ -8516,7 +8534,7 @@
         <v>271</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P118" s="6" t="s">
         <v>273</v>
@@ -8541,16 +8559,16 @@
         <v>46191.79466525463</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H119" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I119" s="9"/>
       <c r="J119" s="8">
@@ -8569,7 +8587,7 @@
         <v>271</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P119" s="9" t="s">
         <v>273</v>
@@ -8594,16 +8612,16 @@
         <v>46191.794671875</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I120" s="6"/>
       <c r="J120" s="5">
@@ -8622,7 +8640,7 @@
         <v>271</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P120" s="6" t="s">
         <v>273</v>
@@ -8647,16 +8665,16 @@
         <v>46191.79473787037</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G121" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H121" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I121" s="9"/>
       <c r="J121" s="8">
@@ -8675,7 +8693,7 @@
         <v>271</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P121" s="9" t="s">
         <v>273</v>
@@ -8706,10 +8724,10 @@
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I122" s="5">
         <v>46064</v>
@@ -8765,16 +8783,16 @@
         <v>46157.49878587963</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G123" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H123" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I123" s="8">
         <v>46064</v>
@@ -8795,7 +8813,7 @@
         <v>286</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P123" s="9" t="s">
         <v>288</v>
@@ -8820,16 +8838,16 @@
         <v>46157.49878896991</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I124" s="5">
         <v>46064</v>
@@ -8850,7 +8868,7 @@
         <v>286</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P124" s="6" t="s">
         <v>288</v>
@@ -8875,16 +8893,16 @@
         <v>46157.49879293982</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H125" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I125" s="8">
         <v>46064</v>
@@ -8905,7 +8923,7 @@
         <v>286</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P125" s="9" t="s">
         <v>288</v>
@@ -8930,16 +8948,16 @@
         <v>46157.498799560184</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I126" s="5">
         <v>46064</v>
@@ -8960,7 +8978,7 @@
         <v>286</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P126" s="6" t="s">
         <v>288</v>
@@ -8985,16 +9003,16 @@
         <v>46157.49885005787</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H127" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I127" s="8">
         <v>46064</v>
@@ -9015,7 +9033,7 @@
         <v>286</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P127" s="9" t="s">
         <v>288</v>
@@ -9040,16 +9058,16 @@
         <v>46157.4988055787</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I128" s="5">
         <v>46064</v>
@@ -9070,7 +9088,7 @@
         <v>286</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P128" s="6" t="s">
         <v>288</v>
@@ -9095,16 +9113,16 @@
         <v>46157.49893354166</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H129" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I129" s="8">
         <v>46064</v>
@@ -9125,7 +9143,7 @@
         <v>286</v>
       </c>
       <c r="O129" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P129" s="9" t="s">
         <v>288</v>
@@ -9150,16 +9168,16 @@
         <v>46157.49900008102</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I130" s="5">
         <v>46064</v>
@@ -9180,7 +9198,7 @@
         <v>286</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P130" s="6" t="s">
         <v>288</v>
@@ -9205,16 +9223,16 @@
         <v>46191.7937930787</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H131" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I131" s="8">
         <v>46064</v>
@@ -9235,7 +9253,7 @@
         <v>286</v>
       </c>
       <c r="O131" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P131" s="9" t="s">
         <v>288</v>
@@ -9260,16 +9278,16 @@
         <v>46191.79424862268</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I132" s="5">
         <v>46064</v>
@@ -9290,7 +9308,7 @@
         <v>286</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P132" s="6" t="s">
         <v>288</v>
@@ -9315,16 +9333,16 @@
         <v>46191.79439909723</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H133" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I133" s="8">
         <v>46064</v>
@@ -9345,7 +9363,7 @@
         <v>286</v>
       </c>
       <c r="O133" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P133" s="9" t="s">
         <v>288</v>
@@ -9370,16 +9388,16 @@
         <v>46191.79452946759</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I134" s="5">
         <v>46064</v>
@@ -9400,7 +9418,7 @@
         <v>286</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P134" s="6" t="s">
         <v>288</v>
@@ -9431,10 +9449,10 @@
         <v>26</v>
       </c>
       <c r="G135" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H135" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I135" s="9"/>
       <c r="J135" s="8">
@@ -9471,7 +9489,7 @@
         <v>1</v>
       </c>
       <c r="U135" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
@@ -9488,16 +9506,16 @@
         <v>46157.49801296296</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I136" s="5">
         <v>46065</v>
@@ -9518,7 +9536,7 @@
         <v>301</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P136" s="6" t="s">
         <v>304</v>
@@ -9543,16 +9561,16 @@
         <v>46157.49802616898</v>
       </c>
       <c r="E137" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G137" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H137" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I137" s="8">
         <v>46065</v>
@@ -9573,7 +9591,7 @@
         <v>301</v>
       </c>
       <c r="O137" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P137" s="9" t="s">
         <v>304</v>
@@ -9598,16 +9616,16 @@
         <v>46157.49803459491</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I138" s="5">
         <v>46065</v>
@@ -9628,7 +9646,7 @@
         <v>301</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P138" s="6" t="s">
         <v>304</v>
@@ -9653,16 +9671,16 @@
         <v>46157.4980403588</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G139" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H139" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I139" s="8">
         <v>46065</v>
@@ -9683,7 +9701,7 @@
         <v>301</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P139" s="9" t="s">
         <v>304</v>
@@ -9708,16 +9726,16 @@
         <v>46157.49804547454</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I140" s="5">
         <v>46065</v>
@@ -9738,7 +9756,7 @@
         <v>301</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P140" s="6" t="s">
         <v>304</v>
@@ -9763,16 +9781,16 @@
         <v>46157.49809685185</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G141" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H141" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I141" s="8">
         <v>46065</v>
@@ -9793,7 +9811,7 @@
         <v>301</v>
       </c>
       <c r="O141" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P141" s="9" t="s">
         <v>304</v>
@@ -9818,16 +9836,16 @@
         <v>46157.498176423614</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I142" s="5">
         <v>46065</v>
@@ -9848,7 +9866,7 @@
         <v>301</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P142" s="6" t="s">
         <v>304</v>
@@ -9873,16 +9891,16 @@
         <v>46157.49829290509</v>
       </c>
       <c r="E143" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F143" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G143" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H143" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I143" s="8">
         <v>46065</v>
@@ -9903,7 +9921,7 @@
         <v>301</v>
       </c>
       <c r="O143" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P143" s="9" t="s">
         <v>304</v>
@@ -9928,16 +9946,16 @@
         <v>46191.793351631946</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H144" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I144" s="5">
         <v>46065</v>
@@ -9958,7 +9976,7 @@
         <v>301</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P144" s="6" t="s">
         <v>304</v>
@@ -9983,16 +10001,16 @@
         <v>46191.79344340278</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G145" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H145" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I145" s="8">
         <v>46065</v>
@@ -10013,7 +10031,7 @@
         <v>301</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P145" s="9" t="s">
         <v>304</v>
@@ -10038,16 +10056,16 @@
         <v>46191.79351224537</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I146" s="5">
         <v>46065</v>
@@ -10068,7 +10086,7 @@
         <v>301</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P146" s="6" t="s">
         <v>304</v>
@@ -10093,16 +10111,16 @@
         <v>46191.7935915625</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G147" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H147" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I147" s="8">
         <v>46065</v>
@@ -10123,7 +10141,7 @@
         <v>301</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P147" s="9" t="s">
         <v>304</v>
@@ -10154,10 +10172,10 @@
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H148" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I148" s="6"/>
       <c r="J148" s="5">
@@ -10194,7 +10212,7 @@
         <v>1</v>
       </c>
       <c r="U148" s="12" t="s">
-        <v>55</v>
+        <v>208</v>
       </c>
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
@@ -10211,16 +10229,16 @@
         <v>46191.79532310185</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G149" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H149" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I149" s="9"/>
       <c r="J149" s="8">
@@ -10239,7 +10257,7 @@
         <v>317</v>
       </c>
       <c r="O149" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P149" s="9" t="s">
         <v>319</v>
@@ -10264,16 +10282,16 @@
         <v>46191.7953178125</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G150" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H150" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I150" s="6"/>
       <c r="J150" s="5">
@@ -10292,7 +10310,7 @@
         <v>317</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P150" s="6" t="s">
         <v>319</v>
@@ -10317,16 +10335,16 @@
         <v>46191.79531292824</v>
       </c>
       <c r="E151" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F151" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G151" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H151" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I151" s="9"/>
       <c r="J151" s="8">
@@ -10345,7 +10363,7 @@
         <v>317</v>
       </c>
       <c r="O151" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P151" s="9" t="s">
         <v>319</v>
@@ -10370,16 +10388,16 @@
         <v>46191.79530751157</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G152" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H152" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I152" s="6"/>
       <c r="J152" s="5">
@@ -10398,7 +10416,7 @@
         <v>317</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P152" s="6" t="s">
         <v>323</v>
@@ -10423,16 +10441,16 @@
         <v>46191.79530002315</v>
       </c>
       <c r="E153" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F153" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G153" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H153" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I153" s="9"/>
       <c r="J153" s="8">
@@ -10451,7 +10469,7 @@
         <v>317</v>
       </c>
       <c r="O153" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P153" s="9" t="s">
         <v>319</v>
@@ -10476,16 +10494,16 @@
         <v>46191.79528344907</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G154" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H154" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I154" s="6"/>
       <c r="J154" s="5">
@@ -10504,7 +10522,7 @@
         <v>317</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P154" s="6" t="s">
         <v>319</v>
@@ -10529,16 +10547,16 @@
         <v>46191.79527836805</v>
       </c>
       <c r="E155" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F155" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G155" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H155" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I155" s="9"/>
       <c r="J155" s="8">
@@ -10557,7 +10575,7 @@
         <v>317</v>
       </c>
       <c r="O155" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P155" s="9" t="s">
         <v>319</v>
@@ -10582,16 +10600,16 @@
         <v>46191.79527357639</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G156" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H156" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I156" s="6"/>
       <c r="J156" s="5">
@@ -10610,7 +10628,7 @@
         <v>317</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P156" s="6" t="s">
         <v>319</v>
@@ -10635,16 +10653,16 @@
         <v>46191.795267951384</v>
       </c>
       <c r="E157" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F157" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G157" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H157" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I157" s="9"/>
       <c r="J157" s="8">
@@ -10663,7 +10681,7 @@
         <v>317</v>
       </c>
       <c r="O157" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P157" s="9" t="s">
         <v>319</v>
@@ -10688,16 +10706,16 @@
         <v>46191.79526363426</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G158" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H158" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I158" s="6"/>
       <c r="J158" s="5">
@@ -10716,7 +10734,7 @@
         <v>317</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P158" s="6" t="s">
         <v>319</v>
@@ -10741,16 +10759,16 @@
         <v>46191.79525519676</v>
       </c>
       <c r="E159" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F159" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G159" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H159" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I159" s="9"/>
       <c r="J159" s="8">
@@ -10769,7 +10787,7 @@
         <v>317</v>
       </c>
       <c r="O159" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P159" s="9" t="s">
         <v>319</v>
@@ -10794,16 +10812,16 @@
         <v>46191.795250173614</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G160" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H160" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I160" s="6"/>
       <c r="J160" s="5">
@@ -10822,7 +10840,7 @@
         <v>317</v>
       </c>
       <c r="O160" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P160" s="6" t="s">
         <v>319</v>
@@ -10853,10 +10871,10 @@
         <v>26</v>
       </c>
       <c r="G161" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H161" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I161" s="9"/>
       <c r="J161" s="8">
@@ -10893,7 +10911,7 @@
         <v>1</v>
       </c>
       <c r="U161" s="12" t="s">
-        <v>55</v>
+        <v>208</v>
       </c>
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.25">
@@ -10910,16 +10928,16 @@
         <v>46191.796622511574</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F162" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G162" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H162" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I162" s="6"/>
       <c r="J162" s="5">
@@ -10938,7 +10956,7 @@
         <v>333</v>
       </c>
       <c r="O162" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P162" s="6" t="s">
         <v>336</v>
@@ -10963,16 +10981,16 @@
         <v>46191.796466134256</v>
       </c>
       <c r="E163" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F163" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G163" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H163" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I163" s="9"/>
       <c r="J163" s="8">
@@ -10991,7 +11009,7 @@
         <v>333</v>
       </c>
       <c r="O163" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P163" s="9" t="s">
         <v>336</v>
@@ -11016,16 +11034,16 @@
         <v>46191.79639206019</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G164" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H164" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I164" s="6"/>
       <c r="J164" s="5">
@@ -11044,7 +11062,7 @@
         <v>333</v>
       </c>
       <c r="O164" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P164" s="6" t="s">
         <v>336</v>
@@ -11069,16 +11087,16 @@
         <v>46191.796298194444</v>
       </c>
       <c r="E165" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F165" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G165" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H165" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I165" s="9"/>
       <c r="J165" s="8">
@@ -11097,7 +11115,7 @@
         <v>333</v>
       </c>
       <c r="O165" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P165" s="9" t="s">
         <v>336</v>
@@ -11122,16 +11140,16 @@
         <v>46191.79617392361</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G166" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H166" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I166" s="6"/>
       <c r="J166" s="5">
@@ -11150,7 +11168,7 @@
         <v>333</v>
       </c>
       <c r="O166" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P166" s="6" t="s">
         <v>336</v>
@@ -11175,16 +11193,16 @@
         <v>46191.796110972224</v>
       </c>
       <c r="E167" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F167" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G167" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H167" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I167" s="9"/>
       <c r="J167" s="8">
@@ -11203,7 +11221,7 @@
         <v>333</v>
       </c>
       <c r="O167" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P167" s="9" t="s">
         <v>336</v>
@@ -11228,16 +11246,16 @@
         <v>46191.7960453125</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G168" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H168" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I168" s="6"/>
       <c r="J168" s="5">
@@ -11256,7 +11274,7 @@
         <v>333</v>
       </c>
       <c r="O168" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P168" s="6" t="s">
         <v>336</v>
@@ -11281,16 +11299,16 @@
         <v>46191.79597306713</v>
       </c>
       <c r="E169" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F169" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G169" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H169" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I169" s="9"/>
       <c r="J169" s="8">
@@ -11309,7 +11327,7 @@
         <v>333</v>
       </c>
       <c r="O169" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P169" s="9" t="s">
         <v>336</v>
@@ -11334,16 +11352,16 @@
         <v>46191.79585737269</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G170" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H170" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I170" s="6"/>
       <c r="J170" s="5">
@@ -11362,7 +11380,7 @@
         <v>333</v>
       </c>
       <c r="O170" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P170" s="6" t="s">
         <v>336</v>
@@ -11387,16 +11405,16 @@
         <v>46191.79577540509</v>
       </c>
       <c r="E171" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F171" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G171" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H171" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I171" s="9"/>
       <c r="J171" s="8">
@@ -11415,7 +11433,7 @@
         <v>333</v>
       </c>
       <c r="O171" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P171" s="9" t="s">
         <v>336</v>
@@ -11440,16 +11458,16 @@
         <v>46191.795636319446</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F172" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G172" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H172" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I172" s="6"/>
       <c r="J172" s="5">
@@ -11468,7 +11486,7 @@
         <v>333</v>
       </c>
       <c r="O172" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P172" s="6" t="s">
         <v>336</v>
@@ -11493,16 +11511,16 @@
         <v>46191.79555090278</v>
       </c>
       <c r="E173" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F173" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G173" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H173" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I173" s="9"/>
       <c r="J173" s="8">
@@ -11521,7 +11539,7 @@
         <v>333</v>
       </c>
       <c r="O173" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P173" s="9" t="s">
         <v>336</v>
@@ -11588,7 +11606,7 @@
       </c>
       <c r="C175" s="9"/>
       <c r="D175" s="8">
-        <v>46191.795426412034</v>
+        <v>46191.89507545139</v>
       </c>
       <c r="E175" s="9" t="s">
         <v>352</v>
@@ -11639,7 +11657,7 @@
         <v>0</v>
       </c>
       <c r="U175" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="176" spans="1:21" x14ac:dyDescent="0.25">
@@ -11651,10 +11669,10 @@
       </c>
       <c r="C176" s="6"/>
       <c r="D176" s="5">
-        <v>46191.79663023148</v>
+        <v>46191.885297430556</v>
       </c>
       <c r="E176" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F176" s="6" t="s">
         <v>26</v>
@@ -11682,7 +11700,7 @@
         <v>352</v>
       </c>
       <c r="O176" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P176" s="6" t="s">
         <v>357</v>
@@ -11702,10 +11720,10 @@
       </c>
       <c r="C177" s="9"/>
       <c r="D177" s="8">
-        <v>46191.79647164352</v>
+        <v>46191.88571055555</v>
       </c>
       <c r="E177" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F177" s="9" t="s">
         <v>26</v>
@@ -11733,7 +11751,7 @@
         <v>352</v>
       </c>
       <c r="O177" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P177" s="9" t="s">
         <v>357</v>
@@ -11753,10 +11771,10 @@
       </c>
       <c r="C178" s="6"/>
       <c r="D178" s="5">
-        <v>46191.796397881946</v>
+        <v>46191.88526354167</v>
       </c>
       <c r="E178" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F178" s="6" t="s">
         <v>26</v>
@@ -11784,7 +11802,7 @@
         <v>352</v>
       </c>
       <c r="O178" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P178" s="6" t="s">
         <v>357</v>
@@ -11804,10 +11822,10 @@
       </c>
       <c r="C179" s="9"/>
       <c r="D179" s="8">
-        <v>46191.796304710646</v>
+        <v>46191.88525847222</v>
       </c>
       <c r="E179" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F179" s="9" t="s">
         <v>26</v>
@@ -11835,7 +11853,7 @@
         <v>352</v>
       </c>
       <c r="O179" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P179" s="9" t="s">
         <v>357</v>
@@ -11855,10 +11873,10 @@
       </c>
       <c r="C180" s="6"/>
       <c r="D180" s="5">
-        <v>46191.79617898148</v>
+        <v>46191.88525349537</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F180" s="6" t="s">
         <v>26</v>
@@ -11886,7 +11904,7 @@
         <v>352</v>
       </c>
       <c r="O180" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P180" s="6" t="s">
         <v>357</v>
@@ -11906,10 +11924,10 @@
       </c>
       <c r="C181" s="9"/>
       <c r="D181" s="8">
-        <v>46191.79611597222</v>
+        <v>46191.885310405094</v>
       </c>
       <c r="E181" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F181" s="9" t="s">
         <v>26</v>
@@ -11937,7 +11955,7 @@
         <v>352</v>
       </c>
       <c r="O181" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P181" s="9" t="s">
         <v>357</v>
@@ -11960,7 +11978,7 @@
         <v>46191.796051701385</v>
       </c>
       <c r="E182" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F182" s="6" t="s">
         <v>26</v>
@@ -11988,7 +12006,7 @@
         <v>352</v>
       </c>
       <c r="O182" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P182" s="6" t="s">
         <v>357</v>
@@ -12011,7 +12029,7 @@
         <v>46191.795977581016</v>
       </c>
       <c r="E183" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F183" s="9" t="s">
         <v>26</v>
@@ -12039,7 +12057,7 @@
         <v>352</v>
       </c>
       <c r="O183" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P183" s="9" t="s">
         <v>365</v>
@@ -12062,7 +12080,7 @@
         <v>46191.795861736115</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F184" s="6" t="s">
         <v>26</v>
@@ -12090,7 +12108,7 @@
         <v>352</v>
       </c>
       <c r="O184" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P184" s="6" t="s">
         <v>357</v>
@@ -12113,7 +12131,7 @@
         <v>46191.795781168985</v>
       </c>
       <c r="E185" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F185" s="9" t="s">
         <v>26</v>
@@ -12141,7 +12159,7 @@
         <v>352</v>
       </c>
       <c r="O185" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P185" s="9" t="s">
         <v>357</v>
@@ -12164,7 +12182,7 @@
         <v>46191.795643460646</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F186" s="6" t="s">
         <v>26</v>
@@ -12192,7 +12210,7 @@
         <v>352</v>
       </c>
       <c r="O186" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P186" s="6" t="s">
         <v>357</v>
@@ -12215,7 +12233,7 @@
         <v>46191.795556990735</v>
       </c>
       <c r="E187" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F187" s="9" t="s">
         <v>26</v>
@@ -12243,7 +12261,7 @@
         <v>352</v>
       </c>
       <c r="O187" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P187" s="9" t="s">
         <v>357</v>
@@ -12259,13 +12277,11 @@
         <v>370</v>
       </c>
       <c r="B188" s="5">
-        <v>46073.7678383912</v>
-      </c>
-      <c r="C188" s="5">
-        <v>46191.796778240736</v>
-      </c>
+        <v>46191.895071886574</v>
+      </c>
+      <c r="C188" s="6"/>
       <c r="D188" s="5">
-        <v>46191.79679478009</v>
+        <v>46191.895473171295</v>
       </c>
       <c r="E188" s="6" t="s">
         <v>371</v>
@@ -12274,16 +12290,14 @@
         <v>26</v>
       </c>
       <c r="G188" s="6" t="s">
-        <v>86</v>
+        <v>353</v>
       </c>
       <c r="H188" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="I188" s="5">
-        <v>46077</v>
-      </c>
+        <v>354</v>
+      </c>
+      <c r="I188" s="6"/>
       <c r="J188" s="5">
-        <v>46077</v>
+        <v>46071</v>
       </c>
       <c r="K188" s="6" t="s">
         <v>26</v>
@@ -12295,52 +12309,44 @@
         <v>26</v>
       </c>
       <c r="N188" s="6" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="O188" s="6" t="s">
-        <v>256</v>
+        <v>26</v>
       </c>
       <c r="P188" s="6" t="s">
-        <v>349</v>
-      </c>
-      <c r="Q188" s="5">
-        <v>46077</v>
-      </c>
-      <c r="R188" s="5">
-        <v>46077</v>
-      </c>
-      <c r="S188" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="T188" s="6">
-        <v>1</v>
-      </c>
-      <c r="U188" s="11" t="s">
-        <v>32</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q188" s="6"/>
+      <c r="R188" s="6"/>
+      <c r="S188" s="6"/>
+      <c r="T188" s="6"/>
+      <c r="U188" s="6"/>
     </row>
     <row r="189" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A189" s="7" t="s">
         <v>372</v>
       </c>
       <c r="B189" s="8">
-        <v>46128.56718193287</v>
-      </c>
-      <c r="C189" s="9"/>
+        <v>46073.7678383912</v>
+      </c>
+      <c r="C189" s="8">
+        <v>46191.796778240736</v>
+      </c>
       <c r="D189" s="8">
-        <v>46129.683195879625</v>
+        <v>46191.79679478009</v>
       </c>
       <c r="E189" s="9" t="s">
-        <v>171</v>
+        <v>373</v>
       </c>
       <c r="F189" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G189" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H189" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I189" s="8">
         <v>46077</v>
@@ -12358,42 +12364,52 @@
         <v>26</v>
       </c>
       <c r="N189" s="9" t="s">
-        <v>371</v>
+        <v>349</v>
       </c>
       <c r="O189" s="9" t="s">
-        <v>171</v>
+        <v>256</v>
       </c>
       <c r="P189" s="9" t="s">
-        <v>373</v>
-      </c>
-      <c r="Q189" s="9"/>
-      <c r="R189" s="9"/>
-      <c r="S189" s="9"/>
-      <c r="T189" s="9"/>
-      <c r="U189" s="9"/>
+        <v>349</v>
+      </c>
+      <c r="Q189" s="8">
+        <v>46077</v>
+      </c>
+      <c r="R189" s="8">
+        <v>46077</v>
+      </c>
+      <c r="S189" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="T189" s="9">
+        <v>1</v>
+      </c>
+      <c r="U189" s="11" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="190" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
         <v>374</v>
       </c>
       <c r="B190" s="5">
-        <v>46128.567190092595</v>
+        <v>46128.56718193287</v>
       </c>
       <c r="C190" s="6"/>
       <c r="D190" s="5">
-        <v>46129.68319659722</v>
+        <v>46191.885307627315</v>
       </c>
       <c r="E190" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F190" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G190" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H190" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I190" s="5">
         <v>46077</v>
@@ -12411,13 +12427,13 @@
         <v>26</v>
       </c>
       <c r="N190" s="6" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="O190" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P190" s="6" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Q190" s="6"/>
       <c r="R190" s="6"/>
@@ -12427,26 +12443,26 @@
     </row>
     <row r="191" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A191" s="7" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B191" s="8">
-        <v>46128.567196550925</v>
+        <v>46128.567190092595</v>
       </c>
       <c r="C191" s="9"/>
       <c r="D191" s="8">
-        <v>46129.683197314815</v>
+        <v>46191.88571938657</v>
       </c>
       <c r="E191" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F191" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G191" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H191" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I191" s="8">
         <v>46077</v>
@@ -12464,13 +12480,13 @@
         <v>26</v>
       </c>
       <c r="N191" s="9" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="O191" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P191" s="9" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Q191" s="9"/>
       <c r="R191" s="9"/>
@@ -12480,26 +12496,26 @@
     </row>
     <row r="192" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B192" s="5">
-        <v>46128.56720474537</v>
+        <v>46128.567196550925</v>
       </c>
       <c r="C192" s="6"/>
       <c r="D192" s="5">
-        <v>46129.68319802084</v>
+        <v>46191.8852687037</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F192" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G192" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H192" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I192" s="5">
         <v>46077</v>
@@ -12517,13 +12533,13 @@
         <v>26</v>
       </c>
       <c r="N192" s="6" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="O192" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P192" s="6" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Q192" s="6"/>
       <c r="R192" s="6"/>
@@ -12533,26 +12549,26 @@
     </row>
     <row r="193" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A193" s="7" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B193" s="8">
-        <v>46128.56721146991</v>
+        <v>46128.56720474537</v>
       </c>
       <c r="C193" s="9"/>
       <c r="D193" s="8">
-        <v>46129.68319877315</v>
+        <v>46191.88526256944</v>
       </c>
       <c r="E193" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F193" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G193" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H193" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I193" s="8">
         <v>46077</v>
@@ -12570,13 +12586,13 @@
         <v>26</v>
       </c>
       <c r="N193" s="9" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="O193" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P193" s="9" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Q193" s="9"/>
       <c r="R193" s="9"/>
@@ -12586,26 +12602,26 @@
     </row>
     <row r="194" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B194" s="5">
-        <v>46128.56721795139</v>
+        <v>46128.56721146991</v>
       </c>
       <c r="C194" s="6"/>
       <c r="D194" s="5">
-        <v>46129.68319951389</v>
+        <v>46191.885259710645</v>
       </c>
       <c r="E194" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F194" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G194" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H194" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I194" s="5">
         <v>46077</v>
@@ -12623,13 +12639,13 @@
         <v>26</v>
       </c>
       <c r="N194" s="6" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="O194" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P194" s="6" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Q194" s="6"/>
       <c r="R194" s="6"/>
@@ -12639,26 +12655,26 @@
     </row>
     <row r="195" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A195" s="7" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B195" s="8">
-        <v>46128.56722548611</v>
+        <v>46128.56721795139</v>
       </c>
       <c r="C195" s="9"/>
       <c r="D195" s="8">
-        <v>46129.68320027778</v>
+        <v>46191.88531537037</v>
       </c>
       <c r="E195" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F195" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G195" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H195" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I195" s="8">
         <v>46077</v>
@@ -12676,13 +12692,13 @@
         <v>26</v>
       </c>
       <c r="N195" s="9" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="O195" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P195" s="9" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Q195" s="9"/>
       <c r="R195" s="9"/>
@@ -12692,26 +12708,26 @@
     </row>
     <row r="196" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B196" s="5">
-        <v>46128.567233333335</v>
+        <v>46128.56722548611</v>
       </c>
       <c r="C196" s="6"/>
       <c r="D196" s="5">
-        <v>46129.68320100695</v>
+        <v>46129.68320027778</v>
       </c>
       <c r="E196" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F196" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G196" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H196" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I196" s="5">
         <v>46077</v>
@@ -12729,13 +12745,13 @@
         <v>26</v>
       </c>
       <c r="N196" s="6" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="O196" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P196" s="6" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Q196" s="6"/>
       <c r="R196" s="6"/>
@@ -12745,26 +12761,26 @@
     </row>
     <row r="197" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A197" s="7" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B197" s="8">
-        <v>46128.56724010417</v>
+        <v>46128.567233333335</v>
       </c>
       <c r="C197" s="9"/>
       <c r="D197" s="8">
-        <v>46129.683201747685</v>
+        <v>46129.68320100695</v>
       </c>
       <c r="E197" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F197" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G197" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H197" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I197" s="8">
         <v>46077</v>
@@ -12782,13 +12798,13 @@
         <v>26</v>
       </c>
       <c r="N197" s="9" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="O197" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P197" s="9" t="s">
-        <v>26</v>
+        <v>375</v>
       </c>
       <c r="Q197" s="9"/>
       <c r="R197" s="9"/>
@@ -12798,26 +12814,26 @@
     </row>
     <row r="198" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B198" s="5">
-        <v>46128.56724606482</v>
+        <v>46128.56724010417</v>
       </c>
       <c r="C198" s="6"/>
       <c r="D198" s="5">
-        <v>46129.683202500004</v>
+        <v>46129.683201747685</v>
       </c>
       <c r="E198" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F198" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G198" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H198" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I198" s="5">
         <v>46077</v>
@@ -12835,13 +12851,13 @@
         <v>26</v>
       </c>
       <c r="N198" s="6" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="O198" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P198" s="6" t="s">
-        <v>373</v>
+        <v>26</v>
       </c>
       <c r="Q198" s="6"/>
       <c r="R198" s="6"/>
@@ -12851,26 +12867,26 @@
     </row>
     <row r="199" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A199" s="7" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B199" s="8">
-        <v>46128.56725237268</v>
+        <v>46128.56724606482</v>
       </c>
       <c r="C199" s="9"/>
       <c r="D199" s="8">
-        <v>46129.683203252316</v>
+        <v>46129.683202500004</v>
       </c>
       <c r="E199" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F199" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G199" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H199" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I199" s="8">
         <v>46077</v>
@@ -12888,13 +12904,13 @@
         <v>26</v>
       </c>
       <c r="N199" s="9" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="O199" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P199" s="9" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Q199" s="9"/>
       <c r="R199" s="9"/>
@@ -12904,26 +12920,26 @@
     </row>
     <row r="200" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B200" s="5">
-        <v>46128.56725944445</v>
+        <v>46128.56725237268</v>
       </c>
       <c r="C200" s="6"/>
       <c r="D200" s="5">
-        <v>46129.683203981476</v>
+        <v>46129.683203252316</v>
       </c>
       <c r="E200" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F200" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G200" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H200" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I200" s="5">
         <v>46077</v>
@@ -12941,13 +12957,13 @@
         <v>26</v>
       </c>
       <c r="N200" s="6" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="O200" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P200" s="6" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Q200" s="6"/>
       <c r="R200" s="6"/>
@@ -12957,32 +12973,32 @@
     </row>
     <row r="201" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A201" s="7" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B201" s="8">
-        <v>46073.76783868056</v>
-      </c>
-      <c r="C201" s="8">
-        <v>46191.79687179398</v>
-      </c>
+        <v>46128.56725944445</v>
+      </c>
+      <c r="C201" s="9"/>
       <c r="D201" s="8">
-        <v>46191.7968871875</v>
+        <v>46129.683203981476</v>
       </c>
       <c r="E201" s="9" t="s">
-        <v>386</v>
+        <v>170</v>
       </c>
       <c r="F201" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G201" s="9" t="s">
-        <v>203</v>
+        <v>85</v>
       </c>
       <c r="H201" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="I201" s="9"/>
+        <v>85</v>
+      </c>
+      <c r="I201" s="8">
+        <v>46077</v>
+      </c>
       <c r="J201" s="8">
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="K201" s="9" t="s">
         <v>26</v>
@@ -12994,52 +13010,44 @@
         <v>26</v>
       </c>
       <c r="N201" s="9" t="s">
-        <v>349</v>
+        <v>373</v>
       </c>
       <c r="O201" s="9" t="s">
-        <v>256</v>
+        <v>170</v>
       </c>
       <c r="P201" s="9" t="s">
-        <v>349</v>
-      </c>
-      <c r="Q201" s="8">
-        <v>46078</v>
-      </c>
-      <c r="R201" s="8">
-        <v>46078</v>
-      </c>
-      <c r="S201" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="T201" s="9">
-        <v>1</v>
-      </c>
-      <c r="U201" s="11" t="s">
-        <v>32</v>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="Q201" s="9"/>
+      <c r="R201" s="9"/>
+      <c r="S201" s="9"/>
+      <c r="T201" s="9"/>
+      <c r="U201" s="9"/>
     </row>
     <row r="202" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
         <v>387</v>
       </c>
       <c r="B202" s="5">
-        <v>46128.567313437496</v>
-      </c>
-      <c r="C202" s="6"/>
+        <v>46073.76783868056</v>
+      </c>
+      <c r="C202" s="5">
+        <v>46191.79687179398</v>
+      </c>
       <c r="D202" s="5">
-        <v>46129.68352643518</v>
+        <v>46191.7968871875</v>
       </c>
       <c r="E202" s="6" t="s">
-        <v>171</v>
+        <v>388</v>
       </c>
       <c r="F202" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G202" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="H202" s="6" t="s">
         <v>203</v>
-      </c>
-      <c r="H202" s="6" t="s">
-        <v>204</v>
       </c>
       <c r="I202" s="6"/>
       <c r="J202" s="5">
@@ -13055,42 +13063,52 @@
         <v>26</v>
       </c>
       <c r="N202" s="6" t="s">
-        <v>386</v>
+        <v>349</v>
       </c>
       <c r="O202" s="6" t="s">
-        <v>171</v>
+        <v>256</v>
       </c>
       <c r="P202" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="Q202" s="6"/>
-      <c r="R202" s="6"/>
-      <c r="S202" s="6"/>
-      <c r="T202" s="6"/>
-      <c r="U202" s="6"/>
+        <v>349</v>
+      </c>
+      <c r="Q202" s="5">
+        <v>46078</v>
+      </c>
+      <c r="R202" s="5">
+        <v>46078</v>
+      </c>
+      <c r="S202" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="T202" s="6">
+        <v>1</v>
+      </c>
+      <c r="U202" s="11" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="203" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A203" s="7" t="s">
         <v>389</v>
       </c>
       <c r="B203" s="8">
-        <v>46128.56732054398</v>
+        <v>46128.567313437496</v>
       </c>
       <c r="C203" s="9"/>
       <c r="D203" s="8">
-        <v>46129.68352717593</v>
+        <v>46129.68352643518</v>
       </c>
       <c r="E203" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F203" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G203" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="H203" s="9" t="s">
         <v>203</v>
-      </c>
-      <c r="H203" s="9" t="s">
-        <v>204</v>
       </c>
       <c r="I203" s="9"/>
       <c r="J203" s="8">
@@ -13106,13 +13124,13 @@
         <v>26</v>
       </c>
       <c r="N203" s="9" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="O203" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P203" s="9" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="Q203" s="9"/>
       <c r="R203" s="9"/>
@@ -13122,26 +13140,26 @@
     </row>
     <row r="204" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B204" s="5">
-        <v>46128.5673266088</v>
+        <v>46128.56732054398</v>
       </c>
       <c r="C204" s="6"/>
       <c r="D204" s="5">
-        <v>46129.68352791667</v>
+        <v>46129.68352717593</v>
       </c>
       <c r="E204" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F204" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G204" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="H204" s="6" t="s">
         <v>203</v>
-      </c>
-      <c r="H204" s="6" t="s">
-        <v>204</v>
       </c>
       <c r="I204" s="6"/>
       <c r="J204" s="5">
@@ -13157,13 +13175,13 @@
         <v>26</v>
       </c>
       <c r="N204" s="6" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="O204" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P204" s="6" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="Q204" s="6"/>
       <c r="R204" s="6"/>
@@ -13173,26 +13191,26 @@
     </row>
     <row r="205" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A205" s="7" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B205" s="8">
-        <v>46128.56733295139</v>
+        <v>46128.5673266088</v>
       </c>
       <c r="C205" s="9"/>
       <c r="D205" s="8">
-        <v>46129.683528657406</v>
+        <v>46129.68352791667</v>
       </c>
       <c r="E205" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F205" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G205" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="H205" s="9" t="s">
         <v>203</v>
-      </c>
-      <c r="H205" s="9" t="s">
-        <v>204</v>
       </c>
       <c r="I205" s="9"/>
       <c r="J205" s="8">
@@ -13208,13 +13226,13 @@
         <v>26</v>
       </c>
       <c r="N205" s="9" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="O205" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P205" s="9" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="Q205" s="9"/>
       <c r="R205" s="9"/>
@@ -13224,26 +13242,26 @@
     </row>
     <row r="206" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B206" s="5">
-        <v>46128.56733854167</v>
+        <v>46128.56733295139</v>
       </c>
       <c r="C206" s="6"/>
       <c r="D206" s="5">
-        <v>46129.68352943287</v>
+        <v>46129.683528657406</v>
       </c>
       <c r="E206" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F206" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G206" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="H206" s="6" t="s">
         <v>203</v>
-      </c>
-      <c r="H206" s="6" t="s">
-        <v>204</v>
       </c>
       <c r="I206" s="6"/>
       <c r="J206" s="5">
@@ -13259,13 +13277,13 @@
         <v>26</v>
       </c>
       <c r="N206" s="6" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="O206" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P206" s="6" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="Q206" s="6"/>
       <c r="R206" s="6"/>
@@ -13275,26 +13293,26 @@
     </row>
     <row r="207" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A207" s="7" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B207" s="8">
-        <v>46128.56734518518</v>
+        <v>46128.56733854167</v>
       </c>
       <c r="C207" s="9"/>
       <c r="D207" s="8">
-        <v>46129.68353019676</v>
+        <v>46129.68352943287</v>
       </c>
       <c r="E207" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F207" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G207" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="H207" s="9" t="s">
         <v>203</v>
-      </c>
-      <c r="H207" s="9" t="s">
-        <v>204</v>
       </c>
       <c r="I207" s="9"/>
       <c r="J207" s="8">
@@ -13310,13 +13328,13 @@
         <v>26</v>
       </c>
       <c r="N207" s="9" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="O207" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P207" s="9" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="Q207" s="9"/>
       <c r="R207" s="9"/>
@@ -13326,26 +13344,26 @@
     </row>
     <row r="208" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B208" s="5">
-        <v>46128.567351770835</v>
+        <v>46128.56734518518</v>
       </c>
       <c r="C208" s="6"/>
       <c r="D208" s="5">
-        <v>46129.683530891205</v>
+        <v>46129.68353019676</v>
       </c>
       <c r="E208" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F208" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G208" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="H208" s="6" t="s">
         <v>203</v>
-      </c>
-      <c r="H208" s="6" t="s">
-        <v>204</v>
       </c>
       <c r="I208" s="6"/>
       <c r="J208" s="5">
@@ -13361,13 +13379,13 @@
         <v>26</v>
       </c>
       <c r="N208" s="6" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="O208" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P208" s="6" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="Q208" s="6"/>
       <c r="R208" s="6"/>
@@ -13380,23 +13398,23 @@
         <v>396</v>
       </c>
       <c r="B209" s="8">
-        <v>46128.56735738426</v>
+        <v>46128.567351770835</v>
       </c>
       <c r="C209" s="9"/>
       <c r="D209" s="8">
-        <v>46129.68353159723</v>
+        <v>46129.683530891205</v>
       </c>
       <c r="E209" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F209" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G209" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="H209" s="9" t="s">
         <v>203</v>
-      </c>
-      <c r="H209" s="9" t="s">
-        <v>204</v>
       </c>
       <c r="I209" s="9"/>
       <c r="J209" s="8">
@@ -13412,13 +13430,13 @@
         <v>26</v>
       </c>
       <c r="N209" s="9" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="O209" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P209" s="9" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="Q209" s="9"/>
       <c r="R209" s="9"/>
@@ -13428,26 +13446,26 @@
     </row>
     <row r="210" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B210" s="5">
-        <v>46128.56736256945</v>
+        <v>46128.56735738426</v>
       </c>
       <c r="C210" s="6"/>
       <c r="D210" s="5">
-        <v>46129.68353232639</v>
+        <v>46129.68353159723</v>
       </c>
       <c r="E210" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F210" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G210" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="H210" s="6" t="s">
         <v>203</v>
-      </c>
-      <c r="H210" s="6" t="s">
-        <v>204</v>
       </c>
       <c r="I210" s="6"/>
       <c r="J210" s="5">
@@ -13463,13 +13481,13 @@
         <v>26</v>
       </c>
       <c r="N210" s="6" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="O210" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P210" s="6" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="Q210" s="6"/>
       <c r="R210" s="6"/>
@@ -13479,26 +13497,26 @@
     </row>
     <row r="211" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A211" s="7" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B211" s="8">
-        <v>46128.567368206015</v>
+        <v>46128.56736256945</v>
       </c>
       <c r="C211" s="9"/>
       <c r="D211" s="8">
-        <v>46129.683533125004</v>
+        <v>46129.68353232639</v>
       </c>
       <c r="E211" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F211" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G211" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="H211" s="9" t="s">
         <v>203</v>
-      </c>
-      <c r="H211" s="9" t="s">
-        <v>204</v>
       </c>
       <c r="I211" s="9"/>
       <c r="J211" s="8">
@@ -13514,13 +13532,13 @@
         <v>26</v>
       </c>
       <c r="N211" s="9" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="O211" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P211" s="9" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="Q211" s="9"/>
       <c r="R211" s="9"/>
@@ -13530,26 +13548,26 @@
     </row>
     <row r="212" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B212" s="5">
-        <v>46128.56737366898</v>
+        <v>46128.567368206015</v>
       </c>
       <c r="C212" s="6"/>
       <c r="D212" s="5">
-        <v>46129.68353385417</v>
+        <v>46129.683533125004</v>
       </c>
       <c r="E212" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F212" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G212" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="H212" s="6" t="s">
         <v>203</v>
-      </c>
-      <c r="H212" s="6" t="s">
-        <v>204</v>
       </c>
       <c r="I212" s="6"/>
       <c r="J212" s="5">
@@ -13565,13 +13583,13 @@
         <v>26</v>
       </c>
       <c r="N212" s="6" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="O212" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P212" s="6" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="Q212" s="6"/>
       <c r="R212" s="6"/>
@@ -13581,26 +13599,26 @@
     </row>
     <row r="213" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A213" s="7" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B213" s="8">
-        <v>46128.56737853009</v>
+        <v>46128.56737366898</v>
       </c>
       <c r="C213" s="9"/>
       <c r="D213" s="8">
-        <v>46129.68353459491</v>
+        <v>46129.68353385417</v>
       </c>
       <c r="E213" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F213" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G213" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="H213" s="9" t="s">
         <v>203</v>
-      </c>
-      <c r="H213" s="9" t="s">
-        <v>204</v>
       </c>
       <c r="I213" s="9"/>
       <c r="J213" s="8">
@@ -13616,13 +13634,13 @@
         <v>26</v>
       </c>
       <c r="N213" s="9" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="O213" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P213" s="9" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="Q213" s="9"/>
       <c r="R213" s="9"/>
@@ -13632,32 +13650,30 @@
     </row>
     <row r="214" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B214" s="5">
-        <v>46073.76783895833</v>
-      </c>
-      <c r="C214" s="5">
-        <v>46191.79693015046</v>
-      </c>
+        <v>46128.56737853009</v>
+      </c>
+      <c r="C214" s="6"/>
       <c r="D214" s="5">
-        <v>46191.79694662037</v>
+        <v>46129.68353459491</v>
       </c>
       <c r="E214" s="6" t="s">
-        <v>402</v>
+        <v>170</v>
       </c>
       <c r="F214" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G214" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="H214" s="6" t="s">
         <v>203</v>
-      </c>
-      <c r="H214" s="6" t="s">
-        <v>204</v>
       </c>
       <c r="I214" s="6"/>
       <c r="J214" s="5">
-        <v>46079</v>
+        <v>46078</v>
       </c>
       <c r="K214" s="6" t="s">
         <v>26</v>
@@ -13669,52 +13685,44 @@
         <v>26</v>
       </c>
       <c r="N214" s="6" t="s">
-        <v>349</v>
+        <v>388</v>
       </c>
       <c r="O214" s="6" t="s">
-        <v>256</v>
+        <v>170</v>
       </c>
       <c r="P214" s="6" t="s">
-        <v>403</v>
-      </c>
-      <c r="Q214" s="5">
-        <v>46079</v>
-      </c>
-      <c r="R214" s="5">
-        <v>46079</v>
-      </c>
-      <c r="S214" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="T214" s="6">
-        <v>1</v>
-      </c>
-      <c r="U214" s="11" t="s">
-        <v>32</v>
-      </c>
+        <v>397</v>
+      </c>
+      <c r="Q214" s="6"/>
+      <c r="R214" s="6"/>
+      <c r="S214" s="6"/>
+      <c r="T214" s="6"/>
+      <c r="U214" s="6"/>
     </row>
     <row r="215" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A215" s="7" t="s">
+        <v>403</v>
+      </c>
+      <c r="B215" s="8">
+        <v>46073.76783895833</v>
+      </c>
+      <c r="C215" s="8">
+        <v>46191.79693015046</v>
+      </c>
+      <c r="D215" s="8">
+        <v>46191.79694662037</v>
+      </c>
+      <c r="E215" s="9" t="s">
         <v>404</v>
       </c>
-      <c r="B215" s="8">
-        <v>46128.56746619213</v>
-      </c>
-      <c r="C215" s="9"/>
-      <c r="D215" s="8">
-        <v>46129.69451681713</v>
-      </c>
-      <c r="E215" s="9" t="s">
-        <v>171</v>
-      </c>
       <c r="F215" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G215" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="H215" s="9" t="s">
         <v>203</v>
-      </c>
-      <c r="H215" s="9" t="s">
-        <v>204</v>
       </c>
       <c r="I215" s="9"/>
       <c r="J215" s="8">
@@ -13730,42 +13738,52 @@
         <v>26</v>
       </c>
       <c r="N215" s="9" t="s">
-        <v>402</v>
+        <v>349</v>
       </c>
       <c r="O215" s="9" t="s">
-        <v>171</v>
+        <v>256</v>
       </c>
       <c r="P215" s="9" t="s">
-        <v>402</v>
-      </c>
-      <c r="Q215" s="9"/>
-      <c r="R215" s="9"/>
-      <c r="S215" s="9"/>
-      <c r="T215" s="9"/>
-      <c r="U215" s="9"/>
+        <v>405</v>
+      </c>
+      <c r="Q215" s="8">
+        <v>46079</v>
+      </c>
+      <c r="R215" s="8">
+        <v>46079</v>
+      </c>
+      <c r="S215" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="T215" s="9">
+        <v>1</v>
+      </c>
+      <c r="U215" s="11" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="216" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B216" s="5">
-        <v>46128.56747375</v>
+        <v>46128.56746619213</v>
       </c>
       <c r="C216" s="6"/>
       <c r="D216" s="5">
-        <v>46129.69454358796</v>
+        <v>46129.69451681713</v>
       </c>
       <c r="E216" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F216" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G216" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="H216" s="6" t="s">
         <v>203</v>
-      </c>
-      <c r="H216" s="6" t="s">
-        <v>204</v>
       </c>
       <c r="I216" s="6"/>
       <c r="J216" s="5">
@@ -13781,13 +13799,13 @@
         <v>26</v>
       </c>
       <c r="N216" s="6" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="O216" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P216" s="6" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="Q216" s="6"/>
       <c r="R216" s="6"/>
@@ -13797,26 +13815,26 @@
     </row>
     <row r="217" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A217" s="7" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B217" s="8">
-        <v>46128.567480833335</v>
+        <v>46128.56747375</v>
       </c>
       <c r="C217" s="9"/>
       <c r="D217" s="8">
-        <v>46129.694564502315</v>
+        <v>46129.69454358796</v>
       </c>
       <c r="E217" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F217" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G217" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="H217" s="9" t="s">
         <v>203</v>
-      </c>
-      <c r="H217" s="9" t="s">
-        <v>204</v>
       </c>
       <c r="I217" s="9"/>
       <c r="J217" s="8">
@@ -13832,13 +13850,13 @@
         <v>26</v>
       </c>
       <c r="N217" s="9" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="O217" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P217" s="9" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="Q217" s="9"/>
       <c r="R217" s="9"/>
@@ -13848,26 +13866,26 @@
     </row>
     <row r="218" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B218" s="5">
-        <v>46128.56748863426</v>
+        <v>46128.567480833335</v>
       </c>
       <c r="C218" s="6"/>
       <c r="D218" s="5">
-        <v>46129.694584282406</v>
+        <v>46129.694564502315</v>
       </c>
       <c r="E218" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F218" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G218" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="H218" s="6" t="s">
         <v>203</v>
-      </c>
-      <c r="H218" s="6" t="s">
-        <v>204</v>
       </c>
       <c r="I218" s="6"/>
       <c r="J218" s="5">
@@ -13883,13 +13901,13 @@
         <v>26</v>
       </c>
       <c r="N218" s="6" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="O218" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P218" s="6" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="Q218" s="6"/>
       <c r="R218" s="6"/>
@@ -13899,26 +13917,26 @@
     </row>
     <row r="219" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A219" s="7" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B219" s="8">
-        <v>46128.5674962037</v>
+        <v>46128.56748863426</v>
       </c>
       <c r="C219" s="9"/>
       <c r="D219" s="8">
-        <v>46129.69460693287</v>
+        <v>46129.694584282406</v>
       </c>
       <c r="E219" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F219" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G219" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="H219" s="9" t="s">
         <v>203</v>
-      </c>
-      <c r="H219" s="9" t="s">
-        <v>204</v>
       </c>
       <c r="I219" s="9"/>
       <c r="J219" s="8">
@@ -13934,13 +13952,13 @@
         <v>26</v>
       </c>
       <c r="N219" s="9" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="O219" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P219" s="9" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="Q219" s="9"/>
       <c r="R219" s="9"/>
@@ -13950,26 +13968,26 @@
     </row>
     <row r="220" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A220" s="4" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B220" s="5">
-        <v>46128.567504074075</v>
+        <v>46128.5674962037</v>
       </c>
       <c r="C220" s="6"/>
       <c r="D220" s="5">
-        <v>46129.69462627315</v>
+        <v>46129.69460693287</v>
       </c>
       <c r="E220" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F220" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G220" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="H220" s="6" t="s">
         <v>203</v>
-      </c>
-      <c r="H220" s="6" t="s">
-        <v>204</v>
       </c>
       <c r="I220" s="6"/>
       <c r="J220" s="5">
@@ -13985,13 +14003,13 @@
         <v>26</v>
       </c>
       <c r="N220" s="6" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="O220" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P220" s="6" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="Q220" s="6"/>
       <c r="R220" s="6"/>
@@ -14001,26 +14019,26 @@
     </row>
     <row r="221" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A221" s="7" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B221" s="8">
-        <v>46128.56751277778</v>
+        <v>46128.567504074075</v>
       </c>
       <c r="C221" s="9"/>
       <c r="D221" s="8">
-        <v>46129.69465064815</v>
+        <v>46129.69462627315</v>
       </c>
       <c r="E221" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F221" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G221" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="H221" s="9" t="s">
         <v>203</v>
-      </c>
-      <c r="H221" s="9" t="s">
-        <v>204</v>
       </c>
       <c r="I221" s="9"/>
       <c r="J221" s="8">
@@ -14036,13 +14054,13 @@
         <v>26</v>
       </c>
       <c r="N221" s="9" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="O221" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P221" s="9" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="Q221" s="9"/>
       <c r="R221" s="9"/>
@@ -14052,26 +14070,26 @@
     </row>
     <row r="222" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A222" s="4" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B222" s="5">
-        <v>46128.56752138889</v>
+        <v>46128.56751277778</v>
       </c>
       <c r="C222" s="6"/>
       <c r="D222" s="5">
-        <v>46129.69467157408</v>
+        <v>46129.69465064815</v>
       </c>
       <c r="E222" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F222" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G222" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="H222" s="6" t="s">
         <v>203</v>
-      </c>
-      <c r="H222" s="6" t="s">
-        <v>204</v>
       </c>
       <c r="I222" s="6"/>
       <c r="J222" s="5">
@@ -14087,13 +14105,13 @@
         <v>26</v>
       </c>
       <c r="N222" s="6" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="O222" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P222" s="6" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="Q222" s="6"/>
       <c r="R222" s="6"/>
@@ -14103,26 +14121,26 @@
     </row>
     <row r="223" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A223" s="7" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B223" s="8">
-        <v>46128.56752835648</v>
+        <v>46128.56752138889</v>
       </c>
       <c r="C223" s="9"/>
       <c r="D223" s="8">
-        <v>46129.69469225695</v>
+        <v>46129.69467157408</v>
       </c>
       <c r="E223" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F223" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G223" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="H223" s="9" t="s">
         <v>203</v>
-      </c>
-      <c r="H223" s="9" t="s">
-        <v>204</v>
       </c>
       <c r="I223" s="9"/>
       <c r="J223" s="8">
@@ -14138,13 +14156,13 @@
         <v>26</v>
       </c>
       <c r="N223" s="9" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="O223" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P223" s="9" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="Q223" s="9"/>
       <c r="R223" s="9"/>
@@ -14154,26 +14172,26 @@
     </row>
     <row r="224" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A224" s="4" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B224" s="5">
-        <v>46128.567536284725</v>
+        <v>46128.56752835648</v>
       </c>
       <c r="C224" s="6"/>
       <c r="D224" s="5">
-        <v>46129.694713379635</v>
+        <v>46129.69469225695</v>
       </c>
       <c r="E224" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F224" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G224" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="H224" s="6" t="s">
         <v>203</v>
-      </c>
-      <c r="H224" s="6" t="s">
-        <v>204</v>
       </c>
       <c r="I224" s="6"/>
       <c r="J224" s="5">
@@ -14189,13 +14207,13 @@
         <v>26</v>
       </c>
       <c r="N224" s="6" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="O224" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P224" s="6" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="Q224" s="6"/>
       <c r="R224" s="6"/>
@@ -14205,26 +14223,26 @@
     </row>
     <row r="225" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A225" s="7" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B225" s="8">
-        <v>46128.56754392361</v>
+        <v>46128.567536284725</v>
       </c>
       <c r="C225" s="9"/>
       <c r="D225" s="8">
-        <v>46129.694735682875</v>
+        <v>46129.694713379635</v>
       </c>
       <c r="E225" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F225" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G225" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="H225" s="9" t="s">
         <v>203</v>
-      </c>
-      <c r="H225" s="9" t="s">
-        <v>204</v>
       </c>
       <c r="I225" s="9"/>
       <c r="J225" s="8">
@@ -14240,13 +14258,13 @@
         <v>26</v>
       </c>
       <c r="N225" s="9" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="O225" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P225" s="9" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="Q225" s="9"/>
       <c r="R225" s="9"/>
@@ -14256,26 +14274,26 @@
     </row>
     <row r="226" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A226" s="4" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B226" s="5">
-        <v>46128.567550949076</v>
+        <v>46128.56754392361</v>
       </c>
       <c r="C226" s="6"/>
       <c r="D226" s="5">
-        <v>46129.694774895834</v>
+        <v>46129.694735682875</v>
       </c>
       <c r="E226" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F226" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G226" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="H226" s="6" t="s">
         <v>203</v>
-      </c>
-      <c r="H226" s="6" t="s">
-        <v>204</v>
       </c>
       <c r="I226" s="6"/>
       <c r="J226" s="5">
@@ -14291,13 +14309,13 @@
         <v>26</v>
       </c>
       <c r="N226" s="6" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="O226" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P226" s="6" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="Q226" s="6"/>
       <c r="R226" s="6"/>
@@ -14307,27 +14325,31 @@
     </row>
     <row r="227" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A227" s="7" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B227" s="8">
-        <v>46073.76783957176</v>
+        <v>46128.567550949076</v>
       </c>
       <c r="C227" s="9"/>
       <c r="D227" s="8">
-        <v>46076.83478885417</v>
+        <v>46129.694774895834</v>
       </c>
       <c r="E227" s="9" t="s">
-        <v>417</v>
+        <v>170</v>
       </c>
       <c r="F227" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G227" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H227" s="9"/>
+        <v>202</v>
+      </c>
+      <c r="H227" s="9" t="s">
+        <v>203</v>
+      </c>
       <c r="I227" s="9"/>
-      <c r="J227" s="9"/>
+      <c r="J227" s="8">
+        <v>46079</v>
+      </c>
       <c r="K227" s="9" t="s">
         <v>26</v>
       </c>
@@ -14335,16 +14357,16 @@
         <v>26</v>
       </c>
       <c r="M227" s="9" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N227" s="9" t="s">
-        <v>26</v>
+        <v>404</v>
       </c>
       <c r="O227" s="9" t="s">
-        <v>418</v>
+        <v>170</v>
       </c>
       <c r="P227" s="9" t="s">
-        <v>26</v>
+        <v>404</v>
       </c>
       <c r="Q227" s="9"/>
       <c r="R227" s="9"/>
@@ -14354,89 +14376,73 @@
     </row>
     <row r="228" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A228" s="4" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B228" s="5">
-        <v>46073.76783986111</v>
+        <v>46073.76783957176</v>
       </c>
       <c r="C228" s="6"/>
       <c r="D228" s="5">
-        <v>46191.79694986111</v>
+        <v>46076.83478885417</v>
       </c>
       <c r="E228" s="6" t="s">
+        <v>419</v>
+      </c>
+      <c r="F228" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G228" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H228" s="6"/>
+      <c r="I228" s="6"/>
+      <c r="J228" s="6"/>
+      <c r="K228" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L228" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M228" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="N228" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="O228" s="6" t="s">
         <v>420</v>
       </c>
-      <c r="F228" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G228" s="6" t="s">
-        <v>421</v>
-      </c>
-      <c r="H228" s="6" t="s">
-        <v>422</v>
-      </c>
-      <c r="I228" s="5">
-        <v>46080</v>
-      </c>
-      <c r="J228" s="5">
-        <v>46090</v>
-      </c>
-      <c r="K228" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L228" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M228" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N228" s="6" t="s">
-        <v>417</v>
-      </c>
-      <c r="O228" s="6" t="s">
-        <v>402</v>
-      </c>
       <c r="P228" s="6" t="s">
-        <v>417</v>
-      </c>
-      <c r="Q228" s="5">
-        <v>46080</v>
-      </c>
-      <c r="R228" s="5">
-        <v>46090</v>
-      </c>
-      <c r="S228" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="T228" s="6">
-        <v>0</v>
-      </c>
-      <c r="U228" s="12" t="s">
-        <v>55</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q228" s="6"/>
+      <c r="R228" s="6"/>
+      <c r="S228" s="6"/>
+      <c r="T228" s="6"/>
+      <c r="U228" s="6"/>
     </row>
     <row r="229" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A229" s="7" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B229" s="8">
-        <v>46073.767840127315</v>
+        <v>46073.76783986111</v>
       </c>
       <c r="C229" s="9"/>
       <c r="D229" s="8">
-        <v>46191.79695027778</v>
+        <v>46191.79694986111</v>
       </c>
       <c r="E229" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="F229" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G229" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="H229" s="9" t="s">
         <v>424</v>
-      </c>
-      <c r="F229" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G229" s="9" t="s">
-        <v>421</v>
-      </c>
-      <c r="H229" s="9" t="s">
-        <v>422</v>
       </c>
       <c r="I229" s="8">
         <v>46080</v>
@@ -14454,13 +14460,13 @@
         <v>26</v>
       </c>
       <c r="N229" s="9" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="O229" s="9" t="s">
-        <v>425</v>
+        <v>404</v>
       </c>
       <c r="P229" s="9" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="Q229" s="8">
         <v>46080</v>
@@ -14475,134 +14481,134 @@
         <v>0</v>
       </c>
       <c r="U229" s="12" t="s">
-        <v>55</v>
+        <v>208</v>
       </c>
     </row>
     <row r="230" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A230" s="4" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B230" s="5">
-        <v>46090.63839974537</v>
+        <v>46073.767840127315</v>
       </c>
       <c r="C230" s="6"/>
       <c r="D230" s="5">
-        <v>46091.862923043984</v>
+        <v>46191.79695027778</v>
       </c>
       <c r="E230" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="F230" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G230" s="6" t="s">
+        <v>423</v>
+      </c>
+      <c r="H230" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="I230" s="5">
+        <v>46080</v>
+      </c>
+      <c r="J230" s="5">
+        <v>46090</v>
+      </c>
+      <c r="K230" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L230" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M230" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N230" s="6" t="s">
+        <v>419</v>
+      </c>
+      <c r="O230" s="6" t="s">
         <v>427</v>
       </c>
-      <c r="F230" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G230" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H230" s="6"/>
-      <c r="I230" s="6"/>
-      <c r="J230" s="6"/>
-      <c r="K230" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L230" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M230" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="N230" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O230" s="6" t="s">
-        <v>428</v>
-      </c>
       <c r="P230" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q230" s="6"/>
-      <c r="R230" s="6"/>
-      <c r="S230" s="6"/>
+        <v>419</v>
+      </c>
+      <c r="Q230" s="5">
+        <v>46080</v>
+      </c>
+      <c r="R230" s="5">
+        <v>46090</v>
+      </c>
+      <c r="S230" s="10" t="s">
+        <v>31</v>
+      </c>
       <c r="T230" s="6">
         <v>0</v>
       </c>
-      <c r="U230" s="6"/>
+      <c r="U230" s="12" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="231" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A231" s="7" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B231" s="8">
-        <v>46090.638496851854</v>
+        <v>46090.63839974537</v>
       </c>
       <c r="C231" s="9"/>
       <c r="D231" s="8">
-        <v>46191.79695047454</v>
+        <v>46091.862923043984</v>
       </c>
       <c r="E231" s="9" t="s">
+        <v>429</v>
+      </c>
+      <c r="F231" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="G231" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H231" s="9"/>
+      <c r="I231" s="9"/>
+      <c r="J231" s="9"/>
+      <c r="K231" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L231" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M231" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="N231" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="O231" s="9" t="s">
         <v>430</v>
       </c>
-      <c r="F231" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G231" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="H231" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="I231" s="8">
-        <v>46080</v>
-      </c>
-      <c r="J231" s="8">
-        <v>46090</v>
-      </c>
-      <c r="K231" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L231" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M231" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N231" s="9" t="s">
-        <v>427</v>
-      </c>
-      <c r="O231" s="9" t="s">
-        <v>402</v>
-      </c>
       <c r="P231" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="Q231" s="8">
-        <v>46080</v>
-      </c>
-      <c r="R231" s="8">
-        <v>46090</v>
-      </c>
-      <c r="S231" s="10" t="s">
-        <v>31</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q231" s="9"/>
+      <c r="R231" s="9"/>
+      <c r="S231" s="9"/>
       <c r="T231" s="9">
         <v>0</v>
       </c>
-      <c r="U231" s="12" t="s">
-        <v>55</v>
-      </c>
+      <c r="U231" s="9"/>
     </row>
     <row r="232" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A232" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B232" s="5">
-        <v>46090.63872243055</v>
+        <v>46090.638496851854</v>
       </c>
       <c r="C232" s="6"/>
       <c r="D232" s="5">
-        <v>46100.13550428241</v>
+        <v>46191.79695047454</v>
       </c>
       <c r="E232" s="6" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="F232" s="6" t="s">
         <v>26</v>
@@ -14614,10 +14620,10 @@
         <v>50</v>
       </c>
       <c r="I232" s="5">
-        <v>46091</v>
+        <v>46080</v>
       </c>
       <c r="J232" s="5">
-        <v>46099</v>
+        <v>46090</v>
       </c>
       <c r="K232" s="6" t="s">
         <v>26</v>
@@ -14629,19 +14635,19 @@
         <v>26</v>
       </c>
       <c r="N232" s="6" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="O232" s="6" t="s">
-        <v>430</v>
+        <v>404</v>
       </c>
       <c r="P232" s="6" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="Q232" s="5">
-        <v>46091</v>
+        <v>46080</v>
       </c>
       <c r="R232" s="5">
-        <v>46099</v>
+        <v>46090</v>
       </c>
       <c r="S232" s="10" t="s">
         <v>31</v>
@@ -14649,8 +14655,71 @@
       <c r="T232" s="6">
         <v>0</v>
       </c>
-      <c r="U232" s="10" t="s">
-        <v>107</v>
+      <c r="U232" s="12" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="233" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A233" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="B233" s="8">
+        <v>46090.63872243055</v>
+      </c>
+      <c r="C233" s="9"/>
+      <c r="D233" s="8">
+        <v>46100.13550428241</v>
+      </c>
+      <c r="E233" s="9" t="s">
+        <v>435</v>
+      </c>
+      <c r="F233" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G233" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="H233" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="I233" s="8">
+        <v>46091</v>
+      </c>
+      <c r="J233" s="8">
+        <v>46099</v>
+      </c>
+      <c r="K233" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L233" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M233" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N233" s="9" t="s">
+        <v>429</v>
+      </c>
+      <c r="O233" s="9" t="s">
+        <v>432</v>
+      </c>
+      <c r="P233" s="9" t="s">
+        <v>429</v>
+      </c>
+      <c r="Q233" s="8">
+        <v>46091</v>
+      </c>
+      <c r="R233" s="8">
+        <v>46099</v>
+      </c>
+      <c r="S233" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="T233" s="9">
+        <v>0</v>
+      </c>
+      <c r="U233" s="10" t="s">
+        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001501 - EQ MIN LA HACIENDA B.xlsx
+++ b/data/50001501 - EQ MIN LA HACIENDA B.xlsx
@@ -12334,7 +12334,7 @@
         <v>46191.796778240736</v>
       </c>
       <c r="D189" s="8">
-        <v>46191.79679478009</v>
+        <v>46192.64719054398</v>
       </c>
       <c r="E189" s="9" t="s">
         <v>373</v>
@@ -12395,9 +12395,11 @@
       <c r="B190" s="5">
         <v>46128.56718193287</v>
       </c>
-      <c r="C190" s="6"/>
+      <c r="C190" s="5">
+        <v>46192.64706778935</v>
+      </c>
       <c r="D190" s="5">
-        <v>46191.885307627315</v>
+        <v>46192.64706957176</v>
       </c>
       <c r="E190" s="6" t="s">
         <v>170</v>
@@ -12448,9 +12450,11 @@
       <c r="B191" s="8">
         <v>46128.567190092595</v>
       </c>
-      <c r="C191" s="9"/>
+      <c r="C191" s="8">
+        <v>46192.64718554398</v>
+      </c>
       <c r="D191" s="8">
-        <v>46191.88571938657</v>
+        <v>46192.647186875</v>
       </c>
       <c r="E191" s="9" t="s">
         <v>170</v>
@@ -13096,7 +13100,7 @@
       </c>
       <c r="C203" s="9"/>
       <c r="D203" s="8">
-        <v>46129.68352643518</v>
+        <v>46192.64707679398</v>
       </c>
       <c r="E203" s="9" t="s">
         <v>170</v>
@@ -13147,7 +13151,7 @@
       </c>
       <c r="C204" s="6"/>
       <c r="D204" s="5">
-        <v>46129.68352717593</v>
+        <v>46192.64719189815</v>
       </c>
       <c r="E204" s="6" t="s">
         <v>170</v>

--- a/data/50001501 - EQ MIN LA HACIENDA B.xlsx
+++ b/data/50001501 - EQ MIN LA HACIENDA B.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2667" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2668" uniqueCount="436">
   <si>
     <t>50001501 - EQ. MIN. LA HACIENDA</t>
   </si>
@@ -520,6 +520,9 @@
     <t>OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2 ,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2</t>
   </si>
   <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
     <t>1214075676500814</t>
   </si>
   <si>
@@ -635,9 +638,6 @@
   </si>
   <si>
     <t>Preparación1 Materiales,Check Planos,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2,OT 4213 ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1214075676500706</t>
@@ -4289,9 +4289,11 @@
       <c r="B42" s="5">
         <v>46073.76783873842</v>
       </c>
-      <c r="C42" s="6"/>
+      <c r="C42" s="5">
+        <v>46192.762426898145</v>
+      </c>
       <c r="D42" s="5">
-        <v>46142.64957708333</v>
+        <v>46192.76244386574</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>150</v>
@@ -4326,8 +4328,12 @@
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
       <c r="S42" s="6"/>
-      <c r="T42" s="6"/>
-      <c r="U42" s="6"/>
+      <c r="T42" s="6">
+        <v>1</v>
+      </c>
+      <c r="U42" s="11" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
@@ -4529,9 +4535,11 @@
       <c r="B46" s="5">
         <v>46090.493990891206</v>
       </c>
-      <c r="C46" s="6"/>
+      <c r="C46" s="5">
+        <v>46192.76206953704</v>
+      </c>
       <c r="D46" s="5">
-        <v>46129.678973692135</v>
+        <v>46192.76208826389</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>165</v>
@@ -4577,25 +4585,27 @@
         <v>31</v>
       </c>
       <c r="T46" s="6">
-        <v>0</v>
-      </c>
-      <c r="U46" s="10" t="s">
-        <v>106</v>
+        <v>1</v>
+      </c>
+      <c r="U46" s="12" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B47" s="8">
         <v>46128.56674524306</v>
       </c>
-      <c r="C47" s="9"/>
+      <c r="C47" s="8">
+        <v>46192.761913993054</v>
+      </c>
       <c r="D47" s="8">
-        <v>46191.79533020833</v>
+        <v>46192.7619153125</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
@@ -4623,10 +4633,10 @@
         <v>165</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q47" s="9"/>
       <c r="R47" s="9"/>
@@ -4636,17 +4646,19 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B48" s="5">
         <v>46128.566755555556</v>
       </c>
-      <c r="C48" s="6"/>
+      <c r="C48" s="5">
+        <v>46192.76204381944</v>
+      </c>
       <c r="D48" s="5">
-        <v>46191.795324189814</v>
+        <v>46192.76205100694</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
@@ -4674,10 +4686,10 @@
         <v>165</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4687,17 +4699,19 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B49" s="8">
         <v>46128.56676210648</v>
       </c>
-      <c r="C49" s="9"/>
+      <c r="C49" s="8">
+        <v>46192.76204465277</v>
+      </c>
       <c r="D49" s="8">
-        <v>46191.79531811342</v>
+        <v>46192.76205135416</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
@@ -4725,10 +4739,10 @@
         <v>165</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q49" s="9"/>
       <c r="R49" s="9"/>
@@ -4738,17 +4752,19 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B50" s="5">
         <v>46128.56676847222</v>
       </c>
-      <c r="C50" s="6"/>
+      <c r="C50" s="5">
+        <v>46192.76204524306</v>
+      </c>
       <c r="D50" s="5">
-        <v>46191.79531166666</v>
+        <v>46192.762051655096</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
@@ -4776,10 +4792,10 @@
         <v>165</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4789,17 +4805,19 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B51" s="8">
         <v>46128.566774120365</v>
       </c>
-      <c r="C51" s="9"/>
+      <c r="C51" s="8">
+        <v>46192.76204579861</v>
+      </c>
       <c r="D51" s="8">
-        <v>46191.795306423606</v>
+        <v>46192.762051990736</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
@@ -4827,10 +4845,10 @@
         <v>165</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -4840,17 +4858,19 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B52" s="5">
         <v>46128.566780127316</v>
       </c>
-      <c r="C52" s="6"/>
+      <c r="C52" s="5">
+        <v>46192.76204636574</v>
+      </c>
       <c r="D52" s="5">
-        <v>46191.7952890625</v>
+        <v>46192.76205229167</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
@@ -4878,10 +4898,10 @@
         <v>165</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4891,17 +4911,19 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B53" s="8">
         <v>46128.56678613426</v>
       </c>
-      <c r="C53" s="9"/>
+      <c r="C53" s="8">
+        <v>46192.76204696759</v>
+      </c>
       <c r="D53" s="8">
-        <v>46191.79528329861</v>
+        <v>46192.762052569444</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
@@ -4929,10 +4951,10 @@
         <v>165</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -4942,17 +4964,19 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B54" s="5">
         <v>46128.566790682875</v>
       </c>
-      <c r="C54" s="6"/>
+      <c r="C54" s="5">
+        <v>46192.7620475</v>
+      </c>
       <c r="D54" s="5">
-        <v>46191.79527969907</v>
+        <v>46192.7620528588</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
@@ -4980,10 +5004,10 @@
         <v>165</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4993,17 +5017,19 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B55" s="8">
         <v>46128.5667968287</v>
       </c>
-      <c r="C55" s="9"/>
+      <c r="C55" s="8">
+        <v>46192.76204800926</v>
+      </c>
       <c r="D55" s="8">
-        <v>46191.795272557865</v>
+        <v>46192.76205314815</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
@@ -5031,10 +5057,10 @@
         <v>165</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q55" s="9"/>
       <c r="R55" s="9"/>
@@ -5044,17 +5070,19 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B56" s="5">
         <v>46128.56680166667</v>
       </c>
-      <c r="C56" s="6"/>
+      <c r="C56" s="5">
+        <v>46192.762048530094</v>
+      </c>
       <c r="D56" s="5">
-        <v>46191.795269375</v>
+        <v>46192.76205344907</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
@@ -5082,10 +5110,10 @@
         <v>165</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -5095,17 +5123,19 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B57" s="8">
         <v>46128.566807256946</v>
       </c>
-      <c r="C57" s="9"/>
+      <c r="C57" s="8">
+        <v>46192.76204903935</v>
+      </c>
       <c r="D57" s="8">
-        <v>46191.7952605787</v>
+        <v>46192.762053784725</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
@@ -5133,10 +5163,10 @@
         <v>165</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q57" s="9"/>
       <c r="R57" s="9"/>
@@ -5146,17 +5176,19 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B58" s="5">
         <v>46128.56681135416</v>
       </c>
-      <c r="C58" s="6"/>
+      <c r="C58" s="5">
+        <v>46192.76204957176</v>
+      </c>
       <c r="D58" s="5">
-        <v>46191.79525575231</v>
+        <v>46192.762054108796</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
@@ -5184,10 +5216,10 @@
         <v>165</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -5197,7 +5229,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B59" s="8">
         <v>46073.76783778935</v>
@@ -5209,7 +5241,7 @@
         <v>46097.81565780092</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>25</v>
@@ -5233,7 +5265,7 @@
         <v>26</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P59" s="9" t="s">
         <v>26</v>
@@ -5250,7 +5282,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B60" s="5">
         <v>46073.767838078704</v>
@@ -5262,16 +5294,16 @@
         <v>46097.81529010416</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I60" s="5">
         <v>46041</v>
@@ -5289,13 +5321,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>147</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q60" s="5">
         <v>46041</v>
@@ -5315,7 +5347,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B61" s="8">
         <v>46073.7678383912</v>
@@ -5327,16 +5359,16 @@
         <v>46097.81562871528</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I61" s="8">
         <v>46043</v>
@@ -5354,13 +5386,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q61" s="8">
         <v>46043</v>
@@ -5380,7 +5412,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B62" s="5">
         <v>46073.76783866898</v>
@@ -5392,7 +5424,7 @@
         <v>46191.77291996528</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>25</v>
@@ -5416,7 +5448,7 @@
         <v>26</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>26</v>
@@ -5433,7 +5465,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B63" s="8">
         <v>46073.767838935186</v>
@@ -5445,16 +5477,16 @@
         <v>46128.58222162037</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I63" s="8">
         <v>46045</v>
@@ -5472,13 +5504,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q63" s="8">
         <v>46045</v>
@@ -5498,7 +5530,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B64" s="5">
         <v>46073.76783921296</v>
@@ -5510,16 +5542,16 @@
         <v>46158.97116490741</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I64" s="5">
         <v>46050</v>
@@ -5537,13 +5569,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q64" s="5">
         <v>46050</v>
@@ -5558,7 +5590,7 @@
         <v>1</v>
       </c>
       <c r="U64" s="12" t="s">
-        <v>208</v>
+        <v>169</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
@@ -5575,16 +5607,16 @@
         <v>46129.68420498843</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I65" s="8">
         <v>46050</v>
@@ -5602,7 +5634,7 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O65" s="9" t="s">
         <v>210</v>
@@ -5630,16 +5662,16 @@
         <v>46129.684215497684</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I66" s="5">
         <v>46050</v>
@@ -5657,10 +5689,10 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>211</v>
@@ -5685,16 +5717,16 @@
         <v>46129.68427572917</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I67" s="8">
         <v>46050</v>
@@ -5712,10 +5744,10 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="P67" s="9" t="s">
         <v>211</v>
@@ -5740,16 +5772,16 @@
         <v>46129.68422782407</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I68" s="5">
         <v>46050</v>
@@ -5767,10 +5799,10 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>211</v>
@@ -5795,16 +5827,16 @@
         <v>46129.684293784725</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I69" s="8">
         <v>46050</v>
@@ -5822,10 +5854,10 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="P69" s="9" t="s">
         <v>211</v>
@@ -5850,16 +5882,16 @@
         <v>46129.68430454861</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I70" s="5">
         <v>46050</v>
@@ -5877,7 +5909,7 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>26</v>
@@ -5905,16 +5937,16 @@
         <v>46146.89516151621</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I71" s="8">
         <v>46050</v>
@@ -5932,7 +5964,7 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O71" s="9" t="s">
         <v>218</v>
@@ -5960,16 +5992,16 @@
         <v>46146.89517496528</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I72" s="5">
         <v>46050</v>
@@ -5987,10 +6019,10 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>211</v>
@@ -6015,16 +6047,16 @@
         <v>46146.895229745365</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I73" s="8">
         <v>46050</v>
@@ -6042,10 +6074,10 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="P73" s="9" t="s">
         <v>211</v>
@@ -6070,16 +6102,16 @@
         <v>46146.8951958449</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I74" s="5">
         <v>46050</v>
@@ -6097,10 +6129,10 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>211</v>
@@ -6125,16 +6157,16 @@
         <v>46146.8953142824</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I75" s="8">
         <v>46050</v>
@@ -6152,10 +6184,10 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="P75" s="9" t="s">
         <v>211</v>
@@ -6180,16 +6212,16 @@
         <v>46146.895330486106</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I76" s="5">
         <v>46050</v>
@@ -6207,10 +6239,10 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>211</v>
@@ -6241,10 +6273,10 @@
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I77" s="9"/>
       <c r="J77" s="8">
@@ -6260,13 +6292,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O77" s="9" t="s">
         <v>226</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q77" s="8">
         <v>46055</v>
@@ -6298,16 +6330,16 @@
         <v>46129.6858422338</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I78" s="6"/>
       <c r="J78" s="5">
@@ -6326,7 +6358,7 @@
         <v>225</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>228</v>
@@ -6351,16 +6383,16 @@
         <v>46129.68585466435</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I79" s="9"/>
       <c r="J79" s="8">
@@ -6379,7 +6411,7 @@
         <v>225</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P79" s="9" t="s">
         <v>228</v>
@@ -6404,16 +6436,16 @@
         <v>46129.68589648148</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I80" s="6"/>
       <c r="J80" s="5">
@@ -6432,7 +6464,7 @@
         <v>225</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>228</v>
@@ -6457,16 +6489,16 @@
         <v>46129.685910949076</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I81" s="9"/>
       <c r="J81" s="8">
@@ -6485,7 +6517,7 @@
         <v>225</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P81" s="9" t="s">
         <v>228</v>
@@ -6510,16 +6542,16 @@
         <v>46129.68592581019</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I82" s="6"/>
       <c r="J82" s="5">
@@ -6538,7 +6570,7 @@
         <v>225</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>228</v>
@@ -6563,16 +6595,16 @@
         <v>46129.68595777778</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I83" s="9"/>
       <c r="J83" s="8">
@@ -6591,7 +6623,7 @@
         <v>225</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P83" s="9" t="s">
         <v>228</v>
@@ -6616,16 +6648,16 @@
         <v>46146.897389502315</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I84" s="6"/>
       <c r="J84" s="5">
@@ -6644,7 +6676,7 @@
         <v>225</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>228</v>
@@ -6669,16 +6701,16 @@
         <v>46146.89739724537</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I85" s="9"/>
       <c r="J85" s="8">
@@ -6697,7 +6729,7 @@
         <v>225</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P85" s="9" t="s">
         <v>228</v>
@@ -6722,16 +6754,16 @@
         <v>46146.89740662037</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I86" s="6"/>
       <c r="J86" s="5">
@@ -6750,7 +6782,7 @@
         <v>225</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>228</v>
@@ -6775,16 +6807,16 @@
         <v>46158.971886354164</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I87" s="9"/>
       <c r="J87" s="8">
@@ -6803,7 +6835,7 @@
         <v>225</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P87" s="9" t="s">
         <v>228</v>
@@ -6828,16 +6860,16 @@
         <v>46158.971913587964</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I88" s="6"/>
       <c r="J88" s="5">
@@ -6856,7 +6888,7 @@
         <v>225</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>228</v>
@@ -6881,16 +6913,16 @@
         <v>46158.971926909726</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I89" s="9"/>
       <c r="J89" s="8">
@@ -6909,7 +6941,7 @@
         <v>225</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P89" s="9" t="s">
         <v>228</v>
@@ -6934,7 +6966,7 @@
         <v>46191.79356716435</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>25</v>
@@ -6993,10 +7025,10 @@
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I91" s="9"/>
       <c r="J91" s="8">
@@ -7012,13 +7044,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O91" s="9" t="s">
         <v>126</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q91" s="8">
         <v>46030</v>
@@ -7033,7 +7065,7 @@
         <v>0.2</v>
       </c>
       <c r="U91" s="12" t="s">
-        <v>208</v>
+        <v>169</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
@@ -7056,10 +7088,10 @@
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I92" s="5">
         <v>46069</v>
@@ -7077,7 +7109,7 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O92" s="6" t="s">
         <v>117</v>
@@ -7121,10 +7153,10 @@
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H93" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I93" s="9"/>
       <c r="J93" s="8">
@@ -7140,13 +7172,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O93" s="9" t="s">
         <v>108</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q93" s="8">
         <v>46014</v>
@@ -7161,7 +7193,7 @@
         <v>0</v>
       </c>
       <c r="U93" s="12" t="s">
-        <v>208</v>
+        <v>169</v>
       </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
@@ -7184,10 +7216,10 @@
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I94" s="6"/>
       <c r="J94" s="5">
@@ -7203,7 +7235,7 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O94" s="6" t="s">
         <v>135</v>
@@ -7359,7 +7391,7 @@
         <v>46129.68866337963</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
@@ -7389,7 +7421,7 @@
         <v>255</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P97" s="9" t="s">
         <v>258</v>
@@ -7414,7 +7446,7 @@
         <v>46129.688671157404</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7444,7 +7476,7 @@
         <v>255</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P98" s="6" t="s">
         <v>258</v>
@@ -7469,7 +7501,7 @@
         <v>46129.68868245371</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
@@ -7499,7 +7531,7 @@
         <v>255</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P99" s="9" t="s">
         <v>258</v>
@@ -7524,7 +7556,7 @@
         <v>46129.688693171294</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7554,7 +7586,7 @@
         <v>255</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P100" s="6" t="s">
         <v>258</v>
@@ -7579,7 +7611,7 @@
         <v>46129.68870375</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
@@ -7609,7 +7641,7 @@
         <v>255</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P101" s="9" t="s">
         <v>258</v>
@@ -7634,7 +7666,7 @@
         <v>46158.974908738426</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7664,7 +7696,7 @@
         <v>255</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>258</v>
@@ -7689,7 +7721,7 @@
         <v>46158.97511034722</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
@@ -7719,7 +7751,7 @@
         <v>255</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P103" s="9" t="s">
         <v>258</v>
@@ -7744,7 +7776,7 @@
         <v>46158.975184641204</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7774,7 +7806,7 @@
         <v>255</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P104" s="6" t="s">
         <v>258</v>
@@ -7799,7 +7831,7 @@
         <v>46191.79465511574</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
@@ -7829,7 +7861,7 @@
         <v>255</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P105" s="9" t="s">
         <v>258</v>
@@ -7854,7 +7886,7 @@
         <v>46191.79466190972</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7884,7 +7916,7 @@
         <v>255</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P106" s="6" t="s">
         <v>258</v>
@@ -7909,7 +7941,7 @@
         <v>46191.79466734953</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
@@ -7939,7 +7971,7 @@
         <v>255</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P107" s="9" t="s">
         <v>258</v>
@@ -7964,7 +7996,7 @@
         <v>46191.79473116898</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7994,7 +8026,7 @@
         <v>255</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P108" s="6" t="s">
         <v>258</v>
@@ -8082,7 +8114,7 @@
         <v>46157.498779988426</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -8110,7 +8142,7 @@
         <v>271</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>273</v>
@@ -8135,7 +8167,7 @@
         <v>46157.49878368055</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
@@ -8163,7 +8195,7 @@
         <v>271</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P111" s="9" t="s">
         <v>273</v>
@@ -8188,7 +8220,7 @@
         <v>46157.498788240744</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8216,7 +8248,7 @@
         <v>271</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P112" s="6" t="s">
         <v>273</v>
@@ -8241,7 +8273,7 @@
         <v>46157.49879474537</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
@@ -8269,7 +8301,7 @@
         <v>271</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P113" s="9" t="s">
         <v>273</v>
@@ -8294,7 +8326,7 @@
         <v>46157.49884443287</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -8322,7 +8354,7 @@
         <v>271</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>273</v>
@@ -8347,7 +8379,7 @@
         <v>46158.97491230324</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
@@ -8375,7 +8407,7 @@
         <v>271</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P115" s="9" t="s">
         <v>273</v>
@@ -8400,7 +8432,7 @@
         <v>46158.975114155095</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8428,7 +8460,7 @@
         <v>271</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P116" s="6" t="s">
         <v>273</v>
@@ -8453,7 +8485,7 @@
         <v>46158.97518857638</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
@@ -8481,7 +8513,7 @@
         <v>271</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P117" s="9" t="s">
         <v>273</v>
@@ -8506,7 +8538,7 @@
         <v>46191.794660555555</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8534,7 +8566,7 @@
         <v>271</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P118" s="6" t="s">
         <v>273</v>
@@ -8559,7 +8591,7 @@
         <v>46191.79466525463</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
@@ -8587,7 +8619,7 @@
         <v>271</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P119" s="9" t="s">
         <v>273</v>
@@ -8612,7 +8644,7 @@
         <v>46191.794671875</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8640,7 +8672,7 @@
         <v>271</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P120" s="6" t="s">
         <v>273</v>
@@ -8665,7 +8697,7 @@
         <v>46191.79473787037</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
@@ -8693,7 +8725,7 @@
         <v>271</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P121" s="9" t="s">
         <v>273</v>
@@ -8783,7 +8815,7 @@
         <v>46157.49878587963</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>26</v>
@@ -8813,7 +8845,7 @@
         <v>286</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P123" s="9" t="s">
         <v>288</v>
@@ -8838,7 +8870,7 @@
         <v>46157.49878896991</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -8868,7 +8900,7 @@
         <v>286</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P124" s="6" t="s">
         <v>288</v>
@@ -8893,7 +8925,7 @@
         <v>46157.49879293982</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
@@ -8923,7 +8955,7 @@
         <v>286</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P125" s="9" t="s">
         <v>288</v>
@@ -8948,7 +8980,7 @@
         <v>46157.498799560184</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -8978,7 +9010,7 @@
         <v>286</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P126" s="6" t="s">
         <v>288</v>
@@ -9003,7 +9035,7 @@
         <v>46157.49885005787</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>26</v>
@@ -9033,7 +9065,7 @@
         <v>286</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P127" s="9" t="s">
         <v>288</v>
@@ -9058,7 +9090,7 @@
         <v>46157.4988055787</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -9088,7 +9120,7 @@
         <v>286</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P128" s="6" t="s">
         <v>288</v>
@@ -9113,7 +9145,7 @@
         <v>46157.49893354166</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>26</v>
@@ -9143,7 +9175,7 @@
         <v>286</v>
       </c>
       <c r="O129" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P129" s="9" t="s">
         <v>288</v>
@@ -9168,7 +9200,7 @@
         <v>46157.49900008102</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -9198,7 +9230,7 @@
         <v>286</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P130" s="6" t="s">
         <v>288</v>
@@ -9223,7 +9255,7 @@
         <v>46191.7937930787</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>26</v>
@@ -9253,7 +9285,7 @@
         <v>286</v>
       </c>
       <c r="O131" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P131" s="9" t="s">
         <v>288</v>
@@ -9278,7 +9310,7 @@
         <v>46191.79424862268</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
@@ -9308,7 +9340,7 @@
         <v>286</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P132" s="6" t="s">
         <v>288</v>
@@ -9333,7 +9365,7 @@
         <v>46191.79439909723</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>26</v>
@@ -9363,7 +9395,7 @@
         <v>286</v>
       </c>
       <c r="O133" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P133" s="9" t="s">
         <v>288</v>
@@ -9388,7 +9420,7 @@
         <v>46191.79452946759</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
@@ -9418,7 +9450,7 @@
         <v>286</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P134" s="6" t="s">
         <v>288</v>
@@ -9506,7 +9538,7 @@
         <v>46157.49801296296</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9536,7 +9568,7 @@
         <v>301</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P136" s="6" t="s">
         <v>304</v>
@@ -9561,7 +9593,7 @@
         <v>46157.49802616898</v>
       </c>
       <c r="E137" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>26</v>
@@ -9591,7 +9623,7 @@
         <v>301</v>
       </c>
       <c r="O137" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P137" s="9" t="s">
         <v>304</v>
@@ -9616,7 +9648,7 @@
         <v>46157.49803459491</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
@@ -9646,7 +9678,7 @@
         <v>301</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P138" s="6" t="s">
         <v>304</v>
@@ -9671,7 +9703,7 @@
         <v>46157.4980403588</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
@@ -9701,7 +9733,7 @@
         <v>301</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P139" s="9" t="s">
         <v>304</v>
@@ -9726,7 +9758,7 @@
         <v>46157.49804547454</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
@@ -9756,7 +9788,7 @@
         <v>301</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P140" s="6" t="s">
         <v>304</v>
@@ -9781,7 +9813,7 @@
         <v>46157.49809685185</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>26</v>
@@ -9811,7 +9843,7 @@
         <v>301</v>
       </c>
       <c r="O141" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P141" s="9" t="s">
         <v>304</v>
@@ -9836,7 +9868,7 @@
         <v>46157.498176423614</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
@@ -9866,7 +9898,7 @@
         <v>301</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P142" s="6" t="s">
         <v>304</v>
@@ -9891,7 +9923,7 @@
         <v>46157.49829290509</v>
       </c>
       <c r="E143" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F143" s="9" t="s">
         <v>26</v>
@@ -9921,7 +9953,7 @@
         <v>301</v>
       </c>
       <c r="O143" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P143" s="9" t="s">
         <v>304</v>
@@ -9946,7 +9978,7 @@
         <v>46191.793351631946</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
@@ -9976,7 +10008,7 @@
         <v>301</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P144" s="6" t="s">
         <v>304</v>
@@ -10001,7 +10033,7 @@
         <v>46191.79344340278</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>26</v>
@@ -10031,7 +10063,7 @@
         <v>301</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P145" s="9" t="s">
         <v>304</v>
@@ -10056,7 +10088,7 @@
         <v>46191.79351224537</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
@@ -10086,7 +10118,7 @@
         <v>301</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P146" s="6" t="s">
         <v>304</v>
@@ -10111,7 +10143,7 @@
         <v>46191.7935915625</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>26</v>
@@ -10141,7 +10173,7 @@
         <v>301</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P147" s="9" t="s">
         <v>304</v>
@@ -10212,7 +10244,7 @@
         <v>1</v>
       </c>
       <c r="U148" s="12" t="s">
-        <v>208</v>
+        <v>169</v>
       </c>
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
@@ -10229,7 +10261,7 @@
         <v>46191.79532310185</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>26</v>
@@ -10257,7 +10289,7 @@
         <v>317</v>
       </c>
       <c r="O149" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P149" s="9" t="s">
         <v>319</v>
@@ -10282,7 +10314,7 @@
         <v>46191.7953178125</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
@@ -10310,7 +10342,7 @@
         <v>317</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P150" s="6" t="s">
         <v>319</v>
@@ -10335,7 +10367,7 @@
         <v>46191.79531292824</v>
       </c>
       <c r="E151" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F151" s="9" t="s">
         <v>26</v>
@@ -10363,7 +10395,7 @@
         <v>317</v>
       </c>
       <c r="O151" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P151" s="9" t="s">
         <v>319</v>
@@ -10388,7 +10420,7 @@
         <v>46191.79530751157</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
@@ -10416,7 +10448,7 @@
         <v>317</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P152" s="6" t="s">
         <v>323</v>
@@ -10441,7 +10473,7 @@
         <v>46191.79530002315</v>
       </c>
       <c r="E153" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F153" s="9" t="s">
         <v>26</v>
@@ -10469,7 +10501,7 @@
         <v>317</v>
       </c>
       <c r="O153" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P153" s="9" t="s">
         <v>319</v>
@@ -10494,7 +10526,7 @@
         <v>46191.79528344907</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>26</v>
@@ -10522,7 +10554,7 @@
         <v>317</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P154" s="6" t="s">
         <v>319</v>
@@ -10547,7 +10579,7 @@
         <v>46191.79527836805</v>
       </c>
       <c r="E155" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F155" s="9" t="s">
         <v>26</v>
@@ -10575,7 +10607,7 @@
         <v>317</v>
       </c>
       <c r="O155" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P155" s="9" t="s">
         <v>319</v>
@@ -10600,7 +10632,7 @@
         <v>46191.79527357639</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
@@ -10628,7 +10660,7 @@
         <v>317</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P156" s="6" t="s">
         <v>319</v>
@@ -10653,7 +10685,7 @@
         <v>46191.795267951384</v>
       </c>
       <c r="E157" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F157" s="9" t="s">
         <v>26</v>
@@ -10681,7 +10713,7 @@
         <v>317</v>
       </c>
       <c r="O157" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P157" s="9" t="s">
         <v>319</v>
@@ -10706,7 +10738,7 @@
         <v>46191.79526363426</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
@@ -10734,7 +10766,7 @@
         <v>317</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P158" s="6" t="s">
         <v>319</v>
@@ -10759,7 +10791,7 @@
         <v>46191.79525519676</v>
       </c>
       <c r="E159" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F159" s="9" t="s">
         <v>26</v>
@@ -10787,7 +10819,7 @@
         <v>317</v>
       </c>
       <c r="O159" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P159" s="9" t="s">
         <v>319</v>
@@ -10812,7 +10844,7 @@
         <v>46191.795250173614</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>26</v>
@@ -10840,7 +10872,7 @@
         <v>317</v>
       </c>
       <c r="O160" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P160" s="6" t="s">
         <v>319</v>
@@ -10911,7 +10943,7 @@
         <v>1</v>
       </c>
       <c r="U161" s="12" t="s">
-        <v>208</v>
+        <v>169</v>
       </c>
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.25">
@@ -10925,10 +10957,10 @@
         <v>46191.79662097222</v>
       </c>
       <c r="D162" s="5">
-        <v>46191.796622511574</v>
+        <v>46192.76192157407</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F162" s="6" t="s">
         <v>26</v>
@@ -10956,7 +10988,7 @@
         <v>333</v>
       </c>
       <c r="O162" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P162" s="6" t="s">
         <v>336</v>
@@ -10978,10 +11010,10 @@
         <v>46191.796464733794</v>
       </c>
       <c r="D163" s="8">
-        <v>46191.796466134256</v>
+        <v>46192.76206450231</v>
       </c>
       <c r="E163" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F163" s="9" t="s">
         <v>26</v>
@@ -11009,7 +11041,7 @@
         <v>333</v>
       </c>
       <c r="O163" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P163" s="9" t="s">
         <v>336</v>
@@ -11031,10 +11063,10 @@
         <v>46191.79639053241</v>
       </c>
       <c r="D164" s="5">
-        <v>46191.79639206019</v>
+        <v>46192.76206446759</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>26</v>
@@ -11062,7 +11094,7 @@
         <v>333</v>
       </c>
       <c r="O164" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P164" s="6" t="s">
         <v>336</v>
@@ -11084,10 +11116,10 @@
         <v>46191.79629663195</v>
       </c>
       <c r="D165" s="8">
-        <v>46191.796298194444</v>
+        <v>46192.76206489583</v>
       </c>
       <c r="E165" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F165" s="9" t="s">
         <v>26</v>
@@ -11115,7 +11147,7 @@
         <v>333</v>
       </c>
       <c r="O165" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P165" s="9" t="s">
         <v>336</v>
@@ -11137,10 +11169,10 @@
         <v>46191.79617204861</v>
       </c>
       <c r="D166" s="5">
-        <v>46191.79617392361</v>
+        <v>46192.76206432871</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>26</v>
@@ -11168,7 +11200,7 @@
         <v>333</v>
       </c>
       <c r="O166" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P166" s="6" t="s">
         <v>336</v>
@@ -11190,10 +11222,10 @@
         <v>46191.79610912037</v>
       </c>
       <c r="D167" s="8">
-        <v>46191.796110972224</v>
+        <v>46192.76206412037</v>
       </c>
       <c r="E167" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F167" s="9" t="s">
         <v>26</v>
@@ -11221,7 +11253,7 @@
         <v>333</v>
       </c>
       <c r="O167" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P167" s="9" t="s">
         <v>336</v>
@@ -11243,10 +11275,10 @@
         <v>46191.796043587965</v>
       </c>
       <c r="D168" s="5">
-        <v>46191.7960453125</v>
+        <v>46192.762064131944</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>26</v>
@@ -11274,7 +11306,7 @@
         <v>333</v>
       </c>
       <c r="O168" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P168" s="6" t="s">
         <v>336</v>
@@ -11296,10 +11328,10 @@
         <v>46191.795971342595</v>
       </c>
       <c r="D169" s="8">
-        <v>46191.79597306713</v>
+        <v>46192.762064131944</v>
       </c>
       <c r="E169" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F169" s="9" t="s">
         <v>26</v>
@@ -11327,7 +11359,7 @@
         <v>333</v>
       </c>
       <c r="O169" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P169" s="9" t="s">
         <v>336</v>
@@ -11349,10 +11381,10 @@
         <v>46191.79585572917</v>
       </c>
       <c r="D170" s="5">
-        <v>46191.79585737269</v>
+        <v>46192.76206414352</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>26</v>
@@ -11380,7 +11412,7 @@
         <v>333</v>
       </c>
       <c r="O170" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P170" s="6" t="s">
         <v>336</v>
@@ -11402,10 +11434,10 @@
         <v>46191.795773958336</v>
       </c>
       <c r="D171" s="8">
-        <v>46191.79577540509</v>
+        <v>46192.76206392361</v>
       </c>
       <c r="E171" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F171" s="9" t="s">
         <v>26</v>
@@ -11433,7 +11465,7 @@
         <v>333</v>
       </c>
       <c r="O171" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P171" s="9" t="s">
         <v>336</v>
@@ -11455,10 +11487,10 @@
         <v>46191.79563440972</v>
       </c>
       <c r="D172" s="5">
-        <v>46191.795636319446</v>
+        <v>46192.76206421296</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F172" s="6" t="s">
         <v>26</v>
@@ -11486,7 +11518,7 @@
         <v>333</v>
       </c>
       <c r="O172" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P172" s="6" t="s">
         <v>336</v>
@@ -11508,10 +11540,10 @@
         <v>46191.79554900463</v>
       </c>
       <c r="D173" s="8">
-        <v>46191.79555090278</v>
+        <v>46192.762064305556</v>
       </c>
       <c r="E173" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F173" s="9" t="s">
         <v>26</v>
@@ -11539,7 +11571,7 @@
         <v>333</v>
       </c>
       <c r="O173" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P173" s="9" t="s">
         <v>336</v>
@@ -11672,7 +11704,7 @@
         <v>46191.885297430556</v>
       </c>
       <c r="E176" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F176" s="6" t="s">
         <v>26</v>
@@ -11700,7 +11732,7 @@
         <v>352</v>
       </c>
       <c r="O176" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P176" s="6" t="s">
         <v>357</v>
@@ -11723,7 +11755,7 @@
         <v>46191.88571055555</v>
       </c>
       <c r="E177" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F177" s="9" t="s">
         <v>26</v>
@@ -11751,7 +11783,7 @@
         <v>352</v>
       </c>
       <c r="O177" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P177" s="9" t="s">
         <v>357</v>
@@ -11774,7 +11806,7 @@
         <v>46191.88526354167</v>
       </c>
       <c r="E178" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F178" s="6" t="s">
         <v>26</v>
@@ -11802,7 +11834,7 @@
         <v>352</v>
       </c>
       <c r="O178" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P178" s="6" t="s">
         <v>357</v>
@@ -11825,7 +11857,7 @@
         <v>46191.88525847222</v>
       </c>
       <c r="E179" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F179" s="9" t="s">
         <v>26</v>
@@ -11853,7 +11885,7 @@
         <v>352</v>
       </c>
       <c r="O179" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P179" s="9" t="s">
         <v>357</v>
@@ -11876,7 +11908,7 @@
         <v>46191.88525349537</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F180" s="6" t="s">
         <v>26</v>
@@ -11904,7 +11936,7 @@
         <v>352</v>
       </c>
       <c r="O180" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P180" s="6" t="s">
         <v>357</v>
@@ -11927,7 +11959,7 @@
         <v>46191.885310405094</v>
       </c>
       <c r="E181" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F181" s="9" t="s">
         <v>26</v>
@@ -11955,7 +11987,7 @@
         <v>352</v>
       </c>
       <c r="O181" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P181" s="9" t="s">
         <v>357</v>
@@ -11978,7 +12010,7 @@
         <v>46191.796051701385</v>
       </c>
       <c r="E182" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F182" s="6" t="s">
         <v>26</v>
@@ -12006,7 +12038,7 @@
         <v>352</v>
       </c>
       <c r="O182" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P182" s="6" t="s">
         <v>357</v>
@@ -12029,7 +12061,7 @@
         <v>46191.795977581016</v>
       </c>
       <c r="E183" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F183" s="9" t="s">
         <v>26</v>
@@ -12057,7 +12089,7 @@
         <v>352</v>
       </c>
       <c r="O183" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P183" s="9" t="s">
         <v>365</v>
@@ -12080,7 +12112,7 @@
         <v>46191.795861736115</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F184" s="6" t="s">
         <v>26</v>
@@ -12108,7 +12140,7 @@
         <v>352</v>
       </c>
       <c r="O184" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P184" s="6" t="s">
         <v>357</v>
@@ -12131,7 +12163,7 @@
         <v>46191.795781168985</v>
       </c>
       <c r="E185" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F185" s="9" t="s">
         <v>26</v>
@@ -12159,7 +12191,7 @@
         <v>352</v>
       </c>
       <c r="O185" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P185" s="9" t="s">
         <v>357</v>
@@ -12182,7 +12214,7 @@
         <v>46191.795643460646</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F186" s="6" t="s">
         <v>26</v>
@@ -12210,7 +12242,7 @@
         <v>352</v>
       </c>
       <c r="O186" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P186" s="6" t="s">
         <v>357</v>
@@ -12233,7 +12265,7 @@
         <v>46191.795556990735</v>
       </c>
       <c r="E187" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F187" s="9" t="s">
         <v>26</v>
@@ -12261,7 +12293,7 @@
         <v>352</v>
       </c>
       <c r="O187" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P187" s="9" t="s">
         <v>357</v>
@@ -12402,7 +12434,7 @@
         <v>46192.64706957176</v>
       </c>
       <c r="E190" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F190" s="6" t="s">
         <v>26</v>
@@ -12432,7 +12464,7 @@
         <v>373</v>
       </c>
       <c r="O190" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P190" s="6" t="s">
         <v>375</v>
@@ -12457,7 +12489,7 @@
         <v>46192.647186875</v>
       </c>
       <c r="E191" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F191" s="9" t="s">
         <v>26</v>
@@ -12487,7 +12519,7 @@
         <v>373</v>
       </c>
       <c r="O191" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P191" s="9" t="s">
         <v>375</v>
@@ -12510,7 +12542,7 @@
         <v>46191.8852687037</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F192" s="6" t="s">
         <v>26</v>
@@ -12540,7 +12572,7 @@
         <v>373</v>
       </c>
       <c r="O192" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P192" s="6" t="s">
         <v>375</v>
@@ -12563,7 +12595,7 @@
         <v>46191.88526256944</v>
       </c>
       <c r="E193" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F193" s="9" t="s">
         <v>26</v>
@@ -12593,7 +12625,7 @@
         <v>373</v>
       </c>
       <c r="O193" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P193" s="9" t="s">
         <v>375</v>
@@ -12616,7 +12648,7 @@
         <v>46191.885259710645</v>
       </c>
       <c r="E194" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F194" s="6" t="s">
         <v>26</v>
@@ -12646,7 +12678,7 @@
         <v>373</v>
       </c>
       <c r="O194" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P194" s="6" t="s">
         <v>375</v>
@@ -12669,7 +12701,7 @@
         <v>46191.88531537037</v>
       </c>
       <c r="E195" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F195" s="9" t="s">
         <v>26</v>
@@ -12699,7 +12731,7 @@
         <v>373</v>
       </c>
       <c r="O195" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P195" s="9" t="s">
         <v>375</v>
@@ -12722,7 +12754,7 @@
         <v>46129.68320027778</v>
       </c>
       <c r="E196" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F196" s="6" t="s">
         <v>26</v>
@@ -12752,7 +12784,7 @@
         <v>373</v>
       </c>
       <c r="O196" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P196" s="6" t="s">
         <v>375</v>
@@ -12775,7 +12807,7 @@
         <v>46129.68320100695</v>
       </c>
       <c r="E197" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F197" s="9" t="s">
         <v>26</v>
@@ -12805,7 +12837,7 @@
         <v>373</v>
       </c>
       <c r="O197" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P197" s="9" t="s">
         <v>375</v>
@@ -12828,7 +12860,7 @@
         <v>46129.683201747685</v>
       </c>
       <c r="E198" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F198" s="6" t="s">
         <v>26</v>
@@ -12858,7 +12890,7 @@
         <v>373</v>
       </c>
       <c r="O198" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P198" s="6" t="s">
         <v>26</v>
@@ -12881,7 +12913,7 @@
         <v>46129.683202500004</v>
       </c>
       <c r="E199" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F199" s="9" t="s">
         <v>26</v>
@@ -12911,7 +12943,7 @@
         <v>373</v>
       </c>
       <c r="O199" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P199" s="9" t="s">
         <v>375</v>
@@ -12934,7 +12966,7 @@
         <v>46129.683203252316</v>
       </c>
       <c r="E200" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F200" s="6" t="s">
         <v>26</v>
@@ -12964,7 +12996,7 @@
         <v>373</v>
       </c>
       <c r="O200" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P200" s="6" t="s">
         <v>375</v>
@@ -12987,7 +13019,7 @@
         <v>46129.683203981476</v>
       </c>
       <c r="E201" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F201" s="9" t="s">
         <v>26</v>
@@ -13017,7 +13049,7 @@
         <v>373</v>
       </c>
       <c r="O201" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P201" s="9" t="s">
         <v>375</v>
@@ -13048,10 +13080,10 @@
         <v>26</v>
       </c>
       <c r="G202" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H202" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I202" s="6"/>
       <c r="J202" s="5">
@@ -13103,16 +13135,16 @@
         <v>46192.64707679398</v>
       </c>
       <c r="E203" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F203" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G203" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H203" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I203" s="9"/>
       <c r="J203" s="8">
@@ -13131,7 +13163,7 @@
         <v>388</v>
       </c>
       <c r="O203" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P203" s="9" t="s">
         <v>390</v>
@@ -13154,16 +13186,16 @@
         <v>46192.64719189815</v>
       </c>
       <c r="E204" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F204" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G204" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H204" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I204" s="6"/>
       <c r="J204" s="5">
@@ -13182,7 +13214,7 @@
         <v>388</v>
       </c>
       <c r="O204" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P204" s="6" t="s">
         <v>390</v>
@@ -13205,16 +13237,16 @@
         <v>46129.68352791667</v>
       </c>
       <c r="E205" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F205" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G205" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H205" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I205" s="9"/>
       <c r="J205" s="8">
@@ -13233,7 +13265,7 @@
         <v>388</v>
       </c>
       <c r="O205" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P205" s="9" t="s">
         <v>390</v>
@@ -13256,16 +13288,16 @@
         <v>46129.683528657406</v>
       </c>
       <c r="E206" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F206" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G206" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H206" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I206" s="6"/>
       <c r="J206" s="5">
@@ -13284,7 +13316,7 @@
         <v>388</v>
       </c>
       <c r="O206" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P206" s="6" t="s">
         <v>390</v>
@@ -13307,16 +13339,16 @@
         <v>46129.68352943287</v>
       </c>
       <c r="E207" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F207" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G207" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H207" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I207" s="9"/>
       <c r="J207" s="8">
@@ -13335,7 +13367,7 @@
         <v>388</v>
       </c>
       <c r="O207" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P207" s="9" t="s">
         <v>390</v>
@@ -13358,16 +13390,16 @@
         <v>46129.68353019676</v>
       </c>
       <c r="E208" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F208" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G208" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H208" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I208" s="6"/>
       <c r="J208" s="5">
@@ -13386,7 +13418,7 @@
         <v>388</v>
       </c>
       <c r="O208" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P208" s="6" t="s">
         <v>390</v>
@@ -13409,16 +13441,16 @@
         <v>46129.683530891205</v>
       </c>
       <c r="E209" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F209" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G209" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H209" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I209" s="9"/>
       <c r="J209" s="8">
@@ -13437,7 +13469,7 @@
         <v>388</v>
       </c>
       <c r="O209" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P209" s="9" t="s">
         <v>397</v>
@@ -13460,16 +13492,16 @@
         <v>46129.68353159723</v>
       </c>
       <c r="E210" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F210" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G210" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H210" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I210" s="6"/>
       <c r="J210" s="5">
@@ -13488,7 +13520,7 @@
         <v>388</v>
       </c>
       <c r="O210" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P210" s="6" t="s">
         <v>397</v>
@@ -13511,16 +13543,16 @@
         <v>46129.68353232639</v>
       </c>
       <c r="E211" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F211" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G211" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H211" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I211" s="9"/>
       <c r="J211" s="8">
@@ -13539,7 +13571,7 @@
         <v>388</v>
       </c>
       <c r="O211" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P211" s="9" t="s">
         <v>397</v>
@@ -13562,16 +13594,16 @@
         <v>46129.683533125004</v>
       </c>
       <c r="E212" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F212" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G212" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H212" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I212" s="6"/>
       <c r="J212" s="5">
@@ -13590,7 +13622,7 @@
         <v>388</v>
       </c>
       <c r="O212" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P212" s="6" t="s">
         <v>397</v>
@@ -13613,16 +13645,16 @@
         <v>46129.68353385417</v>
       </c>
       <c r="E213" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F213" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G213" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H213" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I213" s="9"/>
       <c r="J213" s="8">
@@ -13641,7 +13673,7 @@
         <v>388</v>
       </c>
       <c r="O213" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P213" s="9" t="s">
         <v>397</v>
@@ -13664,16 +13696,16 @@
         <v>46129.68353459491</v>
       </c>
       <c r="E214" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F214" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G214" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H214" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I214" s="6"/>
       <c r="J214" s="5">
@@ -13692,7 +13724,7 @@
         <v>388</v>
       </c>
       <c r="O214" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P214" s="6" t="s">
         <v>397</v>
@@ -13723,10 +13755,10 @@
         <v>26</v>
       </c>
       <c r="G215" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H215" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I215" s="9"/>
       <c r="J215" s="8">
@@ -13778,16 +13810,16 @@
         <v>46129.69451681713</v>
       </c>
       <c r="E216" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F216" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G216" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H216" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I216" s="6"/>
       <c r="J216" s="5">
@@ -13806,7 +13838,7 @@
         <v>404</v>
       </c>
       <c r="O216" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P216" s="6" t="s">
         <v>404</v>
@@ -13829,16 +13861,16 @@
         <v>46129.69454358796</v>
       </c>
       <c r="E217" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F217" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G217" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H217" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I217" s="9"/>
       <c r="J217" s="8">
@@ -13857,7 +13889,7 @@
         <v>404</v>
       </c>
       <c r="O217" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P217" s="9" t="s">
         <v>404</v>
@@ -13880,16 +13912,16 @@
         <v>46129.694564502315</v>
       </c>
       <c r="E218" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F218" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G218" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H218" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I218" s="6"/>
       <c r="J218" s="5">
@@ -13908,7 +13940,7 @@
         <v>404</v>
       </c>
       <c r="O218" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P218" s="6" t="s">
         <v>404</v>
@@ -13931,16 +13963,16 @@
         <v>46129.694584282406</v>
       </c>
       <c r="E219" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F219" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G219" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H219" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I219" s="9"/>
       <c r="J219" s="8">
@@ -13959,7 +13991,7 @@
         <v>404</v>
       </c>
       <c r="O219" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P219" s="9" t="s">
         <v>404</v>
@@ -13982,16 +14014,16 @@
         <v>46129.69460693287</v>
       </c>
       <c r="E220" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F220" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G220" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H220" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I220" s="6"/>
       <c r="J220" s="5">
@@ -14010,7 +14042,7 @@
         <v>404</v>
       </c>
       <c r="O220" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P220" s="6" t="s">
         <v>404</v>
@@ -14033,16 +14065,16 @@
         <v>46129.69462627315</v>
       </c>
       <c r="E221" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F221" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G221" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H221" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I221" s="9"/>
       <c r="J221" s="8">
@@ -14061,7 +14093,7 @@
         <v>404</v>
       </c>
       <c r="O221" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P221" s="9" t="s">
         <v>404</v>
@@ -14084,16 +14116,16 @@
         <v>46129.69465064815</v>
       </c>
       <c r="E222" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F222" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G222" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H222" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I222" s="6"/>
       <c r="J222" s="5">
@@ -14112,7 +14144,7 @@
         <v>404</v>
       </c>
       <c r="O222" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P222" s="6" t="s">
         <v>404</v>
@@ -14135,16 +14167,16 @@
         <v>46129.69467157408</v>
       </c>
       <c r="E223" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F223" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G223" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H223" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I223" s="9"/>
       <c r="J223" s="8">
@@ -14163,7 +14195,7 @@
         <v>404</v>
       </c>
       <c r="O223" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P223" s="9" t="s">
         <v>404</v>
@@ -14186,16 +14218,16 @@
         <v>46129.69469225695</v>
       </c>
       <c r="E224" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F224" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G224" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H224" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I224" s="6"/>
       <c r="J224" s="5">
@@ -14214,7 +14246,7 @@
         <v>404</v>
       </c>
       <c r="O224" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P224" s="6" t="s">
         <v>404</v>
@@ -14237,16 +14269,16 @@
         <v>46129.694713379635</v>
       </c>
       <c r="E225" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F225" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G225" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H225" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I225" s="9"/>
       <c r="J225" s="8">
@@ -14265,7 +14297,7 @@
         <v>404</v>
       </c>
       <c r="O225" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P225" s="9" t="s">
         <v>404</v>
@@ -14288,16 +14320,16 @@
         <v>46129.694735682875</v>
       </c>
       <c r="E226" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F226" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G226" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H226" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I226" s="6"/>
       <c r="J226" s="5">
@@ -14316,7 +14348,7 @@
         <v>404</v>
       </c>
       <c r="O226" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P226" s="6" t="s">
         <v>404</v>
@@ -14339,16 +14371,16 @@
         <v>46129.694774895834</v>
       </c>
       <c r="E227" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F227" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G227" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H227" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I227" s="9"/>
       <c r="J227" s="8">
@@ -14367,7 +14399,7 @@
         <v>404</v>
       </c>
       <c r="O227" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P227" s="9" t="s">
         <v>404</v>
@@ -14485,7 +14517,7 @@
         <v>0</v>
       </c>
       <c r="U229" s="12" t="s">
-        <v>208</v>
+        <v>169</v>
       </c>
     </row>
     <row r="230" spans="1:21" x14ac:dyDescent="0.25">
@@ -14548,7 +14580,7 @@
         <v>0</v>
       </c>
       <c r="U230" s="12" t="s">
-        <v>208</v>
+        <v>169</v>
       </c>
     </row>
     <row r="231" spans="1:21" x14ac:dyDescent="0.25">
@@ -14660,7 +14692,7 @@
         <v>0</v>
       </c>
       <c r="U232" s="12" t="s">
-        <v>208</v>
+        <v>169</v>
       </c>
     </row>
     <row r="233" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001501 - EQ MIN LA HACIENDA B.xlsx
+++ b/data/50001501 - EQ MIN LA HACIENDA B.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2668" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2669" uniqueCount="436">
   <si>
     <t>50001501 - EQ. MIN. LA HACIENDA</t>
   </si>
@@ -11589,9 +11589,11 @@
       <c r="B174" s="5">
         <v>46073.767837719904</v>
       </c>
-      <c r="C174" s="6"/>
+      <c r="C174" s="5">
+        <v>46193.560764988426</v>
+      </c>
       <c r="D174" s="5">
-        <v>46191.79694226852</v>
+        <v>46193.561065925926</v>
       </c>
       <c r="E174" s="6" t="s">
         <v>349</v>
@@ -11626,8 +11628,12 @@
       <c r="Q174" s="6"/>
       <c r="R174" s="6"/>
       <c r="S174" s="6"/>
-      <c r="T174" s="6"/>
-      <c r="U174" s="6"/>
+      <c r="T174" s="6">
+        <v>1</v>
+      </c>
+      <c r="U174" s="12" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="175" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A175" s="7" t="s">
@@ -11636,9 +11642,11 @@
       <c r="B175" s="8">
         <v>46073.76783810185</v>
       </c>
-      <c r="C175" s="9"/>
+      <c r="C175" s="8">
+        <v>46193.56105240741</v>
+      </c>
       <c r="D175" s="8">
-        <v>46191.89507545139</v>
+        <v>46193.56105853009</v>
       </c>
       <c r="E175" s="9" t="s">
         <v>352</v>
@@ -11686,10 +11694,10 @@
         <v>31</v>
       </c>
       <c r="T175" s="9">
-        <v>0</v>
-      </c>
-      <c r="U175" s="10" t="s">
-        <v>106</v>
+        <v>1</v>
+      </c>
+      <c r="U175" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="176" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001501 - EQ MIN LA HACIENDA B.xlsx
+++ b/data/50001501 - EQ MIN LA HACIENDA B.xlsx
@@ -11646,7 +11646,7 @@
         <v>46193.56105240741</v>
       </c>
       <c r="D175" s="8">
-        <v>46193.56105853009</v>
+        <v>46194.709360277775</v>
       </c>
       <c r="E175" s="9" t="s">
         <v>352</v>
@@ -11696,8 +11696,8 @@
       <c r="T175" s="9">
         <v>1</v>
       </c>
-      <c r="U175" s="11" t="s">
-        <v>32</v>
+      <c r="U175" s="12" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="176" spans="1:21" x14ac:dyDescent="0.25">
@@ -11707,9 +11707,11 @@
       <c r="B176" s="5">
         <v>46128.56704659722</v>
       </c>
-      <c r="C176" s="6"/>
+      <c r="C176" s="5">
+        <v>46194.70201375</v>
+      </c>
       <c r="D176" s="5">
-        <v>46191.885297430556</v>
+        <v>46194.70208606482</v>
       </c>
       <c r="E176" s="6" t="s">
         <v>171</v>
@@ -11758,9 +11760,11 @@
       <c r="B177" s="8">
         <v>46128.56705305555</v>
       </c>
-      <c r="C177" s="9"/>
+      <c r="C177" s="8">
+        <v>46194.70201552083</v>
+      </c>
       <c r="D177" s="8">
-        <v>46191.88571055555</v>
+        <v>46194.70208699074</v>
       </c>
       <c r="E177" s="9" t="s">
         <v>171</v>
@@ -11809,9 +11813,11 @@
       <c r="B178" s="5">
         <v>46128.567060127316</v>
       </c>
-      <c r="C178" s="6"/>
+      <c r="C178" s="5">
+        <v>46194.702016446754</v>
+      </c>
       <c r="D178" s="5">
-        <v>46191.88526354167</v>
+        <v>46194.702087638885</v>
       </c>
       <c r="E178" s="6" t="s">
         <v>171</v>
@@ -11860,9 +11866,11 @@
       <c r="B179" s="8">
         <v>46128.56706601851</v>
       </c>
-      <c r="C179" s="9"/>
+      <c r="C179" s="8">
+        <v>46194.702017372685</v>
+      </c>
       <c r="D179" s="8">
-        <v>46191.88525847222</v>
+        <v>46194.70208831019</v>
       </c>
       <c r="E179" s="9" t="s">
         <v>171</v>
@@ -11911,9 +11919,11 @@
       <c r="B180" s="5">
         <v>46128.56707302084</v>
       </c>
-      <c r="C180" s="6"/>
+      <c r="C180" s="5">
+        <v>46194.70201841435</v>
+      </c>
       <c r="D180" s="5">
-        <v>46191.88525349537</v>
+        <v>46194.70208899306</v>
       </c>
       <c r="E180" s="6" t="s">
         <v>171</v>
@@ -11962,9 +11972,11 @@
       <c r="B181" s="8">
         <v>46128.56708030093</v>
       </c>
-      <c r="C181" s="9"/>
+      <c r="C181" s="8">
+        <v>46194.702019247685</v>
+      </c>
       <c r="D181" s="8">
-        <v>46191.885310405094</v>
+        <v>46194.70208959491</v>
       </c>
       <c r="E181" s="9" t="s">
         <v>171</v>
@@ -12013,9 +12025,11 @@
       <c r="B182" s="5">
         <v>46128.56708731482</v>
       </c>
-      <c r="C182" s="6"/>
+      <c r="C182" s="5">
+        <v>46194.70206814815</v>
+      </c>
       <c r="D182" s="5">
-        <v>46191.796051701385</v>
+        <v>46194.70209015046</v>
       </c>
       <c r="E182" s="6" t="s">
         <v>171</v>
@@ -12064,9 +12078,11 @@
       <c r="B183" s="8">
         <v>46128.567094432874</v>
       </c>
-      <c r="C183" s="9"/>
+      <c r="C183" s="8">
+        <v>46194.70207223379</v>
+      </c>
       <c r="D183" s="8">
-        <v>46191.795977581016</v>
+        <v>46194.702090729166</v>
       </c>
       <c r="E183" s="9" t="s">
         <v>171</v>
@@ -12115,9 +12131,11 @@
       <c r="B184" s="5">
         <v>46128.56710209491</v>
       </c>
-      <c r="C184" s="6"/>
+      <c r="C184" s="5">
+        <v>46194.70207326389</v>
+      </c>
       <c r="D184" s="5">
-        <v>46191.795861736115</v>
+        <v>46194.702091354164</v>
       </c>
       <c r="E184" s="6" t="s">
         <v>171</v>
@@ -12166,9 +12184,11 @@
       <c r="B185" s="8">
         <v>46128.56710883102</v>
       </c>
-      <c r="C185" s="9"/>
+      <c r="C185" s="8">
+        <v>46194.70207423611</v>
+      </c>
       <c r="D185" s="8">
-        <v>46191.795781168985</v>
+        <v>46194.70209196759</v>
       </c>
       <c r="E185" s="9" t="s">
         <v>171</v>
@@ -12217,9 +12237,11 @@
       <c r="B186" s="5">
         <v>46128.56711633102</v>
       </c>
-      <c r="C186" s="6"/>
+      <c r="C186" s="5">
+        <v>46194.70208087963</v>
+      </c>
       <c r="D186" s="5">
-        <v>46191.795643460646</v>
+        <v>46194.7020958912</v>
       </c>
       <c r="E186" s="6" t="s">
         <v>171</v>
@@ -12268,9 +12290,11 @@
       <c r="B187" s="8">
         <v>46128.56712334491</v>
       </c>
-      <c r="C187" s="9"/>
+      <c r="C187" s="8">
+        <v>46194.70208171297</v>
+      </c>
       <c r="D187" s="8">
-        <v>46191.795556990735</v>
+        <v>46194.70209655093</v>
       </c>
       <c r="E187" s="9" t="s">
         <v>171</v>
@@ -12319,9 +12343,11 @@
       <c r="B188" s="5">
         <v>46191.895071886574</v>
       </c>
-      <c r="C188" s="6"/>
+      <c r="C188" s="5">
+        <v>46194.702082511576</v>
+      </c>
       <c r="D188" s="5">
-        <v>46191.895473171295</v>
+        <v>46194.702097546295</v>
       </c>
       <c r="E188" s="6" t="s">
         <v>371</v>
@@ -12374,7 +12400,7 @@
         <v>46191.796778240736</v>
       </c>
       <c r="D189" s="8">
-        <v>46192.64719054398</v>
+        <v>46194.70536553241</v>
       </c>
       <c r="E189" s="9" t="s">
         <v>373</v>
@@ -12439,7 +12465,7 @@
         <v>46192.64706778935</v>
       </c>
       <c r="D190" s="5">
-        <v>46192.64706957176</v>
+        <v>46194.70885945602</v>
       </c>
       <c r="E190" s="6" t="s">
         <v>171</v>
@@ -12494,7 +12520,7 @@
         <v>46192.64718554398</v>
       </c>
       <c r="D191" s="8">
-        <v>46192.647186875</v>
+        <v>46194.706768668984</v>
       </c>
       <c r="E191" s="9" t="s">
         <v>171</v>
@@ -12547,7 +12573,7 @@
       </c>
       <c r="C192" s="6"/>
       <c r="D192" s="5">
-        <v>46191.8852687037</v>
+        <v>46194.70287113426</v>
       </c>
       <c r="E192" s="6" t="s">
         <v>171</v>
@@ -12600,7 +12626,7 @@
       </c>
       <c r="C193" s="9"/>
       <c r="D193" s="8">
-        <v>46191.88526256944</v>
+        <v>46194.70272818287</v>
       </c>
       <c r="E193" s="9" t="s">
         <v>171</v>
@@ -12653,7 +12679,7 @@
       </c>
       <c r="C194" s="6"/>
       <c r="D194" s="5">
-        <v>46191.885259710645</v>
+        <v>46194.70217247686</v>
       </c>
       <c r="E194" s="6" t="s">
         <v>171</v>
@@ -12706,7 +12732,7 @@
       </c>
       <c r="C195" s="9"/>
       <c r="D195" s="8">
-        <v>46191.88531537037</v>
+        <v>46194.70884659722</v>
       </c>
       <c r="E195" s="9" t="s">
         <v>171</v>
@@ -12759,7 +12785,7 @@
       </c>
       <c r="C196" s="6"/>
       <c r="D196" s="5">
-        <v>46129.68320027778</v>
+        <v>46194.7024039699</v>
       </c>
       <c r="E196" s="6" t="s">
         <v>171</v>
@@ -12812,7 +12838,7 @@
       </c>
       <c r="C197" s="9"/>
       <c r="D197" s="8">
-        <v>46129.68320100695</v>
+        <v>46194.70536497685</v>
       </c>
       <c r="E197" s="9" t="s">
         <v>171</v>
@@ -12865,7 +12891,7 @@
       </c>
       <c r="C198" s="6"/>
       <c r="D198" s="5">
-        <v>46129.683201747685</v>
+        <v>46194.70870311343</v>
       </c>
       <c r="E198" s="6" t="s">
         <v>171</v>
@@ -12918,7 +12944,7 @@
       </c>
       <c r="C199" s="9"/>
       <c r="D199" s="8">
-        <v>46129.683202500004</v>
+        <v>46194.70256980324</v>
       </c>
       <c r="E199" s="9" t="s">
         <v>171</v>
@@ -12971,7 +12997,7 @@
       </c>
       <c r="C200" s="6"/>
       <c r="D200" s="5">
-        <v>46129.683203252316</v>
+        <v>46194.70497310185</v>
       </c>
       <c r="E200" s="6" t="s">
         <v>171</v>
@@ -13024,7 +13050,7 @@
       </c>
       <c r="C201" s="9"/>
       <c r="D201" s="8">
-        <v>46129.683203981476</v>
+        <v>46194.703054178244</v>
       </c>
       <c r="E201" s="9" t="s">
         <v>171</v>
@@ -13497,7 +13523,7 @@
       </c>
       <c r="C210" s="6"/>
       <c r="D210" s="5">
-        <v>46129.68353159723</v>
+        <v>46194.70536717593</v>
       </c>
       <c r="E210" s="6" t="s">
         <v>171</v>

--- a/data/50001501 - EQ MIN LA HACIENDA B.xlsx
+++ b/data/50001501 - EQ MIN LA HACIENDA B.xlsx
@@ -12400,7 +12400,7 @@
         <v>46191.796778240736</v>
       </c>
       <c r="D189" s="8">
-        <v>46194.70536553241</v>
+        <v>46194.7453605787</v>
       </c>
       <c r="E189" s="9" t="s">
         <v>373</v>
@@ -12450,8 +12450,8 @@
       <c r="T189" s="9">
         <v>1</v>
       </c>
-      <c r="U189" s="11" t="s">
-        <v>32</v>
+      <c r="U189" s="12" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="190" spans="1:21" x14ac:dyDescent="0.25">
@@ -12571,9 +12571,11 @@
       <c r="B192" s="5">
         <v>46128.567196550925</v>
       </c>
-      <c r="C192" s="6"/>
+      <c r="C192" s="5">
+        <v>46194.745200694444</v>
+      </c>
       <c r="D192" s="5">
-        <v>46194.70287113426</v>
+        <v>46194.7452021412</v>
       </c>
       <c r="E192" s="6" t="s">
         <v>171</v>
@@ -12624,9 +12626,11 @@
       <c r="B193" s="8">
         <v>46128.56720474537</v>
       </c>
-      <c r="C193" s="9"/>
+      <c r="C193" s="8">
+        <v>46194.7452541088</v>
+      </c>
       <c r="D193" s="8">
-        <v>46194.70272818287</v>
+        <v>46194.74525607639</v>
       </c>
       <c r="E193" s="9" t="s">
         <v>171</v>
@@ -12677,9 +12681,11 @@
       <c r="B194" s="5">
         <v>46128.56721146991</v>
       </c>
-      <c r="C194" s="6"/>
+      <c r="C194" s="5">
+        <v>46194.74508903935</v>
+      </c>
       <c r="D194" s="5">
-        <v>46194.70217247686</v>
+        <v>46194.74509084491</v>
       </c>
       <c r="E194" s="6" t="s">
         <v>171</v>
@@ -12730,9 +12736,11 @@
       <c r="B195" s="8">
         <v>46128.56721795139</v>
       </c>
-      <c r="C195" s="9"/>
+      <c r="C195" s="8">
+        <v>46194.74486503472</v>
+      </c>
       <c r="D195" s="8">
-        <v>46194.70884659722</v>
+        <v>46194.74486726851</v>
       </c>
       <c r="E195" s="9" t="s">
         <v>171</v>
@@ -12783,9 +12791,11 @@
       <c r="B196" s="5">
         <v>46128.56722548611</v>
       </c>
-      <c r="C196" s="6"/>
+      <c r="C196" s="5">
+        <v>46194.74534504629</v>
+      </c>
       <c r="D196" s="5">
-        <v>46194.7024039699</v>
+        <v>46194.74534685185</v>
       </c>
       <c r="E196" s="6" t="s">
         <v>171</v>
@@ -12836,9 +12846,11 @@
       <c r="B197" s="8">
         <v>46128.567233333335</v>
       </c>
-      <c r="C197" s="9"/>
+      <c r="C197" s="8">
+        <v>46194.7449961574</v>
+      </c>
       <c r="D197" s="8">
-        <v>46194.70536497685</v>
+        <v>46194.74499798611</v>
       </c>
       <c r="E197" s="9" t="s">
         <v>171</v>
@@ -12889,9 +12901,11 @@
       <c r="B198" s="5">
         <v>46128.56724010417</v>
       </c>
-      <c r="C198" s="6"/>
+      <c r="C198" s="5">
+        <v>46194.744955497685</v>
+      </c>
       <c r="D198" s="5">
-        <v>46194.70870311343</v>
+        <v>46194.74495716435</v>
       </c>
       <c r="E198" s="6" t="s">
         <v>171</v>
@@ -12942,9 +12956,11 @@
       <c r="B199" s="8">
         <v>46128.56724606482</v>
       </c>
-      <c r="C199" s="9"/>
+      <c r="C199" s="8">
+        <v>46194.74529594908</v>
+      </c>
       <c r="D199" s="8">
-        <v>46194.70256980324</v>
+        <v>46194.74529774305</v>
       </c>
       <c r="E199" s="9" t="s">
         <v>171</v>
@@ -12995,9 +13011,11 @@
       <c r="B200" s="5">
         <v>46128.56725237268</v>
       </c>
-      <c r="C200" s="6"/>
+      <c r="C200" s="5">
+        <v>46194.745028819445</v>
+      </c>
       <c r="D200" s="5">
-        <v>46194.70497310185</v>
+        <v>46194.74503064815</v>
       </c>
       <c r="E200" s="6" t="s">
         <v>171</v>
@@ -13048,9 +13066,11 @@
       <c r="B201" s="8">
         <v>46128.56725944445</v>
       </c>
-      <c r="C201" s="9"/>
+      <c r="C201" s="8">
+        <v>46194.745127002316</v>
+      </c>
       <c r="D201" s="8">
-        <v>46194.703054178244</v>
+        <v>46194.74512893519</v>
       </c>
       <c r="E201" s="9" t="s">
         <v>171</v>
@@ -13268,7 +13288,7 @@
       </c>
       <c r="C205" s="9"/>
       <c r="D205" s="8">
-        <v>46129.68352791667</v>
+        <v>46194.745209120374</v>
       </c>
       <c r="E205" s="9" t="s">
         <v>171</v>
@@ -13319,7 +13339,7 @@
       </c>
       <c r="C206" s="6"/>
       <c r="D206" s="5">
-        <v>46129.683528657406</v>
+        <v>46194.74526217593</v>
       </c>
       <c r="E206" s="6" t="s">
         <v>171</v>
@@ -13370,7 +13390,7 @@
       </c>
       <c r="C207" s="9"/>
       <c r="D207" s="8">
-        <v>46129.68352943287</v>
+        <v>46194.74509618056</v>
       </c>
       <c r="E207" s="9" t="s">
         <v>171</v>
@@ -13421,7 +13441,7 @@
       </c>
       <c r="C208" s="6"/>
       <c r="D208" s="5">
-        <v>46129.68353019676</v>
+        <v>46194.74487355324</v>
       </c>
       <c r="E208" s="6" t="s">
         <v>171</v>
@@ -13472,7 +13492,7 @@
       </c>
       <c r="C209" s="9"/>
       <c r="D209" s="8">
-        <v>46129.683530891205</v>
+        <v>46194.74535369213</v>
       </c>
       <c r="E209" s="9" t="s">
         <v>171</v>
@@ -13574,7 +13594,7 @@
       </c>
       <c r="C211" s="9"/>
       <c r="D211" s="8">
-        <v>46129.68353232639</v>
+        <v>46194.74500435185</v>
       </c>
       <c r="E211" s="9" t="s">
         <v>171</v>
@@ -13625,7 +13645,7 @@
       </c>
       <c r="C212" s="6"/>
       <c r="D212" s="5">
-        <v>46129.683533125004</v>
+        <v>46194.74530193287</v>
       </c>
       <c r="E212" s="6" t="s">
         <v>171</v>
@@ -13676,7 +13696,7 @@
       </c>
       <c r="C213" s="9"/>
       <c r="D213" s="8">
-        <v>46129.68353385417</v>
+        <v>46194.7450368287</v>
       </c>
       <c r="E213" s="9" t="s">
         <v>171</v>
@@ -13727,7 +13747,7 @@
       </c>
       <c r="C214" s="6"/>
       <c r="D214" s="5">
-        <v>46129.68353459491</v>
+        <v>46194.74513560185</v>
       </c>
       <c r="E214" s="6" t="s">
         <v>171</v>

--- a/data/50001501 - EQ MIN LA HACIENDA B.xlsx
+++ b/data/50001501 - EQ MIN LA HACIENDA B.xlsx
@@ -13125,7 +13125,7 @@
         <v>46191.79687179398</v>
       </c>
       <c r="D202" s="5">
-        <v>46191.7968871875</v>
+        <v>46195.89050030093</v>
       </c>
       <c r="E202" s="6" t="s">
         <v>388</v>
@@ -13173,8 +13173,8 @@
       <c r="T202" s="6">
         <v>1</v>
       </c>
-      <c r="U202" s="11" t="s">
-        <v>32</v>
+      <c r="U202" s="12" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="203" spans="1:21" x14ac:dyDescent="0.25">
@@ -13184,9 +13184,11 @@
       <c r="B203" s="8">
         <v>46128.567313437496</v>
       </c>
-      <c r="C203" s="9"/>
+      <c r="C203" s="8">
+        <v>46195.888619652775</v>
+      </c>
       <c r="D203" s="8">
-        <v>46192.64707679398</v>
+        <v>46195.88862107639</v>
       </c>
       <c r="E203" s="9" t="s">
         <v>171</v>
@@ -13235,9 +13237,11 @@
       <c r="B204" s="5">
         <v>46128.56732054398</v>
       </c>
-      <c r="C204" s="6"/>
+      <c r="C204" s="5">
+        <v>46195.888511909725</v>
+      </c>
       <c r="D204" s="5">
-        <v>46192.64719189815</v>
+        <v>46195.88851415509</v>
       </c>
       <c r="E204" s="6" t="s">
         <v>171</v>
@@ -13286,9 +13290,11 @@
       <c r="B205" s="8">
         <v>46128.5673266088</v>
       </c>
-      <c r="C205" s="9"/>
+      <c r="C205" s="8">
+        <v>46195.888713912034</v>
+      </c>
       <c r="D205" s="8">
-        <v>46194.745209120374</v>
+        <v>46195.88871565972</v>
       </c>
       <c r="E205" s="9" t="s">
         <v>171</v>
@@ -13337,9 +13343,11 @@
       <c r="B206" s="5">
         <v>46128.56733295139</v>
       </c>
-      <c r="C206" s="6"/>
+      <c r="C206" s="5">
+        <v>46195.890410821754</v>
+      </c>
       <c r="D206" s="5">
-        <v>46194.74526217593</v>
+        <v>46195.89041287037</v>
       </c>
       <c r="E206" s="6" t="s">
         <v>171</v>
@@ -13388,9 +13396,11 @@
       <c r="B207" s="8">
         <v>46128.56733854167</v>
       </c>
-      <c r="C207" s="9"/>
+      <c r="C207" s="8">
+        <v>46195.89042074074</v>
+      </c>
       <c r="D207" s="8">
-        <v>46194.74509618056</v>
+        <v>46195.89042275463</v>
       </c>
       <c r="E207" s="9" t="s">
         <v>171</v>
@@ -13439,9 +13449,11 @@
       <c r="B208" s="5">
         <v>46128.56734518518</v>
       </c>
-      <c r="C208" s="6"/>
+      <c r="C208" s="5">
+        <v>46195.89043005787</v>
+      </c>
       <c r="D208" s="5">
-        <v>46194.74487355324</v>
+        <v>46195.89043167824</v>
       </c>
       <c r="E208" s="6" t="s">
         <v>171</v>
@@ -13490,9 +13502,11 @@
       <c r="B209" s="8">
         <v>46128.567351770835</v>
       </c>
-      <c r="C209" s="9"/>
+      <c r="C209" s="8">
+        <v>46195.89043835648</v>
+      </c>
       <c r="D209" s="8">
-        <v>46194.74535369213</v>
+        <v>46195.89044037037</v>
       </c>
       <c r="E209" s="9" t="s">
         <v>171</v>
@@ -13541,9 +13555,11 @@
       <c r="B210" s="5">
         <v>46128.56735738426</v>
       </c>
-      <c r="C210" s="6"/>
+      <c r="C210" s="5">
+        <v>46195.8904453588</v>
+      </c>
       <c r="D210" s="5">
-        <v>46194.70536717593</v>
+        <v>46195.890446805555</v>
       </c>
       <c r="E210" s="6" t="s">
         <v>171</v>
@@ -13592,9 +13608,11 @@
       <c r="B211" s="8">
         <v>46128.56736256945</v>
       </c>
-      <c r="C211" s="9"/>
+      <c r="C211" s="8">
+        <v>46195.890451921296</v>
+      </c>
       <c r="D211" s="8">
-        <v>46194.74500435185</v>
+        <v>46195.89045333333</v>
       </c>
       <c r="E211" s="9" t="s">
         <v>171</v>
@@ -13643,9 +13661,11 @@
       <c r="B212" s="5">
         <v>46128.567368206015</v>
       </c>
-      <c r="C212" s="6"/>
+      <c r="C212" s="5">
+        <v>46195.890460787035</v>
+      </c>
       <c r="D212" s="5">
-        <v>46194.74530193287</v>
+        <v>46195.890462361116</v>
       </c>
       <c r="E212" s="6" t="s">
         <v>171</v>
@@ -13694,9 +13714,11 @@
       <c r="B213" s="8">
         <v>46128.56737366898</v>
       </c>
-      <c r="C213" s="9"/>
+      <c r="C213" s="8">
+        <v>46195.89046549769</v>
+      </c>
       <c r="D213" s="8">
-        <v>46194.7450368287</v>
+        <v>46195.89046699074</v>
       </c>
       <c r="E213" s="9" t="s">
         <v>171</v>
@@ -13745,9 +13767,11 @@
       <c r="B214" s="5">
         <v>46128.56737853009</v>
       </c>
-      <c r="C214" s="6"/>
+      <c r="C214" s="5">
+        <v>46195.89047841435</v>
+      </c>
       <c r="D214" s="5">
-        <v>46194.74513560185</v>
+        <v>46195.89048138889</v>
       </c>
       <c r="E214" s="6" t="s">
         <v>171</v>
@@ -13800,7 +13824,7 @@
         <v>46191.79693015046</v>
       </c>
       <c r="D215" s="8">
-        <v>46191.79694662037</v>
+        <v>46195.890647175926</v>
       </c>
       <c r="E215" s="9" t="s">
         <v>404</v>
@@ -13848,8 +13872,8 @@
       <c r="T215" s="9">
         <v>1</v>
       </c>
-      <c r="U215" s="11" t="s">
-        <v>32</v>
+      <c r="U215" s="12" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="216" spans="1:21" x14ac:dyDescent="0.25">
@@ -13859,9 +13883,11 @@
       <c r="B216" s="5">
         <v>46128.56746619213</v>
       </c>
-      <c r="C216" s="6"/>
+      <c r="C216" s="5">
+        <v>46195.890531701385</v>
+      </c>
       <c r="D216" s="5">
-        <v>46129.69451681713</v>
+        <v>46195.890533206024</v>
       </c>
       <c r="E216" s="6" t="s">
         <v>171</v>
@@ -13910,9 +13936,11 @@
       <c r="B217" s="8">
         <v>46128.56747375</v>
       </c>
-      <c r="C217" s="9"/>
+      <c r="C217" s="8">
+        <v>46195.89053809027</v>
+      </c>
       <c r="D217" s="8">
-        <v>46129.69454358796</v>
+        <v>46195.890539699074</v>
       </c>
       <c r="E217" s="9" t="s">
         <v>171</v>
@@ -13961,9 +13989,11 @@
       <c r="B218" s="5">
         <v>46128.567480833335</v>
       </c>
-      <c r="C218" s="6"/>
+      <c r="C218" s="5">
+        <v>46195.890545682865</v>
+      </c>
       <c r="D218" s="5">
-        <v>46129.694564502315</v>
+        <v>46195.890547476854</v>
       </c>
       <c r="E218" s="6" t="s">
         <v>171</v>
@@ -14012,9 +14042,11 @@
       <c r="B219" s="8">
         <v>46128.56748863426</v>
       </c>
-      <c r="C219" s="9"/>
+      <c r="C219" s="8">
+        <v>46195.89055040509</v>
+      </c>
       <c r="D219" s="8">
-        <v>46129.694584282406</v>
+        <v>46195.890552048615</v>
       </c>
       <c r="E219" s="9" t="s">
         <v>171</v>
@@ -14063,9 +14095,11 @@
       <c r="B220" s="5">
         <v>46128.5674962037</v>
       </c>
-      <c r="C220" s="6"/>
+      <c r="C220" s="5">
+        <v>46195.89055759259</v>
+      </c>
       <c r="D220" s="5">
-        <v>46129.69460693287</v>
+        <v>46195.890559074076</v>
       </c>
       <c r="E220" s="6" t="s">
         <v>171</v>
@@ -14114,9 +14148,11 @@
       <c r="B221" s="8">
         <v>46128.567504074075</v>
       </c>
-      <c r="C221" s="9"/>
+      <c r="C221" s="8">
+        <v>46195.89058274306</v>
+      </c>
       <c r="D221" s="8">
-        <v>46129.69462627315</v>
+        <v>46195.89058465278</v>
       </c>
       <c r="E221" s="9" t="s">
         <v>171</v>
@@ -14165,9 +14201,11 @@
       <c r="B222" s="5">
         <v>46128.56751277778</v>
       </c>
-      <c r="C222" s="6"/>
+      <c r="C222" s="5">
+        <v>46195.89056908565</v>
+      </c>
       <c r="D222" s="5">
-        <v>46129.69465064815</v>
+        <v>46195.8905709838</v>
       </c>
       <c r="E222" s="6" t="s">
         <v>171</v>
@@ -14216,9 +14254,11 @@
       <c r="B223" s="8">
         <v>46128.56752138889</v>
       </c>
-      <c r="C223" s="9"/>
+      <c r="C223" s="8">
+        <v>46195.89059236112</v>
+      </c>
       <c r="D223" s="8">
-        <v>46129.69467157408</v>
+        <v>46195.89059417824</v>
       </c>
       <c r="E223" s="9" t="s">
         <v>171</v>
@@ -14267,9 +14307,11 @@
       <c r="B224" s="5">
         <v>46128.56752835648</v>
       </c>
-      <c r="C224" s="6"/>
+      <c r="C224" s="5">
+        <v>46195.89060629629</v>
+      </c>
       <c r="D224" s="5">
-        <v>46129.69469225695</v>
+        <v>46195.89060789352</v>
       </c>
       <c r="E224" s="6" t="s">
         <v>171</v>
@@ -14318,9 +14360,11 @@
       <c r="B225" s="8">
         <v>46128.567536284725</v>
       </c>
-      <c r="C225" s="9"/>
+      <c r="C225" s="8">
+        <v>46195.890615173616</v>
+      </c>
       <c r="D225" s="8">
-        <v>46129.694713379635</v>
+        <v>46195.890617060184</v>
       </c>
       <c r="E225" s="9" t="s">
         <v>171</v>
@@ -14369,9 +14413,11 @@
       <c r="B226" s="5">
         <v>46128.56754392361</v>
       </c>
-      <c r="C226" s="6"/>
+      <c r="C226" s="5">
+        <v>46195.89062324074</v>
+      </c>
       <c r="D226" s="5">
-        <v>46129.694735682875</v>
+        <v>46195.89062482639</v>
       </c>
       <c r="E226" s="6" t="s">
         <v>171</v>
@@ -14420,9 +14466,11 @@
       <c r="B227" s="8">
         <v>46128.567550949076</v>
       </c>
-      <c r="C227" s="9"/>
+      <c r="C227" s="8">
+        <v>46195.89063059028</v>
+      </c>
       <c r="D227" s="8">
-        <v>46129.694774895834</v>
+        <v>46195.89063229167</v>
       </c>
       <c r="E227" s="9" t="s">
         <v>171</v>

--- a/data/50001501 - EQ MIN LA HACIENDA B.xlsx
+++ b/data/50001501 - EQ MIN LA HACIENDA B.xlsx
@@ -1945,13 +1945,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46073.76783712963</v>
+        <v>46073.60117046296</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.71761209491</v>
+        <v>46092.550945428244</v>
       </c>
       <c r="D4" s="5">
-        <v>46111.80568236111</v>
+        <v>46111.63901569444</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1994,13 +1994,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46073.76783748843</v>
+        <v>46073.601170821756</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.71758320602</v>
+        <v>46092.55091653935</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.71761317129</v>
+        <v>46092.550946504634</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -2057,13 +2057,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46073.76783778935</v>
+        <v>46073.60117112269</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.71758373843</v>
+        <v>46092.550917071756</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.71761302083</v>
+        <v>46092.55094635417</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -2120,13 +2120,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46073.76783810185</v>
+        <v>46073.601171435184</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.717584178245</v>
+        <v>46092.55091751157</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.71761260417</v>
+        <v>46092.5509459375</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -2183,13 +2183,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46073.76783840278</v>
+        <v>46073.60117173611</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.71758460648</v>
+        <v>46092.550917939814</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.7815690625</v>
+        <v>46100.614902395835</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -2246,13 +2246,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46073.7678387037</v>
+        <v>46073.60117203704</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.71758519676</v>
+        <v>46092.55091853009</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.7176125</v>
+        <v>46092.55094583333</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -2309,13 +2309,13 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46073.767839004635</v>
+        <v>46073.60117233796</v>
       </c>
       <c r="C10" s="5">
-        <v>46191.89493512732</v>
+        <v>46191.72826846065</v>
       </c>
       <c r="D10" s="5">
-        <v>46191.89494637732</v>
+        <v>46191.728279710645</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -2362,13 +2362,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46073.767839340275</v>
+        <v>46073.60117267361</v>
       </c>
       <c r="C11" s="8">
-        <v>46114.51731486111</v>
+        <v>46114.35064819445</v>
       </c>
       <c r="D11" s="8">
-        <v>46114.517330092596</v>
+        <v>46114.350663425925</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -2427,13 +2427,13 @@
         <v>52</v>
       </c>
       <c r="B12" s="5">
-        <v>46073.7678396875</v>
+        <v>46073.601173020834</v>
       </c>
       <c r="C12" s="5">
-        <v>46191.89490662037</v>
+        <v>46191.72823995371</v>
       </c>
       <c r="D12" s="5">
-        <v>46191.894935613425</v>
+        <v>46191.728268946754</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2492,13 +2492,13 @@
         <v>55</v>
       </c>
       <c r="B13" s="8">
-        <v>46073.76784</v>
+        <v>46073.60117333333</v>
       </c>
       <c r="C13" s="8">
-        <v>46114.51739915509</v>
+        <v>46114.35073248843</v>
       </c>
       <c r="D13" s="8">
-        <v>46114.517410451386</v>
+        <v>46114.35074378472</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>56</v>
@@ -2545,13 +2545,13 @@
         <v>58</v>
       </c>
       <c r="B14" s="5">
-        <v>46073.76783829861</v>
+        <v>46073.60117163195</v>
       </c>
       <c r="C14" s="5">
-        <v>46097.549839722225</v>
+        <v>46097.383173055554</v>
       </c>
       <c r="D14" s="5">
-        <v>46097.549856875004</v>
+        <v>46097.38319020833</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>59</v>
@@ -2610,13 +2610,13 @@
         <v>61</v>
       </c>
       <c r="B15" s="8">
-        <v>46073.76783899305</v>
+        <v>46073.60117232639</v>
       </c>
       <c r="C15" s="8">
-        <v>46114.5170559838</v>
+        <v>46114.35038931713</v>
       </c>
       <c r="D15" s="8">
-        <v>46114.517243159724</v>
+        <v>46114.35057649306</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>62</v>
@@ -2675,13 +2675,13 @@
         <v>64</v>
       </c>
       <c r="B16" s="5">
-        <v>46073.767839328706</v>
+        <v>46073.601172662035</v>
       </c>
       <c r="C16" s="5">
-        <v>46097.55011791667</v>
+        <v>46097.38345125</v>
       </c>
       <c r="D16" s="5">
-        <v>46097.550135625</v>
+        <v>46097.38346895833</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>65</v>
@@ -2740,13 +2740,13 @@
         <v>67</v>
       </c>
       <c r="B17" s="8">
-        <v>46073.7678396875</v>
+        <v>46073.601173020834</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.517383831015</v>
+        <v>46114.35071716435</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.517399375</v>
+        <v>46114.350732708335</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>68</v>
@@ -2805,13 +2805,13 @@
         <v>71</v>
       </c>
       <c r="B18" s="5">
-        <v>46073.767839988424</v>
+        <v>46073.60117332176</v>
       </c>
       <c r="C18" s="5">
-        <v>46122.65802675926</v>
+        <v>46122.491360092594</v>
       </c>
       <c r="D18" s="5">
-        <v>46146.4968544213</v>
+        <v>46146.33018775463</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>72</v>
@@ -2858,13 +2858,13 @@
         <v>74</v>
       </c>
       <c r="B19" s="8">
-        <v>46073.76784025463</v>
+        <v>46073.60117358796</v>
       </c>
       <c r="C19" s="8">
-        <v>46114.517502268514</v>
+        <v>46114.35083560185</v>
       </c>
       <c r="D19" s="8">
-        <v>46114.517520312496</v>
+        <v>46114.35085364583</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>75</v>
@@ -2923,13 +2923,13 @@
         <v>77</v>
       </c>
       <c r="B20" s="5">
-        <v>46073.76784056713</v>
+        <v>46073.60117390046</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.54988795139</v>
+        <v>46097.38322128472</v>
       </c>
       <c r="D20" s="5">
-        <v>46097.54990454861</v>
+        <v>46097.38323788195</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>78</v>
@@ -2988,13 +2988,13 @@
         <v>80</v>
       </c>
       <c r="B21" s="8">
-        <v>46073.767840879635</v>
+        <v>46073.60117421296</v>
       </c>
       <c r="C21" s="8">
-        <v>46114.51758513889</v>
+        <v>46114.35091847222</v>
       </c>
       <c r="D21" s="8">
-        <v>46114.51760107639</v>
+        <v>46114.350934409726</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>81</v>
@@ -3053,13 +3053,13 @@
         <v>83</v>
       </c>
       <c r="B22" s="5">
-        <v>46073.76784115741</v>
+        <v>46073.601174490745</v>
       </c>
       <c r="C22" s="5">
-        <v>46122.65800895833</v>
+        <v>46122.491342291665</v>
       </c>
       <c r="D22" s="5">
-        <v>46135.43132456018</v>
+        <v>46135.264657893524</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>84</v>
@@ -3118,13 +3118,13 @@
         <v>87</v>
       </c>
       <c r="B23" s="8">
-        <v>46073.76783766204</v>
+        <v>46073.601170995375</v>
       </c>
       <c r="C23" s="8">
-        <v>46097.55018090278</v>
+        <v>46097.383514236106</v>
       </c>
       <c r="D23" s="8">
-        <v>46100.78183767361</v>
+        <v>46100.615171006946</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>88</v>
@@ -3183,13 +3183,13 @@
         <v>92</v>
       </c>
       <c r="B24" s="5">
-        <v>46114.77467594907</v>
+        <v>46114.60800928241</v>
       </c>
       <c r="C24" s="5">
-        <v>46114.77592616898</v>
+        <v>46114.609259502315</v>
       </c>
       <c r="D24" s="5">
-        <v>46114.77593953704</v>
+        <v>46114.609272870366</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>93</v>
@@ -3238,13 +3238,13 @@
         <v>94</v>
       </c>
       <c r="B25" s="8">
-        <v>46073.767838009255</v>
+        <v>46073.6011713426</v>
       </c>
       <c r="C25" s="8">
-        <v>46191.89589885417</v>
+        <v>46191.7292321875</v>
       </c>
       <c r="D25" s="8">
-        <v>46191.89593702546</v>
+        <v>46191.729270358795</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>95</v>
@@ -3291,13 +3291,13 @@
         <v>97</v>
       </c>
       <c r="B26" s="5">
-        <v>46073.76783827547</v>
+        <v>46073.601171608796</v>
       </c>
       <c r="C26" s="5">
-        <v>46114.51787440972</v>
+        <v>46114.35120774306</v>
       </c>
       <c r="D26" s="5">
-        <v>46114.51796603009</v>
+        <v>46114.35129936342</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>98</v>
@@ -3356,13 +3356,13 @@
         <v>102</v>
       </c>
       <c r="B27" s="8">
-        <v>46073.7678385301</v>
+        <v>46073.601171863425</v>
       </c>
       <c r="C27" s="8">
-        <v>46114.517756608795</v>
+        <v>46114.35108994213</v>
       </c>
       <c r="D27" s="8">
-        <v>46114.5177578588</v>
+        <v>46114.35109119213</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>103</v>
@@ -3417,13 +3417,13 @@
         <v>107</v>
       </c>
       <c r="B28" s="5">
-        <v>46073.767838796295</v>
+        <v>46073.60117212963</v>
       </c>
       <c r="C28" s="5">
-        <v>46114.51779525463</v>
+        <v>46114.351128587965</v>
       </c>
       <c r="D28" s="5">
-        <v>46114.517796608794</v>
+        <v>46114.35112994213</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>108</v>
@@ -3478,13 +3478,13 @@
         <v>110</v>
       </c>
       <c r="B29" s="8">
-        <v>46073.767839120366</v>
+        <v>46073.6011724537</v>
       </c>
       <c r="C29" s="8">
-        <v>46191.79343924769</v>
+        <v>46191.62677258102</v>
       </c>
       <c r="D29" s="8">
-        <v>46191.793455046296</v>
+        <v>46191.626788379624</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>111</v>
@@ -3543,13 +3543,13 @@
         <v>113</v>
       </c>
       <c r="B30" s="5">
-        <v>46073.76783938658</v>
+        <v>46073.60117271991</v>
       </c>
       <c r="C30" s="5">
-        <v>46114.77614469908</v>
+        <v>46114.609478032406</v>
       </c>
       <c r="D30" s="5">
-        <v>46169.84669766204</v>
+        <v>46169.68003099537</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>114</v>
@@ -3604,13 +3604,13 @@
         <v>116</v>
       </c>
       <c r="B31" s="8">
-        <v>46073.7678396875</v>
+        <v>46073.601173020834</v>
       </c>
       <c r="C31" s="8">
-        <v>46191.79342321759</v>
+        <v>46191.626756550926</v>
       </c>
       <c r="D31" s="8">
-        <v>46191.79342476852</v>
+        <v>46191.62675810185</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>117</v>
@@ -3665,13 +3665,13 @@
         <v>119</v>
       </c>
       <c r="B32" s="5">
-        <v>46073.76784030093</v>
+        <v>46073.60117363426</v>
       </c>
       <c r="C32" s="5">
-        <v>46122.65816556713</v>
+        <v>46122.49149890046</v>
       </c>
       <c r="D32" s="5">
-        <v>46122.658178784724</v>
+        <v>46122.49151211805</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>120</v>
@@ -3730,13 +3730,13 @@
         <v>122</v>
       </c>
       <c r="B33" s="8">
-        <v>46073.7678405787</v>
+        <v>46073.60117391204</v>
       </c>
       <c r="C33" s="8">
-        <v>46122.65810836805</v>
+        <v>46122.49144170139</v>
       </c>
       <c r="D33" s="8">
-        <v>46122.65810958333</v>
+        <v>46122.49144291667</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>123</v>
@@ -3791,13 +3791,13 @@
         <v>125</v>
       </c>
       <c r="B34" s="5">
-        <v>46073.76783680556</v>
+        <v>46073.60117013889</v>
       </c>
       <c r="C34" s="5">
-        <v>46122.65815113426</v>
+        <v>46122.491484467595</v>
       </c>
       <c r="D34" s="5">
-        <v>46122.658152662036</v>
+        <v>46122.49148599537</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>126</v>
@@ -3852,13 +3852,13 @@
         <v>128</v>
       </c>
       <c r="B35" s="8">
-        <v>46073.76783711805</v>
+        <v>46073.60117045139</v>
       </c>
       <c r="C35" s="8">
-        <v>46097.55003329861</v>
+        <v>46097.38336663194</v>
       </c>
       <c r="D35" s="8">
-        <v>46097.55004581019</v>
+        <v>46097.38337914352</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>129</v>
@@ -3917,13 +3917,13 @@
         <v>131</v>
       </c>
       <c r="B36" s="5">
-        <v>46073.76783739583</v>
+        <v>46073.60117072916</v>
       </c>
       <c r="C36" s="5">
-        <v>46097.54995318287</v>
+        <v>46097.383286516204</v>
       </c>
       <c r="D36" s="5">
-        <v>46097.54995472222</v>
+        <v>46097.38328805556</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>132</v>
@@ -3978,13 +3978,13 @@
         <v>134</v>
       </c>
       <c r="B37" s="8">
-        <v>46073.76783761574</v>
+        <v>46073.60117094907</v>
       </c>
       <c r="C37" s="8">
-        <v>46097.54999658564</v>
+        <v>46097.38332991899</v>
       </c>
       <c r="D37" s="8">
-        <v>46097.54999799769</v>
+        <v>46097.38333133102</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>135</v>
@@ -4039,13 +4039,13 @@
         <v>137</v>
       </c>
       <c r="B38" s="5">
-        <v>46073.76783783565</v>
+        <v>46073.60117116898</v>
       </c>
       <c r="C38" s="5">
-        <v>46097.55001859953</v>
+        <v>46097.38335193287</v>
       </c>
       <c r="D38" s="5">
-        <v>46097.55002008102</v>
+        <v>46097.38335341435</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>138</v>
@@ -4100,13 +4100,13 @@
         <v>140</v>
       </c>
       <c r="B39" s="8">
-        <v>46073.76783806713</v>
+        <v>46073.60117140046</v>
       </c>
       <c r="C39" s="8">
-        <v>46097.550334432875</v>
+        <v>46097.383667766204</v>
       </c>
       <c r="D39" s="8">
-        <v>46097.550347881945</v>
+        <v>46097.38368121527</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>141</v>
@@ -4165,13 +4165,13 @@
         <v>143</v>
       </c>
       <c r="B40" s="5">
-        <v>46073.76783829861</v>
+        <v>46073.60117163195</v>
       </c>
       <c r="C40" s="5">
-        <v>46097.55025366898</v>
+        <v>46097.38358700232</v>
       </c>
       <c r="D40" s="5">
-        <v>46097.55025519676</v>
+        <v>46097.383588530094</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>144</v>
@@ -4226,13 +4226,13 @@
         <v>146</v>
       </c>
       <c r="B41" s="8">
-        <v>46073.76783851851</v>
+        <v>46073.60117185186</v>
       </c>
       <c r="C41" s="8">
-        <v>46097.55031997686</v>
+        <v>46097.383653310186</v>
       </c>
       <c r="D41" s="8">
-        <v>46097.550321400464</v>
+        <v>46097.3836547338</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>147</v>
@@ -4287,13 +4287,13 @@
         <v>149</v>
       </c>
       <c r="B42" s="5">
-        <v>46073.76783873842</v>
+        <v>46073.60117207176</v>
       </c>
       <c r="C42" s="5">
-        <v>46192.762426898145</v>
+        <v>46192.59576023148</v>
       </c>
       <c r="D42" s="5">
-        <v>46192.76244386574</v>
+        <v>46192.59577719907</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>150</v>
@@ -4340,13 +4340,13 @@
         <v>152</v>
       </c>
       <c r="B43" s="8">
-        <v>46073.76783896991</v>
+        <v>46073.60117230324</v>
       </c>
       <c r="C43" s="8">
-        <v>46097.81489017361</v>
+        <v>46097.64822350694</v>
       </c>
       <c r="D43" s="8">
-        <v>46097.814911249996</v>
+        <v>46097.64824458333</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>153</v>
@@ -4405,13 +4405,13 @@
         <v>157</v>
       </c>
       <c r="B44" s="5">
-        <v>46073.76783739583</v>
+        <v>46073.60117072916</v>
       </c>
       <c r="C44" s="5">
-        <v>46097.8149991088</v>
+        <v>46097.64833244213</v>
       </c>
       <c r="D44" s="5">
-        <v>46097.8150140162</v>
+        <v>46097.64834734953</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>158</v>
@@ -4470,13 +4470,13 @@
         <v>161</v>
       </c>
       <c r="B45" s="8">
-        <v>46090.4939284838</v>
+        <v>46090.32726181713</v>
       </c>
       <c r="C45" s="8">
-        <v>46097.81504469908</v>
+        <v>46097.648378032405</v>
       </c>
       <c r="D45" s="8">
-        <v>46097.815063622686</v>
+        <v>46097.64839695602</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>162</v>
@@ -4533,13 +4533,13 @@
         <v>164</v>
       </c>
       <c r="B46" s="5">
-        <v>46090.493990891206</v>
+        <v>46090.327324224534</v>
       </c>
       <c r="C46" s="5">
-        <v>46192.76206953704</v>
+        <v>46192.59540287037</v>
       </c>
       <c r="D46" s="5">
-        <v>46192.76208826389</v>
+        <v>46192.59542159722</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>165</v>
@@ -4596,13 +4596,13 @@
         <v>170</v>
       </c>
       <c r="B47" s="8">
-        <v>46128.56674524306</v>
+        <v>46128.40007857639</v>
       </c>
       <c r="C47" s="8">
-        <v>46192.761913993054</v>
+        <v>46192.59524732639</v>
       </c>
       <c r="D47" s="8">
-        <v>46192.7619153125</v>
+        <v>46192.59524864583</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>171</v>
@@ -4649,13 +4649,13 @@
         <v>173</v>
       </c>
       <c r="B48" s="5">
-        <v>46128.566755555556</v>
+        <v>46128.400088888884</v>
       </c>
       <c r="C48" s="5">
-        <v>46192.76204381944</v>
+        <v>46192.59537715278</v>
       </c>
       <c r="D48" s="5">
-        <v>46192.76205100694</v>
+        <v>46192.59538434028</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>171</v>
@@ -4702,13 +4702,13 @@
         <v>174</v>
       </c>
       <c r="B49" s="8">
-        <v>46128.56676210648</v>
+        <v>46128.400095439814</v>
       </c>
       <c r="C49" s="8">
-        <v>46192.76204465277</v>
+        <v>46192.595377986116</v>
       </c>
       <c r="D49" s="8">
-        <v>46192.76205135416</v>
+        <v>46192.595384687505</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>171</v>
@@ -4755,13 +4755,13 @@
         <v>175</v>
       </c>
       <c r="B50" s="5">
-        <v>46128.56676847222</v>
+        <v>46128.40010180556</v>
       </c>
       <c r="C50" s="5">
-        <v>46192.76204524306</v>
+        <v>46192.595378576385</v>
       </c>
       <c r="D50" s="5">
-        <v>46192.762051655096</v>
+        <v>46192.595384988424</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>176</v>
@@ -4808,13 +4808,13 @@
         <v>177</v>
       </c>
       <c r="B51" s="8">
-        <v>46128.566774120365</v>
+        <v>46128.40010745371</v>
       </c>
       <c r="C51" s="8">
-        <v>46192.76204579861</v>
+        <v>46192.59537913195</v>
       </c>
       <c r="D51" s="8">
-        <v>46192.762051990736</v>
+        <v>46192.59538532408</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>171</v>
@@ -4861,13 +4861,13 @@
         <v>178</v>
       </c>
       <c r="B52" s="5">
-        <v>46128.566780127316</v>
+        <v>46128.40011346065</v>
       </c>
       <c r="C52" s="5">
-        <v>46192.76204636574</v>
+        <v>46192.59537969907</v>
       </c>
       <c r="D52" s="5">
-        <v>46192.76205229167</v>
+        <v>46192.595385625</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>171</v>
@@ -4914,13 +4914,13 @@
         <v>179</v>
       </c>
       <c r="B53" s="8">
-        <v>46128.56678613426</v>
+        <v>46128.400119467595</v>
       </c>
       <c r="C53" s="8">
-        <v>46192.76204696759</v>
+        <v>46192.595380300925</v>
       </c>
       <c r="D53" s="8">
-        <v>46192.762052569444</v>
+        <v>46192.59538590278</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>171</v>
@@ -4967,13 +4967,13 @@
         <v>180</v>
       </c>
       <c r="B54" s="5">
-        <v>46128.566790682875</v>
+        <v>46128.4001240162</v>
       </c>
       <c r="C54" s="5">
-        <v>46192.7620475</v>
+        <v>46192.59538083333</v>
       </c>
       <c r="D54" s="5">
-        <v>46192.7620528588</v>
+        <v>46192.59538619213</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>171</v>
@@ -5020,13 +5020,13 @@
         <v>181</v>
       </c>
       <c r="B55" s="8">
-        <v>46128.5667968287</v>
+        <v>46128.40013016204</v>
       </c>
       <c r="C55" s="8">
-        <v>46192.76204800926</v>
+        <v>46192.59538134259</v>
       </c>
       <c r="D55" s="8">
-        <v>46192.76205314815</v>
+        <v>46192.59538648148</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>171</v>
@@ -5073,13 +5073,13 @@
         <v>182</v>
       </c>
       <c r="B56" s="5">
-        <v>46128.56680166667</v>
+        <v>46128.400135</v>
       </c>
       <c r="C56" s="5">
-        <v>46192.762048530094</v>
+        <v>46192.59538186343</v>
       </c>
       <c r="D56" s="5">
-        <v>46192.76205344907</v>
+        <v>46192.59538678241</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>171</v>
@@ -5126,13 +5126,13 @@
         <v>183</v>
       </c>
       <c r="B57" s="8">
-        <v>46128.566807256946</v>
+        <v>46128.40014059028</v>
       </c>
       <c r="C57" s="8">
-        <v>46192.76204903935</v>
+        <v>46192.59538237269</v>
       </c>
       <c r="D57" s="8">
-        <v>46192.762053784725</v>
+        <v>46192.59538711805</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>171</v>
@@ -5179,13 +5179,13 @@
         <v>184</v>
       </c>
       <c r="B58" s="5">
-        <v>46128.56681135416</v>
+        <v>46128.400144687505</v>
       </c>
       <c r="C58" s="5">
-        <v>46192.76204957176</v>
+        <v>46192.59538290509</v>
       </c>
       <c r="D58" s="5">
-        <v>46192.762054108796</v>
+        <v>46192.595387442125</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>171</v>
@@ -5232,13 +5232,13 @@
         <v>185</v>
       </c>
       <c r="B59" s="8">
-        <v>46073.76783778935</v>
+        <v>46073.60117112269</v>
       </c>
       <c r="C59" s="8">
-        <v>46097.815627476855</v>
+        <v>46097.648960810184</v>
       </c>
       <c r="D59" s="8">
-        <v>46097.81565780092</v>
+        <v>46097.64899113426</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>186</v>
@@ -5285,13 +5285,13 @@
         <v>188</v>
       </c>
       <c r="B60" s="5">
-        <v>46073.767838078704</v>
+        <v>46073.60117141204</v>
       </c>
       <c r="C60" s="5">
-        <v>46097.8152718287</v>
+        <v>46097.64860516204</v>
       </c>
       <c r="D60" s="5">
-        <v>46097.81529010416</v>
+        <v>46097.648623437504</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>189</v>
@@ -5350,13 +5350,13 @@
         <v>193</v>
       </c>
       <c r="B61" s="8">
-        <v>46073.7678383912</v>
+        <v>46073.60117172454</v>
       </c>
       <c r="C61" s="8">
-        <v>46097.81561164352</v>
+        <v>46097.648944976856</v>
       </c>
       <c r="D61" s="8">
-        <v>46097.81562871528</v>
+        <v>46097.64896204861</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>194</v>
@@ -5415,13 +5415,13 @@
         <v>198</v>
       </c>
       <c r="B62" s="5">
-        <v>46073.76783866898</v>
+        <v>46073.601172002316</v>
       </c>
       <c r="C62" s="5">
-        <v>46191.772903206016</v>
+        <v>46191.60623653935</v>
       </c>
       <c r="D62" s="5">
-        <v>46191.77291996528</v>
+        <v>46191.60625329861</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>199</v>
@@ -5468,13 +5468,13 @@
         <v>201</v>
       </c>
       <c r="B63" s="8">
-        <v>46073.767838935186</v>
+        <v>46073.60117226852</v>
       </c>
       <c r="C63" s="8">
-        <v>46111.806281701385</v>
+        <v>46111.63961503472</v>
       </c>
       <c r="D63" s="8">
-        <v>46128.58222162037</v>
+        <v>46128.4155549537</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>202</v>
@@ -5533,13 +5533,13 @@
         <v>206</v>
       </c>
       <c r="B64" s="5">
-        <v>46073.76783921296</v>
+        <v>46073.601172546296</v>
       </c>
       <c r="C64" s="5">
-        <v>46146.89556576389</v>
+        <v>46146.72889909722</v>
       </c>
       <c r="D64" s="5">
-        <v>46158.97116490741</v>
+        <v>46158.804498240745</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>207</v>
@@ -5598,13 +5598,13 @@
         <v>209</v>
       </c>
       <c r="B65" s="8">
-        <v>46128.56456767361</v>
+        <v>46128.397901006945</v>
       </c>
       <c r="C65" s="8">
-        <v>46129.6842038426</v>
+        <v>46129.517537175925</v>
       </c>
       <c r="D65" s="8">
-        <v>46129.68420498843</v>
+        <v>46129.51753832176</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>171</v>
@@ -5653,13 +5653,13 @@
         <v>212</v>
       </c>
       <c r="B66" s="5">
-        <v>46128.56458466435</v>
+        <v>46128.39791799769</v>
       </c>
       <c r="C66" s="5">
-        <v>46129.68421431713</v>
+        <v>46129.51754765047</v>
       </c>
       <c r="D66" s="5">
-        <v>46129.684215497684</v>
+        <v>46129.51754883102</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>171</v>
@@ -5708,13 +5708,13 @@
         <v>213</v>
       </c>
       <c r="B67" s="8">
-        <v>46128.56459681713</v>
+        <v>46128.39793015046</v>
       </c>
       <c r="C67" s="8">
-        <v>46129.68427453704</v>
+        <v>46129.517607870366</v>
       </c>
       <c r="D67" s="8">
-        <v>46129.68427572917</v>
+        <v>46129.5176090625</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>171</v>
@@ -5763,13 +5763,13 @@
         <v>214</v>
       </c>
       <c r="B68" s="5">
-        <v>46128.564601666665</v>
+        <v>46128.397935</v>
       </c>
       <c r="C68" s="5">
-        <v>46129.68422667824</v>
+        <v>46129.517560011576</v>
       </c>
       <c r="D68" s="5">
-        <v>46129.68422782407</v>
+        <v>46129.51756115741</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>171</v>
@@ -5818,13 +5818,13 @@
         <v>215</v>
       </c>
       <c r="B69" s="8">
-        <v>46128.56463256944</v>
+        <v>46128.39796590278</v>
       </c>
       <c r="C69" s="8">
-        <v>46129.68429238426</v>
+        <v>46129.51762571759</v>
       </c>
       <c r="D69" s="8">
-        <v>46129.684293784725</v>
+        <v>46129.51762711805</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>171</v>
@@ -5873,13 +5873,13 @@
         <v>216</v>
       </c>
       <c r="B70" s="5">
-        <v>46128.56464445602</v>
+        <v>46128.397977789355</v>
       </c>
       <c r="C70" s="5">
-        <v>46129.68430334491</v>
+        <v>46129.51763667824</v>
       </c>
       <c r="D70" s="5">
-        <v>46129.68430454861</v>
+        <v>46129.517637881945</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>171</v>
@@ -5928,13 +5928,13 @@
         <v>217</v>
       </c>
       <c r="B71" s="8">
-        <v>46128.56465615741</v>
+        <v>46128.39798949074</v>
       </c>
       <c r="C71" s="8">
-        <v>46146.89516018519</v>
+        <v>46146.728493518516</v>
       </c>
       <c r="D71" s="8">
-        <v>46146.89516151621</v>
+        <v>46146.728494849536</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>171</v>
@@ -5983,13 +5983,13 @@
         <v>219</v>
       </c>
       <c r="B72" s="5">
-        <v>46128.564667314815</v>
+        <v>46128.39800064814</v>
       </c>
       <c r="C72" s="5">
-        <v>46146.89517333334</v>
+        <v>46146.72850666667</v>
       </c>
       <c r="D72" s="5">
-        <v>46146.89517496528</v>
+        <v>46146.72850829861</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>171</v>
@@ -6038,13 +6038,13 @@
         <v>220</v>
       </c>
       <c r="B73" s="8">
-        <v>46128.56467849537</v>
+        <v>46128.3980118287</v>
       </c>
       <c r="C73" s="8">
-        <v>46146.89522835649</v>
+        <v>46146.728561689815</v>
       </c>
       <c r="D73" s="8">
-        <v>46146.895229745365</v>
+        <v>46146.72856307871</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>171</v>
@@ -6093,13 +6093,13 @@
         <v>221</v>
       </c>
       <c r="B74" s="5">
-        <v>46128.56469162037</v>
+        <v>46128.398024953705</v>
       </c>
       <c r="C74" s="5">
-        <v>46146.89519443287</v>
+        <v>46146.7285277662</v>
       </c>
       <c r="D74" s="5">
-        <v>46146.8951958449</v>
+        <v>46146.72852917824</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>171</v>
@@ -6148,13 +6148,13 @@
         <v>222</v>
       </c>
       <c r="B75" s="8">
-        <v>46128.5647016088</v>
+        <v>46128.39803494213</v>
       </c>
       <c r="C75" s="8">
-        <v>46146.89531295139</v>
+        <v>46146.728646284726</v>
       </c>
       <c r="D75" s="8">
-        <v>46146.8953142824</v>
+        <v>46146.728647615746</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>171</v>
@@ -6203,13 +6203,13 @@
         <v>223</v>
       </c>
       <c r="B76" s="5">
-        <v>46128.56471310185</v>
+        <v>46128.398046435184</v>
       </c>
       <c r="C76" s="5">
-        <v>46146.89532916667</v>
+        <v>46146.7286625</v>
       </c>
       <c r="D76" s="5">
-        <v>46146.895330486106</v>
+        <v>46146.72866381945</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>171</v>
@@ -6258,13 +6258,13 @@
         <v>224</v>
       </c>
       <c r="B77" s="8">
-        <v>46073.76783949074</v>
+        <v>46073.60117282407</v>
       </c>
       <c r="C77" s="8">
-        <v>46150.783820937504</v>
+        <v>46150.61715427083</v>
       </c>
       <c r="D77" s="8">
-        <v>46158.971930879634</v>
+        <v>46158.80526421296</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>225</v>
@@ -6321,13 +6321,13 @@
         <v>227</v>
       </c>
       <c r="B78" s="5">
-        <v>46128.565652731486</v>
+        <v>46128.398986064814</v>
       </c>
       <c r="C78" s="5">
-        <v>46129.685841053244</v>
+        <v>46129.51917438657</v>
       </c>
       <c r="D78" s="5">
-        <v>46129.6858422338</v>
+        <v>46129.519175567126</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>171</v>
@@ -6374,13 +6374,13 @@
         <v>229</v>
       </c>
       <c r="B79" s="8">
-        <v>46128.5656710301</v>
+        <v>46128.399004363426</v>
       </c>
       <c r="C79" s="8">
-        <v>46129.68585329861</v>
+        <v>46129.519186631944</v>
       </c>
       <c r="D79" s="8">
-        <v>46129.68585466435</v>
+        <v>46129.519187997685</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>171</v>
@@ -6427,13 +6427,13 @@
         <v>230</v>
       </c>
       <c r="B80" s="5">
-        <v>46128.56567894676</v>
+        <v>46128.39901228009</v>
       </c>
       <c r="C80" s="5">
-        <v>46129.68589530092</v>
+        <v>46129.519228634264</v>
       </c>
       <c r="D80" s="5">
-        <v>46129.68589648148</v>
+        <v>46129.51922981482</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>171</v>
@@ -6480,13 +6480,13 @@
         <v>231</v>
       </c>
       <c r="B81" s="8">
-        <v>46128.565685671296</v>
+        <v>46128.39901900463</v>
       </c>
       <c r="C81" s="8">
-        <v>46129.685909803244</v>
+        <v>46129.51924313657</v>
       </c>
       <c r="D81" s="8">
-        <v>46129.685910949076</v>
+        <v>46129.519244282405</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>171</v>
@@ -6533,13 +6533,13 @@
         <v>232</v>
       </c>
       <c r="B82" s="5">
-        <v>46128.5656928588</v>
+        <v>46128.39902619213</v>
       </c>
       <c r="C82" s="5">
-        <v>46129.68592458333</v>
+        <v>46129.51925791666</v>
       </c>
       <c r="D82" s="5">
-        <v>46129.68592581019</v>
+        <v>46129.51925914352</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>171</v>
@@ -6586,13 +6586,13 @@
         <v>233</v>
       </c>
       <c r="B83" s="8">
-        <v>46128.56569912037</v>
+        <v>46128.3990324537</v>
       </c>
       <c r="C83" s="8">
-        <v>46129.68595658564</v>
+        <v>46129.519289918986</v>
       </c>
       <c r="D83" s="8">
-        <v>46129.68595777778</v>
+        <v>46129.51929111111</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>171</v>
@@ -6639,13 +6639,13 @@
         <v>234</v>
       </c>
       <c r="B84" s="5">
-        <v>46128.56570560185</v>
+        <v>46128.39903893518</v>
       </c>
       <c r="C84" s="5">
-        <v>46146.89738783565</v>
+        <v>46146.73072116898</v>
       </c>
       <c r="D84" s="5">
-        <v>46146.897389502315</v>
+        <v>46146.73072283565</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>171</v>
@@ -6692,13 +6692,13 @@
         <v>235</v>
       </c>
       <c r="B85" s="8">
-        <v>46128.56571177083</v>
+        <v>46128.39904510417</v>
       </c>
       <c r="C85" s="8">
-        <v>46146.89739570602</v>
+        <v>46146.73072903935</v>
       </c>
       <c r="D85" s="8">
-        <v>46146.89739724537</v>
+        <v>46146.7307305787</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>171</v>
@@ -6745,13 +6745,13 @@
         <v>236</v>
       </c>
       <c r="B86" s="5">
-        <v>46128.565718275466</v>
+        <v>46128.399051608794</v>
       </c>
       <c r="C86" s="5">
-        <v>46146.897404930554</v>
+        <v>46146.73073826389</v>
       </c>
       <c r="D86" s="5">
-        <v>46146.89740662037</v>
+        <v>46146.7307399537</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>171</v>
@@ -6798,13 +6798,13 @@
         <v>237</v>
       </c>
       <c r="B87" s="8">
-        <v>46128.565725266206</v>
+        <v>46128.399058599534</v>
       </c>
       <c r="C87" s="8">
-        <v>46158.97188491898</v>
+        <v>46158.80521825231</v>
       </c>
       <c r="D87" s="8">
-        <v>46158.971886354164</v>
+        <v>46158.8052196875</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>171</v>
@@ -6851,13 +6851,13 @@
         <v>238</v>
       </c>
       <c r="B88" s="5">
-        <v>46128.56573148148</v>
+        <v>46128.39906481482</v>
       </c>
       <c r="C88" s="5">
-        <v>46158.97191256944</v>
+        <v>46158.80524590278</v>
       </c>
       <c r="D88" s="5">
-        <v>46158.971913587964</v>
+        <v>46158.8052469213</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>171</v>
@@ -6904,13 +6904,13 @@
         <v>239</v>
       </c>
       <c r="B89" s="8">
-        <v>46128.56573783565</v>
+        <v>46128.399071168984</v>
       </c>
       <c r="C89" s="8">
-        <v>46158.971925555554</v>
+        <v>46158.80525888889</v>
       </c>
       <c r="D89" s="8">
-        <v>46158.971926909726</v>
+        <v>46158.805260243054</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>171</v>
@@ -6957,13 +6957,13 @@
         <v>240</v>
       </c>
       <c r="B90" s="5">
-        <v>46073.76783978009</v>
+        <v>46073.60117311343</v>
       </c>
       <c r="C90" s="5">
-        <v>46191.79355605324</v>
+        <v>46191.62688938658</v>
       </c>
       <c r="D90" s="5">
-        <v>46191.79356716435</v>
+        <v>46191.626900497686</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>186</v>
@@ -7010,13 +7010,13 @@
         <v>242</v>
       </c>
       <c r="B91" s="8">
-        <v>46073.76784008102</v>
+        <v>46073.601173414354</v>
       </c>
       <c r="C91" s="8">
-        <v>46157.49932912037</v>
+        <v>46157.3326624537</v>
       </c>
       <c r="D91" s="8">
-        <v>46157.499330590275</v>
+        <v>46157.33266392361</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>243</v>
@@ -7073,13 +7073,13 @@
         <v>244</v>
       </c>
       <c r="B92" s="5">
-        <v>46073.7678375463</v>
+        <v>46073.60117087963</v>
       </c>
       <c r="C92" s="5">
-        <v>46191.79353944444</v>
+        <v>46191.62687277778</v>
       </c>
       <c r="D92" s="5">
-        <v>46191.79355703703</v>
+        <v>46191.626890370375</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>54</v>
@@ -7138,13 +7138,13 @@
         <v>246</v>
       </c>
       <c r="B93" s="8">
-        <v>46073.76783789352</v>
+        <v>46073.60117122685</v>
       </c>
       <c r="C93" s="8">
-        <v>46157.499181701394</v>
+        <v>46157.33251503472</v>
       </c>
       <c r="D93" s="8">
-        <v>46157.49918305555</v>
+        <v>46157.33251638889</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>247</v>
@@ -7201,13 +7201,13 @@
         <v>248</v>
       </c>
       <c r="B94" s="5">
-        <v>46073.7678381713</v>
+        <v>46073.60117150463</v>
       </c>
       <c r="C94" s="5">
-        <v>46122.65846427083</v>
+        <v>46122.49179760416</v>
       </c>
       <c r="D94" s="5">
-        <v>46122.658478576384</v>
+        <v>46122.49181190973</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>249</v>
@@ -7264,13 +7264,13 @@
         <v>251</v>
       </c>
       <c r="B95" s="8">
-        <v>46073.7678384375</v>
+        <v>46073.60117177083</v>
       </c>
       <c r="C95" s="8">
-        <v>46191.795435520835</v>
+        <v>46191.62876885416</v>
       </c>
       <c r="D95" s="8">
-        <v>46191.79544686343</v>
+        <v>46191.628780196756</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>252</v>
@@ -7317,13 +7317,13 @@
         <v>254</v>
       </c>
       <c r="B96" s="5">
-        <v>46073.76783871528</v>
+        <v>46073.60117204861</v>
       </c>
       <c r="C96" s="5">
-        <v>46191.794743819446</v>
+        <v>46191.62807715278</v>
       </c>
       <c r="D96" s="5">
-        <v>46191.79475693287</v>
+        <v>46191.628090266204</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>255</v>
@@ -7382,13 +7382,13 @@
         <v>257</v>
       </c>
       <c r="B97" s="8">
-        <v>46128.56582575232</v>
+        <v>46128.399159085646</v>
       </c>
       <c r="C97" s="8">
-        <v>46129.68866233796</v>
+        <v>46129.5219956713</v>
       </c>
       <c r="D97" s="8">
-        <v>46129.68866337963</v>
+        <v>46129.52199671297</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>171</v>
@@ -7437,13 +7437,13 @@
         <v>259</v>
       </c>
       <c r="B98" s="5">
-        <v>46128.565833877314</v>
+        <v>46128.39916721065</v>
       </c>
       <c r="C98" s="5">
-        <v>46129.688670034724</v>
+        <v>46129.52200336805</v>
       </c>
       <c r="D98" s="5">
-        <v>46129.688671157404</v>
+        <v>46129.52200449074</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>171</v>
@@ -7492,13 +7492,13 @@
         <v>260</v>
       </c>
       <c r="B99" s="8">
-        <v>46128.56583952546</v>
+        <v>46128.3991728588</v>
       </c>
       <c r="C99" s="8">
-        <v>46129.688681342595</v>
+        <v>46129.522014675924</v>
       </c>
       <c r="D99" s="8">
-        <v>46129.68868245371</v>
+        <v>46129.522015787035</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>171</v>
@@ -7547,13 +7547,13 @@
         <v>261</v>
       </c>
       <c r="B100" s="5">
-        <v>46128.56584787037</v>
+        <v>46128.3991812037</v>
       </c>
       <c r="C100" s="5">
-        <v>46129.68869200231</v>
+        <v>46129.52202533565</v>
       </c>
       <c r="D100" s="5">
-        <v>46129.688693171294</v>
+        <v>46129.52202650463</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>171</v>
@@ -7602,13 +7602,13 @@
         <v>262</v>
       </c>
       <c r="B101" s="8">
-        <v>46128.565854120374</v>
+        <v>46128.3991874537</v>
       </c>
       <c r="C101" s="8">
-        <v>46129.6887024537</v>
+        <v>46129.52203578704</v>
       </c>
       <c r="D101" s="8">
-        <v>46129.68870375</v>
+        <v>46129.522037083334</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>171</v>
@@ -7657,13 +7657,13 @@
         <v>263</v>
       </c>
       <c r="B102" s="5">
-        <v>46128.565860069444</v>
+        <v>46128.39919340277</v>
       </c>
       <c r="C102" s="5">
-        <v>46158.97490728009</v>
+        <v>46158.80824061343</v>
       </c>
       <c r="D102" s="5">
-        <v>46158.974908738426</v>
+        <v>46158.808242071755</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>171</v>
@@ -7712,13 +7712,13 @@
         <v>264</v>
       </c>
       <c r="B103" s="8">
-        <v>46128.56586609954</v>
+        <v>46128.39919943287</v>
       </c>
       <c r="C103" s="8">
-        <v>46158.97510939815</v>
+        <v>46158.80844273148</v>
       </c>
       <c r="D103" s="8">
-        <v>46158.97511034722</v>
+        <v>46158.80844368055</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>171</v>
@@ -7767,13 +7767,13 @@
         <v>265</v>
       </c>
       <c r="B104" s="5">
-        <v>46128.56587251158</v>
+        <v>46128.39920584491</v>
       </c>
       <c r="C104" s="5">
-        <v>46158.97518298611</v>
+        <v>46158.80851631945</v>
       </c>
       <c r="D104" s="5">
-        <v>46158.975184641204</v>
+        <v>46158.80851797454</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>171</v>
@@ -7822,13 +7822,13 @@
         <v>266</v>
       </c>
       <c r="B105" s="8">
-        <v>46128.56587943287</v>
+        <v>46128.399212766206</v>
       </c>
       <c r="C105" s="8">
-        <v>46191.794653784724</v>
+        <v>46191.62798711806</v>
       </c>
       <c r="D105" s="8">
-        <v>46191.79465511574</v>
+        <v>46191.62798844907</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>171</v>
@@ -7877,13 +7877,13 @@
         <v>267</v>
       </c>
       <c r="B106" s="5">
-        <v>46128.565885625</v>
+        <v>46128.39921895834</v>
       </c>
       <c r="C106" s="5">
-        <v>46191.7946603125</v>
+        <v>46191.62799364583</v>
       </c>
       <c r="D106" s="5">
-        <v>46191.79466190972</v>
+        <v>46191.627995243056</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>171</v>
@@ -7932,13 +7932,13 @@
         <v>268</v>
       </c>
       <c r="B107" s="8">
-        <v>46128.56589248843</v>
+        <v>46128.39922582176</v>
       </c>
       <c r="C107" s="8">
-        <v>46191.79466587963</v>
+        <v>46191.627999212964</v>
       </c>
       <c r="D107" s="8">
-        <v>46191.79466734953</v>
+        <v>46191.628000682875</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>171</v>
@@ -7987,13 +7987,13 @@
         <v>269</v>
       </c>
       <c r="B108" s="5">
-        <v>46128.56589891204</v>
+        <v>46128.39923224537</v>
       </c>
       <c r="C108" s="5">
-        <v>46191.79472609954</v>
+        <v>46191.62805943287</v>
       </c>
       <c r="D108" s="5">
-        <v>46191.79473116898</v>
+        <v>46191.628064502314</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>171</v>
@@ -8042,13 +8042,13 @@
         <v>270</v>
       </c>
       <c r="B109" s="8">
-        <v>46073.76783924768</v>
+        <v>46073.60117258102</v>
       </c>
       <c r="C109" s="8">
-        <v>46191.794535196765</v>
+        <v>46191.62786853009</v>
       </c>
       <c r="D109" s="8">
-        <v>46191.79454671296</v>
+        <v>46191.6278800463</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>271</v>
@@ -8105,13 +8105,13 @@
         <v>272</v>
       </c>
       <c r="B110" s="5">
-        <v>46128.565956562496</v>
+        <v>46128.39928989584</v>
       </c>
       <c r="C110" s="5">
-        <v>46157.49877814815</v>
+        <v>46157.33211148148</v>
       </c>
       <c r="D110" s="5">
-        <v>46157.498779988426</v>
+        <v>46157.332113321754</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>171</v>
@@ -8158,13 +8158,13 @@
         <v>274</v>
       </c>
       <c r="B111" s="8">
-        <v>46128.565968229166</v>
+        <v>46128.3993015625</v>
       </c>
       <c r="C111" s="8">
-        <v>46157.49878232639</v>
+        <v>46157.33211565972</v>
       </c>
       <c r="D111" s="8">
-        <v>46157.49878368055</v>
+        <v>46157.33211701389</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>171</v>
@@ -8211,13 +8211,13 @@
         <v>275</v>
       </c>
       <c r="B112" s="5">
-        <v>46128.565975833335</v>
+        <v>46128.39930916666</v>
       </c>
       <c r="C112" s="5">
-        <v>46157.49878706018</v>
+        <v>46157.33212039352</v>
       </c>
       <c r="D112" s="5">
-        <v>46157.498788240744</v>
+        <v>46157.33212157407</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>171</v>
@@ -8264,13 +8264,13 @@
         <v>276</v>
       </c>
       <c r="B113" s="8">
-        <v>46128.56598180556</v>
+        <v>46128.399315138886</v>
       </c>
       <c r="C113" s="8">
-        <v>46157.49879349537</v>
+        <v>46157.3321268287</v>
       </c>
       <c r="D113" s="8">
-        <v>46157.49879474537</v>
+        <v>46157.332128078706</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>171</v>
@@ -8317,13 +8317,13 @@
         <v>277</v>
       </c>
       <c r="B114" s="5">
-        <v>46128.56598935185</v>
+        <v>46128.39932268519</v>
       </c>
       <c r="C114" s="5">
-        <v>46157.498842939814</v>
+        <v>46157.33217627315</v>
       </c>
       <c r="D114" s="5">
-        <v>46157.49884443287</v>
+        <v>46157.332177766206</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>171</v>
@@ -8370,13 +8370,13 @@
         <v>278</v>
       </c>
       <c r="B115" s="8">
-        <v>46128.56599642361</v>
+        <v>46128.39932975694</v>
       </c>
       <c r="C115" s="8">
-        <v>46157.49879914352</v>
+        <v>46157.33213247685</v>
       </c>
       <c r="D115" s="8">
-        <v>46158.97491230324</v>
+        <v>46158.808245636574</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>171</v>
@@ -8423,13 +8423,13 @@
         <v>279</v>
       </c>
       <c r="B116" s="5">
-        <v>46128.56600287037</v>
+        <v>46128.3993362037</v>
       </c>
       <c r="C116" s="5">
-        <v>46157.49892672454</v>
+        <v>46157.33226005787</v>
       </c>
       <c r="D116" s="5">
-        <v>46158.975114155095</v>
+        <v>46158.80844748842</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>171</v>
@@ -8476,13 +8476,13 @@
         <v>280</v>
       </c>
       <c r="B117" s="8">
-        <v>46128.56600908565</v>
+        <v>46128.39934241898</v>
       </c>
       <c r="C117" s="8">
-        <v>46157.498990381944</v>
+        <v>46157.33232371528</v>
       </c>
       <c r="D117" s="8">
-        <v>46158.97518857638</v>
+        <v>46158.80852190973</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>171</v>
@@ -8529,13 +8529,13 @@
         <v>281</v>
       </c>
       <c r="B118" s="5">
-        <v>46128.566016111115</v>
+        <v>46128.399349444444</v>
       </c>
       <c r="C118" s="5">
-        <v>46191.79378611111</v>
+        <v>46191.62711944444</v>
       </c>
       <c r="D118" s="5">
-        <v>46191.794660555555</v>
+        <v>46191.62799388889</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>171</v>
@@ -8582,13 +8582,13 @@
         <v>282</v>
       </c>
       <c r="B119" s="8">
-        <v>46128.566022604165</v>
+        <v>46128.3993559375</v>
       </c>
       <c r="C119" s="8">
-        <v>46191.794240787036</v>
+        <v>46191.62757412037</v>
       </c>
       <c r="D119" s="8">
-        <v>46191.79466525463</v>
+        <v>46191.62799858797</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>171</v>
@@ -8635,13 +8635,13 @@
         <v>283</v>
       </c>
       <c r="B120" s="5">
-        <v>46128.56602967593</v>
+        <v>46128.39936300926</v>
       </c>
       <c r="C120" s="5">
-        <v>46191.794392662036</v>
+        <v>46191.62772599537</v>
       </c>
       <c r="D120" s="5">
-        <v>46191.794671875</v>
+        <v>46191.62800520833</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>171</v>
@@ -8688,13 +8688,13 @@
         <v>284</v>
       </c>
       <c r="B121" s="8">
-        <v>46128.56603574074</v>
+        <v>46128.399369074075</v>
       </c>
       <c r="C121" s="8">
-        <v>46191.794520763884</v>
+        <v>46191.62785409723</v>
       </c>
       <c r="D121" s="8">
-        <v>46191.79473787037</v>
+        <v>46191.628071203704</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>171</v>
@@ -8741,13 +8741,13 @@
         <v>285</v>
       </c>
       <c r="B122" s="5">
-        <v>46073.767839618056</v>
+        <v>46073.601172951385</v>
       </c>
       <c r="C122" s="5">
-        <v>46191.793681041665</v>
+        <v>46191.627014375</v>
       </c>
       <c r="D122" s="5">
-        <v>46191.79368314815</v>
+        <v>46191.62701648148</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>286</v>
@@ -8806,13 +8806,13 @@
         <v>287</v>
       </c>
       <c r="B123" s="8">
-        <v>46128.56608430555</v>
+        <v>46128.39941763889</v>
       </c>
       <c r="C123" s="8">
-        <v>46157.49769674768</v>
+        <v>46157.33103008102</v>
       </c>
       <c r="D123" s="8">
-        <v>46157.49878587963</v>
+        <v>46157.332119212966</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>171</v>
@@ -8861,13 +8861,13 @@
         <v>289</v>
       </c>
       <c r="B124" s="5">
-        <v>46128.56609638889</v>
+        <v>46128.39942972222</v>
       </c>
       <c r="C124" s="5">
-        <v>46157.497772268514</v>
+        <v>46157.33110560185</v>
       </c>
       <c r="D124" s="5">
-        <v>46157.49878896991</v>
+        <v>46157.33212230324</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>171</v>
@@ -8916,13 +8916,13 @@
         <v>290</v>
       </c>
       <c r="B125" s="8">
-        <v>46128.56610412037</v>
+        <v>46128.3994374537</v>
       </c>
       <c r="C125" s="8">
-        <v>46157.497836423616</v>
+        <v>46157.331169756944</v>
       </c>
       <c r="D125" s="8">
-        <v>46157.49879293982</v>
+        <v>46157.33212627315</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>171</v>
@@ -8971,13 +8971,13 @@
         <v>291</v>
       </c>
       <c r="B126" s="5">
-        <v>46128.5661109375</v>
+        <v>46128.399444270835</v>
       </c>
       <c r="C126" s="5">
-        <v>46157.49789493055</v>
+        <v>46157.33122826389</v>
       </c>
       <c r="D126" s="5">
-        <v>46157.498799560184</v>
+        <v>46157.33213289352</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>171</v>
@@ -9026,13 +9026,13 @@
         <v>292</v>
       </c>
       <c r="B127" s="8">
-        <v>46128.566116863425</v>
+        <v>46128.39945019676</v>
       </c>
       <c r="C127" s="8">
-        <v>46157.49794486111</v>
+        <v>46157.33127819444</v>
       </c>
       <c r="D127" s="8">
-        <v>46157.49885005787</v>
+        <v>46157.332183391205</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>171</v>
@@ -9081,13 +9081,13 @@
         <v>293</v>
       </c>
       <c r="B128" s="5">
-        <v>46128.566123807876</v>
+        <v>46128.399457141204</v>
       </c>
       <c r="C128" s="5">
-        <v>46157.498090312496</v>
+        <v>46157.33142364583</v>
       </c>
       <c r="D128" s="5">
-        <v>46157.4988055787</v>
+        <v>46157.33213891204</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>171</v>
@@ -9136,13 +9136,13 @@
         <v>294</v>
       </c>
       <c r="B129" s="8">
-        <v>46128.56613028936</v>
+        <v>46128.399463622685</v>
       </c>
       <c r="C129" s="8">
-        <v>46157.49817128472</v>
+        <v>46157.33150461805</v>
       </c>
       <c r="D129" s="8">
-        <v>46157.49893354166</v>
+        <v>46157.332266875004</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>171</v>
@@ -9191,13 +9191,13 @@
         <v>295</v>
       </c>
       <c r="B130" s="5">
-        <v>46128.56613681713</v>
+        <v>46128.39947015046</v>
       </c>
       <c r="C130" s="5">
-        <v>46157.4982853125</v>
+        <v>46157.33161864583</v>
       </c>
       <c r="D130" s="5">
-        <v>46157.49900008102</v>
+        <v>46157.33233341435</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>171</v>
@@ -9246,13 +9246,13 @@
         <v>296</v>
       </c>
       <c r="B131" s="8">
-        <v>46128.56614351852</v>
+        <v>46128.39947685185</v>
       </c>
       <c r="C131" s="8">
-        <v>46191.79334379629</v>
+        <v>46191.62667712963</v>
       </c>
       <c r="D131" s="8">
-        <v>46191.7937930787</v>
+        <v>46191.62712641204</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>171</v>
@@ -9301,13 +9301,13 @@
         <v>297</v>
       </c>
       <c r="B132" s="5">
-        <v>46128.56614934027</v>
+        <v>46128.399482673616</v>
       </c>
       <c r="C132" s="5">
-        <v>46191.793437546294</v>
+        <v>46191.62677087963</v>
       </c>
       <c r="D132" s="5">
-        <v>46191.79424862268</v>
+        <v>46191.62758195602</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>171</v>
@@ -9356,13 +9356,13 @@
         <v>298</v>
       </c>
       <c r="B133" s="8">
-        <v>46128.56615488426</v>
+        <v>46128.39948821759</v>
       </c>
       <c r="C133" s="8">
-        <v>46191.793505208334</v>
+        <v>46191.62683854166</v>
       </c>
       <c r="D133" s="8">
-        <v>46191.79439909723</v>
+        <v>46191.627732430556</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>171</v>
@@ -9411,13 +9411,13 @@
         <v>299</v>
       </c>
       <c r="B134" s="5">
-        <v>46128.566162083334</v>
+        <v>46128.39949541667</v>
       </c>
       <c r="C134" s="5">
-        <v>46191.79358293982</v>
+        <v>46191.62691627315</v>
       </c>
       <c r="D134" s="5">
-        <v>46191.79452946759</v>
+        <v>46191.62786280093</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>171</v>
@@ -9466,13 +9466,13 @@
         <v>300</v>
       </c>
       <c r="B135" s="8">
-        <v>46073.76783899305</v>
+        <v>46073.60117232639</v>
       </c>
       <c r="C135" s="8">
-        <v>46157.497287314814</v>
+        <v>46157.33062064815</v>
       </c>
       <c r="D135" s="8">
-        <v>46158.9753690162</v>
+        <v>46158.80870234953</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>301</v>
@@ -9529,13 +9529,13 @@
         <v>303</v>
       </c>
       <c r="B136" s="5">
-        <v>46128.56622929398</v>
+        <v>46128.39956262731</v>
       </c>
       <c r="C136" s="5">
-        <v>46129.688877824075</v>
+        <v>46129.52221115741</v>
       </c>
       <c r="D136" s="5">
-        <v>46157.49801296296</v>
+        <v>46157.3313462963</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>171</v>
@@ -9584,13 +9584,13 @@
         <v>305</v>
       </c>
       <c r="B137" s="8">
-        <v>46128.56623975694</v>
+        <v>46128.39957309028</v>
       </c>
       <c r="C137" s="8">
-        <v>46129.689167488425</v>
+        <v>46129.52250082176</v>
       </c>
       <c r="D137" s="8">
-        <v>46157.49802616898</v>
+        <v>46157.331359502314</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>171</v>
@@ -9639,13 +9639,13 @@
         <v>306</v>
       </c>
       <c r="B138" s="5">
-        <v>46128.56624731481</v>
+        <v>46128.39958064815</v>
       </c>
       <c r="C138" s="5">
-        <v>46129.68926373843</v>
+        <v>46129.52259707176</v>
       </c>
       <c r="D138" s="5">
-        <v>46157.49803459491</v>
+        <v>46157.331367928244</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>171</v>
@@ -9694,13 +9694,13 @@
         <v>307</v>
       </c>
       <c r="B139" s="8">
-        <v>46128.56625379629</v>
+        <v>46128.39958712963</v>
       </c>
       <c r="C139" s="8">
-        <v>46129.68934679398</v>
+        <v>46129.52268012732</v>
       </c>
       <c r="D139" s="8">
-        <v>46157.4980403588</v>
+        <v>46157.33137369213</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>171</v>
@@ -9749,13 +9749,13 @@
         <v>308</v>
       </c>
       <c r="B140" s="5">
-        <v>46128.56626087963</v>
+        <v>46128.39959421296</v>
       </c>
       <c r="C140" s="5">
-        <v>46129.689462615745</v>
+        <v>46129.52279594907</v>
       </c>
       <c r="D140" s="5">
-        <v>46157.49804547454</v>
+        <v>46157.33137880787</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>171</v>
@@ -9804,13 +9804,13 @@
         <v>309</v>
       </c>
       <c r="B141" s="8">
-        <v>46128.566268298615</v>
+        <v>46128.39960163194</v>
       </c>
       <c r="C141" s="8">
-        <v>46157.4969264699</v>
+        <v>46157.330259803246</v>
       </c>
       <c r="D141" s="8">
-        <v>46157.49809685185</v>
+        <v>46157.331430185186</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>171</v>
@@ -9859,13 +9859,13 @@
         <v>310</v>
       </c>
       <c r="B142" s="5">
-        <v>46128.566275324076</v>
+        <v>46128.399608657404</v>
       </c>
       <c r="C142" s="5">
-        <v>46157.49707239583</v>
+        <v>46157.33040572917</v>
       </c>
       <c r="D142" s="5">
-        <v>46157.498176423614</v>
+        <v>46157.33150975694</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>171</v>
@@ -9914,13 +9914,13 @@
         <v>311</v>
       </c>
       <c r="B143" s="8">
-        <v>46128.56628170139</v>
+        <v>46128.39961503472</v>
       </c>
       <c r="C143" s="8">
-        <v>46157.4965396412</v>
+        <v>46157.32987297454</v>
       </c>
       <c r="D143" s="8">
-        <v>46157.49829290509</v>
+        <v>46157.331626238425</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>171</v>
@@ -9969,13 +9969,13 @@
         <v>312</v>
       </c>
       <c r="B144" s="5">
-        <v>46128.56628802083</v>
+        <v>46128.39962135417</v>
       </c>
       <c r="C144" s="5">
-        <v>46157.49722258102</v>
+        <v>46157.33055591435</v>
       </c>
       <c r="D144" s="5">
-        <v>46191.793351631946</v>
+        <v>46191.626684965275</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>171</v>
@@ -10024,13 +10024,13 @@
         <v>313</v>
       </c>
       <c r="B145" s="8">
-        <v>46128.56629480324</v>
+        <v>46128.39962813657</v>
       </c>
       <c r="C145" s="8">
-        <v>46157.49736403935</v>
+        <v>46157.33069737269</v>
       </c>
       <c r="D145" s="8">
-        <v>46191.79344340278</v>
+        <v>46191.62677673611</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>171</v>
@@ -10079,13 +10079,13 @@
         <v>314</v>
       </c>
       <c r="B146" s="5">
-        <v>46128.5663033912</v>
+        <v>46128.39963672454</v>
       </c>
       <c r="C146" s="5">
-        <v>46157.49741939815</v>
+        <v>46157.33075273148</v>
       </c>
       <c r="D146" s="5">
-        <v>46191.79351224537</v>
+        <v>46191.62684557871</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>171</v>
@@ -10134,13 +10134,13 @@
         <v>315</v>
       </c>
       <c r="B147" s="8">
-        <v>46128.566309918984</v>
+        <v>46128.39964325231</v>
       </c>
       <c r="C147" s="8">
-        <v>46157.49748150463</v>
+        <v>46157.33081483796</v>
       </c>
       <c r="D147" s="8">
-        <v>46191.7935915625</v>
+        <v>46191.626924895834</v>
       </c>
       <c r="E147" s="9" t="s">
         <v>171</v>
@@ -10189,13 +10189,13 @@
         <v>316</v>
       </c>
       <c r="B148" s="5">
-        <v>46073.76784</v>
+        <v>46073.60117333333</v>
       </c>
       <c r="C148" s="5">
-        <v>46191.795175555555</v>
+        <v>46191.62850888888</v>
       </c>
       <c r="D148" s="5">
-        <v>46191.79533850694</v>
+        <v>46191.62867184028</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>317</v>
@@ -10252,13 +10252,13 @@
         <v>318</v>
       </c>
       <c r="B149" s="8">
-        <v>46128.566370555556</v>
+        <v>46128.39970388889</v>
       </c>
       <c r="C149" s="8">
-        <v>46191.79532146991</v>
+        <v>46191.62865480324</v>
       </c>
       <c r="D149" s="8">
-        <v>46191.79532310185</v>
+        <v>46191.62865643519</v>
       </c>
       <c r="E149" s="9" t="s">
         <v>171</v>
@@ -10305,13 +10305,13 @@
         <v>320</v>
       </c>
       <c r="B150" s="5">
-        <v>46128.56638481481</v>
+        <v>46128.399718148146</v>
       </c>
       <c r="C150" s="5">
-        <v>46191.79531609954</v>
+        <v>46191.62864943287</v>
       </c>
       <c r="D150" s="5">
-        <v>46191.7953178125</v>
+        <v>46191.62865114583</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>171</v>
@@ -10358,13 +10358,13 @@
         <v>321</v>
       </c>
       <c r="B151" s="8">
-        <v>46128.56639143519</v>
+        <v>46128.39972476852</v>
       </c>
       <c r="C151" s="8">
-        <v>46191.79531059028</v>
+        <v>46191.628643923614</v>
       </c>
       <c r="D151" s="8">
-        <v>46191.79531292824</v>
+        <v>46191.628646261575</v>
       </c>
       <c r="E151" s="9" t="s">
         <v>171</v>
@@ -10411,13 +10411,13 @@
         <v>322</v>
       </c>
       <c r="B152" s="5">
-        <v>46128.56639815972</v>
+        <v>46128.39973149306</v>
       </c>
       <c r="C152" s="5">
-        <v>46191.795305625</v>
+        <v>46191.62863895833</v>
       </c>
       <c r="D152" s="5">
-        <v>46191.79530751157</v>
+        <v>46191.62864084491</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>171</v>
@@ -10464,13 +10464,13 @@
         <v>324</v>
       </c>
       <c r="B153" s="8">
-        <v>46128.566405729165</v>
+        <v>46128.3997390625</v>
       </c>
       <c r="C153" s="8">
-        <v>46191.79529790509</v>
+        <v>46191.628631238425</v>
       </c>
       <c r="D153" s="8">
-        <v>46191.79530002315</v>
+        <v>46191.62863335648</v>
       </c>
       <c r="E153" s="9" t="s">
         <v>171</v>
@@ -10517,13 +10517,13 @@
         <v>325</v>
       </c>
       <c r="B154" s="5">
-        <v>46128.566412581014</v>
+        <v>46128.39974591435</v>
       </c>
       <c r="C154" s="5">
-        <v>46191.795281377315</v>
+        <v>46191.628614710644</v>
       </c>
       <c r="D154" s="5">
-        <v>46191.79528344907</v>
+        <v>46191.62861678241</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>171</v>
@@ -10570,13 +10570,13 @@
         <v>326</v>
       </c>
       <c r="B155" s="8">
-        <v>46128.56641917824</v>
+        <v>46128.39975251157</v>
       </c>
       <c r="C155" s="8">
-        <v>46191.79527634259</v>
+        <v>46191.62860967593</v>
       </c>
       <c r="D155" s="8">
-        <v>46191.79527836805</v>
+        <v>46191.62861170139</v>
       </c>
       <c r="E155" s="9" t="s">
         <v>171</v>
@@ -10623,13 +10623,13 @@
         <v>327</v>
       </c>
       <c r="B156" s="5">
-        <v>46128.566427337966</v>
+        <v>46128.399760671295</v>
       </c>
       <c r="C156" s="5">
-        <v>46191.795271967596</v>
+        <v>46191.628605300924</v>
       </c>
       <c r="D156" s="5">
-        <v>46191.79527357639</v>
+        <v>46191.628606909726</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>171</v>
@@ -10676,13 +10676,13 @@
         <v>328</v>
       </c>
       <c r="B157" s="8">
-        <v>46128.566433761574</v>
+        <v>46128.3997670949</v>
       </c>
       <c r="C157" s="8">
-        <v>46191.79526633101</v>
+        <v>46191.62859966436</v>
       </c>
       <c r="D157" s="8">
-        <v>46191.795267951384</v>
+        <v>46191.62860128473</v>
       </c>
       <c r="E157" s="9" t="s">
         <v>171</v>
@@ -10729,13 +10729,13 @@
         <v>329</v>
       </c>
       <c r="B158" s="5">
-        <v>46128.56643997685</v>
+        <v>46128.399773310186</v>
       </c>
       <c r="C158" s="5">
-        <v>46191.79526179398</v>
+        <v>46191.62859512732</v>
       </c>
       <c r="D158" s="5">
-        <v>46191.79526363426</v>
+        <v>46191.628596967596</v>
       </c>
       <c r="E158" s="6" t="s">
         <v>171</v>
@@ -10782,13 +10782,13 @@
         <v>330</v>
       </c>
       <c r="B159" s="8">
-        <v>46128.56644631944</v>
+        <v>46128.39977965278</v>
       </c>
       <c r="C159" s="8">
-        <v>46191.795253749995</v>
+        <v>46191.62858708334</v>
       </c>
       <c r="D159" s="8">
-        <v>46191.79525519676</v>
+        <v>46191.62858853009</v>
       </c>
       <c r="E159" s="9" t="s">
         <v>171</v>
@@ -10835,13 +10835,13 @@
         <v>331</v>
       </c>
       <c r="B160" s="5">
-        <v>46128.56645381944</v>
+        <v>46128.39978715278</v>
       </c>
       <c r="C160" s="5">
-        <v>46191.79524839121</v>
+        <v>46191.62858172454</v>
       </c>
       <c r="D160" s="5">
-        <v>46191.795250173614</v>
+        <v>46191.62858350694</v>
       </c>
       <c r="E160" s="6" t="s">
         <v>171</v>
@@ -10888,13 +10888,13 @@
         <v>332</v>
       </c>
       <c r="B161" s="8">
-        <v>46073.76784028935</v>
+        <v>46073.60117362269</v>
       </c>
       <c r="C161" s="8">
-        <v>46191.7954187963</v>
+        <v>46191.62875212963</v>
       </c>
       <c r="D161" s="8">
-        <v>46191.796637673615</v>
+        <v>46191.62997100694</v>
       </c>
       <c r="E161" s="9" t="s">
         <v>333</v>
@@ -10951,13 +10951,13 @@
         <v>335</v>
       </c>
       <c r="B162" s="5">
-        <v>46128.566525625</v>
+        <v>46128.399858958335</v>
       </c>
       <c r="C162" s="5">
-        <v>46191.79662097222</v>
+        <v>46191.62995430555</v>
       </c>
       <c r="D162" s="5">
-        <v>46192.76192157407</v>
+        <v>46192.595254907406</v>
       </c>
       <c r="E162" s="6" t="s">
         <v>171</v>
@@ -11004,13 +11004,13 @@
         <v>337</v>
       </c>
       <c r="B163" s="8">
-        <v>46128.566532013894</v>
+        <v>46128.39986534722</v>
       </c>
       <c r="C163" s="8">
-        <v>46191.796464733794</v>
+        <v>46191.62979806713</v>
       </c>
       <c r="D163" s="8">
-        <v>46192.76206450231</v>
+        <v>46192.59539783565</v>
       </c>
       <c r="E163" s="9" t="s">
         <v>171</v>
@@ -11057,13 +11057,13 @@
         <v>338</v>
       </c>
       <c r="B164" s="5">
-        <v>46128.566539224536</v>
+        <v>46128.39987255787</v>
       </c>
       <c r="C164" s="5">
-        <v>46191.79639053241</v>
+        <v>46191.62972386574</v>
       </c>
       <c r="D164" s="5">
-        <v>46192.76206446759</v>
+        <v>46192.59539780093</v>
       </c>
       <c r="E164" s="6" t="s">
         <v>171</v>
@@ -11110,13 +11110,13 @@
         <v>339</v>
       </c>
       <c r="B165" s="8">
-        <v>46128.56654532407</v>
+        <v>46128.39987865741</v>
       </c>
       <c r="C165" s="8">
-        <v>46191.79629663195</v>
+        <v>46191.629629965275</v>
       </c>
       <c r="D165" s="8">
-        <v>46192.76206489583</v>
+        <v>46192.59539822917</v>
       </c>
       <c r="E165" s="9" t="s">
         <v>171</v>
@@ -11163,13 +11163,13 @@
         <v>340</v>
       </c>
       <c r="B166" s="5">
-        <v>46128.566551689815</v>
+        <v>46128.399885023144</v>
       </c>
       <c r="C166" s="5">
-        <v>46191.79617204861</v>
+        <v>46191.62950538195</v>
       </c>
       <c r="D166" s="5">
-        <v>46192.76206432871</v>
+        <v>46192.59539766204</v>
       </c>
       <c r="E166" s="6" t="s">
         <v>171</v>
@@ -11216,13 +11216,13 @@
         <v>341</v>
       </c>
       <c r="B167" s="8">
-        <v>46128.56655853009</v>
+        <v>46128.399891863424</v>
       </c>
       <c r="C167" s="8">
-        <v>46191.79610912037</v>
+        <v>46191.629442453705</v>
       </c>
       <c r="D167" s="8">
-        <v>46192.76206412037</v>
+        <v>46192.595397453704</v>
       </c>
       <c r="E167" s="9" t="s">
         <v>171</v>
@@ -11269,13 +11269,13 @@
         <v>342</v>
       </c>
       <c r="B168" s="5">
-        <v>46128.56656431713</v>
+        <v>46128.399897650466</v>
       </c>
       <c r="C168" s="5">
-        <v>46191.796043587965</v>
+        <v>46191.62937692129</v>
       </c>
       <c r="D168" s="5">
-        <v>46192.762064131944</v>
+        <v>46192.59539746528</v>
       </c>
       <c r="E168" s="6" t="s">
         <v>171</v>
@@ -11322,13 +11322,13 @@
         <v>343</v>
       </c>
       <c r="B169" s="8">
-        <v>46128.56657081019</v>
+        <v>46128.399904143516</v>
       </c>
       <c r="C169" s="8">
-        <v>46191.795971342595</v>
+        <v>46191.629304675924</v>
       </c>
       <c r="D169" s="8">
-        <v>46192.762064131944</v>
+        <v>46192.59539746528</v>
       </c>
       <c r="E169" s="9" t="s">
         <v>171</v>
@@ -11375,13 +11375,13 @@
         <v>344</v>
       </c>
       <c r="B170" s="5">
-        <v>46128.56657746527</v>
+        <v>46128.39991079862</v>
       </c>
       <c r="C170" s="5">
-        <v>46191.79585572917</v>
+        <v>46191.6291890625</v>
       </c>
       <c r="D170" s="5">
-        <v>46192.76206414352</v>
+        <v>46192.59539747685</v>
       </c>
       <c r="E170" s="6" t="s">
         <v>171</v>
@@ -11428,13 +11428,13 @@
         <v>345</v>
       </c>
       <c r="B171" s="8">
-        <v>46128.566583113425</v>
+        <v>46128.39991644676</v>
       </c>
       <c r="C171" s="8">
-        <v>46191.795773958336</v>
+        <v>46191.629107291665</v>
       </c>
       <c r="D171" s="8">
-        <v>46192.76206392361</v>
+        <v>46192.59539725694</v>
       </c>
       <c r="E171" s="9" t="s">
         <v>171</v>
@@ -11481,13 +11481,13 @@
         <v>346</v>
       </c>
       <c r="B172" s="5">
-        <v>46128.56659069445</v>
+        <v>46128.39992402778</v>
       </c>
       <c r="C172" s="5">
-        <v>46191.79563440972</v>
+        <v>46191.628967743054</v>
       </c>
       <c r="D172" s="5">
-        <v>46192.76206421296</v>
+        <v>46192.5953975463</v>
       </c>
       <c r="E172" s="6" t="s">
         <v>171</v>
@@ -11534,13 +11534,13 @@
         <v>347</v>
       </c>
       <c r="B173" s="8">
-        <v>46128.56659782407</v>
+        <v>46128.39993115741</v>
       </c>
       <c r="C173" s="8">
-        <v>46191.79554900463</v>
+        <v>46191.62888233796</v>
       </c>
       <c r="D173" s="8">
-        <v>46192.762064305556</v>
+        <v>46192.595397638885</v>
       </c>
       <c r="E173" s="9" t="s">
         <v>171</v>
@@ -11587,13 +11587,13 @@
         <v>348</v>
       </c>
       <c r="B174" s="5">
-        <v>46073.767837719904</v>
+        <v>46073.60117105324</v>
       </c>
       <c r="C174" s="5">
-        <v>46193.560764988426</v>
+        <v>46193.39409832176</v>
       </c>
       <c r="D174" s="5">
-        <v>46193.561065925926</v>
+        <v>46193.394399259254</v>
       </c>
       <c r="E174" s="6" t="s">
         <v>349</v>
@@ -11640,13 +11640,13 @@
         <v>351</v>
       </c>
       <c r="B175" s="8">
-        <v>46073.76783810185</v>
+        <v>46073.601171435184</v>
       </c>
       <c r="C175" s="8">
-        <v>46193.56105240741</v>
+        <v>46193.39438574074</v>
       </c>
       <c r="D175" s="8">
-        <v>46194.709360277775</v>
+        <v>46194.54269361111</v>
       </c>
       <c r="E175" s="9" t="s">
         <v>352</v>
@@ -11705,13 +11705,13 @@
         <v>356</v>
       </c>
       <c r="B176" s="5">
-        <v>46128.56704659722</v>
+        <v>46128.40037993055</v>
       </c>
       <c r="C176" s="5">
-        <v>46194.70201375</v>
+        <v>46194.535347083336</v>
       </c>
       <c r="D176" s="5">
-        <v>46194.70208606482</v>
+        <v>46194.53541939815</v>
       </c>
       <c r="E176" s="6" t="s">
         <v>171</v>
@@ -11758,13 +11758,13 @@
         <v>358</v>
       </c>
       <c r="B177" s="8">
-        <v>46128.56705305555</v>
+        <v>46128.400386388894</v>
       </c>
       <c r="C177" s="8">
-        <v>46194.70201552083</v>
+        <v>46194.535348854166</v>
       </c>
       <c r="D177" s="8">
-        <v>46194.70208699074</v>
+        <v>46194.53542032407</v>
       </c>
       <c r="E177" s="9" t="s">
         <v>171</v>
@@ -11811,13 +11811,13 @@
         <v>359</v>
       </c>
       <c r="B178" s="5">
-        <v>46128.567060127316</v>
+        <v>46128.400393460644</v>
       </c>
       <c r="C178" s="5">
-        <v>46194.702016446754</v>
+        <v>46194.5353497801</v>
       </c>
       <c r="D178" s="5">
-        <v>46194.702087638885</v>
+        <v>46194.53542097222</v>
       </c>
       <c r="E178" s="6" t="s">
         <v>171</v>
@@ -11864,13 +11864,13 @@
         <v>360</v>
       </c>
       <c r="B179" s="8">
-        <v>46128.56706601851</v>
+        <v>46128.400399351856</v>
       </c>
       <c r="C179" s="8">
-        <v>46194.702017372685</v>
+        <v>46194.53535070602</v>
       </c>
       <c r="D179" s="8">
-        <v>46194.70208831019</v>
+        <v>46194.53542164352</v>
       </c>
       <c r="E179" s="9" t="s">
         <v>171</v>
@@ -11917,13 +11917,13 @@
         <v>361</v>
       </c>
       <c r="B180" s="5">
-        <v>46128.56707302084</v>
+        <v>46128.400406354165</v>
       </c>
       <c r="C180" s="5">
-        <v>46194.70201841435</v>
+        <v>46194.53535174769</v>
       </c>
       <c r="D180" s="5">
-        <v>46194.70208899306</v>
+        <v>46194.535422326386</v>
       </c>
       <c r="E180" s="6" t="s">
         <v>171</v>
@@ -11970,13 +11970,13 @@
         <v>362</v>
       </c>
       <c r="B181" s="8">
-        <v>46128.56708030093</v>
+        <v>46128.400413634256</v>
       </c>
       <c r="C181" s="8">
-        <v>46194.702019247685</v>
+        <v>46194.53535258102</v>
       </c>
       <c r="D181" s="8">
-        <v>46194.70208959491</v>
+        <v>46194.53542292824</v>
       </c>
       <c r="E181" s="9" t="s">
         <v>171</v>
@@ -12023,13 +12023,13 @@
         <v>363</v>
       </c>
       <c r="B182" s="5">
-        <v>46128.56708731482</v>
+        <v>46128.40042064815</v>
       </c>
       <c r="C182" s="5">
-        <v>46194.70206814815</v>
+        <v>46194.53540148148</v>
       </c>
       <c r="D182" s="5">
-        <v>46194.70209015046</v>
+        <v>46194.5354234838</v>
       </c>
       <c r="E182" s="6" t="s">
         <v>171</v>
@@ -12076,13 +12076,13 @@
         <v>364</v>
       </c>
       <c r="B183" s="8">
-        <v>46128.567094432874</v>
+        <v>46128.4004277662</v>
       </c>
       <c r="C183" s="8">
-        <v>46194.70207223379</v>
+        <v>46194.535405567134</v>
       </c>
       <c r="D183" s="8">
-        <v>46194.702090729166</v>
+        <v>46194.5354240625</v>
       </c>
       <c r="E183" s="9" t="s">
         <v>171</v>
@@ -12129,13 +12129,13 @@
         <v>366</v>
       </c>
       <c r="B184" s="5">
-        <v>46128.56710209491</v>
+        <v>46128.40043542824</v>
       </c>
       <c r="C184" s="5">
-        <v>46194.70207326389</v>
+        <v>46194.53540659722</v>
       </c>
       <c r="D184" s="5">
-        <v>46194.702091354164</v>
+        <v>46194.5354246875</v>
       </c>
       <c r="E184" s="6" t="s">
         <v>171</v>
@@ -12182,13 +12182,13 @@
         <v>367</v>
       </c>
       <c r="B185" s="8">
-        <v>46128.56710883102</v>
+        <v>46128.40044216435</v>
       </c>
       <c r="C185" s="8">
-        <v>46194.70207423611</v>
+        <v>46194.53540756945</v>
       </c>
       <c r="D185" s="8">
-        <v>46194.70209196759</v>
+        <v>46194.53542530093</v>
       </c>
       <c r="E185" s="9" t="s">
         <v>171</v>
@@ -12235,13 +12235,13 @@
         <v>368</v>
       </c>
       <c r="B186" s="5">
-        <v>46128.56711633102</v>
+        <v>46128.40044966435</v>
       </c>
       <c r="C186" s="5">
-        <v>46194.70208087963</v>
+        <v>46194.535414212965</v>
       </c>
       <c r="D186" s="5">
-        <v>46194.7020958912</v>
+        <v>46194.53542922453</v>
       </c>
       <c r="E186" s="6" t="s">
         <v>171</v>
@@ -12288,13 +12288,13 @@
         <v>369</v>
       </c>
       <c r="B187" s="8">
-        <v>46128.56712334491</v>
+        <v>46128.40045667824</v>
       </c>
       <c r="C187" s="8">
-        <v>46194.70208171297</v>
+        <v>46194.535415046295</v>
       </c>
       <c r="D187" s="8">
-        <v>46194.70209655093</v>
+        <v>46194.53542988426</v>
       </c>
       <c r="E187" s="9" t="s">
         <v>171</v>
@@ -12341,13 +12341,13 @@
         <v>370</v>
       </c>
       <c r="B188" s="5">
-        <v>46191.895071886574</v>
+        <v>46191.72840521991</v>
       </c>
       <c r="C188" s="5">
-        <v>46194.702082511576</v>
+        <v>46194.535415844904</v>
       </c>
       <c r="D188" s="5">
-        <v>46194.702097546295</v>
+        <v>46194.53543087963</v>
       </c>
       <c r="E188" s="6" t="s">
         <v>371</v>
@@ -12394,13 +12394,13 @@
         <v>372</v>
       </c>
       <c r="B189" s="8">
-        <v>46073.7678383912</v>
+        <v>46073.60117172454</v>
       </c>
       <c r="C189" s="8">
-        <v>46191.796778240736</v>
+        <v>46191.63011157408</v>
       </c>
       <c r="D189" s="8">
-        <v>46194.7453605787</v>
+        <v>46194.57869391204</v>
       </c>
       <c r="E189" s="9" t="s">
         <v>373</v>
@@ -12459,13 +12459,13 @@
         <v>374</v>
       </c>
       <c r="B190" s="5">
-        <v>46128.56718193287</v>
+        <v>46128.4005152662</v>
       </c>
       <c r="C190" s="5">
-        <v>46192.64706778935</v>
+        <v>46192.48040112268</v>
       </c>
       <c r="D190" s="5">
-        <v>46194.70885945602</v>
+        <v>46194.54219278935</v>
       </c>
       <c r="E190" s="6" t="s">
         <v>171</v>
@@ -12514,13 +12514,13 @@
         <v>376</v>
       </c>
       <c r="B191" s="8">
-        <v>46128.567190092595</v>
+        <v>46128.400523425924</v>
       </c>
       <c r="C191" s="8">
-        <v>46192.64718554398</v>
+        <v>46192.48051887732</v>
       </c>
       <c r="D191" s="8">
-        <v>46194.706768668984</v>
+        <v>46194.54010200231</v>
       </c>
       <c r="E191" s="9" t="s">
         <v>171</v>
@@ -12569,13 +12569,13 @@
         <v>377</v>
       </c>
       <c r="B192" s="5">
-        <v>46128.567196550925</v>
+        <v>46128.40052988426</v>
       </c>
       <c r="C192" s="5">
-        <v>46194.745200694444</v>
+        <v>46194.57853402778</v>
       </c>
       <c r="D192" s="5">
-        <v>46194.7452021412</v>
+        <v>46194.57853547454</v>
       </c>
       <c r="E192" s="6" t="s">
         <v>171</v>
@@ -12624,13 +12624,13 @@
         <v>378</v>
       </c>
       <c r="B193" s="8">
-        <v>46128.56720474537</v>
+        <v>46128.4005380787</v>
       </c>
       <c r="C193" s="8">
-        <v>46194.7452541088</v>
+        <v>46194.57858744213</v>
       </c>
       <c r="D193" s="8">
-        <v>46194.74525607639</v>
+        <v>46194.57858940972</v>
       </c>
       <c r="E193" s="9" t="s">
         <v>171</v>
@@ -12679,13 +12679,13 @@
         <v>379</v>
       </c>
       <c r="B194" s="5">
-        <v>46128.56721146991</v>
+        <v>46128.40054480324</v>
       </c>
       <c r="C194" s="5">
-        <v>46194.74508903935</v>
+        <v>46194.57842237268</v>
       </c>
       <c r="D194" s="5">
-        <v>46194.74509084491</v>
+        <v>46194.57842417824</v>
       </c>
       <c r="E194" s="6" t="s">
         <v>171</v>
@@ -12734,13 +12734,13 @@
         <v>380</v>
       </c>
       <c r="B195" s="8">
-        <v>46128.56721795139</v>
+        <v>46128.40055128472</v>
       </c>
       <c r="C195" s="8">
-        <v>46194.74486503472</v>
+        <v>46194.57819836806</v>
       </c>
       <c r="D195" s="8">
-        <v>46194.74486726851</v>
+        <v>46194.578200601856</v>
       </c>
       <c r="E195" s="9" t="s">
         <v>171</v>
@@ -12789,13 +12789,13 @@
         <v>381</v>
       </c>
       <c r="B196" s="5">
-        <v>46128.56722548611</v>
+        <v>46128.40055881944</v>
       </c>
       <c r="C196" s="5">
-        <v>46194.74534504629</v>
+        <v>46194.57867837963</v>
       </c>
       <c r="D196" s="5">
-        <v>46194.74534685185</v>
+        <v>46194.57868018519</v>
       </c>
       <c r="E196" s="6" t="s">
         <v>171</v>
@@ -12844,13 +12844,13 @@
         <v>382</v>
       </c>
       <c r="B197" s="8">
-        <v>46128.567233333335</v>
+        <v>46128.40056666666</v>
       </c>
       <c r="C197" s="8">
-        <v>46194.7449961574</v>
+        <v>46194.578329490745</v>
       </c>
       <c r="D197" s="8">
-        <v>46194.74499798611</v>
+        <v>46194.57833131944</v>
       </c>
       <c r="E197" s="9" t="s">
         <v>171</v>
@@ -12899,13 +12899,13 @@
         <v>383</v>
       </c>
       <c r="B198" s="5">
-        <v>46128.56724010417</v>
+        <v>46128.400573437495</v>
       </c>
       <c r="C198" s="5">
-        <v>46194.744955497685</v>
+        <v>46194.57828883102</v>
       </c>
       <c r="D198" s="5">
-        <v>46194.74495716435</v>
+        <v>46194.57829049768</v>
       </c>
       <c r="E198" s="6" t="s">
         <v>171</v>
@@ -12954,13 +12954,13 @@
         <v>384</v>
       </c>
       <c r="B199" s="8">
-        <v>46128.56724606482</v>
+        <v>46128.40057939815</v>
       </c>
       <c r="C199" s="8">
-        <v>46194.74529594908</v>
+        <v>46194.578629282405</v>
       </c>
       <c r="D199" s="8">
-        <v>46194.74529774305</v>
+        <v>46194.578631076394</v>
       </c>
       <c r="E199" s="9" t="s">
         <v>171</v>
@@ -13009,13 +13009,13 @@
         <v>385</v>
       </c>
       <c r="B200" s="5">
-        <v>46128.56725237268</v>
+        <v>46128.40058570602</v>
       </c>
       <c r="C200" s="5">
-        <v>46194.745028819445</v>
+        <v>46194.57836215278</v>
       </c>
       <c r="D200" s="5">
-        <v>46194.74503064815</v>
+        <v>46194.578363981476</v>
       </c>
       <c r="E200" s="6" t="s">
         <v>171</v>
@@ -13064,13 +13064,13 @@
         <v>386</v>
       </c>
       <c r="B201" s="8">
-        <v>46128.56725944445</v>
+        <v>46128.400592777776</v>
       </c>
       <c r="C201" s="8">
-        <v>46194.745127002316</v>
+        <v>46194.578460335644</v>
       </c>
       <c r="D201" s="8">
-        <v>46194.74512893519</v>
+        <v>46194.57846226852</v>
       </c>
       <c r="E201" s="9" t="s">
         <v>171</v>
@@ -13119,13 +13119,13 @@
         <v>387</v>
       </c>
       <c r="B202" s="5">
-        <v>46073.76783868056</v>
+        <v>46073.60117201389</v>
       </c>
       <c r="C202" s="5">
-        <v>46191.79687179398</v>
+        <v>46191.630205127316</v>
       </c>
       <c r="D202" s="5">
-        <v>46195.89050030093</v>
+        <v>46195.723833634256</v>
       </c>
       <c r="E202" s="6" t="s">
         <v>388</v>
@@ -13182,13 +13182,13 @@
         <v>389</v>
       </c>
       <c r="B203" s="8">
-        <v>46128.567313437496</v>
+        <v>46128.40064677084</v>
       </c>
       <c r="C203" s="8">
-        <v>46195.888619652775</v>
+        <v>46195.72195298611</v>
       </c>
       <c r="D203" s="8">
-        <v>46195.88862107639</v>
+        <v>46195.72195440972</v>
       </c>
       <c r="E203" s="9" t="s">
         <v>171</v>
@@ -13235,13 +13235,13 @@
         <v>391</v>
       </c>
       <c r="B204" s="5">
-        <v>46128.56732054398</v>
+        <v>46128.40065387731</v>
       </c>
       <c r="C204" s="5">
-        <v>46195.888511909725</v>
+        <v>46195.72184524305</v>
       </c>
       <c r="D204" s="5">
-        <v>46195.88851415509</v>
+        <v>46195.72184748843</v>
       </c>
       <c r="E204" s="6" t="s">
         <v>171</v>
@@ -13288,13 +13288,13 @@
         <v>392</v>
       </c>
       <c r="B205" s="8">
-        <v>46128.5673266088</v>
+        <v>46128.40065994213</v>
       </c>
       <c r="C205" s="8">
-        <v>46195.888713912034</v>
+        <v>46195.72204724537</v>
       </c>
       <c r="D205" s="8">
-        <v>46195.88871565972</v>
+        <v>46195.722048993055</v>
       </c>
       <c r="E205" s="9" t="s">
         <v>171</v>
@@ -13341,13 +13341,13 @@
         <v>393</v>
       </c>
       <c r="B206" s="5">
-        <v>46128.56733295139</v>
+        <v>46128.400666284724</v>
       </c>
       <c r="C206" s="5">
-        <v>46195.890410821754</v>
+        <v>46195.7237441551</v>
       </c>
       <c r="D206" s="5">
-        <v>46195.89041287037</v>
+        <v>46195.7237462037</v>
       </c>
       <c r="E206" s="6" t="s">
         <v>171</v>
@@ -13394,13 +13394,13 @@
         <v>394</v>
       </c>
       <c r="B207" s="8">
-        <v>46128.56733854167</v>
+        <v>46128.400671875</v>
       </c>
       <c r="C207" s="8">
-        <v>46195.89042074074</v>
+        <v>46195.723754074075</v>
       </c>
       <c r="D207" s="8">
-        <v>46195.89042275463</v>
+        <v>46195.72375608796</v>
       </c>
       <c r="E207" s="9" t="s">
         <v>171</v>
@@ -13447,13 +13447,13 @@
         <v>395</v>
       </c>
       <c r="B208" s="5">
-        <v>46128.56734518518</v>
+        <v>46128.40067851852</v>
       </c>
       <c r="C208" s="5">
-        <v>46195.89043005787</v>
+        <v>46195.7237633912</v>
       </c>
       <c r="D208" s="5">
-        <v>46195.89043167824</v>
+        <v>46195.72376501157</v>
       </c>
       <c r="E208" s="6" t="s">
         <v>171</v>
@@ -13500,13 +13500,13 @@
         <v>396</v>
       </c>
       <c r="B209" s="8">
-        <v>46128.567351770835</v>
+        <v>46128.40068510416</v>
       </c>
       <c r="C209" s="8">
-        <v>46195.89043835648</v>
+        <v>46195.723771689816</v>
       </c>
       <c r="D209" s="8">
-        <v>46195.89044037037</v>
+        <v>46195.72377370371</v>
       </c>
       <c r="E209" s="9" t="s">
         <v>171</v>
@@ -13553,13 +13553,13 @@
         <v>398</v>
       </c>
       <c r="B210" s="5">
-        <v>46128.56735738426</v>
+        <v>46128.40069071759</v>
       </c>
       <c r="C210" s="5">
-        <v>46195.8904453588</v>
+        <v>46195.72377869213</v>
       </c>
       <c r="D210" s="5">
-        <v>46195.890446805555</v>
+        <v>46195.723780138884</v>
       </c>
       <c r="E210" s="6" t="s">
         <v>171</v>
@@ -13606,13 +13606,13 @@
         <v>399</v>
       </c>
       <c r="B211" s="8">
-        <v>46128.56736256945</v>
+        <v>46128.400695902776</v>
       </c>
       <c r="C211" s="8">
-        <v>46195.890451921296</v>
+        <v>46195.72378525463</v>
       </c>
       <c r="D211" s="8">
-        <v>46195.89045333333</v>
+        <v>46195.72378666667</v>
       </c>
       <c r="E211" s="9" t="s">
         <v>171</v>
@@ -13659,13 +13659,13 @@
         <v>400</v>
       </c>
       <c r="B212" s="5">
-        <v>46128.567368206015</v>
+        <v>46128.40070153935</v>
       </c>
       <c r="C212" s="5">
-        <v>46195.890460787035</v>
+        <v>46195.72379412037</v>
       </c>
       <c r="D212" s="5">
-        <v>46195.890462361116</v>
+        <v>46195.723795694445</v>
       </c>
       <c r="E212" s="6" t="s">
         <v>171</v>
@@ -13712,13 +13712,13 @@
         <v>401</v>
       </c>
       <c r="B213" s="8">
-        <v>46128.56737366898</v>
+        <v>46128.400707002314</v>
       </c>
       <c r="C213" s="8">
-        <v>46195.89046549769</v>
+        <v>46195.72379883102</v>
       </c>
       <c r="D213" s="8">
-        <v>46195.89046699074</v>
+        <v>46195.72380032408</v>
       </c>
       <c r="E213" s="9" t="s">
         <v>171</v>
@@ -13765,13 +13765,13 @@
         <v>402</v>
       </c>
       <c r="B214" s="5">
-        <v>46128.56737853009</v>
+        <v>46128.400711863425</v>
       </c>
       <c r="C214" s="5">
-        <v>46195.89047841435</v>
+        <v>46195.72381174768</v>
       </c>
       <c r="D214" s="5">
-        <v>46195.89048138889</v>
+        <v>46195.72381472222</v>
       </c>
       <c r="E214" s="6" t="s">
         <v>171</v>
@@ -13818,13 +13818,13 @@
         <v>403</v>
       </c>
       <c r="B215" s="8">
-        <v>46073.76783895833</v>
+        <v>46073.60117229167</v>
       </c>
       <c r="C215" s="8">
-        <v>46191.79693015046</v>
+        <v>46191.63026348379</v>
       </c>
       <c r="D215" s="8">
-        <v>46195.890647175926</v>
+        <v>46195.723980509254</v>
       </c>
       <c r="E215" s="9" t="s">
         <v>404</v>
@@ -13881,13 +13881,13 @@
         <v>406</v>
       </c>
       <c r="B216" s="5">
-        <v>46128.56746619213</v>
+        <v>46128.400799525465</v>
       </c>
       <c r="C216" s="5">
-        <v>46195.890531701385</v>
+        <v>46195.72386503472</v>
       </c>
       <c r="D216" s="5">
-        <v>46195.890533206024</v>
+        <v>46195.72386653935</v>
       </c>
       <c r="E216" s="6" t="s">
         <v>171</v>
@@ -13934,13 +13934,13 @@
         <v>407</v>
       </c>
       <c r="B217" s="8">
-        <v>46128.56747375</v>
+        <v>46128.40080708334</v>
       </c>
       <c r="C217" s="8">
-        <v>46195.89053809027</v>
+        <v>46195.723871423615</v>
       </c>
       <c r="D217" s="8">
-        <v>46195.890539699074</v>
+        <v>46195.7238730324</v>
       </c>
       <c r="E217" s="9" t="s">
         <v>171</v>
@@ -13987,13 +13987,13 @@
         <v>408</v>
       </c>
       <c r="B218" s="5">
-        <v>46128.567480833335</v>
+        <v>46128.40081416667</v>
       </c>
       <c r="C218" s="5">
-        <v>46195.890545682865</v>
+        <v>46195.72387901621</v>
       </c>
       <c r="D218" s="5">
-        <v>46195.890547476854</v>
+        <v>46195.72388081018</v>
       </c>
       <c r="E218" s="6" t="s">
         <v>171</v>
@@ -14040,13 +14040,13 @@
         <v>409</v>
       </c>
       <c r="B219" s="8">
-        <v>46128.56748863426</v>
+        <v>46128.40082196759</v>
       </c>
       <c r="C219" s="8">
-        <v>46195.89055040509</v>
+        <v>46195.72388373842</v>
       </c>
       <c r="D219" s="8">
-        <v>46195.890552048615</v>
+        <v>46195.72388538194</v>
       </c>
       <c r="E219" s="9" t="s">
         <v>171</v>
@@ -14093,13 +14093,13 @@
         <v>410</v>
       </c>
       <c r="B220" s="5">
-        <v>46128.5674962037</v>
+        <v>46128.40082953704</v>
       </c>
       <c r="C220" s="5">
-        <v>46195.89055759259</v>
+        <v>46195.723890925925</v>
       </c>
       <c r="D220" s="5">
-        <v>46195.890559074076</v>
+        <v>46195.723892407404</v>
       </c>
       <c r="E220" s="6" t="s">
         <v>171</v>
@@ -14146,13 +14146,13 @@
         <v>411</v>
       </c>
       <c r="B221" s="8">
-        <v>46128.567504074075</v>
+        <v>46128.400837407404</v>
       </c>
       <c r="C221" s="8">
-        <v>46195.89058274306</v>
+        <v>46195.723916076386</v>
       </c>
       <c r="D221" s="8">
-        <v>46195.89058465278</v>
+        <v>46195.723917986106</v>
       </c>
       <c r="E221" s="9" t="s">
         <v>171</v>
@@ -14199,13 +14199,13 @@
         <v>412</v>
       </c>
       <c r="B222" s="5">
-        <v>46128.56751277778</v>
+        <v>46128.40084611111</v>
       </c>
       <c r="C222" s="5">
-        <v>46195.89056908565</v>
+        <v>46195.72390241898</v>
       </c>
       <c r="D222" s="5">
-        <v>46195.8905709838</v>
+        <v>46195.72390431713</v>
       </c>
       <c r="E222" s="6" t="s">
         <v>171</v>
@@ -14252,13 +14252,13 @@
         <v>413</v>
       </c>
       <c r="B223" s="8">
-        <v>46128.56752138889</v>
+        <v>46128.40085472222</v>
       </c>
       <c r="C223" s="8">
-        <v>46195.89059236112</v>
+        <v>46195.723925694445</v>
       </c>
       <c r="D223" s="8">
-        <v>46195.89059417824</v>
+        <v>46195.72392751157</v>
       </c>
       <c r="E223" s="9" t="s">
         <v>171</v>
@@ -14305,13 +14305,13 @@
         <v>414</v>
       </c>
       <c r="B224" s="5">
-        <v>46128.56752835648</v>
+        <v>46128.40086168981</v>
       </c>
       <c r="C224" s="5">
-        <v>46195.89060629629</v>
+        <v>46195.72393962963</v>
       </c>
       <c r="D224" s="5">
-        <v>46195.89060789352</v>
+        <v>46195.723941226854</v>
       </c>
       <c r="E224" s="6" t="s">
         <v>171</v>
@@ -14358,13 +14358,13 @@
         <v>415</v>
       </c>
       <c r="B225" s="8">
-        <v>46128.567536284725</v>
+        <v>46128.40086961805</v>
       </c>
       <c r="C225" s="8">
-        <v>46195.890615173616</v>
+        <v>46195.723948506944</v>
       </c>
       <c r="D225" s="8">
-        <v>46195.890617060184</v>
+        <v>46195.72395039352</v>
       </c>
       <c r="E225" s="9" t="s">
         <v>171</v>
@@ -14411,13 +14411,13 @@
         <v>416</v>
       </c>
       <c r="B226" s="5">
-        <v>46128.56754392361</v>
+        <v>46128.40087725694</v>
       </c>
       <c r="C226" s="5">
-        <v>46195.89062324074</v>
+        <v>46195.723956574075</v>
       </c>
       <c r="D226" s="5">
-        <v>46195.89062482639</v>
+        <v>46195.723958159724</v>
       </c>
       <c r="E226" s="6" t="s">
         <v>171</v>
@@ -14464,13 +14464,13 @@
         <v>417</v>
       </c>
       <c r="B227" s="8">
-        <v>46128.567550949076</v>
+        <v>46128.40088428241</v>
       </c>
       <c r="C227" s="8">
-        <v>46195.89063059028</v>
+        <v>46195.72396392361</v>
       </c>
       <c r="D227" s="8">
-        <v>46195.89063229167</v>
+        <v>46195.723965625</v>
       </c>
       <c r="E227" s="9" t="s">
         <v>171</v>
@@ -14517,11 +14517,11 @@
         <v>418</v>
       </c>
       <c r="B228" s="5">
-        <v>46073.76783957176</v>
+        <v>46073.601172905095</v>
       </c>
       <c r="C228" s="6"/>
       <c r="D228" s="5">
-        <v>46076.83478885417</v>
+        <v>46076.668122187504</v>
       </c>
       <c r="E228" s="6" t="s">
         <v>419</v>
@@ -14564,11 +14564,11 @@
         <v>421</v>
       </c>
       <c r="B229" s="8">
-        <v>46073.76783986111</v>
+        <v>46073.601173194445</v>
       </c>
       <c r="C229" s="9"/>
       <c r="D229" s="8">
-        <v>46191.79694986111</v>
+        <v>46191.63028319445</v>
       </c>
       <c r="E229" s="9" t="s">
         <v>422</v>
@@ -14627,11 +14627,11 @@
         <v>425</v>
       </c>
       <c r="B230" s="5">
-        <v>46073.767840127315</v>
+        <v>46073.60117346064</v>
       </c>
       <c r="C230" s="6"/>
       <c r="D230" s="5">
-        <v>46191.79695027778</v>
+        <v>46191.63028361111</v>
       </c>
       <c r="E230" s="6" t="s">
         <v>426</v>
@@ -14690,11 +14690,11 @@
         <v>428</v>
       </c>
       <c r="B231" s="8">
-        <v>46090.63839974537</v>
+        <v>46090.4717330787</v>
       </c>
       <c r="C231" s="9"/>
       <c r="D231" s="8">
-        <v>46091.862923043984</v>
+        <v>46091.69625637731</v>
       </c>
       <c r="E231" s="9" t="s">
         <v>429</v>
@@ -14739,11 +14739,11 @@
         <v>431</v>
       </c>
       <c r="B232" s="5">
-        <v>46090.638496851854</v>
+        <v>46090.47183018518</v>
       </c>
       <c r="C232" s="6"/>
       <c r="D232" s="5">
-        <v>46191.79695047454</v>
+        <v>46191.63028380787</v>
       </c>
       <c r="E232" s="6" t="s">
         <v>432</v>
@@ -14802,11 +14802,11 @@
         <v>434</v>
       </c>
       <c r="B233" s="8">
-        <v>46090.63872243055</v>
+        <v>46090.472055763894</v>
       </c>
       <c r="C233" s="9"/>
       <c r="D233" s="8">
-        <v>46100.13550428241</v>
+        <v>46099.96883761574</v>
       </c>
       <c r="E233" s="9" t="s">
         <v>435</v>

--- a/data/50001501 - EQ MIN LA HACIENDA B.xlsx
+++ b/data/50001501 - EQ MIN LA HACIENDA B.xlsx
@@ -1945,13 +1945,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46073.60117046296</v>
+        <v>46073.76783712963</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.550945428244</v>
+        <v>46092.71761209491</v>
       </c>
       <c r="D4" s="5">
-        <v>46111.63901569444</v>
+        <v>46111.80568236111</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1994,13 +1994,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46073.601170821756</v>
+        <v>46073.76783748843</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.55091653935</v>
+        <v>46092.71758320602</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.550946504634</v>
+        <v>46092.71761317129</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -2057,13 +2057,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46073.60117112269</v>
+        <v>46073.76783778935</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.550917071756</v>
+        <v>46092.71758373843</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.55094635417</v>
+        <v>46092.71761302083</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -2120,13 +2120,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46073.601171435184</v>
+        <v>46073.76783810185</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.55091751157</v>
+        <v>46092.717584178245</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.5509459375</v>
+        <v>46092.71761260417</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -2183,13 +2183,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46073.60117173611</v>
+        <v>46073.76783840278</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.550917939814</v>
+        <v>46092.71758460648</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.614902395835</v>
+        <v>46100.7815690625</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -2246,13 +2246,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46073.60117203704</v>
+        <v>46073.7678387037</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.55091853009</v>
+        <v>46092.71758519676</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.55094583333</v>
+        <v>46092.7176125</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -2309,13 +2309,13 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46073.60117233796</v>
+        <v>46073.767839004635</v>
       </c>
       <c r="C10" s="5">
-        <v>46191.72826846065</v>
+        <v>46191.89493512732</v>
       </c>
       <c r="D10" s="5">
-        <v>46191.728279710645</v>
+        <v>46191.89494637732</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -2362,13 +2362,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46073.60117267361</v>
+        <v>46073.767839340275</v>
       </c>
       <c r="C11" s="8">
-        <v>46114.35064819445</v>
+        <v>46114.51731486111</v>
       </c>
       <c r="D11" s="8">
-        <v>46114.350663425925</v>
+        <v>46114.517330092596</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -2427,13 +2427,13 @@
         <v>52</v>
       </c>
       <c r="B12" s="5">
-        <v>46073.601173020834</v>
+        <v>46073.7678396875</v>
       </c>
       <c r="C12" s="5">
-        <v>46191.72823995371</v>
+        <v>46191.89490662037</v>
       </c>
       <c r="D12" s="5">
-        <v>46191.728268946754</v>
+        <v>46191.894935613425</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2492,13 +2492,13 @@
         <v>55</v>
       </c>
       <c r="B13" s="8">
-        <v>46073.60117333333</v>
+        <v>46073.76784</v>
       </c>
       <c r="C13" s="8">
-        <v>46114.35073248843</v>
+        <v>46114.51739915509</v>
       </c>
       <c r="D13" s="8">
-        <v>46114.35074378472</v>
+        <v>46114.517410451386</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>56</v>
@@ -2545,13 +2545,13 @@
         <v>58</v>
       </c>
       <c r="B14" s="5">
-        <v>46073.60117163195</v>
+        <v>46073.76783829861</v>
       </c>
       <c r="C14" s="5">
-        <v>46097.383173055554</v>
+        <v>46097.549839722225</v>
       </c>
       <c r="D14" s="5">
-        <v>46097.38319020833</v>
+        <v>46097.549856875004</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>59</v>
@@ -2610,13 +2610,13 @@
         <v>61</v>
       </c>
       <c r="B15" s="8">
-        <v>46073.60117232639</v>
+        <v>46073.76783899305</v>
       </c>
       <c r="C15" s="8">
-        <v>46114.35038931713</v>
+        <v>46114.5170559838</v>
       </c>
       <c r="D15" s="8">
-        <v>46114.35057649306</v>
+        <v>46114.517243159724</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>62</v>
@@ -2675,13 +2675,13 @@
         <v>64</v>
       </c>
       <c r="B16" s="5">
-        <v>46073.601172662035</v>
+        <v>46073.767839328706</v>
       </c>
       <c r="C16" s="5">
-        <v>46097.38345125</v>
+        <v>46097.55011791667</v>
       </c>
       <c r="D16" s="5">
-        <v>46097.38346895833</v>
+        <v>46097.550135625</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>65</v>
@@ -2740,13 +2740,13 @@
         <v>67</v>
       </c>
       <c r="B17" s="8">
-        <v>46073.601173020834</v>
+        <v>46073.7678396875</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.35071716435</v>
+        <v>46114.517383831015</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.350732708335</v>
+        <v>46114.517399375</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>68</v>
@@ -2805,13 +2805,13 @@
         <v>71</v>
       </c>
       <c r="B18" s="5">
-        <v>46073.60117332176</v>
+        <v>46073.767839988424</v>
       </c>
       <c r="C18" s="5">
-        <v>46122.491360092594</v>
+        <v>46122.65802675926</v>
       </c>
       <c r="D18" s="5">
-        <v>46146.33018775463</v>
+        <v>46146.4968544213</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>72</v>
@@ -2858,13 +2858,13 @@
         <v>74</v>
       </c>
       <c r="B19" s="8">
-        <v>46073.60117358796</v>
+        <v>46073.76784025463</v>
       </c>
       <c r="C19" s="8">
-        <v>46114.35083560185</v>
+        <v>46114.517502268514</v>
       </c>
       <c r="D19" s="8">
-        <v>46114.35085364583</v>
+        <v>46114.517520312496</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>75</v>
@@ -2923,13 +2923,13 @@
         <v>77</v>
       </c>
       <c r="B20" s="5">
-        <v>46073.60117390046</v>
+        <v>46073.76784056713</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.38322128472</v>
+        <v>46097.54988795139</v>
       </c>
       <c r="D20" s="5">
-        <v>46097.38323788195</v>
+        <v>46097.54990454861</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>78</v>
@@ -2988,13 +2988,13 @@
         <v>80</v>
       </c>
       <c r="B21" s="8">
-        <v>46073.60117421296</v>
+        <v>46073.767840879635</v>
       </c>
       <c r="C21" s="8">
-        <v>46114.35091847222</v>
+        <v>46114.51758513889</v>
       </c>
       <c r="D21" s="8">
-        <v>46114.350934409726</v>
+        <v>46114.51760107639</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>81</v>
@@ -3053,13 +3053,13 @@
         <v>83</v>
       </c>
       <c r="B22" s="5">
-        <v>46073.601174490745</v>
+        <v>46073.76784115741</v>
       </c>
       <c r="C22" s="5">
-        <v>46122.491342291665</v>
+        <v>46122.65800895833</v>
       </c>
       <c r="D22" s="5">
-        <v>46135.264657893524</v>
+        <v>46135.43132456018</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>84</v>
@@ -3118,13 +3118,13 @@
         <v>87</v>
       </c>
       <c r="B23" s="8">
-        <v>46073.601170995375</v>
+        <v>46073.76783766204</v>
       </c>
       <c r="C23" s="8">
-        <v>46097.383514236106</v>
+        <v>46097.55018090278</v>
       </c>
       <c r="D23" s="8">
-        <v>46100.615171006946</v>
+        <v>46100.78183767361</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>88</v>
@@ -3183,13 +3183,13 @@
         <v>92</v>
       </c>
       <c r="B24" s="5">
-        <v>46114.60800928241</v>
+        <v>46114.77467594907</v>
       </c>
       <c r="C24" s="5">
-        <v>46114.609259502315</v>
+        <v>46114.77592616898</v>
       </c>
       <c r="D24" s="5">
-        <v>46114.609272870366</v>
+        <v>46114.77593953704</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>93</v>
@@ -3238,13 +3238,13 @@
         <v>94</v>
       </c>
       <c r="B25" s="8">
-        <v>46073.6011713426</v>
+        <v>46073.767838009255</v>
       </c>
       <c r="C25" s="8">
-        <v>46191.7292321875</v>
+        <v>46191.89589885417</v>
       </c>
       <c r="D25" s="8">
-        <v>46191.729270358795</v>
+        <v>46191.89593702546</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>95</v>
@@ -3291,13 +3291,13 @@
         <v>97</v>
       </c>
       <c r="B26" s="5">
-        <v>46073.601171608796</v>
+        <v>46073.76783827547</v>
       </c>
       <c r="C26" s="5">
-        <v>46114.35120774306</v>
+        <v>46114.51787440972</v>
       </c>
       <c r="D26" s="5">
-        <v>46114.35129936342</v>
+        <v>46114.51796603009</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>98</v>
@@ -3356,13 +3356,13 @@
         <v>102</v>
       </c>
       <c r="B27" s="8">
-        <v>46073.601171863425</v>
+        <v>46073.7678385301</v>
       </c>
       <c r="C27" s="8">
-        <v>46114.35108994213</v>
+        <v>46114.517756608795</v>
       </c>
       <c r="D27" s="8">
-        <v>46114.35109119213</v>
+        <v>46114.5177578588</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>103</v>
@@ -3417,13 +3417,13 @@
         <v>107</v>
       </c>
       <c r="B28" s="5">
-        <v>46073.60117212963</v>
+        <v>46073.767838796295</v>
       </c>
       <c r="C28" s="5">
-        <v>46114.351128587965</v>
+        <v>46114.51779525463</v>
       </c>
       <c r="D28" s="5">
-        <v>46114.35112994213</v>
+        <v>46114.517796608794</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>108</v>
@@ -3478,13 +3478,13 @@
         <v>110</v>
       </c>
       <c r="B29" s="8">
-        <v>46073.6011724537</v>
+        <v>46073.767839120366</v>
       </c>
       <c r="C29" s="8">
-        <v>46191.62677258102</v>
+        <v>46191.79343924769</v>
       </c>
       <c r="D29" s="8">
-        <v>46191.626788379624</v>
+        <v>46191.793455046296</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>111</v>
@@ -3543,13 +3543,13 @@
         <v>113</v>
       </c>
       <c r="B30" s="5">
-        <v>46073.60117271991</v>
+        <v>46073.76783938658</v>
       </c>
       <c r="C30" s="5">
-        <v>46114.609478032406</v>
+        <v>46114.77614469908</v>
       </c>
       <c r="D30" s="5">
-        <v>46169.68003099537</v>
+        <v>46169.84669766204</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>114</v>
@@ -3604,13 +3604,13 @@
         <v>116</v>
       </c>
       <c r="B31" s="8">
-        <v>46073.601173020834</v>
+        <v>46073.7678396875</v>
       </c>
       <c r="C31" s="8">
-        <v>46191.626756550926</v>
+        <v>46191.79342321759</v>
       </c>
       <c r="D31" s="8">
-        <v>46191.62675810185</v>
+        <v>46191.79342476852</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>117</v>
@@ -3665,13 +3665,13 @@
         <v>119</v>
       </c>
       <c r="B32" s="5">
-        <v>46073.60117363426</v>
+        <v>46073.76784030093</v>
       </c>
       <c r="C32" s="5">
-        <v>46122.49149890046</v>
+        <v>46122.65816556713</v>
       </c>
       <c r="D32" s="5">
-        <v>46122.49151211805</v>
+        <v>46122.658178784724</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>120</v>
@@ -3730,13 +3730,13 @@
         <v>122</v>
       </c>
       <c r="B33" s="8">
-        <v>46073.60117391204</v>
+        <v>46073.7678405787</v>
       </c>
       <c r="C33" s="8">
-        <v>46122.49144170139</v>
+        <v>46122.65810836805</v>
       </c>
       <c r="D33" s="8">
-        <v>46122.49144291667</v>
+        <v>46122.65810958333</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>123</v>
@@ -3791,13 +3791,13 @@
         <v>125</v>
       </c>
       <c r="B34" s="5">
-        <v>46073.60117013889</v>
+        <v>46073.76783680556</v>
       </c>
       <c r="C34" s="5">
-        <v>46122.491484467595</v>
+        <v>46122.65815113426</v>
       </c>
       <c r="D34" s="5">
-        <v>46122.49148599537</v>
+        <v>46122.658152662036</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>126</v>
@@ -3852,13 +3852,13 @@
         <v>128</v>
       </c>
       <c r="B35" s="8">
-        <v>46073.60117045139</v>
+        <v>46073.76783711805</v>
       </c>
       <c r="C35" s="8">
-        <v>46097.38336663194</v>
+        <v>46097.55003329861</v>
       </c>
       <c r="D35" s="8">
-        <v>46097.38337914352</v>
+        <v>46097.55004581019</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>129</v>
@@ -3917,13 +3917,13 @@
         <v>131</v>
       </c>
       <c r="B36" s="5">
-        <v>46073.60117072916</v>
+        <v>46073.76783739583</v>
       </c>
       <c r="C36" s="5">
-        <v>46097.383286516204</v>
+        <v>46097.54995318287</v>
       </c>
       <c r="D36" s="5">
-        <v>46097.38328805556</v>
+        <v>46097.54995472222</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>132</v>
@@ -3978,13 +3978,13 @@
         <v>134</v>
       </c>
       <c r="B37" s="8">
-        <v>46073.60117094907</v>
+        <v>46073.76783761574</v>
       </c>
       <c r="C37" s="8">
-        <v>46097.38332991899</v>
+        <v>46097.54999658564</v>
       </c>
       <c r="D37" s="8">
-        <v>46097.38333133102</v>
+        <v>46097.54999799769</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>135</v>
@@ -4039,13 +4039,13 @@
         <v>137</v>
       </c>
       <c r="B38" s="5">
-        <v>46073.60117116898</v>
+        <v>46073.76783783565</v>
       </c>
       <c r="C38" s="5">
-        <v>46097.38335193287</v>
+        <v>46097.55001859953</v>
       </c>
       <c r="D38" s="5">
-        <v>46097.38335341435</v>
+        <v>46097.55002008102</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>138</v>
@@ -4100,13 +4100,13 @@
         <v>140</v>
       </c>
       <c r="B39" s="8">
-        <v>46073.60117140046</v>
+        <v>46073.76783806713</v>
       </c>
       <c r="C39" s="8">
-        <v>46097.383667766204</v>
+        <v>46097.550334432875</v>
       </c>
       <c r="D39" s="8">
-        <v>46097.38368121527</v>
+        <v>46097.550347881945</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>141</v>
@@ -4165,13 +4165,13 @@
         <v>143</v>
       </c>
       <c r="B40" s="5">
-        <v>46073.60117163195</v>
+        <v>46073.76783829861</v>
       </c>
       <c r="C40" s="5">
-        <v>46097.38358700232</v>
+        <v>46097.55025366898</v>
       </c>
       <c r="D40" s="5">
-        <v>46097.383588530094</v>
+        <v>46097.55025519676</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>144</v>
@@ -4226,13 +4226,13 @@
         <v>146</v>
       </c>
       <c r="B41" s="8">
-        <v>46073.60117185186</v>
+        <v>46073.76783851851</v>
       </c>
       <c r="C41" s="8">
-        <v>46097.383653310186</v>
+        <v>46097.55031997686</v>
       </c>
       <c r="D41" s="8">
-        <v>46097.3836547338</v>
+        <v>46097.550321400464</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>147</v>
@@ -4287,13 +4287,13 @@
         <v>149</v>
       </c>
       <c r="B42" s="5">
-        <v>46073.60117207176</v>
+        <v>46073.76783873842</v>
       </c>
       <c r="C42" s="5">
-        <v>46192.59576023148</v>
+        <v>46192.762426898145</v>
       </c>
       <c r="D42" s="5">
-        <v>46192.59577719907</v>
+        <v>46192.76244386574</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>150</v>
@@ -4340,13 +4340,13 @@
         <v>152</v>
       </c>
       <c r="B43" s="8">
-        <v>46073.60117230324</v>
+        <v>46073.76783896991</v>
       </c>
       <c r="C43" s="8">
-        <v>46097.64822350694</v>
+        <v>46097.81489017361</v>
       </c>
       <c r="D43" s="8">
-        <v>46097.64824458333</v>
+        <v>46097.814911249996</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>153</v>
@@ -4405,13 +4405,13 @@
         <v>157</v>
       </c>
       <c r="B44" s="5">
-        <v>46073.60117072916</v>
+        <v>46073.76783739583</v>
       </c>
       <c r="C44" s="5">
-        <v>46097.64833244213</v>
+        <v>46097.8149991088</v>
       </c>
       <c r="D44" s="5">
-        <v>46097.64834734953</v>
+        <v>46097.8150140162</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>158</v>
@@ -4470,13 +4470,13 @@
         <v>161</v>
       </c>
       <c r="B45" s="8">
-        <v>46090.32726181713</v>
+        <v>46090.4939284838</v>
       </c>
       <c r="C45" s="8">
-        <v>46097.648378032405</v>
+        <v>46097.81504469908</v>
       </c>
       <c r="D45" s="8">
-        <v>46097.64839695602</v>
+        <v>46097.815063622686</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>162</v>
@@ -4533,13 +4533,13 @@
         <v>164</v>
       </c>
       <c r="B46" s="5">
-        <v>46090.327324224534</v>
+        <v>46090.493990891206</v>
       </c>
       <c r="C46" s="5">
-        <v>46192.59540287037</v>
+        <v>46192.76206953704</v>
       </c>
       <c r="D46" s="5">
-        <v>46192.59542159722</v>
+        <v>46192.76208826389</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>165</v>
@@ -4596,13 +4596,13 @@
         <v>170</v>
       </c>
       <c r="B47" s="8">
-        <v>46128.40007857639</v>
+        <v>46128.56674524306</v>
       </c>
       <c r="C47" s="8">
-        <v>46192.59524732639</v>
+        <v>46192.761913993054</v>
       </c>
       <c r="D47" s="8">
-        <v>46192.59524864583</v>
+        <v>46192.7619153125</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>171</v>
@@ -4649,13 +4649,13 @@
         <v>173</v>
       </c>
       <c r="B48" s="5">
-        <v>46128.400088888884</v>
+        <v>46128.566755555556</v>
       </c>
       <c r="C48" s="5">
-        <v>46192.59537715278</v>
+        <v>46192.76204381944</v>
       </c>
       <c r="D48" s="5">
-        <v>46192.59538434028</v>
+        <v>46192.76205100694</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>171</v>
@@ -4702,13 +4702,13 @@
         <v>174</v>
       </c>
       <c r="B49" s="8">
-        <v>46128.400095439814</v>
+        <v>46128.56676210648</v>
       </c>
       <c r="C49" s="8">
-        <v>46192.595377986116</v>
+        <v>46192.76204465277</v>
       </c>
       <c r="D49" s="8">
-        <v>46192.595384687505</v>
+        <v>46192.76205135416</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>171</v>
@@ -4755,13 +4755,13 @@
         <v>175</v>
       </c>
       <c r="B50" s="5">
-        <v>46128.40010180556</v>
+        <v>46128.56676847222</v>
       </c>
       <c r="C50" s="5">
-        <v>46192.595378576385</v>
+        <v>46192.76204524306</v>
       </c>
       <c r="D50" s="5">
-        <v>46192.595384988424</v>
+        <v>46192.762051655096</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>176</v>
@@ -4808,13 +4808,13 @@
         <v>177</v>
       </c>
       <c r="B51" s="8">
-        <v>46128.40010745371</v>
+        <v>46128.566774120365</v>
       </c>
       <c r="C51" s="8">
-        <v>46192.59537913195</v>
+        <v>46192.76204579861</v>
       </c>
       <c r="D51" s="8">
-        <v>46192.59538532408</v>
+        <v>46192.762051990736</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>171</v>
@@ -4861,13 +4861,13 @@
         <v>178</v>
       </c>
       <c r="B52" s="5">
-        <v>46128.40011346065</v>
+        <v>46128.566780127316</v>
       </c>
       <c r="C52" s="5">
-        <v>46192.59537969907</v>
+        <v>46192.76204636574</v>
       </c>
       <c r="D52" s="5">
-        <v>46192.595385625</v>
+        <v>46192.76205229167</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>171</v>
@@ -4914,13 +4914,13 @@
         <v>179</v>
       </c>
       <c r="B53" s="8">
-        <v>46128.400119467595</v>
+        <v>46128.56678613426</v>
       </c>
       <c r="C53" s="8">
-        <v>46192.595380300925</v>
+        <v>46192.76204696759</v>
       </c>
       <c r="D53" s="8">
-        <v>46192.59538590278</v>
+        <v>46192.762052569444</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>171</v>
@@ -4967,13 +4967,13 @@
         <v>180</v>
       </c>
       <c r="B54" s="5">
-        <v>46128.4001240162</v>
+        <v>46128.566790682875</v>
       </c>
       <c r="C54" s="5">
-        <v>46192.59538083333</v>
+        <v>46192.7620475</v>
       </c>
       <c r="D54" s="5">
-        <v>46192.59538619213</v>
+        <v>46192.7620528588</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>171</v>
@@ -5020,13 +5020,13 @@
         <v>181</v>
       </c>
       <c r="B55" s="8">
-        <v>46128.40013016204</v>
+        <v>46128.5667968287</v>
       </c>
       <c r="C55" s="8">
-        <v>46192.59538134259</v>
+        <v>46192.76204800926</v>
       </c>
       <c r="D55" s="8">
-        <v>46192.59538648148</v>
+        <v>46192.76205314815</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>171</v>
@@ -5073,13 +5073,13 @@
         <v>182</v>
       </c>
       <c r="B56" s="5">
-        <v>46128.400135</v>
+        <v>46128.56680166667</v>
       </c>
       <c r="C56" s="5">
-        <v>46192.59538186343</v>
+        <v>46192.762048530094</v>
       </c>
       <c r="D56" s="5">
-        <v>46192.59538678241</v>
+        <v>46192.76205344907</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>171</v>
@@ -5126,13 +5126,13 @@
         <v>183</v>
       </c>
       <c r="B57" s="8">
-        <v>46128.40014059028</v>
+        <v>46128.566807256946</v>
       </c>
       <c r="C57" s="8">
-        <v>46192.59538237269</v>
+        <v>46192.76204903935</v>
       </c>
       <c r="D57" s="8">
-        <v>46192.59538711805</v>
+        <v>46192.762053784725</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>171</v>
@@ -5179,13 +5179,13 @@
         <v>184</v>
       </c>
       <c r="B58" s="5">
-        <v>46128.400144687505</v>
+        <v>46128.56681135416</v>
       </c>
       <c r="C58" s="5">
-        <v>46192.59538290509</v>
+        <v>46192.76204957176</v>
       </c>
       <c r="D58" s="5">
-        <v>46192.595387442125</v>
+        <v>46192.762054108796</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>171</v>
@@ -5232,13 +5232,13 @@
         <v>185</v>
       </c>
       <c r="B59" s="8">
-        <v>46073.60117112269</v>
+        <v>46073.76783778935</v>
       </c>
       <c r="C59" s="8">
-        <v>46097.648960810184</v>
+        <v>46097.815627476855</v>
       </c>
       <c r="D59" s="8">
-        <v>46097.64899113426</v>
+        <v>46097.81565780092</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>186</v>
@@ -5285,13 +5285,13 @@
         <v>188</v>
       </c>
       <c r="B60" s="5">
-        <v>46073.60117141204</v>
+        <v>46073.767838078704</v>
       </c>
       <c r="C60" s="5">
-        <v>46097.64860516204</v>
+        <v>46097.8152718287</v>
       </c>
       <c r="D60" s="5">
-        <v>46097.648623437504</v>
+        <v>46097.81529010416</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>189</v>
@@ -5350,13 +5350,13 @@
         <v>193</v>
       </c>
       <c r="B61" s="8">
-        <v>46073.60117172454</v>
+        <v>46073.7678383912</v>
       </c>
       <c r="C61" s="8">
-        <v>46097.648944976856</v>
+        <v>46097.81561164352</v>
       </c>
       <c r="D61" s="8">
-        <v>46097.64896204861</v>
+        <v>46097.81562871528</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>194</v>
@@ -5415,13 +5415,13 @@
         <v>198</v>
       </c>
       <c r="B62" s="5">
-        <v>46073.601172002316</v>
+        <v>46073.76783866898</v>
       </c>
       <c r="C62" s="5">
-        <v>46191.60623653935</v>
+        <v>46191.772903206016</v>
       </c>
       <c r="D62" s="5">
-        <v>46191.60625329861</v>
+        <v>46191.77291996528</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>199</v>
@@ -5468,13 +5468,13 @@
         <v>201</v>
       </c>
       <c r="B63" s="8">
-        <v>46073.60117226852</v>
+        <v>46073.767838935186</v>
       </c>
       <c r="C63" s="8">
-        <v>46111.63961503472</v>
+        <v>46111.806281701385</v>
       </c>
       <c r="D63" s="8">
-        <v>46128.4155549537</v>
+        <v>46128.58222162037</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>202</v>
@@ -5533,13 +5533,13 @@
         <v>206</v>
       </c>
       <c r="B64" s="5">
-        <v>46073.601172546296</v>
+        <v>46073.76783921296</v>
       </c>
       <c r="C64" s="5">
-        <v>46146.72889909722</v>
+        <v>46146.89556576389</v>
       </c>
       <c r="D64" s="5">
-        <v>46158.804498240745</v>
+        <v>46158.97116490741</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>207</v>
@@ -5598,13 +5598,13 @@
         <v>209</v>
       </c>
       <c r="B65" s="8">
-        <v>46128.397901006945</v>
+        <v>46128.56456767361</v>
       </c>
       <c r="C65" s="8">
-        <v>46129.517537175925</v>
+        <v>46129.6842038426</v>
       </c>
       <c r="D65" s="8">
-        <v>46129.51753832176</v>
+        <v>46129.68420498843</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>171</v>
@@ -5653,13 +5653,13 @@
         <v>212</v>
       </c>
       <c r="B66" s="5">
-        <v>46128.39791799769</v>
+        <v>46128.56458466435</v>
       </c>
       <c r="C66" s="5">
-        <v>46129.51754765047</v>
+        <v>46129.68421431713</v>
       </c>
       <c r="D66" s="5">
-        <v>46129.51754883102</v>
+        <v>46129.684215497684</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>171</v>
@@ -5708,13 +5708,13 @@
         <v>213</v>
       </c>
       <c r="B67" s="8">
-        <v>46128.39793015046</v>
+        <v>46128.56459681713</v>
       </c>
       <c r="C67" s="8">
-        <v>46129.517607870366</v>
+        <v>46129.68427453704</v>
       </c>
       <c r="D67" s="8">
-        <v>46129.5176090625</v>
+        <v>46129.68427572917</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>171</v>
@@ -5763,13 +5763,13 @@
         <v>214</v>
       </c>
       <c r="B68" s="5">
-        <v>46128.397935</v>
+        <v>46128.564601666665</v>
       </c>
       <c r="C68" s="5">
-        <v>46129.517560011576</v>
+        <v>46129.68422667824</v>
       </c>
       <c r="D68" s="5">
-        <v>46129.51756115741</v>
+        <v>46129.68422782407</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>171</v>
@@ -5818,13 +5818,13 @@
         <v>215</v>
       </c>
       <c r="B69" s="8">
-        <v>46128.39796590278</v>
+        <v>46128.56463256944</v>
       </c>
       <c r="C69" s="8">
-        <v>46129.51762571759</v>
+        <v>46129.68429238426</v>
       </c>
       <c r="D69" s="8">
-        <v>46129.51762711805</v>
+        <v>46129.684293784725</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>171</v>
@@ -5873,13 +5873,13 @@
         <v>216</v>
       </c>
       <c r="B70" s="5">
-        <v>46128.397977789355</v>
+        <v>46128.56464445602</v>
       </c>
       <c r="C70" s="5">
-        <v>46129.51763667824</v>
+        <v>46129.68430334491</v>
       </c>
       <c r="D70" s="5">
-        <v>46129.517637881945</v>
+        <v>46129.68430454861</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>171</v>
@@ -5928,13 +5928,13 @@
         <v>217</v>
       </c>
       <c r="B71" s="8">
-        <v>46128.39798949074</v>
+        <v>46128.56465615741</v>
       </c>
       <c r="C71" s="8">
-        <v>46146.728493518516</v>
+        <v>46146.89516018519</v>
       </c>
       <c r="D71" s="8">
-        <v>46146.728494849536</v>
+        <v>46146.89516151621</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>171</v>
@@ -5983,13 +5983,13 @@
         <v>219</v>
       </c>
       <c r="B72" s="5">
-        <v>46128.39800064814</v>
+        <v>46128.564667314815</v>
       </c>
       <c r="C72" s="5">
-        <v>46146.72850666667</v>
+        <v>46146.89517333334</v>
       </c>
       <c r="D72" s="5">
-        <v>46146.72850829861</v>
+        <v>46146.89517496528</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>171</v>
@@ -6038,13 +6038,13 @@
         <v>220</v>
       </c>
       <c r="B73" s="8">
-        <v>46128.3980118287</v>
+        <v>46128.56467849537</v>
       </c>
       <c r="C73" s="8">
-        <v>46146.728561689815</v>
+        <v>46146.89522835649</v>
       </c>
       <c r="D73" s="8">
-        <v>46146.72856307871</v>
+        <v>46146.895229745365</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>171</v>
@@ -6093,13 +6093,13 @@
         <v>221</v>
       </c>
       <c r="B74" s="5">
-        <v>46128.398024953705</v>
+        <v>46128.56469162037</v>
       </c>
       <c r="C74" s="5">
-        <v>46146.7285277662</v>
+        <v>46146.89519443287</v>
       </c>
       <c r="D74" s="5">
-        <v>46146.72852917824</v>
+        <v>46146.8951958449</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>171</v>
@@ -6148,13 +6148,13 @@
         <v>222</v>
       </c>
       <c r="B75" s="8">
-        <v>46128.39803494213</v>
+        <v>46128.5647016088</v>
       </c>
       <c r="C75" s="8">
-        <v>46146.728646284726</v>
+        <v>46146.89531295139</v>
       </c>
       <c r="D75" s="8">
-        <v>46146.728647615746</v>
+        <v>46146.8953142824</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>171</v>
@@ -6203,13 +6203,13 @@
         <v>223</v>
       </c>
       <c r="B76" s="5">
-        <v>46128.398046435184</v>
+        <v>46128.56471310185</v>
       </c>
       <c r="C76" s="5">
-        <v>46146.7286625</v>
+        <v>46146.89532916667</v>
       </c>
       <c r="D76" s="5">
-        <v>46146.72866381945</v>
+        <v>46146.895330486106</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>171</v>
@@ -6258,13 +6258,13 @@
         <v>224</v>
       </c>
       <c r="B77" s="8">
-        <v>46073.60117282407</v>
+        <v>46073.76783949074</v>
       </c>
       <c r="C77" s="8">
-        <v>46150.61715427083</v>
+        <v>46150.783820937504</v>
       </c>
       <c r="D77" s="8">
-        <v>46158.80526421296</v>
+        <v>46158.971930879634</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>225</v>
@@ -6321,13 +6321,13 @@
         <v>227</v>
       </c>
       <c r="B78" s="5">
-        <v>46128.398986064814</v>
+        <v>46128.565652731486</v>
       </c>
       <c r="C78" s="5">
-        <v>46129.51917438657</v>
+        <v>46129.685841053244</v>
       </c>
       <c r="D78" s="5">
-        <v>46129.519175567126</v>
+        <v>46129.6858422338</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>171</v>
@@ -6374,13 +6374,13 @@
         <v>229</v>
       </c>
       <c r="B79" s="8">
-        <v>46128.399004363426</v>
+        <v>46128.5656710301</v>
       </c>
       <c r="C79" s="8">
-        <v>46129.519186631944</v>
+        <v>46129.68585329861</v>
       </c>
       <c r="D79" s="8">
-        <v>46129.519187997685</v>
+        <v>46129.68585466435</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>171</v>
@@ -6427,13 +6427,13 @@
         <v>230</v>
       </c>
       <c r="B80" s="5">
-        <v>46128.39901228009</v>
+        <v>46128.56567894676</v>
       </c>
       <c r="C80" s="5">
-        <v>46129.519228634264</v>
+        <v>46129.68589530092</v>
       </c>
       <c r="D80" s="5">
-        <v>46129.51922981482</v>
+        <v>46129.68589648148</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>171</v>
@@ -6480,13 +6480,13 @@
         <v>231</v>
       </c>
       <c r="B81" s="8">
-        <v>46128.39901900463</v>
+        <v>46128.565685671296</v>
       </c>
       <c r="C81" s="8">
-        <v>46129.51924313657</v>
+        <v>46129.685909803244</v>
       </c>
       <c r="D81" s="8">
-        <v>46129.519244282405</v>
+        <v>46129.685910949076</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>171</v>
@@ -6533,13 +6533,13 @@
         <v>232</v>
       </c>
       <c r="B82" s="5">
-        <v>46128.39902619213</v>
+        <v>46128.5656928588</v>
       </c>
       <c r="C82" s="5">
-        <v>46129.51925791666</v>
+        <v>46129.68592458333</v>
       </c>
       <c r="D82" s="5">
-        <v>46129.51925914352</v>
+        <v>46129.68592581019</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>171</v>
@@ -6586,13 +6586,13 @@
         <v>233</v>
       </c>
       <c r="B83" s="8">
-        <v>46128.3990324537</v>
+        <v>46128.56569912037</v>
       </c>
       <c r="C83" s="8">
-        <v>46129.519289918986</v>
+        <v>46129.68595658564</v>
       </c>
       <c r="D83" s="8">
-        <v>46129.51929111111</v>
+        <v>46129.68595777778</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>171</v>
@@ -6639,13 +6639,13 @@
         <v>234</v>
       </c>
       <c r="B84" s="5">
-        <v>46128.39903893518</v>
+        <v>46128.56570560185</v>
       </c>
       <c r="C84" s="5">
-        <v>46146.73072116898</v>
+        <v>46146.89738783565</v>
       </c>
       <c r="D84" s="5">
-        <v>46146.73072283565</v>
+        <v>46146.897389502315</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>171</v>
@@ -6692,13 +6692,13 @@
         <v>235</v>
       </c>
       <c r="B85" s="8">
-        <v>46128.39904510417</v>
+        <v>46128.56571177083</v>
       </c>
       <c r="C85" s="8">
-        <v>46146.73072903935</v>
+        <v>46146.89739570602</v>
       </c>
       <c r="D85" s="8">
-        <v>46146.7307305787</v>
+        <v>46146.89739724537</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>171</v>
@@ -6745,13 +6745,13 @@
         <v>236</v>
       </c>
       <c r="B86" s="5">
-        <v>46128.399051608794</v>
+        <v>46128.565718275466</v>
       </c>
       <c r="C86" s="5">
-        <v>46146.73073826389</v>
+        <v>46146.897404930554</v>
       </c>
       <c r="D86" s="5">
-        <v>46146.7307399537</v>
+        <v>46146.89740662037</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>171</v>
@@ -6798,13 +6798,13 @@
         <v>237</v>
       </c>
       <c r="B87" s="8">
-        <v>46128.399058599534</v>
+        <v>46128.565725266206</v>
       </c>
       <c r="C87" s="8">
-        <v>46158.80521825231</v>
+        <v>46158.97188491898</v>
       </c>
       <c r="D87" s="8">
-        <v>46158.8052196875</v>
+        <v>46158.971886354164</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>171</v>
@@ -6851,13 +6851,13 @@
         <v>238</v>
       </c>
       <c r="B88" s="5">
-        <v>46128.39906481482</v>
+        <v>46128.56573148148</v>
       </c>
       <c r="C88" s="5">
-        <v>46158.80524590278</v>
+        <v>46158.97191256944</v>
       </c>
       <c r="D88" s="5">
-        <v>46158.8052469213</v>
+        <v>46158.971913587964</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>171</v>
@@ -6904,13 +6904,13 @@
         <v>239</v>
       </c>
       <c r="B89" s="8">
-        <v>46128.399071168984</v>
+        <v>46128.56573783565</v>
       </c>
       <c r="C89" s="8">
-        <v>46158.80525888889</v>
+        <v>46158.971925555554</v>
       </c>
       <c r="D89" s="8">
-        <v>46158.805260243054</v>
+        <v>46158.971926909726</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>171</v>
@@ -6957,13 +6957,13 @@
         <v>240</v>
       </c>
       <c r="B90" s="5">
-        <v>46073.60117311343</v>
+        <v>46073.76783978009</v>
       </c>
       <c r="C90" s="5">
-        <v>46191.62688938658</v>
+        <v>46191.79355605324</v>
       </c>
       <c r="D90" s="5">
-        <v>46191.626900497686</v>
+        <v>46191.79356716435</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>186</v>
@@ -7010,13 +7010,13 @@
         <v>242</v>
       </c>
       <c r="B91" s="8">
-        <v>46073.601173414354</v>
+        <v>46073.76784008102</v>
       </c>
       <c r="C91" s="8">
-        <v>46157.3326624537</v>
+        <v>46157.49932912037</v>
       </c>
       <c r="D91" s="8">
-        <v>46157.33266392361</v>
+        <v>46157.499330590275</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>243</v>
@@ -7073,13 +7073,13 @@
         <v>244</v>
       </c>
       <c r="B92" s="5">
-        <v>46073.60117087963</v>
+        <v>46073.7678375463</v>
       </c>
       <c r="C92" s="5">
-        <v>46191.62687277778</v>
+        <v>46191.79353944444</v>
       </c>
       <c r="D92" s="5">
-        <v>46191.626890370375</v>
+        <v>46191.79355703703</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>54</v>
@@ -7138,13 +7138,13 @@
         <v>246</v>
       </c>
       <c r="B93" s="8">
-        <v>46073.60117122685</v>
+        <v>46073.76783789352</v>
       </c>
       <c r="C93" s="8">
-        <v>46157.33251503472</v>
+        <v>46157.499181701394</v>
       </c>
       <c r="D93" s="8">
-        <v>46157.33251638889</v>
+        <v>46157.49918305555</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>247</v>
@@ -7201,13 +7201,13 @@
         <v>248</v>
       </c>
       <c r="B94" s="5">
-        <v>46073.60117150463</v>
+        <v>46073.7678381713</v>
       </c>
       <c r="C94" s="5">
-        <v>46122.49179760416</v>
+        <v>46122.65846427083</v>
       </c>
       <c r="D94" s="5">
-        <v>46122.49181190973</v>
+        <v>46122.658478576384</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>249</v>
@@ -7264,13 +7264,13 @@
         <v>251</v>
       </c>
       <c r="B95" s="8">
-        <v>46073.60117177083</v>
+        <v>46073.7678384375</v>
       </c>
       <c r="C95" s="8">
-        <v>46191.62876885416</v>
+        <v>46191.795435520835</v>
       </c>
       <c r="D95" s="8">
-        <v>46191.628780196756</v>
+        <v>46191.79544686343</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>252</v>
@@ -7317,13 +7317,13 @@
         <v>254</v>
       </c>
       <c r="B96" s="5">
-        <v>46073.60117204861</v>
+        <v>46073.76783871528</v>
       </c>
       <c r="C96" s="5">
-        <v>46191.62807715278</v>
+        <v>46191.794743819446</v>
       </c>
       <c r="D96" s="5">
-        <v>46191.628090266204</v>
+        <v>46191.79475693287</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>255</v>
@@ -7382,13 +7382,13 @@
         <v>257</v>
       </c>
       <c r="B97" s="8">
-        <v>46128.399159085646</v>
+        <v>46128.56582575232</v>
       </c>
       <c r="C97" s="8">
-        <v>46129.5219956713</v>
+        <v>46129.68866233796</v>
       </c>
       <c r="D97" s="8">
-        <v>46129.52199671297</v>
+        <v>46129.68866337963</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>171</v>
@@ -7437,13 +7437,13 @@
         <v>259</v>
       </c>
       <c r="B98" s="5">
-        <v>46128.39916721065</v>
+        <v>46128.565833877314</v>
       </c>
       <c r="C98" s="5">
-        <v>46129.52200336805</v>
+        <v>46129.688670034724</v>
       </c>
       <c r="D98" s="5">
-        <v>46129.52200449074</v>
+        <v>46129.688671157404</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>171</v>
@@ -7492,13 +7492,13 @@
         <v>260</v>
       </c>
       <c r="B99" s="8">
-        <v>46128.3991728588</v>
+        <v>46128.56583952546</v>
       </c>
       <c r="C99" s="8">
-        <v>46129.522014675924</v>
+        <v>46129.688681342595</v>
       </c>
       <c r="D99" s="8">
-        <v>46129.522015787035</v>
+        <v>46129.68868245371</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>171</v>
@@ -7547,13 +7547,13 @@
         <v>261</v>
       </c>
       <c r="B100" s="5">
-        <v>46128.3991812037</v>
+        <v>46128.56584787037</v>
       </c>
       <c r="C100" s="5">
-        <v>46129.52202533565</v>
+        <v>46129.68869200231</v>
       </c>
       <c r="D100" s="5">
-        <v>46129.52202650463</v>
+        <v>46129.688693171294</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>171</v>
@@ -7602,13 +7602,13 @@
         <v>262</v>
       </c>
       <c r="B101" s="8">
-        <v>46128.3991874537</v>
+        <v>46128.565854120374</v>
       </c>
       <c r="C101" s="8">
-        <v>46129.52203578704</v>
+        <v>46129.6887024537</v>
       </c>
       <c r="D101" s="8">
-        <v>46129.522037083334</v>
+        <v>46129.68870375</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>171</v>
@@ -7657,13 +7657,13 @@
         <v>263</v>
       </c>
       <c r="B102" s="5">
-        <v>46128.39919340277</v>
+        <v>46128.565860069444</v>
       </c>
       <c r="C102" s="5">
-        <v>46158.80824061343</v>
+        <v>46158.97490728009</v>
       </c>
       <c r="D102" s="5">
-        <v>46158.808242071755</v>
+        <v>46158.974908738426</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>171</v>
@@ -7712,13 +7712,13 @@
         <v>264</v>
       </c>
       <c r="B103" s="8">
-        <v>46128.39919943287</v>
+        <v>46128.56586609954</v>
       </c>
       <c r="C103" s="8">
-        <v>46158.80844273148</v>
+        <v>46158.97510939815</v>
       </c>
       <c r="D103" s="8">
-        <v>46158.80844368055</v>
+        <v>46158.97511034722</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>171</v>
@@ -7767,13 +7767,13 @@
         <v>265</v>
       </c>
       <c r="B104" s="5">
-        <v>46128.39920584491</v>
+        <v>46128.56587251158</v>
       </c>
       <c r="C104" s="5">
-        <v>46158.80851631945</v>
+        <v>46158.97518298611</v>
       </c>
       <c r="D104" s="5">
-        <v>46158.80851797454</v>
+        <v>46158.975184641204</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>171</v>
@@ -7822,13 +7822,13 @@
         <v>266</v>
       </c>
       <c r="B105" s="8">
-        <v>46128.399212766206</v>
+        <v>46128.56587943287</v>
       </c>
       <c r="C105" s="8">
-        <v>46191.62798711806</v>
+        <v>46191.794653784724</v>
       </c>
       <c r="D105" s="8">
-        <v>46191.62798844907</v>
+        <v>46191.79465511574</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>171</v>
@@ -7877,13 +7877,13 @@
         <v>267</v>
       </c>
       <c r="B106" s="5">
-        <v>46128.39921895834</v>
+        <v>46128.565885625</v>
       </c>
       <c r="C106" s="5">
-        <v>46191.62799364583</v>
+        <v>46191.7946603125</v>
       </c>
       <c r="D106" s="5">
-        <v>46191.627995243056</v>
+        <v>46191.79466190972</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>171</v>
@@ -7932,13 +7932,13 @@
         <v>268</v>
       </c>
       <c r="B107" s="8">
-        <v>46128.39922582176</v>
+        <v>46128.56589248843</v>
       </c>
       <c r="C107" s="8">
-        <v>46191.627999212964</v>
+        <v>46191.79466587963</v>
       </c>
       <c r="D107" s="8">
-        <v>46191.628000682875</v>
+        <v>46191.79466734953</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>171</v>
@@ -7987,13 +7987,13 @@
         <v>269</v>
       </c>
       <c r="B108" s="5">
-        <v>46128.39923224537</v>
+        <v>46128.56589891204</v>
       </c>
       <c r="C108" s="5">
-        <v>46191.62805943287</v>
+        <v>46191.79472609954</v>
       </c>
       <c r="D108" s="5">
-        <v>46191.628064502314</v>
+        <v>46191.79473116898</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>171</v>
@@ -8042,13 +8042,13 @@
         <v>270</v>
       </c>
       <c r="B109" s="8">
-        <v>46073.60117258102</v>
+        <v>46073.76783924768</v>
       </c>
       <c r="C109" s="8">
-        <v>46191.62786853009</v>
+        <v>46191.794535196765</v>
       </c>
       <c r="D109" s="8">
-        <v>46191.6278800463</v>
+        <v>46191.79454671296</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>271</v>
@@ -8105,13 +8105,13 @@
         <v>272</v>
       </c>
       <c r="B110" s="5">
-        <v>46128.39928989584</v>
+        <v>46128.565956562496</v>
       </c>
       <c r="C110" s="5">
-        <v>46157.33211148148</v>
+        <v>46157.49877814815</v>
       </c>
       <c r="D110" s="5">
-        <v>46157.332113321754</v>
+        <v>46157.498779988426</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>171</v>
@@ -8158,13 +8158,13 @@
         <v>274</v>
       </c>
       <c r="B111" s="8">
-        <v>46128.3993015625</v>
+        <v>46128.565968229166</v>
       </c>
       <c r="C111" s="8">
-        <v>46157.33211565972</v>
+        <v>46157.49878232639</v>
       </c>
       <c r="D111" s="8">
-        <v>46157.33211701389</v>
+        <v>46157.49878368055</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>171</v>
@@ -8211,13 +8211,13 @@
         <v>275</v>
       </c>
       <c r="B112" s="5">
-        <v>46128.39930916666</v>
+        <v>46128.565975833335</v>
       </c>
       <c r="C112" s="5">
-        <v>46157.33212039352</v>
+        <v>46157.49878706018</v>
       </c>
       <c r="D112" s="5">
-        <v>46157.33212157407</v>
+        <v>46157.498788240744</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>171</v>
@@ -8264,13 +8264,13 @@
         <v>276</v>
       </c>
       <c r="B113" s="8">
-        <v>46128.399315138886</v>
+        <v>46128.56598180556</v>
       </c>
       <c r="C113" s="8">
-        <v>46157.3321268287</v>
+        <v>46157.49879349537</v>
       </c>
       <c r="D113" s="8">
-        <v>46157.332128078706</v>
+        <v>46157.49879474537</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>171</v>
@@ -8317,13 +8317,13 @@
         <v>277</v>
       </c>
       <c r="B114" s="5">
-        <v>46128.39932268519</v>
+        <v>46128.56598935185</v>
       </c>
       <c r="C114" s="5">
-        <v>46157.33217627315</v>
+        <v>46157.498842939814</v>
       </c>
       <c r="D114" s="5">
-        <v>46157.332177766206</v>
+        <v>46157.49884443287</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>171</v>
@@ -8370,13 +8370,13 @@
         <v>278</v>
       </c>
       <c r="B115" s="8">
-        <v>46128.39932975694</v>
+        <v>46128.56599642361</v>
       </c>
       <c r="C115" s="8">
-        <v>46157.33213247685</v>
+        <v>46157.49879914352</v>
       </c>
       <c r="D115" s="8">
-        <v>46158.808245636574</v>
+        <v>46158.97491230324</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>171</v>
@@ -8423,13 +8423,13 @@
         <v>279</v>
       </c>
       <c r="B116" s="5">
-        <v>46128.3993362037</v>
+        <v>46128.56600287037</v>
       </c>
       <c r="C116" s="5">
-        <v>46157.33226005787</v>
+        <v>46157.49892672454</v>
       </c>
       <c r="D116" s="5">
-        <v>46158.80844748842</v>
+        <v>46158.975114155095</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>171</v>
@@ -8476,13 +8476,13 @@
         <v>280</v>
       </c>
       <c r="B117" s="8">
-        <v>46128.39934241898</v>
+        <v>46128.56600908565</v>
       </c>
       <c r="C117" s="8">
-        <v>46157.33232371528</v>
+        <v>46157.498990381944</v>
       </c>
       <c r="D117" s="8">
-        <v>46158.80852190973</v>
+        <v>46158.97518857638</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>171</v>
@@ -8529,13 +8529,13 @@
         <v>281</v>
       </c>
       <c r="B118" s="5">
-        <v>46128.399349444444</v>
+        <v>46128.566016111115</v>
       </c>
       <c r="C118" s="5">
-        <v>46191.62711944444</v>
+        <v>46191.79378611111</v>
       </c>
       <c r="D118" s="5">
-        <v>46191.62799388889</v>
+        <v>46191.794660555555</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>171</v>
@@ -8582,13 +8582,13 @@
         <v>282</v>
       </c>
       <c r="B119" s="8">
-        <v>46128.3993559375</v>
+        <v>46128.566022604165</v>
       </c>
       <c r="C119" s="8">
-        <v>46191.62757412037</v>
+        <v>46191.794240787036</v>
       </c>
       <c r="D119" s="8">
-        <v>46191.62799858797</v>
+        <v>46191.79466525463</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>171</v>
@@ -8635,13 +8635,13 @@
         <v>283</v>
       </c>
       <c r="B120" s="5">
-        <v>46128.39936300926</v>
+        <v>46128.56602967593</v>
       </c>
       <c r="C120" s="5">
-        <v>46191.62772599537</v>
+        <v>46191.794392662036</v>
       </c>
       <c r="D120" s="5">
-        <v>46191.62800520833</v>
+        <v>46191.794671875</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>171</v>
@@ -8688,13 +8688,13 @@
         <v>284</v>
       </c>
       <c r="B121" s="8">
-        <v>46128.399369074075</v>
+        <v>46128.56603574074</v>
       </c>
       <c r="C121" s="8">
-        <v>46191.62785409723</v>
+        <v>46191.794520763884</v>
       </c>
       <c r="D121" s="8">
-        <v>46191.628071203704</v>
+        <v>46191.79473787037</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>171</v>
@@ -8741,13 +8741,13 @@
         <v>285</v>
       </c>
       <c r="B122" s="5">
-        <v>46073.601172951385</v>
+        <v>46073.767839618056</v>
       </c>
       <c r="C122" s="5">
-        <v>46191.627014375</v>
+        <v>46191.793681041665</v>
       </c>
       <c r="D122" s="5">
-        <v>46191.62701648148</v>
+        <v>46191.79368314815</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>286</v>
@@ -8806,13 +8806,13 @@
         <v>287</v>
       </c>
       <c r="B123" s="8">
-        <v>46128.39941763889</v>
+        <v>46128.56608430555</v>
       </c>
       <c r="C123" s="8">
-        <v>46157.33103008102</v>
+        <v>46157.49769674768</v>
       </c>
       <c r="D123" s="8">
-        <v>46157.332119212966</v>
+        <v>46157.49878587963</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>171</v>
@@ -8861,13 +8861,13 @@
         <v>289</v>
       </c>
       <c r="B124" s="5">
-        <v>46128.39942972222</v>
+        <v>46128.56609638889</v>
       </c>
       <c r="C124" s="5">
-        <v>46157.33110560185</v>
+        <v>46157.497772268514</v>
       </c>
       <c r="D124" s="5">
-        <v>46157.33212230324</v>
+        <v>46157.49878896991</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>171</v>
@@ -8916,13 +8916,13 @@
         <v>290</v>
       </c>
       <c r="B125" s="8">
-        <v>46128.3994374537</v>
+        <v>46128.56610412037</v>
       </c>
       <c r="C125" s="8">
-        <v>46157.331169756944</v>
+        <v>46157.497836423616</v>
       </c>
       <c r="D125" s="8">
-        <v>46157.33212627315</v>
+        <v>46157.49879293982</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>171</v>
@@ -8971,13 +8971,13 @@
         <v>291</v>
       </c>
       <c r="B126" s="5">
-        <v>46128.399444270835</v>
+        <v>46128.5661109375</v>
       </c>
       <c r="C126" s="5">
-        <v>46157.33122826389</v>
+        <v>46157.49789493055</v>
       </c>
       <c r="D126" s="5">
-        <v>46157.33213289352</v>
+        <v>46157.498799560184</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>171</v>
@@ -9026,13 +9026,13 @@
         <v>292</v>
       </c>
       <c r="B127" s="8">
-        <v>46128.39945019676</v>
+        <v>46128.566116863425</v>
       </c>
       <c r="C127" s="8">
-        <v>46157.33127819444</v>
+        <v>46157.49794486111</v>
       </c>
       <c r="D127" s="8">
-        <v>46157.332183391205</v>
+        <v>46157.49885005787</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>171</v>
@@ -9081,13 +9081,13 @@
         <v>293</v>
       </c>
       <c r="B128" s="5">
-        <v>46128.399457141204</v>
+        <v>46128.566123807876</v>
       </c>
       <c r="C128" s="5">
-        <v>46157.33142364583</v>
+        <v>46157.498090312496</v>
       </c>
       <c r="D128" s="5">
-        <v>46157.33213891204</v>
+        <v>46157.4988055787</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>171</v>
@@ -9136,13 +9136,13 @@
         <v>294</v>
       </c>
       <c r="B129" s="8">
-        <v>46128.399463622685</v>
+        <v>46128.56613028936</v>
       </c>
       <c r="C129" s="8">
-        <v>46157.33150461805</v>
+        <v>46157.49817128472</v>
       </c>
       <c r="D129" s="8">
-        <v>46157.332266875004</v>
+        <v>46157.49893354166</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>171</v>
@@ -9191,13 +9191,13 @@
         <v>295</v>
       </c>
       <c r="B130" s="5">
-        <v>46128.39947015046</v>
+        <v>46128.56613681713</v>
       </c>
       <c r="C130" s="5">
-        <v>46157.33161864583</v>
+        <v>46157.4982853125</v>
       </c>
       <c r="D130" s="5">
-        <v>46157.33233341435</v>
+        <v>46157.49900008102</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>171</v>
@@ -9246,13 +9246,13 @@
         <v>296</v>
       </c>
       <c r="B131" s="8">
-        <v>46128.39947685185</v>
+        <v>46128.56614351852</v>
       </c>
       <c r="C131" s="8">
-        <v>46191.62667712963</v>
+        <v>46191.79334379629</v>
       </c>
       <c r="D131" s="8">
-        <v>46191.62712641204</v>
+        <v>46191.7937930787</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>171</v>
@@ -9301,13 +9301,13 @@
         <v>297</v>
       </c>
       <c r="B132" s="5">
-        <v>46128.399482673616</v>
+        <v>46128.56614934027</v>
       </c>
       <c r="C132" s="5">
-        <v>46191.62677087963</v>
+        <v>46191.793437546294</v>
       </c>
       <c r="D132" s="5">
-        <v>46191.62758195602</v>
+        <v>46191.79424862268</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>171</v>
@@ -9356,13 +9356,13 @@
         <v>298</v>
       </c>
       <c r="B133" s="8">
-        <v>46128.39948821759</v>
+        <v>46128.56615488426</v>
       </c>
       <c r="C133" s="8">
-        <v>46191.62683854166</v>
+        <v>46191.793505208334</v>
       </c>
       <c r="D133" s="8">
-        <v>46191.627732430556</v>
+        <v>46191.79439909723</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>171</v>
@@ -9411,13 +9411,13 @@
         <v>299</v>
       </c>
       <c r="B134" s="5">
-        <v>46128.39949541667</v>
+        <v>46128.566162083334</v>
       </c>
       <c r="C134" s="5">
-        <v>46191.62691627315</v>
+        <v>46191.79358293982</v>
       </c>
       <c r="D134" s="5">
-        <v>46191.62786280093</v>
+        <v>46191.79452946759</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>171</v>
@@ -9466,13 +9466,13 @@
         <v>300</v>
       </c>
       <c r="B135" s="8">
-        <v>46073.60117232639</v>
+        <v>46073.76783899305</v>
       </c>
       <c r="C135" s="8">
-        <v>46157.33062064815</v>
+        <v>46157.497287314814</v>
       </c>
       <c r="D135" s="8">
-        <v>46158.80870234953</v>
+        <v>46158.9753690162</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>301</v>
@@ -9529,13 +9529,13 @@
         <v>303</v>
       </c>
       <c r="B136" s="5">
-        <v>46128.39956262731</v>
+        <v>46128.56622929398</v>
       </c>
       <c r="C136" s="5">
-        <v>46129.52221115741</v>
+        <v>46129.688877824075</v>
       </c>
       <c r="D136" s="5">
-        <v>46157.3313462963</v>
+        <v>46157.49801296296</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>171</v>
@@ -9584,13 +9584,13 @@
         <v>305</v>
       </c>
       <c r="B137" s="8">
-        <v>46128.39957309028</v>
+        <v>46128.56623975694</v>
       </c>
       <c r="C137" s="8">
-        <v>46129.52250082176</v>
+        <v>46129.689167488425</v>
       </c>
       <c r="D137" s="8">
-        <v>46157.331359502314</v>
+        <v>46157.49802616898</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>171</v>
@@ -9639,13 +9639,13 @@
         <v>306</v>
       </c>
       <c r="B138" s="5">
-        <v>46128.39958064815</v>
+        <v>46128.56624731481</v>
       </c>
       <c r="C138" s="5">
-        <v>46129.52259707176</v>
+        <v>46129.68926373843</v>
       </c>
       <c r="D138" s="5">
-        <v>46157.331367928244</v>
+        <v>46157.49803459491</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>171</v>
@@ -9694,13 +9694,13 @@
         <v>307</v>
       </c>
       <c r="B139" s="8">
-        <v>46128.39958712963</v>
+        <v>46128.56625379629</v>
       </c>
       <c r="C139" s="8">
-        <v>46129.52268012732</v>
+        <v>46129.68934679398</v>
       </c>
       <c r="D139" s="8">
-        <v>46157.33137369213</v>
+        <v>46157.4980403588</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>171</v>
@@ -9749,13 +9749,13 @@
         <v>308</v>
       </c>
       <c r="B140" s="5">
-        <v>46128.39959421296</v>
+        <v>46128.56626087963</v>
       </c>
       <c r="C140" s="5">
-        <v>46129.52279594907</v>
+        <v>46129.689462615745</v>
       </c>
       <c r="D140" s="5">
-        <v>46157.33137880787</v>
+        <v>46157.49804547454</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>171</v>
@@ -9804,13 +9804,13 @@
         <v>309</v>
       </c>
       <c r="B141" s="8">
-        <v>46128.39960163194</v>
+        <v>46128.566268298615</v>
       </c>
       <c r="C141" s="8">
-        <v>46157.330259803246</v>
+        <v>46157.4969264699</v>
       </c>
       <c r="D141" s="8">
-        <v>46157.331430185186</v>
+        <v>46157.49809685185</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>171</v>
@@ -9859,13 +9859,13 @@
         <v>310</v>
       </c>
       <c r="B142" s="5">
-        <v>46128.399608657404</v>
+        <v>46128.566275324076</v>
       </c>
       <c r="C142" s="5">
-        <v>46157.33040572917</v>
+        <v>46157.49707239583</v>
       </c>
       <c r="D142" s="5">
-        <v>46157.33150975694</v>
+        <v>46157.498176423614</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>171</v>
@@ -9914,13 +9914,13 @@
         <v>311</v>
       </c>
       <c r="B143" s="8">
-        <v>46128.39961503472</v>
+        <v>46128.56628170139</v>
       </c>
       <c r="C143" s="8">
-        <v>46157.32987297454</v>
+        <v>46157.4965396412</v>
       </c>
       <c r="D143" s="8">
-        <v>46157.331626238425</v>
+        <v>46157.49829290509</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>171</v>
@@ -9969,13 +9969,13 @@
         <v>312</v>
       </c>
       <c r="B144" s="5">
-        <v>46128.39962135417</v>
+        <v>46128.56628802083</v>
       </c>
       <c r="C144" s="5">
-        <v>46157.33055591435</v>
+        <v>46157.49722258102</v>
       </c>
       <c r="D144" s="5">
-        <v>46191.626684965275</v>
+        <v>46191.793351631946</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>171</v>
@@ -10024,13 +10024,13 @@
         <v>313</v>
       </c>
       <c r="B145" s="8">
-        <v>46128.39962813657</v>
+        <v>46128.56629480324</v>
       </c>
       <c r="C145" s="8">
-        <v>46157.33069737269</v>
+        <v>46157.49736403935</v>
       </c>
       <c r="D145" s="8">
-        <v>46191.62677673611</v>
+        <v>46191.79344340278</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>171</v>
@@ -10079,13 +10079,13 @@
         <v>314</v>
       </c>
       <c r="B146" s="5">
-        <v>46128.39963672454</v>
+        <v>46128.5663033912</v>
       </c>
       <c r="C146" s="5">
-        <v>46157.33075273148</v>
+        <v>46157.49741939815</v>
       </c>
       <c r="D146" s="5">
-        <v>46191.62684557871</v>
+        <v>46191.79351224537</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>171</v>
@@ -10134,13 +10134,13 @@
         <v>315</v>
       </c>
       <c r="B147" s="8">
-        <v>46128.39964325231</v>
+        <v>46128.566309918984</v>
       </c>
       <c r="C147" s="8">
-        <v>46157.33081483796</v>
+        <v>46157.49748150463</v>
       </c>
       <c r="D147" s="8">
-        <v>46191.626924895834</v>
+        <v>46191.7935915625</v>
       </c>
       <c r="E147" s="9" t="s">
         <v>171</v>
@@ -10189,13 +10189,13 @@
         <v>316</v>
       </c>
       <c r="B148" s="5">
-        <v>46073.60117333333</v>
+        <v>46073.76784</v>
       </c>
       <c r="C148" s="5">
-        <v>46191.62850888888</v>
+        <v>46191.795175555555</v>
       </c>
       <c r="D148" s="5">
-        <v>46191.62867184028</v>
+        <v>46191.79533850694</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>317</v>
@@ -10252,13 +10252,13 @@
         <v>318</v>
       </c>
       <c r="B149" s="8">
-        <v>46128.39970388889</v>
+        <v>46128.566370555556</v>
       </c>
       <c r="C149" s="8">
-        <v>46191.62865480324</v>
+        <v>46191.79532146991</v>
       </c>
       <c r="D149" s="8">
-        <v>46191.62865643519</v>
+        <v>46191.79532310185</v>
       </c>
       <c r="E149" s="9" t="s">
         <v>171</v>
@@ -10305,13 +10305,13 @@
         <v>320</v>
       </c>
       <c r="B150" s="5">
-        <v>46128.399718148146</v>
+        <v>46128.56638481481</v>
       </c>
       <c r="C150" s="5">
-        <v>46191.62864943287</v>
+        <v>46191.79531609954</v>
       </c>
       <c r="D150" s="5">
-        <v>46191.62865114583</v>
+        <v>46191.7953178125</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>171</v>
@@ -10358,13 +10358,13 @@
         <v>321</v>
       </c>
       <c r="B151" s="8">
-        <v>46128.39972476852</v>
+        <v>46128.56639143519</v>
       </c>
       <c r="C151" s="8">
-        <v>46191.628643923614</v>
+        <v>46191.79531059028</v>
       </c>
       <c r="D151" s="8">
-        <v>46191.628646261575</v>
+        <v>46191.79531292824</v>
       </c>
       <c r="E151" s="9" t="s">
         <v>171</v>
@@ -10411,13 +10411,13 @@
         <v>322</v>
       </c>
       <c r="B152" s="5">
-        <v>46128.39973149306</v>
+        <v>46128.56639815972</v>
       </c>
       <c r="C152" s="5">
-        <v>46191.62863895833</v>
+        <v>46191.795305625</v>
       </c>
       <c r="D152" s="5">
-        <v>46191.62864084491</v>
+        <v>46191.79530751157</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>171</v>
@@ -10464,13 +10464,13 @@
         <v>324</v>
       </c>
       <c r="B153" s="8">
-        <v>46128.3997390625</v>
+        <v>46128.566405729165</v>
       </c>
       <c r="C153" s="8">
-        <v>46191.628631238425</v>
+        <v>46191.79529790509</v>
       </c>
       <c r="D153" s="8">
-        <v>46191.62863335648</v>
+        <v>46191.79530002315</v>
       </c>
       <c r="E153" s="9" t="s">
         <v>171</v>
@@ -10517,13 +10517,13 @@
         <v>325</v>
       </c>
       <c r="B154" s="5">
-        <v>46128.39974591435</v>
+        <v>46128.566412581014</v>
       </c>
       <c r="C154" s="5">
-        <v>46191.628614710644</v>
+        <v>46191.795281377315</v>
       </c>
       <c r="D154" s="5">
-        <v>46191.62861678241</v>
+        <v>46191.79528344907</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>171</v>
@@ -10570,13 +10570,13 @@
         <v>326</v>
       </c>
       <c r="B155" s="8">
-        <v>46128.39975251157</v>
+        <v>46128.56641917824</v>
       </c>
       <c r="C155" s="8">
-        <v>46191.62860967593</v>
+        <v>46191.79527634259</v>
       </c>
       <c r="D155" s="8">
-        <v>46191.62861170139</v>
+        <v>46191.79527836805</v>
       </c>
       <c r="E155" s="9" t="s">
         <v>171</v>
@@ -10623,13 +10623,13 @@
         <v>327</v>
       </c>
       <c r="B156" s="5">
-        <v>46128.399760671295</v>
+        <v>46128.566427337966</v>
       </c>
       <c r="C156" s="5">
-        <v>46191.628605300924</v>
+        <v>46191.795271967596</v>
       </c>
       <c r="D156" s="5">
-        <v>46191.628606909726</v>
+        <v>46191.79527357639</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>171</v>
@@ -10676,13 +10676,13 @@
         <v>328</v>
       </c>
       <c r="B157" s="8">
-        <v>46128.3997670949</v>
+        <v>46128.566433761574</v>
       </c>
       <c r="C157" s="8">
-        <v>46191.62859966436</v>
+        <v>46191.79526633101</v>
       </c>
       <c r="D157" s="8">
-        <v>46191.62860128473</v>
+        <v>46191.795267951384</v>
       </c>
       <c r="E157" s="9" t="s">
         <v>171</v>
@@ -10729,13 +10729,13 @@
         <v>329</v>
       </c>
       <c r="B158" s="5">
-        <v>46128.399773310186</v>
+        <v>46128.56643997685</v>
       </c>
       <c r="C158" s="5">
-        <v>46191.62859512732</v>
+        <v>46191.79526179398</v>
       </c>
       <c r="D158" s="5">
-        <v>46191.628596967596</v>
+        <v>46191.79526363426</v>
       </c>
       <c r="E158" s="6" t="s">
         <v>171</v>
@@ -10782,13 +10782,13 @@
         <v>330</v>
       </c>
       <c r="B159" s="8">
-        <v>46128.39977965278</v>
+        <v>46128.56644631944</v>
       </c>
       <c r="C159" s="8">
-        <v>46191.62858708334</v>
+        <v>46191.795253749995</v>
       </c>
       <c r="D159" s="8">
-        <v>46191.62858853009</v>
+        <v>46191.79525519676</v>
       </c>
       <c r="E159" s="9" t="s">
         <v>171</v>
@@ -10835,13 +10835,13 @@
         <v>331</v>
       </c>
       <c r="B160" s="5">
-        <v>46128.39978715278</v>
+        <v>46128.56645381944</v>
       </c>
       <c r="C160" s="5">
-        <v>46191.62858172454</v>
+        <v>46191.79524839121</v>
       </c>
       <c r="D160" s="5">
-        <v>46191.62858350694</v>
+        <v>46191.795250173614</v>
       </c>
       <c r="E160" s="6" t="s">
         <v>171</v>
@@ -10888,13 +10888,13 @@
         <v>332</v>
       </c>
       <c r="B161" s="8">
-        <v>46073.60117362269</v>
+        <v>46073.76784028935</v>
       </c>
       <c r="C161" s="8">
-        <v>46191.62875212963</v>
+        <v>46191.7954187963</v>
       </c>
       <c r="D161" s="8">
-        <v>46191.62997100694</v>
+        <v>46191.796637673615</v>
       </c>
       <c r="E161" s="9" t="s">
         <v>333</v>
@@ -10951,13 +10951,13 @@
         <v>335</v>
       </c>
       <c r="B162" s="5">
-        <v>46128.399858958335</v>
+        <v>46128.566525625</v>
       </c>
       <c r="C162" s="5">
-        <v>46191.62995430555</v>
+        <v>46191.79662097222</v>
       </c>
       <c r="D162" s="5">
-        <v>46192.595254907406</v>
+        <v>46192.76192157407</v>
       </c>
       <c r="E162" s="6" t="s">
         <v>171</v>
@@ -11004,13 +11004,13 @@
         <v>337</v>
       </c>
       <c r="B163" s="8">
-        <v>46128.39986534722</v>
+        <v>46128.566532013894</v>
       </c>
       <c r="C163" s="8">
-        <v>46191.62979806713</v>
+        <v>46191.796464733794</v>
       </c>
       <c r="D163" s="8">
-        <v>46192.59539783565</v>
+        <v>46192.76206450231</v>
       </c>
       <c r="E163" s="9" t="s">
         <v>171</v>
@@ -11057,13 +11057,13 @@
         <v>338</v>
       </c>
       <c r="B164" s="5">
-        <v>46128.39987255787</v>
+        <v>46128.566539224536</v>
       </c>
       <c r="C164" s="5">
-        <v>46191.62972386574</v>
+        <v>46191.79639053241</v>
       </c>
       <c r="D164" s="5">
-        <v>46192.59539780093</v>
+        <v>46192.76206446759</v>
       </c>
       <c r="E164" s="6" t="s">
         <v>171</v>
@@ -11110,13 +11110,13 @@
         <v>339</v>
       </c>
       <c r="B165" s="8">
-        <v>46128.39987865741</v>
+        <v>46128.56654532407</v>
       </c>
       <c r="C165" s="8">
-        <v>46191.629629965275</v>
+        <v>46191.79629663195</v>
       </c>
       <c r="D165" s="8">
-        <v>46192.59539822917</v>
+        <v>46192.76206489583</v>
       </c>
       <c r="E165" s="9" t="s">
         <v>171</v>
@@ -11163,13 +11163,13 @@
         <v>340</v>
       </c>
       <c r="B166" s="5">
-        <v>46128.399885023144</v>
+        <v>46128.566551689815</v>
       </c>
       <c r="C166" s="5">
-        <v>46191.62950538195</v>
+        <v>46191.79617204861</v>
       </c>
       <c r="D166" s="5">
-        <v>46192.59539766204</v>
+        <v>46192.76206432871</v>
       </c>
       <c r="E166" s="6" t="s">
         <v>171</v>
@@ -11216,13 +11216,13 @@
         <v>341</v>
       </c>
       <c r="B167" s="8">
-        <v>46128.399891863424</v>
+        <v>46128.56655853009</v>
       </c>
       <c r="C167" s="8">
-        <v>46191.629442453705</v>
+        <v>46191.79610912037</v>
       </c>
       <c r="D167" s="8">
-        <v>46192.595397453704</v>
+        <v>46192.76206412037</v>
       </c>
       <c r="E167" s="9" t="s">
         <v>171</v>
@@ -11269,13 +11269,13 @@
         <v>342</v>
       </c>
       <c r="B168" s="5">
-        <v>46128.399897650466</v>
+        <v>46128.56656431713</v>
       </c>
       <c r="C168" s="5">
-        <v>46191.62937692129</v>
+        <v>46191.796043587965</v>
       </c>
       <c r="D168" s="5">
-        <v>46192.59539746528</v>
+        <v>46192.762064131944</v>
       </c>
       <c r="E168" s="6" t="s">
         <v>171</v>
@@ -11322,13 +11322,13 @@
         <v>343</v>
       </c>
       <c r="B169" s="8">
-        <v>46128.399904143516</v>
+        <v>46128.56657081019</v>
       </c>
       <c r="C169" s="8">
-        <v>46191.629304675924</v>
+        <v>46191.795971342595</v>
       </c>
       <c r="D169" s="8">
-        <v>46192.59539746528</v>
+        <v>46192.762064131944</v>
       </c>
       <c r="E169" s="9" t="s">
         <v>171</v>
@@ -11375,13 +11375,13 @@
         <v>344</v>
       </c>
       <c r="B170" s="5">
-        <v>46128.39991079862</v>
+        <v>46128.56657746527</v>
       </c>
       <c r="C170" s="5">
-        <v>46191.6291890625</v>
+        <v>46191.79585572917</v>
       </c>
       <c r="D170" s="5">
-        <v>46192.59539747685</v>
+        <v>46192.76206414352</v>
       </c>
       <c r="E170" s="6" t="s">
         <v>171</v>
@@ -11428,13 +11428,13 @@
         <v>345</v>
       </c>
       <c r="B171" s="8">
-        <v>46128.39991644676</v>
+        <v>46128.566583113425</v>
       </c>
       <c r="C171" s="8">
-        <v>46191.629107291665</v>
+        <v>46191.795773958336</v>
       </c>
       <c r="D171" s="8">
-        <v>46192.59539725694</v>
+        <v>46192.76206392361</v>
       </c>
       <c r="E171" s="9" t="s">
         <v>171</v>
@@ -11481,13 +11481,13 @@
         <v>346</v>
       </c>
       <c r="B172" s="5">
-        <v>46128.39992402778</v>
+        <v>46128.56659069445</v>
       </c>
       <c r="C172" s="5">
-        <v>46191.628967743054</v>
+        <v>46191.79563440972</v>
       </c>
       <c r="D172" s="5">
-        <v>46192.5953975463</v>
+        <v>46192.76206421296</v>
       </c>
       <c r="E172" s="6" t="s">
         <v>171</v>
@@ -11534,13 +11534,13 @@
         <v>347</v>
       </c>
       <c r="B173" s="8">
-        <v>46128.39993115741</v>
+        <v>46128.56659782407</v>
       </c>
       <c r="C173" s="8">
-        <v>46191.62888233796</v>
+        <v>46191.79554900463</v>
       </c>
       <c r="D173" s="8">
-        <v>46192.595397638885</v>
+        <v>46192.762064305556</v>
       </c>
       <c r="E173" s="9" t="s">
         <v>171</v>
@@ -11587,13 +11587,13 @@
         <v>348</v>
       </c>
       <c r="B174" s="5">
-        <v>46073.60117105324</v>
+        <v>46073.767837719904</v>
       </c>
       <c r="C174" s="5">
-        <v>46193.39409832176</v>
+        <v>46193.560764988426</v>
       </c>
       <c r="D174" s="5">
-        <v>46193.394399259254</v>
+        <v>46193.561065925926</v>
       </c>
       <c r="E174" s="6" t="s">
         <v>349</v>
@@ -11640,13 +11640,13 @@
         <v>351</v>
       </c>
       <c r="B175" s="8">
-        <v>46073.601171435184</v>
+        <v>46073.76783810185</v>
       </c>
       <c r="C175" s="8">
-        <v>46193.39438574074</v>
+        <v>46193.56105240741</v>
       </c>
       <c r="D175" s="8">
-        <v>46194.54269361111</v>
+        <v>46194.709360277775</v>
       </c>
       <c r="E175" s="9" t="s">
         <v>352</v>
@@ -11705,13 +11705,13 @@
         <v>356</v>
       </c>
       <c r="B176" s="5">
-        <v>46128.40037993055</v>
+        <v>46128.56704659722</v>
       </c>
       <c r="C176" s="5">
-        <v>46194.535347083336</v>
+        <v>46194.70201375</v>
       </c>
       <c r="D176" s="5">
-        <v>46194.53541939815</v>
+        <v>46194.70208606482</v>
       </c>
       <c r="E176" s="6" t="s">
         <v>171</v>
@@ -11758,13 +11758,13 @@
         <v>358</v>
       </c>
       <c r="B177" s="8">
-        <v>46128.400386388894</v>
+        <v>46128.56705305555</v>
       </c>
       <c r="C177" s="8">
-        <v>46194.535348854166</v>
+        <v>46194.70201552083</v>
       </c>
       <c r="D177" s="8">
-        <v>46194.53542032407</v>
+        <v>46194.70208699074</v>
       </c>
       <c r="E177" s="9" t="s">
         <v>171</v>
@@ -11811,13 +11811,13 @@
         <v>359</v>
       </c>
       <c r="B178" s="5">
-        <v>46128.400393460644</v>
+        <v>46128.567060127316</v>
       </c>
       <c r="C178" s="5">
-        <v>46194.5353497801</v>
+        <v>46194.702016446754</v>
       </c>
       <c r="D178" s="5">
-        <v>46194.53542097222</v>
+        <v>46194.702087638885</v>
       </c>
       <c r="E178" s="6" t="s">
         <v>171</v>
@@ -11864,13 +11864,13 @@
         <v>360</v>
       </c>
       <c r="B179" s="8">
-        <v>46128.400399351856</v>
+        <v>46128.56706601851</v>
       </c>
       <c r="C179" s="8">
-        <v>46194.53535070602</v>
+        <v>46194.702017372685</v>
       </c>
       <c r="D179" s="8">
-        <v>46194.53542164352</v>
+        <v>46194.70208831019</v>
       </c>
       <c r="E179" s="9" t="s">
         <v>171</v>
@@ -11917,13 +11917,13 @@
         <v>361</v>
       </c>
       <c r="B180" s="5">
-        <v>46128.400406354165</v>
+        <v>46128.56707302084</v>
       </c>
       <c r="C180" s="5">
-        <v>46194.53535174769</v>
+        <v>46194.70201841435</v>
       </c>
       <c r="D180" s="5">
-        <v>46194.535422326386</v>
+        <v>46194.70208899306</v>
       </c>
       <c r="E180" s="6" t="s">
         <v>171</v>
@@ -11970,13 +11970,13 @@
         <v>362</v>
       </c>
       <c r="B181" s="8">
-        <v>46128.400413634256</v>
+        <v>46128.56708030093</v>
       </c>
       <c r="C181" s="8">
-        <v>46194.53535258102</v>
+        <v>46194.702019247685</v>
       </c>
       <c r="D181" s="8">
-        <v>46194.53542292824</v>
+        <v>46194.70208959491</v>
       </c>
       <c r="E181" s="9" t="s">
         <v>171</v>
@@ -12023,13 +12023,13 @@
         <v>363</v>
       </c>
       <c r="B182" s="5">
-        <v>46128.40042064815</v>
+        <v>46128.56708731482</v>
       </c>
       <c r="C182" s="5">
-        <v>46194.53540148148</v>
+        <v>46194.70206814815</v>
       </c>
       <c r="D182" s="5">
-        <v>46194.5354234838</v>
+        <v>46194.70209015046</v>
       </c>
       <c r="E182" s="6" t="s">
         <v>171</v>
@@ -12076,13 +12076,13 @@
         <v>364</v>
       </c>
       <c r="B183" s="8">
-        <v>46128.4004277662</v>
+        <v>46128.567094432874</v>
       </c>
       <c r="C183" s="8">
-        <v>46194.535405567134</v>
+        <v>46194.70207223379</v>
       </c>
       <c r="D183" s="8">
-        <v>46194.5354240625</v>
+        <v>46194.702090729166</v>
       </c>
       <c r="E183" s="9" t="s">
         <v>171</v>
@@ -12129,13 +12129,13 @@
         <v>366</v>
       </c>
       <c r="B184" s="5">
-        <v>46128.40043542824</v>
+        <v>46128.56710209491</v>
       </c>
       <c r="C184" s="5">
-        <v>46194.53540659722</v>
+        <v>46194.70207326389</v>
       </c>
       <c r="D184" s="5">
-        <v>46194.5354246875</v>
+        <v>46194.702091354164</v>
       </c>
       <c r="E184" s="6" t="s">
         <v>171</v>
@@ -12182,13 +12182,13 @@
         <v>367</v>
       </c>
       <c r="B185" s="8">
-        <v>46128.40044216435</v>
+        <v>46128.56710883102</v>
       </c>
       <c r="C185" s="8">
-        <v>46194.53540756945</v>
+        <v>46194.70207423611</v>
       </c>
       <c r="D185" s="8">
-        <v>46194.53542530093</v>
+        <v>46194.70209196759</v>
       </c>
       <c r="E185" s="9" t="s">
         <v>171</v>
@@ -12235,13 +12235,13 @@
         <v>368</v>
       </c>
       <c r="B186" s="5">
-        <v>46128.40044966435</v>
+        <v>46128.56711633102</v>
       </c>
       <c r="C186" s="5">
-        <v>46194.535414212965</v>
+        <v>46194.70208087963</v>
       </c>
       <c r="D186" s="5">
-        <v>46194.53542922453</v>
+        <v>46194.7020958912</v>
       </c>
       <c r="E186" s="6" t="s">
         <v>171</v>
@@ -12288,13 +12288,13 @@
         <v>369</v>
       </c>
       <c r="B187" s="8">
-        <v>46128.40045667824</v>
+        <v>46128.56712334491</v>
       </c>
       <c r="C187" s="8">
-        <v>46194.535415046295</v>
+        <v>46194.70208171297</v>
       </c>
       <c r="D187" s="8">
-        <v>46194.53542988426</v>
+        <v>46194.70209655093</v>
       </c>
       <c r="E187" s="9" t="s">
         <v>171</v>
@@ -12341,13 +12341,13 @@
         <v>370</v>
       </c>
       <c r="B188" s="5">
-        <v>46191.72840521991</v>
+        <v>46191.895071886574</v>
       </c>
       <c r="C188" s="5">
-        <v>46194.535415844904</v>
+        <v>46194.702082511576</v>
       </c>
       <c r="D188" s="5">
-        <v>46194.53543087963</v>
+        <v>46194.702097546295</v>
       </c>
       <c r="E188" s="6" t="s">
         <v>371</v>
@@ -12394,13 +12394,13 @@
         <v>372</v>
       </c>
       <c r="B189" s="8">
-        <v>46073.60117172454</v>
+        <v>46073.7678383912</v>
       </c>
       <c r="C189" s="8">
-        <v>46191.63011157408</v>
+        <v>46191.796778240736</v>
       </c>
       <c r="D189" s="8">
-        <v>46194.57869391204</v>
+        <v>46194.7453605787</v>
       </c>
       <c r="E189" s="9" t="s">
         <v>373</v>
@@ -12459,13 +12459,13 @@
         <v>374</v>
       </c>
       <c r="B190" s="5">
-        <v>46128.4005152662</v>
+        <v>46128.56718193287</v>
       </c>
       <c r="C190" s="5">
-        <v>46192.48040112268</v>
+        <v>46192.64706778935</v>
       </c>
       <c r="D190" s="5">
-        <v>46194.54219278935</v>
+        <v>46194.70885945602</v>
       </c>
       <c r="E190" s="6" t="s">
         <v>171</v>
@@ -12514,13 +12514,13 @@
         <v>376</v>
       </c>
       <c r="B191" s="8">
-        <v>46128.400523425924</v>
+        <v>46128.567190092595</v>
       </c>
       <c r="C191" s="8">
-        <v>46192.48051887732</v>
+        <v>46192.64718554398</v>
       </c>
       <c r="D191" s="8">
-        <v>46194.54010200231</v>
+        <v>46194.706768668984</v>
       </c>
       <c r="E191" s="9" t="s">
         <v>171</v>
@@ -12569,13 +12569,13 @@
         <v>377</v>
       </c>
       <c r="B192" s="5">
-        <v>46128.40052988426</v>
+        <v>46128.567196550925</v>
       </c>
       <c r="C192" s="5">
-        <v>46194.57853402778</v>
+        <v>46194.745200694444</v>
       </c>
       <c r="D192" s="5">
-        <v>46194.57853547454</v>
+        <v>46194.7452021412</v>
       </c>
       <c r="E192" s="6" t="s">
         <v>171</v>
@@ -12624,13 +12624,13 @@
         <v>378</v>
       </c>
       <c r="B193" s="8">
-        <v>46128.4005380787</v>
+        <v>46128.56720474537</v>
       </c>
       <c r="C193" s="8">
-        <v>46194.57858744213</v>
+        <v>46194.7452541088</v>
       </c>
       <c r="D193" s="8">
-        <v>46194.57858940972</v>
+        <v>46194.74525607639</v>
       </c>
       <c r="E193" s="9" t="s">
         <v>171</v>
@@ -12679,13 +12679,13 @@
         <v>379</v>
       </c>
       <c r="B194" s="5">
-        <v>46128.40054480324</v>
+        <v>46128.56721146991</v>
       </c>
       <c r="C194" s="5">
-        <v>46194.57842237268</v>
+        <v>46194.74508903935</v>
       </c>
       <c r="D194" s="5">
-        <v>46194.57842417824</v>
+        <v>46194.74509084491</v>
       </c>
       <c r="E194" s="6" t="s">
         <v>171</v>
@@ -12734,13 +12734,13 @@
         <v>380</v>
       </c>
       <c r="B195" s="8">
-        <v>46128.40055128472</v>
+        <v>46128.56721795139</v>
       </c>
       <c r="C195" s="8">
-        <v>46194.57819836806</v>
+        <v>46194.74486503472</v>
       </c>
       <c r="D195" s="8">
-        <v>46194.578200601856</v>
+        <v>46194.74486726851</v>
       </c>
       <c r="E195" s="9" t="s">
         <v>171</v>
@@ -12789,13 +12789,13 @@
         <v>381</v>
       </c>
       <c r="B196" s="5">
-        <v>46128.40055881944</v>
+        <v>46128.56722548611</v>
       </c>
       <c r="C196" s="5">
-        <v>46194.57867837963</v>
+        <v>46194.74534504629</v>
       </c>
       <c r="D196" s="5">
-        <v>46194.57868018519</v>
+        <v>46194.74534685185</v>
       </c>
       <c r="E196" s="6" t="s">
         <v>171</v>
@@ -12844,13 +12844,13 @@
         <v>382</v>
       </c>
       <c r="B197" s="8">
-        <v>46128.40056666666</v>
+        <v>46128.567233333335</v>
       </c>
       <c r="C197" s="8">
-        <v>46194.578329490745</v>
+        <v>46194.7449961574</v>
       </c>
       <c r="D197" s="8">
-        <v>46194.57833131944</v>
+        <v>46194.74499798611</v>
       </c>
       <c r="E197" s="9" t="s">
         <v>171</v>
@@ -12899,13 +12899,13 @@
         <v>383</v>
       </c>
       <c r="B198" s="5">
-        <v>46128.400573437495</v>
+        <v>46128.56724010417</v>
       </c>
       <c r="C198" s="5">
-        <v>46194.57828883102</v>
+        <v>46194.744955497685</v>
       </c>
       <c r="D198" s="5">
-        <v>46194.57829049768</v>
+        <v>46194.74495716435</v>
       </c>
       <c r="E198" s="6" t="s">
         <v>171</v>
@@ -12954,13 +12954,13 @@
         <v>384</v>
       </c>
       <c r="B199" s="8">
-        <v>46128.40057939815</v>
+        <v>46128.56724606482</v>
       </c>
       <c r="C199" s="8">
-        <v>46194.578629282405</v>
+        <v>46194.74529594908</v>
       </c>
       <c r="D199" s="8">
-        <v>46194.578631076394</v>
+        <v>46194.74529774305</v>
       </c>
       <c r="E199" s="9" t="s">
         <v>171</v>
@@ -13009,13 +13009,13 @@
         <v>385</v>
       </c>
       <c r="B200" s="5">
-        <v>46128.40058570602</v>
+        <v>46128.56725237268</v>
       </c>
       <c r="C200" s="5">
-        <v>46194.57836215278</v>
+        <v>46194.745028819445</v>
       </c>
       <c r="D200" s="5">
-        <v>46194.578363981476</v>
+        <v>46194.74503064815</v>
       </c>
       <c r="E200" s="6" t="s">
         <v>171</v>
@@ -13064,13 +13064,13 @@
         <v>386</v>
       </c>
       <c r="B201" s="8">
-        <v>46128.400592777776</v>
+        <v>46128.56725944445</v>
       </c>
       <c r="C201" s="8">
-        <v>46194.578460335644</v>
+        <v>46194.745127002316</v>
       </c>
       <c r="D201" s="8">
-        <v>46194.57846226852</v>
+        <v>46194.74512893519</v>
       </c>
       <c r="E201" s="9" t="s">
         <v>171</v>
@@ -13119,13 +13119,13 @@
         <v>387</v>
       </c>
       <c r="B202" s="5">
-        <v>46073.60117201389</v>
+        <v>46073.76783868056</v>
       </c>
       <c r="C202" s="5">
-        <v>46191.630205127316</v>
+        <v>46191.79687179398</v>
       </c>
       <c r="D202" s="5">
-        <v>46195.723833634256</v>
+        <v>46195.89050030093</v>
       </c>
       <c r="E202" s="6" t="s">
         <v>388</v>
@@ -13182,13 +13182,13 @@
         <v>389</v>
       </c>
       <c r="B203" s="8">
-        <v>46128.40064677084</v>
+        <v>46128.567313437496</v>
       </c>
       <c r="C203" s="8">
-        <v>46195.72195298611</v>
+        <v>46195.888619652775</v>
       </c>
       <c r="D203" s="8">
-        <v>46195.72195440972</v>
+        <v>46195.88862107639</v>
       </c>
       <c r="E203" s="9" t="s">
         <v>171</v>
@@ -13235,13 +13235,13 @@
         <v>391</v>
       </c>
       <c r="B204" s="5">
-        <v>46128.40065387731</v>
+        <v>46128.56732054398</v>
       </c>
       <c r="C204" s="5">
-        <v>46195.72184524305</v>
+        <v>46195.888511909725</v>
       </c>
       <c r="D204" s="5">
-        <v>46195.72184748843</v>
+        <v>46195.88851415509</v>
       </c>
       <c r="E204" s="6" t="s">
         <v>171</v>
@@ -13288,13 +13288,13 @@
         <v>392</v>
       </c>
       <c r="B205" s="8">
-        <v>46128.40065994213</v>
+        <v>46128.5673266088</v>
       </c>
       <c r="C205" s="8">
-        <v>46195.72204724537</v>
+        <v>46195.888713912034</v>
       </c>
       <c r="D205" s="8">
-        <v>46195.722048993055</v>
+        <v>46195.88871565972</v>
       </c>
       <c r="E205" s="9" t="s">
         <v>171</v>
@@ -13341,13 +13341,13 @@
         <v>393</v>
       </c>
       <c r="B206" s="5">
-        <v>46128.400666284724</v>
+        <v>46128.56733295139</v>
       </c>
       <c r="C206" s="5">
-        <v>46195.7237441551</v>
+        <v>46195.890410821754</v>
       </c>
       <c r="D206" s="5">
-        <v>46195.7237462037</v>
+        <v>46195.89041287037</v>
       </c>
       <c r="E206" s="6" t="s">
         <v>171</v>
@@ -13394,13 +13394,13 @@
         <v>394</v>
       </c>
       <c r="B207" s="8">
-        <v>46128.400671875</v>
+        <v>46128.56733854167</v>
       </c>
       <c r="C207" s="8">
-        <v>46195.723754074075</v>
+        <v>46195.89042074074</v>
       </c>
       <c r="D207" s="8">
-        <v>46195.72375608796</v>
+        <v>46195.89042275463</v>
       </c>
       <c r="E207" s="9" t="s">
         <v>171</v>
@@ -13447,13 +13447,13 @@
         <v>395</v>
       </c>
       <c r="B208" s="5">
-        <v>46128.40067851852</v>
+        <v>46128.56734518518</v>
       </c>
       <c r="C208" s="5">
-        <v>46195.7237633912</v>
+        <v>46195.89043005787</v>
       </c>
       <c r="D208" s="5">
-        <v>46195.72376501157</v>
+        <v>46195.89043167824</v>
       </c>
       <c r="E208" s="6" t="s">
         <v>171</v>
@@ -13500,13 +13500,13 @@
         <v>396</v>
       </c>
       <c r="B209" s="8">
-        <v>46128.40068510416</v>
+        <v>46128.567351770835</v>
       </c>
       <c r="C209" s="8">
-        <v>46195.723771689816</v>
+        <v>46195.89043835648</v>
       </c>
       <c r="D209" s="8">
-        <v>46195.72377370371</v>
+        <v>46195.89044037037</v>
       </c>
       <c r="E209" s="9" t="s">
         <v>171</v>
@@ -13553,13 +13553,13 @@
         <v>398</v>
       </c>
       <c r="B210" s="5">
-        <v>46128.40069071759</v>
+        <v>46128.56735738426</v>
       </c>
       <c r="C210" s="5">
-        <v>46195.72377869213</v>
+        <v>46195.8904453588</v>
       </c>
       <c r="D210" s="5">
-        <v>46195.723780138884</v>
+        <v>46195.890446805555</v>
       </c>
       <c r="E210" s="6" t="s">
         <v>171</v>
@@ -13606,13 +13606,13 @@
         <v>399</v>
       </c>
       <c r="B211" s="8">
-        <v>46128.400695902776</v>
+        <v>46128.56736256945</v>
       </c>
       <c r="C211" s="8">
-        <v>46195.72378525463</v>
+        <v>46195.890451921296</v>
       </c>
       <c r="D211" s="8">
-        <v>46195.72378666667</v>
+        <v>46195.89045333333</v>
       </c>
       <c r="E211" s="9" t="s">
         <v>171</v>
@@ -13659,13 +13659,13 @@
         <v>400</v>
       </c>
       <c r="B212" s="5">
-        <v>46128.40070153935</v>
+        <v>46128.567368206015</v>
       </c>
       <c r="C212" s="5">
-        <v>46195.72379412037</v>
+        <v>46195.890460787035</v>
       </c>
       <c r="D212" s="5">
-        <v>46195.723795694445</v>
+        <v>46195.890462361116</v>
       </c>
       <c r="E212" s="6" t="s">
         <v>171</v>
@@ -13712,13 +13712,13 @@
         <v>401</v>
       </c>
       <c r="B213" s="8">
-        <v>46128.400707002314</v>
+        <v>46128.56737366898</v>
       </c>
       <c r="C213" s="8">
-        <v>46195.72379883102</v>
+        <v>46195.89046549769</v>
       </c>
       <c r="D213" s="8">
-        <v>46195.72380032408</v>
+        <v>46195.89046699074</v>
       </c>
       <c r="E213" s="9" t="s">
         <v>171</v>
@@ -13765,13 +13765,13 @@
         <v>402</v>
       </c>
       <c r="B214" s="5">
-        <v>46128.400711863425</v>
+        <v>46128.56737853009</v>
       </c>
       <c r="C214" s="5">
-        <v>46195.72381174768</v>
+        <v>46195.89047841435</v>
       </c>
       <c r="D214" s="5">
-        <v>46195.72381472222</v>
+        <v>46195.89048138889</v>
       </c>
       <c r="E214" s="6" t="s">
         <v>171</v>
@@ -13818,13 +13818,13 @@
         <v>403</v>
       </c>
       <c r="B215" s="8">
-        <v>46073.60117229167</v>
+        <v>46073.76783895833</v>
       </c>
       <c r="C215" s="8">
-        <v>46191.63026348379</v>
+        <v>46191.79693015046</v>
       </c>
       <c r="D215" s="8">
-        <v>46195.723980509254</v>
+        <v>46195.890647175926</v>
       </c>
       <c r="E215" s="9" t="s">
         <v>404</v>
@@ -13881,13 +13881,13 @@
         <v>406</v>
       </c>
       <c r="B216" s="5">
-        <v>46128.400799525465</v>
+        <v>46128.56746619213</v>
       </c>
       <c r="C216" s="5">
-        <v>46195.72386503472</v>
+        <v>46195.890531701385</v>
       </c>
       <c r="D216" s="5">
-        <v>46195.72386653935</v>
+        <v>46195.890533206024</v>
       </c>
       <c r="E216" s="6" t="s">
         <v>171</v>
@@ -13934,13 +13934,13 @@
         <v>407</v>
       </c>
       <c r="B217" s="8">
-        <v>46128.40080708334</v>
+        <v>46128.56747375</v>
       </c>
       <c r="C217" s="8">
-        <v>46195.723871423615</v>
+        <v>46195.89053809027</v>
       </c>
       <c r="D217" s="8">
-        <v>46195.7238730324</v>
+        <v>46195.890539699074</v>
       </c>
       <c r="E217" s="9" t="s">
         <v>171</v>
@@ -13987,13 +13987,13 @@
         <v>408</v>
       </c>
       <c r="B218" s="5">
-        <v>46128.40081416667</v>
+        <v>46128.567480833335</v>
       </c>
       <c r="C218" s="5">
-        <v>46195.72387901621</v>
+        <v>46195.890545682865</v>
       </c>
       <c r="D218" s="5">
-        <v>46195.72388081018</v>
+        <v>46195.890547476854</v>
       </c>
       <c r="E218" s="6" t="s">
         <v>171</v>
@@ -14040,13 +14040,13 @@
         <v>409</v>
       </c>
       <c r="B219" s="8">
-        <v>46128.40082196759</v>
+        <v>46128.56748863426</v>
       </c>
       <c r="C219" s="8">
-        <v>46195.72388373842</v>
+        <v>46195.89055040509</v>
       </c>
       <c r="D219" s="8">
-        <v>46195.72388538194</v>
+        <v>46195.890552048615</v>
       </c>
       <c r="E219" s="9" t="s">
         <v>171</v>
@@ -14093,13 +14093,13 @@
         <v>410</v>
       </c>
       <c r="B220" s="5">
-        <v>46128.40082953704</v>
+        <v>46128.5674962037</v>
       </c>
       <c r="C220" s="5">
-        <v>46195.723890925925</v>
+        <v>46195.89055759259</v>
       </c>
       <c r="D220" s="5">
-        <v>46195.723892407404</v>
+        <v>46195.890559074076</v>
       </c>
       <c r="E220" s="6" t="s">
         <v>171</v>
@@ -14146,13 +14146,13 @@
         <v>411</v>
       </c>
       <c r="B221" s="8">
-        <v>46128.400837407404</v>
+        <v>46128.567504074075</v>
       </c>
       <c r="C221" s="8">
-        <v>46195.723916076386</v>
+        <v>46195.89058274306</v>
       </c>
       <c r="D221" s="8">
-        <v>46195.723917986106</v>
+        <v>46195.89058465278</v>
       </c>
       <c r="E221" s="9" t="s">
         <v>171</v>
@@ -14199,13 +14199,13 @@
         <v>412</v>
       </c>
       <c r="B222" s="5">
-        <v>46128.40084611111</v>
+        <v>46128.56751277778</v>
       </c>
       <c r="C222" s="5">
-        <v>46195.72390241898</v>
+        <v>46195.89056908565</v>
       </c>
       <c r="D222" s="5">
-        <v>46195.72390431713</v>
+        <v>46195.8905709838</v>
       </c>
       <c r="E222" s="6" t="s">
         <v>171</v>
@@ -14252,13 +14252,13 @@
         <v>413</v>
       </c>
       <c r="B223" s="8">
-        <v>46128.40085472222</v>
+        <v>46128.56752138889</v>
       </c>
       <c r="C223" s="8">
-        <v>46195.723925694445</v>
+        <v>46195.89059236112</v>
       </c>
       <c r="D223" s="8">
-        <v>46195.72392751157</v>
+        <v>46195.89059417824</v>
       </c>
       <c r="E223" s="9" t="s">
         <v>171</v>
@@ -14305,13 +14305,13 @@
         <v>414</v>
       </c>
       <c r="B224" s="5">
-        <v>46128.40086168981</v>
+        <v>46128.56752835648</v>
       </c>
       <c r="C224" s="5">
-        <v>46195.72393962963</v>
+        <v>46195.89060629629</v>
       </c>
       <c r="D224" s="5">
-        <v>46195.723941226854</v>
+        <v>46195.89060789352</v>
       </c>
       <c r="E224" s="6" t="s">
         <v>171</v>
@@ -14358,13 +14358,13 @@
         <v>415</v>
       </c>
       <c r="B225" s="8">
-        <v>46128.40086961805</v>
+        <v>46128.567536284725</v>
       </c>
       <c r="C225" s="8">
-        <v>46195.723948506944</v>
+        <v>46195.890615173616</v>
       </c>
       <c r="D225" s="8">
-        <v>46195.72395039352</v>
+        <v>46195.890617060184</v>
       </c>
       <c r="E225" s="9" t="s">
         <v>171</v>
@@ -14411,13 +14411,13 @@
         <v>416</v>
       </c>
       <c r="B226" s="5">
-        <v>46128.40087725694</v>
+        <v>46128.56754392361</v>
       </c>
       <c r="C226" s="5">
-        <v>46195.723956574075</v>
+        <v>46195.89062324074</v>
       </c>
       <c r="D226" s="5">
-        <v>46195.723958159724</v>
+        <v>46195.89062482639</v>
       </c>
       <c r="E226" s="6" t="s">
         <v>171</v>
@@ -14464,13 +14464,13 @@
         <v>417</v>
       </c>
       <c r="B227" s="8">
-        <v>46128.40088428241</v>
+        <v>46128.567550949076</v>
       </c>
       <c r="C227" s="8">
-        <v>46195.72396392361</v>
+        <v>46195.89063059028</v>
       </c>
       <c r="D227" s="8">
-        <v>46195.723965625</v>
+        <v>46195.89063229167</v>
       </c>
       <c r="E227" s="9" t="s">
         <v>171</v>
@@ -14517,11 +14517,11 @@
         <v>418</v>
       </c>
       <c r="B228" s="5">
-        <v>46073.601172905095</v>
+        <v>46073.76783957176</v>
       </c>
       <c r="C228" s="6"/>
       <c r="D228" s="5">
-        <v>46076.668122187504</v>
+        <v>46076.83478885417</v>
       </c>
       <c r="E228" s="6" t="s">
         <v>419</v>
@@ -14564,11 +14564,11 @@
         <v>421</v>
       </c>
       <c r="B229" s="8">
-        <v>46073.601173194445</v>
+        <v>46073.76783986111</v>
       </c>
       <c r="C229" s="9"/>
       <c r="D229" s="8">
-        <v>46191.63028319445</v>
+        <v>46191.79694986111</v>
       </c>
       <c r="E229" s="9" t="s">
         <v>422</v>
@@ -14627,11 +14627,11 @@
         <v>425</v>
       </c>
       <c r="B230" s="5">
-        <v>46073.60117346064</v>
+        <v>46073.767840127315</v>
       </c>
       <c r="C230" s="6"/>
       <c r="D230" s="5">
-        <v>46191.63028361111</v>
+        <v>46191.79695027778</v>
       </c>
       <c r="E230" s="6" t="s">
         <v>426</v>
@@ -14690,11 +14690,11 @@
         <v>428</v>
       </c>
       <c r="B231" s="8">
-        <v>46090.4717330787</v>
+        <v>46090.63839974537</v>
       </c>
       <c r="C231" s="9"/>
       <c r="D231" s="8">
-        <v>46091.69625637731</v>
+        <v>46091.862923043984</v>
       </c>
       <c r="E231" s="9" t="s">
         <v>429</v>
@@ -14739,11 +14739,11 @@
         <v>431</v>
       </c>
       <c r="B232" s="5">
-        <v>46090.47183018518</v>
+        <v>46090.638496851854</v>
       </c>
       <c r="C232" s="6"/>
       <c r="D232" s="5">
-        <v>46191.63028380787</v>
+        <v>46191.79695047454</v>
       </c>
       <c r="E232" s="6" t="s">
         <v>432</v>
@@ -14802,11 +14802,11 @@
         <v>434</v>
       </c>
       <c r="B233" s="8">
-        <v>46090.472055763894</v>
+        <v>46090.63872243055</v>
       </c>
       <c r="C233" s="9"/>
       <c r="D233" s="8">
-        <v>46099.96883761574</v>
+        <v>46100.13550428241</v>
       </c>
       <c r="E233" s="9" t="s">
         <v>435</v>

--- a/data/50001501 - EQ MIN LA HACIENDA B.xlsx
+++ b/data/50001501 - EQ MIN LA HACIENDA B.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2668" uniqueCount="434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2669" uniqueCount="434">
   <si>
     <t>50001501 - EQ. MIN. LA HACIENDA</t>
   </si>
@@ -12394,7 +12394,7 @@
         <v>46191.796778240736</v>
       </c>
       <c r="D189" s="8">
-        <v>46194.7453605787</v>
+        <v>46223.83431805555</v>
       </c>
       <c r="E189" s="9" t="s">
         <v>371</v>
@@ -12403,9 +12403,11 @@
         <v>26</v>
       </c>
       <c r="G189" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H189" s="9"/>
+        <v>85</v>
+      </c>
+      <c r="H189" s="9" t="s">
+        <v>85</v>
+      </c>
       <c r="I189" s="8">
         <v>46077</v>
       </c>

--- a/data/50001501 - EQ MIN LA HACIENDA B.xlsx
+++ b/data/50001501 - EQ MIN LA HACIENDA B.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2669" uniqueCount="434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2669" uniqueCount="435">
   <si>
     <t>50001501 - EQ. MIN. LA HACIENDA</t>
   </si>
@@ -266,6 +266,9 @@
   </si>
   <si>
     <t>propuesta nucleo rodete</t>
+  </si>
+  <si>
+    <t>NATALYA ESPINOZA</t>
   </si>
   <si>
     <t>nespinoza@zitron.com</t>
@@ -3065,7 +3068,7 @@
         <v>85</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I22" s="5">
         <v>46006</v>
@@ -3089,7 +3092,7 @@
         <v>62</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q22" s="5">
         <v>46006</v>
@@ -3109,7 +3112,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B23" s="8">
         <v>46073.76783766204</v>
@@ -3121,7 +3124,7 @@
         <v>46223.8088075</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
@@ -3130,7 +3133,7 @@
         <v>85</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I23" s="8">
         <v>46008</v>
@@ -3154,7 +3157,7 @@
         <v>65</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q23" s="8">
         <v>46008</v>
@@ -3174,7 +3177,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B24" s="5">
         <v>46114.77467594907</v>
@@ -3186,7 +3189,7 @@
         <v>46223.80880381944</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
@@ -3195,7 +3198,7 @@
         <v>85</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I24" s="6"/>
       <c r="J24" s="6"/>
@@ -3229,7 +3232,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B25" s="8">
         <v>46073.767838009255</v>
@@ -3241,7 +3244,7 @@
         <v>46191.89593702546</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>25</v>
@@ -3265,7 +3268,7 @@
         <v>26</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P25" s="9" t="s">
         <v>26</v>
@@ -3282,7 +3285,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B26" s="5">
         <v>46073.76783827547</v>
@@ -3294,16 +3297,16 @@
         <v>46114.51796603009</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I26" s="5">
         <v>46008</v>
@@ -3321,13 +3324,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q26" s="5">
         <v>46008</v>
@@ -3347,7 +3350,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B27" s="8">
         <v>46073.7678385301</v>
@@ -3359,16 +3362,16 @@
         <v>46114.5177578588</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I27" s="8">
         <v>46008</v>
@@ -3386,29 +3389,29 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O27" s="9" t="s">
         <v>75</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
       <c r="S27" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T27" s="9">
         <v>0</v>
       </c>
       <c r="U27" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B28" s="5">
         <v>46073.767838796295</v>
@@ -3420,16 +3423,16 @@
         <v>46114.517796608794</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I28" s="5">
         <v>46010</v>
@@ -3447,29 +3450,29 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
       <c r="S28" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B29" s="8">
         <v>46073.767839120366</v>
@@ -3481,16 +3484,16 @@
         <v>46191.793455046296</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I29" s="8">
         <v>46009</v>
@@ -3508,13 +3511,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q29" s="8">
         <v>46009</v>
@@ -3534,7 +3537,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B30" s="5">
         <v>46073.76783938658</v>
@@ -3546,16 +3549,16 @@
         <v>46169.84669766204</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I30" s="5">
         <v>46009</v>
@@ -3573,29 +3576,29 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>81</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
       <c r="S30" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
       </c>
       <c r="U30" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B31" s="8">
         <v>46073.7678396875</v>
@@ -3607,16 +3610,16 @@
         <v>46191.79342476852</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I31" s="8">
         <v>46020</v>
@@ -3634,29 +3637,29 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
       <c r="S31" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T31" s="9">
         <v>0</v>
       </c>
       <c r="U31" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B32" s="5">
         <v>46073.76784030093</v>
@@ -3668,16 +3671,16 @@
         <v>46122.658178784724</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I32" s="5">
         <v>46008</v>
@@ -3695,13 +3698,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q32" s="5">
         <v>46008</v>
@@ -3721,7 +3724,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B33" s="8">
         <v>46073.7678405787</v>
@@ -3733,16 +3736,16 @@
         <v>46122.65810958333</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I33" s="8">
         <v>46008</v>
@@ -3760,29 +3763,29 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O33" s="9" t="s">
         <v>84</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
       <c r="S33" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T33" s="9">
         <v>0</v>
       </c>
       <c r="U33" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B34" s="5">
         <v>46073.76783680556</v>
@@ -3794,16 +3797,16 @@
         <v>46122.658152662036</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I34" s="5">
         <v>46010</v>
@@ -3821,29 +3824,29 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
       <c r="S34" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T34" s="6">
         <v>0</v>
       </c>
       <c r="U34" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B35" s="8">
         <v>46073.76783711805</v>
@@ -3855,16 +3858,16 @@
         <v>46097.55004581019</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I35" s="8">
         <v>46008</v>
@@ -3882,13 +3885,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q35" s="8">
         <v>46008</v>
@@ -3908,7 +3911,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B36" s="5">
         <v>46073.76783739583</v>
@@ -3920,16 +3923,16 @@
         <v>46097.54995472222</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I36" s="5">
         <v>46008</v>
@@ -3947,29 +3950,29 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>78</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
       <c r="S36" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T36" s="6">
         <v>0</v>
       </c>
       <c r="U36" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B37" s="8">
         <v>46073.76783761574</v>
@@ -3981,16 +3984,16 @@
         <v>46097.54999799769</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I37" s="8">
         <v>46017</v>
@@ -4008,29 +4011,29 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
       <c r="S37" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T37" s="9">
         <v>0</v>
       </c>
       <c r="U37" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B38" s="5">
         <v>46073.76783783565</v>
@@ -4042,16 +4045,16 @@
         <v>46097.55002008102</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I38" s="5">
         <v>46017</v>
@@ -4069,29 +4072,29 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
       <c r="S38" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T38" s="6">
         <v>0</v>
       </c>
       <c r="U38" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B39" s="8">
         <v>46073.76783806713</v>
@@ -4103,16 +4106,16 @@
         <v>46097.550347881945</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I39" s="8">
         <v>46010</v>
@@ -4130,13 +4133,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q39" s="8">
         <v>46010</v>
@@ -4156,7 +4159,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B40" s="5">
         <v>46073.76783829861</v>
@@ -4168,16 +4171,16 @@
         <v>46097.55025519676</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I40" s="5">
         <v>46010</v>
@@ -4195,29 +4198,29 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
       <c r="S40" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T40" s="6">
         <v>0</v>
       </c>
       <c r="U40" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B41" s="8">
         <v>46073.76783851851</v>
@@ -4229,16 +4232,16 @@
         <v>46097.550321400464</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I41" s="8">
         <v>46021</v>
@@ -4256,29 +4259,29 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
       <c r="S41" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T41" s="9">
         <v>0</v>
       </c>
       <c r="U41" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B42" s="5">
         <v>46073.76783873842</v>
@@ -4290,7 +4293,7 @@
         <v>46192.76244386574</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>25</v>
@@ -4314,7 +4317,7 @@
         <v>26</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4331,7 +4334,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B43" s="8">
         <v>46073.76783896991</v>
@@ -4343,16 +4346,16 @@
         <v>46097.814911249996</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I43" s="8">
         <v>46007</v>
@@ -4370,13 +4373,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O43" s="9" t="s">
         <v>65</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q43" s="8">
         <v>46007</v>
@@ -4396,7 +4399,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B44" s="5">
         <v>46073.76783739583</v>
@@ -4408,16 +4411,16 @@
         <v>46097.8150140162</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I44" s="5">
         <v>46028</v>
@@ -4435,13 +4438,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q44" s="5">
         <v>46028</v>
@@ -4461,7 +4464,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B45" s="8">
         <v>46090.4939284838</v>
@@ -4473,16 +4476,16 @@
         <v>46097.815063622686</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I45" s="9"/>
       <c r="J45" s="8">
@@ -4498,13 +4501,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q45" s="8">
         <v>46035</v>
@@ -4524,7 +4527,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B46" s="5">
         <v>46090.493990891206</v>
@@ -4536,16 +4539,16 @@
         <v>46192.76208826389</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I46" s="6"/>
       <c r="J46" s="5">
@@ -4561,10 +4564,10 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4582,12 +4585,12 @@
         <v>1</v>
       </c>
       <c r="U46" s="12" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B47" s="8">
         <v>46128.56674524306</v>
@@ -4599,16 +4602,16 @@
         <v>46192.7619153125</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I47" s="9"/>
       <c r="J47" s="8">
@@ -4624,13 +4627,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q47" s="9"/>
       <c r="R47" s="9"/>
@@ -4640,7 +4643,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B48" s="5">
         <v>46128.566755555556</v>
@@ -4652,16 +4655,16 @@
         <v>46192.76205100694</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I48" s="6"/>
       <c r="J48" s="5">
@@ -4677,13 +4680,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4693,7 +4696,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B49" s="8">
         <v>46128.56676210648</v>
@@ -4705,16 +4708,16 @@
         <v>46192.76205135416</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I49" s="9"/>
       <c r="J49" s="8">
@@ -4730,13 +4733,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q49" s="9"/>
       <c r="R49" s="9"/>
@@ -4746,7 +4749,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B50" s="5">
         <v>46128.56676847222</v>
@@ -4758,16 +4761,16 @@
         <v>46192.762051655096</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I50" s="6"/>
       <c r="J50" s="5">
@@ -4783,13 +4786,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4799,7 +4802,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B51" s="8">
         <v>46128.566774120365</v>
@@ -4811,16 +4814,16 @@
         <v>46192.762051990736</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I51" s="9"/>
       <c r="J51" s="8">
@@ -4836,13 +4839,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -4852,7 +4855,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B52" s="5">
         <v>46128.566780127316</v>
@@ -4864,16 +4867,16 @@
         <v>46192.76205229167</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -4889,13 +4892,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4905,7 +4908,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B53" s="8">
         <v>46128.56678613426</v>
@@ -4917,16 +4920,16 @@
         <v>46192.762052569444</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I53" s="9"/>
       <c r="J53" s="8">
@@ -4942,13 +4945,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -4958,7 +4961,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B54" s="5">
         <v>46128.566790682875</v>
@@ -4970,16 +4973,16 @@
         <v>46192.7620528588</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I54" s="6"/>
       <c r="J54" s="5">
@@ -4995,13 +4998,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -5011,7 +5014,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B55" s="8">
         <v>46128.5667968287</v>
@@ -5023,16 +5026,16 @@
         <v>46192.76205314815</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I55" s="9"/>
       <c r="J55" s="8">
@@ -5048,13 +5051,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q55" s="9"/>
       <c r="R55" s="9"/>
@@ -5064,7 +5067,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B56" s="5">
         <v>46128.56680166667</v>
@@ -5076,16 +5079,16 @@
         <v>46192.76205344907</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I56" s="6"/>
       <c r="J56" s="5">
@@ -5101,13 +5104,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -5117,7 +5120,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B57" s="8">
         <v>46128.566807256946</v>
@@ -5129,16 +5132,16 @@
         <v>46192.762053784725</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I57" s="9"/>
       <c r="J57" s="8">
@@ -5154,13 +5157,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q57" s="9"/>
       <c r="R57" s="9"/>
@@ -5170,7 +5173,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B58" s="5">
         <v>46128.56681135416</v>
@@ -5182,16 +5185,16 @@
         <v>46192.762054108796</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I58" s="6"/>
       <c r="J58" s="5">
@@ -5207,13 +5210,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -5223,7 +5226,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B59" s="8">
         <v>46073.76783778935</v>
@@ -5235,7 +5238,7 @@
         <v>46097.81565780092</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>25</v>
@@ -5259,7 +5262,7 @@
         <v>26</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P59" s="9" t="s">
         <v>26</v>
@@ -5276,7 +5279,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B60" s="5">
         <v>46073.767838078704</v>
@@ -5288,16 +5291,16 @@
         <v>46097.81529010416</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I60" s="5">
         <v>46041</v>
@@ -5315,13 +5318,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q60" s="5">
         <v>46041</v>
@@ -5341,7 +5344,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B61" s="8">
         <v>46073.7678383912</v>
@@ -5353,16 +5356,16 @@
         <v>46097.81562871528</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I61" s="8">
         <v>46043</v>
@@ -5380,13 +5383,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q61" s="8">
         <v>46043</v>
@@ -5406,7 +5409,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B62" s="5">
         <v>46073.76783866898</v>
@@ -5418,7 +5421,7 @@
         <v>46191.77291996528</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>25</v>
@@ -5442,7 +5445,7 @@
         <v>26</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>26</v>
@@ -5459,7 +5462,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B63" s="8">
         <v>46073.767838935186</v>
@@ -5471,16 +5474,16 @@
         <v>46128.58222162037</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I63" s="8">
         <v>46045</v>
@@ -5498,13 +5501,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q63" s="8">
         <v>46045</v>
@@ -5524,7 +5527,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B64" s="5">
         <v>46073.76783921296</v>
@@ -5536,16 +5539,16 @@
         <v>46158.97116490741</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I64" s="5">
         <v>46050</v>
@@ -5563,13 +5566,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q64" s="5">
         <v>46050</v>
@@ -5584,12 +5587,12 @@
         <v>1</v>
       </c>
       <c r="U64" s="12" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B65" s="8">
         <v>46128.56456767361</v>
@@ -5601,16 +5604,16 @@
         <v>46129.68420498843</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I65" s="8">
         <v>46050</v>
@@ -5628,13 +5631,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q65" s="9"/>
       <c r="R65" s="9"/>
@@ -5644,7 +5647,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B66" s="5">
         <v>46128.56458466435</v>
@@ -5656,16 +5659,16 @@
         <v>46129.684215497684</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I66" s="5">
         <v>46050</v>
@@ -5683,13 +5686,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5699,7 +5702,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B67" s="8">
         <v>46128.56459681713</v>
@@ -5711,16 +5714,16 @@
         <v>46129.68427572917</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I67" s="8">
         <v>46050</v>
@@ -5738,13 +5741,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q67" s="9"/>
       <c r="R67" s="9"/>
@@ -5754,7 +5757,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B68" s="5">
         <v>46128.564601666665</v>
@@ -5766,16 +5769,16 @@
         <v>46129.68422782407</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I68" s="5">
         <v>46050</v>
@@ -5793,13 +5796,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5809,7 +5812,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B69" s="8">
         <v>46128.56463256944</v>
@@ -5821,16 +5824,16 @@
         <v>46129.684293784725</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I69" s="8">
         <v>46050</v>
@@ -5848,13 +5851,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q69" s="9"/>
       <c r="R69" s="9"/>
@@ -5864,7 +5867,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B70" s="5">
         <v>46128.56464445602</v>
@@ -5876,16 +5879,16 @@
         <v>46129.68430454861</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I70" s="5">
         <v>46050</v>
@@ -5903,13 +5906,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5919,7 +5922,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B71" s="8">
         <v>46128.56465615741</v>
@@ -5931,16 +5934,16 @@
         <v>46146.89516151621</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I71" s="8">
         <v>46050</v>
@@ -5958,13 +5961,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q71" s="9"/>
       <c r="R71" s="9"/>
@@ -5974,7 +5977,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B72" s="5">
         <v>46128.564667314815</v>
@@ -5986,16 +5989,16 @@
         <v>46146.89517496528</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I72" s="5">
         <v>46050</v>
@@ -6013,13 +6016,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -6029,7 +6032,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B73" s="8">
         <v>46128.56467849537</v>
@@ -6041,16 +6044,16 @@
         <v>46146.895229745365</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I73" s="8">
         <v>46050</v>
@@ -6068,13 +6071,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q73" s="9"/>
       <c r="R73" s="9"/>
@@ -6084,7 +6087,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B74" s="5">
         <v>46128.56469162037</v>
@@ -6096,16 +6099,16 @@
         <v>46146.8951958449</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I74" s="5">
         <v>46050</v>
@@ -6123,13 +6126,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6139,7 +6142,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B75" s="8">
         <v>46128.5647016088</v>
@@ -6151,16 +6154,16 @@
         <v>46146.8953142824</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I75" s="8">
         <v>46050</v>
@@ -6178,13 +6181,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q75" s="9"/>
       <c r="R75" s="9"/>
@@ -6194,7 +6197,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B76" s="5">
         <v>46128.56471310185</v>
@@ -6206,16 +6209,16 @@
         <v>46146.895330486106</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I76" s="5">
         <v>46050</v>
@@ -6233,13 +6236,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6249,7 +6252,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B77" s="8">
         <v>46073.76783949074</v>
@@ -6261,16 +6264,16 @@
         <v>46158.971930879634</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I77" s="9"/>
       <c r="J77" s="8">
@@ -6286,13 +6289,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q77" s="8">
         <v>46055</v>
@@ -6307,12 +6310,12 @@
         <v>1</v>
       </c>
       <c r="U77" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B78" s="5">
         <v>46128.565652731486</v>
@@ -6324,16 +6327,16 @@
         <v>46129.6858422338</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I78" s="6"/>
       <c r="J78" s="5">
@@ -6349,13 +6352,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6365,7 +6368,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B79" s="8">
         <v>46128.5656710301</v>
@@ -6377,16 +6380,16 @@
         <v>46129.68585466435</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I79" s="9"/>
       <c r="J79" s="8">
@@ -6402,13 +6405,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q79" s="9"/>
       <c r="R79" s="9"/>
@@ -6418,7 +6421,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B80" s="5">
         <v>46128.56567894676</v>
@@ -6430,16 +6433,16 @@
         <v>46129.68589648148</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I80" s="6"/>
       <c r="J80" s="5">
@@ -6455,13 +6458,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6471,7 +6474,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B81" s="8">
         <v>46128.565685671296</v>
@@ -6483,16 +6486,16 @@
         <v>46129.685910949076</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I81" s="9"/>
       <c r="J81" s="8">
@@ -6508,13 +6511,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q81" s="9"/>
       <c r="R81" s="9"/>
@@ -6524,7 +6527,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B82" s="5">
         <v>46128.5656928588</v>
@@ -6536,16 +6539,16 @@
         <v>46129.68592581019</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I82" s="6"/>
       <c r="J82" s="5">
@@ -6561,13 +6564,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6577,7 +6580,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B83" s="8">
         <v>46128.56569912037</v>
@@ -6589,16 +6592,16 @@
         <v>46129.68595777778</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I83" s="9"/>
       <c r="J83" s="8">
@@ -6614,13 +6617,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -6630,7 +6633,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B84" s="5">
         <v>46128.56570560185</v>
@@ -6642,16 +6645,16 @@
         <v>46146.897389502315</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I84" s="6"/>
       <c r="J84" s="5">
@@ -6667,13 +6670,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6683,7 +6686,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B85" s="8">
         <v>46128.56571177083</v>
@@ -6695,16 +6698,16 @@
         <v>46146.89739724537</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I85" s="9"/>
       <c r="J85" s="8">
@@ -6720,13 +6723,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q85" s="9"/>
       <c r="R85" s="9"/>
@@ -6736,7 +6739,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B86" s="5">
         <v>46128.565718275466</v>
@@ -6748,16 +6751,16 @@
         <v>46146.89740662037</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I86" s="6"/>
       <c r="J86" s="5">
@@ -6773,13 +6776,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6789,7 +6792,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B87" s="8">
         <v>46128.565725266206</v>
@@ -6801,16 +6804,16 @@
         <v>46158.971886354164</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I87" s="9"/>
       <c r="J87" s="8">
@@ -6826,13 +6829,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q87" s="9"/>
       <c r="R87" s="9"/>
@@ -6842,7 +6845,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B88" s="5">
         <v>46128.56573148148</v>
@@ -6854,16 +6857,16 @@
         <v>46158.971913587964</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I88" s="6"/>
       <c r="J88" s="5">
@@ -6879,13 +6882,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6895,7 +6898,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B89" s="8">
         <v>46128.56573783565</v>
@@ -6907,16 +6910,16 @@
         <v>46158.971926909726</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I89" s="9"/>
       <c r="J89" s="8">
@@ -6932,13 +6935,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q89" s="9"/>
       <c r="R89" s="9"/>
@@ -6948,7 +6951,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B90" s="5">
         <v>46073.76783978009</v>
@@ -6960,7 +6963,7 @@
         <v>46191.79356716435</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>25</v>
@@ -6984,7 +6987,7 @@
         <v>26</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>26</v>
@@ -7001,7 +7004,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B91" s="8">
         <v>46073.76784008102</v>
@@ -7013,16 +7016,16 @@
         <v>46157.499330590275</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I91" s="9"/>
       <c r="J91" s="8">
@@ -7038,13 +7041,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q91" s="8">
         <v>46030</v>
@@ -7059,12 +7062,12 @@
         <v>0.2</v>
       </c>
       <c r="U91" s="12" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B92" s="5">
         <v>46073.7678375463</v>
@@ -7082,10 +7085,10 @@
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I92" s="5">
         <v>46069</v>
@@ -7103,13 +7106,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q92" s="5">
         <v>46069</v>
@@ -7129,7 +7132,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B93" s="8">
         <v>46073.76783789352</v>
@@ -7141,16 +7144,16 @@
         <v>46157.49918305555</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H93" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I93" s="9"/>
       <c r="J93" s="8">
@@ -7166,13 +7169,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q93" s="8">
         <v>46014</v>
@@ -7187,12 +7190,12 @@
         <v>0</v>
       </c>
       <c r="U93" s="12" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B94" s="5">
         <v>46073.7678381713</v>
@@ -7204,16 +7207,16 @@
         <v>46122.658478576384</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I94" s="6"/>
       <c r="J94" s="5">
@@ -7229,13 +7232,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q94" s="5">
         <v>46048</v>
@@ -7255,7 +7258,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B95" s="8">
         <v>46073.7678384375</v>
@@ -7267,7 +7270,7 @@
         <v>46191.79544686343</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>25</v>
@@ -7291,7 +7294,7 @@
         <v>26</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P95" s="9" t="s">
         <v>26</v>
@@ -7308,7 +7311,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B96" s="5">
         <v>46073.76783871528</v>
@@ -7320,7 +7323,7 @@
         <v>46223.808940138886</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7329,7 +7332,7 @@
         <v>85</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I96" s="5">
         <v>46056</v>
@@ -7347,13 +7350,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q96" s="5">
         <v>46056</v>
@@ -7373,7 +7376,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B97" s="8">
         <v>46128.56582575232</v>
@@ -7385,7 +7388,7 @@
         <v>46223.80910453704</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
@@ -7394,7 +7397,7 @@
         <v>85</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I97" s="8">
         <v>46056</v>
@@ -7412,13 +7415,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q97" s="9"/>
       <c r="R97" s="9"/>
@@ -7428,7 +7431,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B98" s="5">
         <v>46128.565833877314</v>
@@ -7440,7 +7443,7 @@
         <v>46223.80910135417</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7449,7 +7452,7 @@
         <v>85</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I98" s="5">
         <v>46056</v>
@@ -7467,13 +7470,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7483,7 +7486,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B99" s="8">
         <v>46128.56583952546</v>
@@ -7495,7 +7498,7 @@
         <v>46223.80909796296</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
@@ -7504,7 +7507,7 @@
         <v>85</v>
       </c>
       <c r="H99" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I99" s="8">
         <v>46056</v>
@@ -7522,13 +7525,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q99" s="9"/>
       <c r="R99" s="9"/>
@@ -7538,7 +7541,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B100" s="5">
         <v>46128.56584787037</v>
@@ -7550,7 +7553,7 @@
         <v>46223.809095046294</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7559,7 +7562,7 @@
         <v>85</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I100" s="5">
         <v>46056</v>
@@ -7577,13 +7580,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7593,7 +7596,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B101" s="8">
         <v>46128.565854120374</v>
@@ -7605,7 +7608,7 @@
         <v>46223.809091620366</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
@@ -7614,7 +7617,7 @@
         <v>85</v>
       </c>
       <c r="H101" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I101" s="8">
         <v>46056</v>
@@ -7632,13 +7635,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -7648,7 +7651,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B102" s="5">
         <v>46128.565860069444</v>
@@ -7660,7 +7663,7 @@
         <v>46223.80908827546</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7669,7 +7672,7 @@
         <v>85</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I102" s="5">
         <v>46056</v>
@@ -7687,13 +7690,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7703,7 +7706,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B103" s="8">
         <v>46128.56586609954</v>
@@ -7715,7 +7718,7 @@
         <v>46223.80908491898</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
@@ -7724,7 +7727,7 @@
         <v>85</v>
       </c>
       <c r="H103" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I103" s="8">
         <v>46056</v>
@@ -7742,13 +7745,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q103" s="9"/>
       <c r="R103" s="9"/>
@@ -7758,7 +7761,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B104" s="5">
         <v>46128.56587251158</v>
@@ -7770,7 +7773,7 @@
         <v>46223.809081342595</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7779,7 +7782,7 @@
         <v>85</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I104" s="5">
         <v>46056</v>
@@ -7797,13 +7800,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7813,7 +7816,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B105" s="8">
         <v>46128.56587943287</v>
@@ -7825,7 +7828,7 @@
         <v>46223.80906777778</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
@@ -7834,7 +7837,7 @@
         <v>85</v>
       </c>
       <c r="H105" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I105" s="8">
         <v>46056</v>
@@ -7852,13 +7855,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P105" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q105" s="9"/>
       <c r="R105" s="9"/>
@@ -7868,7 +7871,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B106" s="5">
         <v>46128.565885625</v>
@@ -7880,7 +7883,7 @@
         <v>46223.809067152775</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7889,7 +7892,7 @@
         <v>85</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I106" s="5">
         <v>46056</v>
@@ -7907,13 +7910,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7923,7 +7926,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B107" s="8">
         <v>46128.56589248843</v>
@@ -7935,7 +7938,7 @@
         <v>46223.8090665162</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
@@ -7944,7 +7947,7 @@
         <v>85</v>
       </c>
       <c r="H107" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I107" s="8">
         <v>46056</v>
@@ -7962,13 +7965,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q107" s="9"/>
       <c r="R107" s="9"/>
@@ -7978,7 +7981,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B108" s="5">
         <v>46128.56589891204</v>
@@ -7990,7 +7993,7 @@
         <v>46223.80906591435</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7999,7 +8002,7 @@
         <v>85</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I108" s="5">
         <v>46056</v>
@@ -8017,13 +8020,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -8033,7 +8036,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B109" s="8">
         <v>46073.76783924768</v>
@@ -8045,7 +8048,7 @@
         <v>46223.80893586806</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
@@ -8054,7 +8057,7 @@
         <v>85</v>
       </c>
       <c r="H109" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I109" s="9"/>
       <c r="J109" s="8">
@@ -8070,13 +8073,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P109" s="9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q109" s="8">
         <v>46063</v>
@@ -8096,7 +8099,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B110" s="5">
         <v>46128.565956562496</v>
@@ -8108,7 +8111,7 @@
         <v>46223.809273425926</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -8117,7 +8120,7 @@
         <v>85</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I110" s="6"/>
       <c r="J110" s="5">
@@ -8133,13 +8136,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8149,7 +8152,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B111" s="8">
         <v>46128.565968229166</v>
@@ -8161,7 +8164,7 @@
         <v>46223.80927013889</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
@@ -8170,7 +8173,7 @@
         <v>85</v>
       </c>
       <c r="H111" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I111" s="9"/>
       <c r="J111" s="8">
@@ -8186,13 +8189,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q111" s="9"/>
       <c r="R111" s="9"/>
@@ -8202,7 +8205,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B112" s="5">
         <v>46128.565975833335</v>
@@ -8214,7 +8217,7 @@
         <v>46223.80926667824</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8223,7 +8226,7 @@
         <v>85</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I112" s="6"/>
       <c r="J112" s="5">
@@ -8239,13 +8242,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8255,7 +8258,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B113" s="8">
         <v>46128.56598180556</v>
@@ -8267,7 +8270,7 @@
         <v>46223.80926277778</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
@@ -8276,7 +8279,7 @@
         <v>85</v>
       </c>
       <c r="H113" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I113" s="9"/>
       <c r="J113" s="8">
@@ -8292,13 +8295,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P113" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q113" s="9"/>
       <c r="R113" s="9"/>
@@ -8308,7 +8311,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B114" s="5">
         <v>46128.56598935185</v>
@@ -8320,7 +8323,7 @@
         <v>46223.809258761576</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -8329,7 +8332,7 @@
         <v>85</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I114" s="6"/>
       <c r="J114" s="5">
@@ -8345,13 +8348,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8361,7 +8364,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B115" s="8">
         <v>46128.56599642361</v>
@@ -8373,7 +8376,7 @@
         <v>46223.809254803244</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
@@ -8382,7 +8385,7 @@
         <v>85</v>
       </c>
       <c r="H115" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I115" s="9"/>
       <c r="J115" s="8">
@@ -8398,13 +8401,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q115" s="9"/>
       <c r="R115" s="9"/>
@@ -8414,7 +8417,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B116" s="5">
         <v>46128.56600287037</v>
@@ -8426,7 +8429,7 @@
         <v>46223.809251099534</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8435,7 +8438,7 @@
         <v>85</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I116" s="6"/>
       <c r="J116" s="5">
@@ -8451,13 +8454,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8467,7 +8470,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B117" s="8">
         <v>46128.56600908565</v>
@@ -8479,7 +8482,7 @@
         <v>46223.80924743056</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
@@ -8488,7 +8491,7 @@
         <v>85</v>
       </c>
       <c r="H117" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I117" s="9"/>
       <c r="J117" s="8">
@@ -8504,13 +8507,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P117" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q117" s="9"/>
       <c r="R117" s="9"/>
@@ -8520,7 +8523,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B118" s="5">
         <v>46128.566016111115</v>
@@ -8532,7 +8535,7 @@
         <v>46223.80924328703</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8541,7 +8544,7 @@
         <v>85</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I118" s="6"/>
       <c r="J118" s="5">
@@ -8557,13 +8560,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8573,7 +8576,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B119" s="8">
         <v>46128.566022604165</v>
@@ -8585,7 +8588,7 @@
         <v>46223.80923994213</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
@@ -8594,7 +8597,7 @@
         <v>85</v>
       </c>
       <c r="H119" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I119" s="9"/>
       <c r="J119" s="8">
@@ -8610,13 +8613,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q119" s="9"/>
       <c r="R119" s="9"/>
@@ -8626,7 +8629,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B120" s="5">
         <v>46128.56602967593</v>
@@ -8638,7 +8641,7 @@
         <v>46223.80923230324</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8647,7 +8650,7 @@
         <v>85</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I120" s="6"/>
       <c r="J120" s="5">
@@ -8663,13 +8666,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8679,7 +8682,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B121" s="8">
         <v>46128.56603574074</v>
@@ -8691,7 +8694,7 @@
         <v>46223.80923167824</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
@@ -8700,7 +8703,7 @@
         <v>85</v>
       </c>
       <c r="H121" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I121" s="9"/>
       <c r="J121" s="8">
@@ -8716,13 +8719,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P121" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
@@ -8732,7 +8735,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B122" s="5">
         <v>46073.767839618056</v>
@@ -8744,7 +8747,7 @@
         <v>46223.8093071412</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8753,7 +8756,7 @@
         <v>85</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I122" s="5">
         <v>46064</v>
@@ -8771,13 +8774,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q122" s="5">
         <v>46064</v>
@@ -8792,12 +8795,12 @@
         <v>1</v>
       </c>
       <c r="U122" s="12" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B123" s="8">
         <v>46128.56608430555</v>
@@ -8809,7 +8812,7 @@
         <v>46223.809458958334</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>26</v>
@@ -8818,7 +8821,7 @@
         <v>85</v>
       </c>
       <c r="H123" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I123" s="8">
         <v>46064</v>
@@ -8836,13 +8839,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P123" s="9" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q123" s="9"/>
       <c r="R123" s="9"/>
@@ -8852,7 +8855,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B124" s="5">
         <v>46128.56609638889</v>
@@ -8864,7 +8867,7 @@
         <v>46223.80945509259</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -8873,7 +8876,7 @@
         <v>85</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I124" s="5">
         <v>46064</v>
@@ -8891,13 +8894,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8907,7 +8910,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B125" s="8">
         <v>46128.56610412037</v>
@@ -8919,7 +8922,7 @@
         <v>46223.809450925924</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
@@ -8928,7 +8931,7 @@
         <v>85</v>
       </c>
       <c r="H125" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I125" s="8">
         <v>46064</v>
@@ -8946,13 +8949,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q125" s="9"/>
       <c r="R125" s="9"/>
@@ -8962,7 +8965,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B126" s="5">
         <v>46128.5661109375</v>
@@ -8974,7 +8977,7 @@
         <v>46223.80944693287</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -8983,7 +8986,7 @@
         <v>85</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I126" s="5">
         <v>46064</v>
@@ -9001,13 +9004,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -9017,7 +9020,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B127" s="8">
         <v>46128.566116863425</v>
@@ -9029,7 +9032,7 @@
         <v>46223.80944331019</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>26</v>
@@ -9038,7 +9041,7 @@
         <v>85</v>
       </c>
       <c r="H127" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I127" s="8">
         <v>46064</v>
@@ -9056,13 +9059,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P127" s="9" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q127" s="9"/>
       <c r="R127" s="9"/>
@@ -9072,7 +9075,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B128" s="5">
         <v>46128.566123807876</v>
@@ -9084,7 +9087,7 @@
         <v>46223.80943890046</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -9093,7 +9096,7 @@
         <v>85</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I128" s="5">
         <v>46064</v>
@@ -9111,13 +9114,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9127,7 +9130,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B129" s="8">
         <v>46128.56613028936</v>
@@ -9139,7 +9142,7 @@
         <v>46223.80943525463</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>26</v>
@@ -9148,7 +9151,7 @@
         <v>85</v>
       </c>
       <c r="H129" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I129" s="8">
         <v>46064</v>
@@ -9166,13 +9169,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O129" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P129" s="9" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q129" s="9"/>
       <c r="R129" s="9"/>
@@ -9182,7 +9185,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B130" s="5">
         <v>46128.56613681713</v>
@@ -9194,7 +9197,7 @@
         <v>46223.809431435184</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -9203,7 +9206,7 @@
         <v>85</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I130" s="5">
         <v>46064</v>
@@ -9221,13 +9224,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9237,7 +9240,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B131" s="8">
         <v>46128.56614351852</v>
@@ -9249,7 +9252,7 @@
         <v>46223.80942751157</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>26</v>
@@ -9258,7 +9261,7 @@
         <v>85</v>
       </c>
       <c r="H131" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I131" s="8">
         <v>46064</v>
@@ -9276,13 +9279,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O131" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P131" s="9" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q131" s="9"/>
       <c r="R131" s="9"/>
@@ -9292,7 +9295,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B132" s="5">
         <v>46128.56614934027</v>
@@ -9304,7 +9307,7 @@
         <v>46223.80942394676</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
@@ -9313,7 +9316,7 @@
         <v>85</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I132" s="5">
         <v>46064</v>
@@ -9331,13 +9334,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9347,7 +9350,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B133" s="8">
         <v>46128.56615488426</v>
@@ -9359,7 +9362,7 @@
         <v>46223.80941592593</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>26</v>
@@ -9368,7 +9371,7 @@
         <v>85</v>
       </c>
       <c r="H133" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I133" s="8">
         <v>46064</v>
@@ -9386,13 +9389,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O133" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P133" s="9" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q133" s="9"/>
       <c r="R133" s="9"/>
@@ -9402,7 +9405,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B134" s="5">
         <v>46128.566162083334</v>
@@ -9414,7 +9417,7 @@
         <v>46223.8094153125</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
@@ -9423,7 +9426,7 @@
         <v>85</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I134" s="5">
         <v>46064</v>
@@ -9441,13 +9444,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9457,7 +9460,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B135" s="8">
         <v>46073.76783899305</v>
@@ -9469,7 +9472,7 @@
         <v>46223.80892628472</v>
       </c>
       <c r="E135" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>26</v>
@@ -9478,7 +9481,7 @@
         <v>85</v>
       </c>
       <c r="H135" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I135" s="9"/>
       <c r="J135" s="8">
@@ -9494,13 +9497,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O135" s="9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P135" s="9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q135" s="8">
         <v>46065</v>
@@ -9515,12 +9518,12 @@
         <v>1</v>
       </c>
       <c r="U135" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B136" s="5">
         <v>46128.56622929398</v>
@@ -9532,7 +9535,7 @@
         <v>46223.8099134375</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9541,7 +9544,7 @@
         <v>85</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I136" s="5">
         <v>46065</v>
@@ -9559,13 +9562,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9575,7 +9578,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B137" s="8">
         <v>46128.56623975694</v>
@@ -9587,7 +9590,7 @@
         <v>46223.809910173615</v>
       </c>
       <c r="E137" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>26</v>
@@ -9596,7 +9599,7 @@
         <v>85</v>
       </c>
       <c r="H137" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I137" s="8">
         <v>46065</v>
@@ -9614,13 +9617,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O137" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P137" s="9" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q137" s="9"/>
       <c r="R137" s="9"/>
@@ -9630,7 +9633,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B138" s="5">
         <v>46128.56624731481</v>
@@ -9642,7 +9645,7 @@
         <v>46223.80990663194</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
@@ -9651,7 +9654,7 @@
         <v>85</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I138" s="5">
         <v>46065</v>
@@ -9669,13 +9672,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9685,7 +9688,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B139" s="8">
         <v>46128.56625379629</v>
@@ -9697,7 +9700,7 @@
         <v>46223.809903506946</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
@@ -9706,7 +9709,7 @@
         <v>85</v>
       </c>
       <c r="H139" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I139" s="8">
         <v>46065</v>
@@ -9724,13 +9727,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P139" s="9" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q139" s="9"/>
       <c r="R139" s="9"/>
@@ -9740,7 +9743,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B140" s="5">
         <v>46128.56626087963</v>
@@ -9752,7 +9755,7 @@
         <v>46223.809900555556</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
@@ -9761,7 +9764,7 @@
         <v>85</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I140" s="5">
         <v>46065</v>
@@ -9779,13 +9782,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9795,7 +9798,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B141" s="8">
         <v>46128.566268298615</v>
@@ -9807,7 +9810,7 @@
         <v>46223.80989733797</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>26</v>
@@ -9816,7 +9819,7 @@
         <v>85</v>
       </c>
       <c r="H141" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I141" s="8">
         <v>46065</v>
@@ -9834,13 +9837,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O141" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P141" s="9" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q141" s="9"/>
       <c r="R141" s="9"/>
@@ -9850,7 +9853,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B142" s="5">
         <v>46128.566275324076</v>
@@ -9862,7 +9865,7 @@
         <v>46223.8098940625</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
@@ -9871,7 +9874,7 @@
         <v>85</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I142" s="5">
         <v>46065</v>
@@ -9889,13 +9892,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -9905,7 +9908,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B143" s="8">
         <v>46128.56628170139</v>
@@ -9917,7 +9920,7 @@
         <v>46223.809890185184</v>
       </c>
       <c r="E143" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F143" s="9" t="s">
         <v>26</v>
@@ -9926,7 +9929,7 @@
         <v>85</v>
       </c>
       <c r="H143" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I143" s="8">
         <v>46065</v>
@@ -9944,13 +9947,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O143" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P143" s="9" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q143" s="9"/>
       <c r="R143" s="9"/>
@@ -9960,7 +9963,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B144" s="5">
         <v>46128.56628802083</v>
@@ -9972,7 +9975,7 @@
         <v>46223.80988670139</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
@@ -9981,7 +9984,7 @@
         <v>85</v>
       </c>
       <c r="H144" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I144" s="5">
         <v>46065</v>
@@ -9999,13 +10002,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -10015,7 +10018,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B145" s="8">
         <v>46128.56629480324</v>
@@ -10027,7 +10030,7 @@
         <v>46223.80988340278</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>26</v>
@@ -10036,7 +10039,7 @@
         <v>85</v>
       </c>
       <c r="H145" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I145" s="8">
         <v>46065</v>
@@ -10054,13 +10057,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P145" s="9" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q145" s="9"/>
       <c r="R145" s="9"/>
@@ -10070,7 +10073,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B146" s="5">
         <v>46128.5663033912</v>
@@ -10082,7 +10085,7 @@
         <v>46223.80987542824</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
@@ -10091,7 +10094,7 @@
         <v>85</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I146" s="5">
         <v>46065</v>
@@ -10109,13 +10112,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -10125,7 +10128,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B147" s="8">
         <v>46128.566309918984</v>
@@ -10137,7 +10140,7 @@
         <v>46223.80987479167</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>26</v>
@@ -10146,7 +10149,7 @@
         <v>85</v>
       </c>
       <c r="H147" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I147" s="8">
         <v>46065</v>
@@ -10164,13 +10167,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P147" s="9" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q147" s="9"/>
       <c r="R147" s="9"/>
@@ -10180,7 +10183,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B148" s="5">
         <v>46073.76784</v>
@@ -10192,7 +10195,7 @@
         <v>46223.80892216435</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
@@ -10201,7 +10204,7 @@
         <v>85</v>
       </c>
       <c r="H148" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I148" s="6"/>
       <c r="J148" s="5">
@@ -10217,13 +10220,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q148" s="5">
         <v>46066</v>
@@ -10238,12 +10241,12 @@
         <v>1</v>
       </c>
       <c r="U148" s="12" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B149" s="8">
         <v>46128.566370555556</v>
@@ -10255,7 +10258,7 @@
         <v>46223.81005180556</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>26</v>
@@ -10264,7 +10267,7 @@
         <v>85</v>
       </c>
       <c r="H149" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I149" s="9"/>
       <c r="J149" s="8">
@@ -10280,13 +10283,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="9" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O149" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P149" s="9" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q149" s="9"/>
       <c r="R149" s="9"/>
@@ -10296,7 +10299,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B150" s="5">
         <v>46128.56638481481</v>
@@ -10308,7 +10311,7 @@
         <v>46223.8100485301</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
@@ -10317,7 +10320,7 @@
         <v>85</v>
       </c>
       <c r="H150" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I150" s="6"/>
       <c r="J150" s="5">
@@ -10333,13 +10336,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10349,7 +10352,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B151" s="8">
         <v>46128.56639143519</v>
@@ -10361,7 +10364,7 @@
         <v>46223.810045081016</v>
       </c>
       <c r="E151" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F151" s="9" t="s">
         <v>26</v>
@@ -10370,7 +10373,7 @@
         <v>85</v>
       </c>
       <c r="H151" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I151" s="9"/>
       <c r="J151" s="8">
@@ -10386,13 +10389,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="9" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O151" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P151" s="9" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q151" s="9"/>
       <c r="R151" s="9"/>
@@ -10402,7 +10405,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B152" s="5">
         <v>46128.56639815972</v>
@@ -10414,7 +10417,7 @@
         <v>46223.81004142361</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
@@ -10423,7 +10426,7 @@
         <v>85</v>
       </c>
       <c r="H152" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I152" s="6"/>
       <c r="J152" s="5">
@@ -10439,13 +10442,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q152" s="6"/>
       <c r="R152" s="6"/>
@@ -10455,7 +10458,7 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B153" s="8">
         <v>46128.566405729165</v>
@@ -10467,7 +10470,7 @@
         <v>46223.81003804399</v>
       </c>
       <c r="E153" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F153" s="9" t="s">
         <v>26</v>
@@ -10476,7 +10479,7 @@
         <v>85</v>
       </c>
       <c r="H153" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I153" s="9"/>
       <c r="J153" s="8">
@@ -10492,13 +10495,13 @@
         <v>26</v>
       </c>
       <c r="N153" s="9" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O153" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P153" s="9" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q153" s="9"/>
       <c r="R153" s="9"/>
@@ -10508,7 +10511,7 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B154" s="5">
         <v>46128.566412581014</v>
@@ -10520,7 +10523,7 @@
         <v>46223.81003443287</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>26</v>
@@ -10529,7 +10532,7 @@
         <v>85</v>
       </c>
       <c r="H154" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I154" s="6"/>
       <c r="J154" s="5">
@@ -10545,13 +10548,13 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q154" s="6"/>
       <c r="R154" s="6"/>
@@ -10561,7 +10564,7 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="7" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B155" s="8">
         <v>46128.56641917824</v>
@@ -10573,7 +10576,7 @@
         <v>46223.81003021991</v>
       </c>
       <c r="E155" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F155" s="9" t="s">
         <v>26</v>
@@ -10582,7 +10585,7 @@
         <v>85</v>
       </c>
       <c r="H155" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I155" s="9"/>
       <c r="J155" s="8">
@@ -10598,13 +10601,13 @@
         <v>26</v>
       </c>
       <c r="N155" s="9" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O155" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P155" s="9" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q155" s="9"/>
       <c r="R155" s="9"/>
@@ -10614,7 +10617,7 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B156" s="5">
         <v>46128.566427337966</v>
@@ -10626,7 +10629,7 @@
         <v>46223.81002679398</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
@@ -10635,7 +10638,7 @@
         <v>85</v>
       </c>
       <c r="H156" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I156" s="6"/>
       <c r="J156" s="5">
@@ -10651,13 +10654,13 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P156" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q156" s="6"/>
       <c r="R156" s="6"/>
@@ -10667,7 +10670,7 @@
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B157" s="8">
         <v>46128.566433761574</v>
@@ -10679,7 +10682,7 @@
         <v>46223.81002371528</v>
       </c>
       <c r="E157" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F157" s="9" t="s">
         <v>26</v>
@@ -10688,7 +10691,7 @@
         <v>85</v>
       </c>
       <c r="H157" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I157" s="9"/>
       <c r="J157" s="8">
@@ -10704,13 +10707,13 @@
         <v>26</v>
       </c>
       <c r="N157" s="9" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O157" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P157" s="9" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q157" s="9"/>
       <c r="R157" s="9"/>
@@ -10720,7 +10723,7 @@
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B158" s="5">
         <v>46128.56643997685</v>
@@ -10732,7 +10735,7 @@
         <v>46223.81002017361</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
@@ -10741,7 +10744,7 @@
         <v>85</v>
       </c>
       <c r="H158" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I158" s="6"/>
       <c r="J158" s="5">
@@ -10757,13 +10760,13 @@
         <v>26</v>
       </c>
       <c r="N158" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P158" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q158" s="6"/>
       <c r="R158" s="6"/>
@@ -10773,7 +10776,7 @@
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="7" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B159" s="8">
         <v>46128.56644631944</v>
@@ -10785,7 +10788,7 @@
         <v>46223.810012511574</v>
       </c>
       <c r="E159" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F159" s="9" t="s">
         <v>26</v>
@@ -10794,7 +10797,7 @@
         <v>85</v>
       </c>
       <c r="H159" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I159" s="9"/>
       <c r="J159" s="8">
@@ -10810,13 +10813,13 @@
         <v>26</v>
       </c>
       <c r="N159" s="9" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O159" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P159" s="9" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q159" s="9"/>
       <c r="R159" s="9"/>
@@ -10826,7 +10829,7 @@
     </row>
     <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B160" s="5">
         <v>46128.56645381944</v>
@@ -10838,7 +10841,7 @@
         <v>46223.81001190972</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>26</v>
@@ -10847,7 +10850,7 @@
         <v>85</v>
       </c>
       <c r="H160" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I160" s="6"/>
       <c r="J160" s="5">
@@ -10863,13 +10866,13 @@
         <v>26</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O160" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P160" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q160" s="6"/>
       <c r="R160" s="6"/>
@@ -10879,7 +10882,7 @@
     </row>
     <row r="161" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A161" s="7" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B161" s="8">
         <v>46073.76784028935</v>
@@ -10891,7 +10894,7 @@
         <v>46223.80891503472</v>
       </c>
       <c r="E161" s="9" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F161" s="9" t="s">
         <v>26</v>
@@ -10900,7 +10903,7 @@
         <v>85</v>
       </c>
       <c r="H161" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I161" s="9"/>
       <c r="J161" s="8">
@@ -10916,13 +10919,13 @@
         <v>26</v>
       </c>
       <c r="N161" s="9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O161" s="9" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P161" s="9" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q161" s="8">
         <v>46070</v>
@@ -10937,12 +10940,12 @@
         <v>1</v>
       </c>
       <c r="U161" s="12" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B162" s="5">
         <v>46128.566525625</v>
@@ -10954,7 +10957,7 @@
         <v>46223.810196631945</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F162" s="6" t="s">
         <v>26</v>
@@ -10963,7 +10966,7 @@
         <v>85</v>
       </c>
       <c r="H162" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I162" s="6"/>
       <c r="J162" s="5">
@@ -10979,13 +10982,13 @@
         <v>26</v>
       </c>
       <c r="N162" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O162" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P162" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q162" s="6"/>
       <c r="R162" s="6"/>
@@ -10995,7 +10998,7 @@
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A163" s="7" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B163" s="8">
         <v>46128.566532013894</v>
@@ -11007,7 +11010,7 @@
         <v>46223.81019344907</v>
       </c>
       <c r="E163" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F163" s="9" t="s">
         <v>26</v>
@@ -11016,7 +11019,7 @@
         <v>85</v>
       </c>
       <c r="H163" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I163" s="9"/>
       <c r="J163" s="8">
@@ -11032,13 +11035,13 @@
         <v>26</v>
       </c>
       <c r="N163" s="9" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O163" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P163" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q163" s="9"/>
       <c r="R163" s="9"/>
@@ -11048,7 +11051,7 @@
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B164" s="5">
         <v>46128.566539224536</v>
@@ -11060,7 +11063,7 @@
         <v>46223.81019019676</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>26</v>
@@ -11069,7 +11072,7 @@
         <v>85</v>
       </c>
       <c r="H164" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I164" s="6"/>
       <c r="J164" s="5">
@@ -11085,13 +11088,13 @@
         <v>26</v>
       </c>
       <c r="N164" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O164" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P164" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q164" s="6"/>
       <c r="R164" s="6"/>
@@ -11101,7 +11104,7 @@
     </row>
     <row r="165" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A165" s="7" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B165" s="8">
         <v>46128.56654532407</v>
@@ -11113,7 +11116,7 @@
         <v>46223.81018667824</v>
       </c>
       <c r="E165" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F165" s="9" t="s">
         <v>26</v>
@@ -11122,7 +11125,7 @@
         <v>85</v>
       </c>
       <c r="H165" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I165" s="9"/>
       <c r="J165" s="8">
@@ -11138,13 +11141,13 @@
         <v>26</v>
       </c>
       <c r="N165" s="9" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O165" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P165" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q165" s="9"/>
       <c r="R165" s="9"/>
@@ -11154,7 +11157,7 @@
     </row>
     <row r="166" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B166" s="5">
         <v>46128.566551689815</v>
@@ -11166,7 +11169,7 @@
         <v>46223.810183333335</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>26</v>
@@ -11175,7 +11178,7 @@
         <v>85</v>
       </c>
       <c r="H166" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I166" s="6"/>
       <c r="J166" s="5">
@@ -11191,13 +11194,13 @@
         <v>26</v>
       </c>
       <c r="N166" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O166" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P166" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q166" s="6"/>
       <c r="R166" s="6"/>
@@ -11207,7 +11210,7 @@
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A167" s="7" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B167" s="8">
         <v>46128.56655853009</v>
@@ -11219,7 +11222,7 @@
         <v>46223.81017978009</v>
       </c>
       <c r="E167" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F167" s="9" t="s">
         <v>26</v>
@@ -11228,7 +11231,7 @@
         <v>85</v>
       </c>
       <c r="H167" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I167" s="9"/>
       <c r="J167" s="8">
@@ -11244,13 +11247,13 @@
         <v>26</v>
       </c>
       <c r="N167" s="9" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O167" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P167" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q167" s="9"/>
       <c r="R167" s="9"/>
@@ -11260,7 +11263,7 @@
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B168" s="5">
         <v>46128.56656431713</v>
@@ -11272,7 +11275,7 @@
         <v>46223.81017621528</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>26</v>
@@ -11281,7 +11284,7 @@
         <v>85</v>
       </c>
       <c r="H168" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I168" s="6"/>
       <c r="J168" s="5">
@@ -11297,13 +11300,13 @@
         <v>26</v>
       </c>
       <c r="N168" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O168" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P168" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q168" s="6"/>
       <c r="R168" s="6"/>
@@ -11313,7 +11316,7 @@
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A169" s="7" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B169" s="8">
         <v>46128.56657081019</v>
@@ -11325,7 +11328,7 @@
         <v>46223.810172708334</v>
       </c>
       <c r="E169" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F169" s="9" t="s">
         <v>26</v>
@@ -11334,7 +11337,7 @@
         <v>85</v>
       </c>
       <c r="H169" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I169" s="9"/>
       <c r="J169" s="8">
@@ -11350,13 +11353,13 @@
         <v>26</v>
       </c>
       <c r="N169" s="9" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O169" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P169" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q169" s="9"/>
       <c r="R169" s="9"/>
@@ -11366,7 +11369,7 @@
     </row>
     <row r="170" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B170" s="5">
         <v>46128.56657746527</v>
@@ -11378,7 +11381,7 @@
         <v>46223.81016853009</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>26</v>
@@ -11387,7 +11390,7 @@
         <v>85</v>
       </c>
       <c r="H170" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I170" s="6"/>
       <c r="J170" s="5">
@@ -11403,13 +11406,13 @@
         <v>26</v>
       </c>
       <c r="N170" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O170" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P170" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q170" s="6"/>
       <c r="R170" s="6"/>
@@ -11419,7 +11422,7 @@
     </row>
     <row r="171" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A171" s="7" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B171" s="8">
         <v>46128.566583113425</v>
@@ -11431,7 +11434,7 @@
         <v>46223.81016511574</v>
       </c>
       <c r="E171" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F171" s="9" t="s">
         <v>26</v>
@@ -11440,7 +11443,7 @@
         <v>85</v>
       </c>
       <c r="H171" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I171" s="9"/>
       <c r="J171" s="8">
@@ -11456,13 +11459,13 @@
         <v>26</v>
       </c>
       <c r="N171" s="9" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O171" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P171" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q171" s="9"/>
       <c r="R171" s="9"/>
@@ -11472,7 +11475,7 @@
     </row>
     <row r="172" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B172" s="5">
         <v>46128.56659069445</v>
@@ -11484,7 +11487,7 @@
         <v>46223.8101528588</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F172" s="6" t="s">
         <v>26</v>
@@ -11493,7 +11496,7 @@
         <v>85</v>
       </c>
       <c r="H172" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I172" s="6"/>
       <c r="J172" s="5">
@@ -11509,13 +11512,13 @@
         <v>26</v>
       </c>
       <c r="N172" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O172" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P172" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q172" s="6"/>
       <c r="R172" s="6"/>
@@ -11525,7 +11528,7 @@
     </row>
     <row r="173" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A173" s="7" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B173" s="8">
         <v>46128.56659782407</v>
@@ -11537,7 +11540,7 @@
         <v>46223.810152245365</v>
       </c>
       <c r="E173" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F173" s="9" t="s">
         <v>26</v>
@@ -11546,7 +11549,7 @@
         <v>85</v>
       </c>
       <c r="H173" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I173" s="9"/>
       <c r="J173" s="8">
@@ -11562,13 +11565,13 @@
         <v>26</v>
       </c>
       <c r="N173" s="9" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O173" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P173" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q173" s="9"/>
       <c r="R173" s="9"/>
@@ -11578,7 +11581,7 @@
     </row>
     <row r="174" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B174" s="5">
         <v>46073.767837719904</v>
@@ -11590,7 +11593,7 @@
         <v>46193.561065925926</v>
       </c>
       <c r="E174" s="6" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F174" s="6" t="s">
         <v>25</v>
@@ -11614,7 +11617,7 @@
         <v>26</v>
       </c>
       <c r="O174" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="P174" s="6" t="s">
         <v>26</v>
@@ -11626,12 +11629,12 @@
         <v>1</v>
       </c>
       <c r="U174" s="12" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="175" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A175" s="7" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B175" s="8">
         <v>46073.76783810185</v>
@@ -11643,16 +11646,16 @@
         <v>46194.709360277775</v>
       </c>
       <c r="E175" s="9" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F175" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G175" s="9" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H175" s="9" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I175" s="8">
         <v>46071</v>
@@ -11670,13 +11673,13 @@
         <v>26</v>
       </c>
       <c r="N175" s="9" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O175" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P175" s="9" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q175" s="8">
         <v>46071</v>
@@ -11691,12 +11694,12 @@
         <v>1</v>
       </c>
       <c r="U175" s="12" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="176" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B176" s="5">
         <v>46128.56704659722</v>
@@ -11708,16 +11711,16 @@
         <v>46194.70208606482</v>
       </c>
       <c r="E176" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F176" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G176" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H176" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I176" s="6"/>
       <c r="J176" s="5">
@@ -11733,13 +11736,13 @@
         <v>26</v>
       </c>
       <c r="N176" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O176" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P176" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q176" s="6"/>
       <c r="R176" s="6"/>
@@ -11749,7 +11752,7 @@
     </row>
     <row r="177" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A177" s="7" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B177" s="8">
         <v>46128.56705305555</v>
@@ -11761,16 +11764,16 @@
         <v>46194.70208699074</v>
       </c>
       <c r="E177" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F177" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G177" s="9" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H177" s="9" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I177" s="9"/>
       <c r="J177" s="8">
@@ -11786,13 +11789,13 @@
         <v>26</v>
       </c>
       <c r="N177" s="9" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O177" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P177" s="9" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q177" s="9"/>
       <c r="R177" s="9"/>
@@ -11802,7 +11805,7 @@
     </row>
     <row r="178" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B178" s="5">
         <v>46128.567060127316</v>
@@ -11814,16 +11817,16 @@
         <v>46194.702087638885</v>
       </c>
       <c r="E178" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F178" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G178" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H178" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I178" s="6"/>
       <c r="J178" s="5">
@@ -11839,13 +11842,13 @@
         <v>26</v>
       </c>
       <c r="N178" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O178" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P178" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q178" s="6"/>
       <c r="R178" s="6"/>
@@ -11855,7 +11858,7 @@
     </row>
     <row r="179" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A179" s="7" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B179" s="8">
         <v>46128.56706601851</v>
@@ -11867,16 +11870,16 @@
         <v>46194.70208831019</v>
       </c>
       <c r="E179" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F179" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G179" s="9" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H179" s="9" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I179" s="9"/>
       <c r="J179" s="8">
@@ -11892,13 +11895,13 @@
         <v>26</v>
       </c>
       <c r="N179" s="9" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O179" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P179" s="9" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q179" s="9"/>
       <c r="R179" s="9"/>
@@ -11908,7 +11911,7 @@
     </row>
     <row r="180" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B180" s="5">
         <v>46128.56707302084</v>
@@ -11920,16 +11923,16 @@
         <v>46194.70208899306</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F180" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G180" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H180" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I180" s="6"/>
       <c r="J180" s="5">
@@ -11945,13 +11948,13 @@
         <v>26</v>
       </c>
       <c r="N180" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O180" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P180" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q180" s="6"/>
       <c r="R180" s="6"/>
@@ -11961,7 +11964,7 @@
     </row>
     <row r="181" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A181" s="7" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B181" s="8">
         <v>46128.56708030093</v>
@@ -11973,16 +11976,16 @@
         <v>46194.70208959491</v>
       </c>
       <c r="E181" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F181" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G181" s="9" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H181" s="9" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I181" s="9"/>
       <c r="J181" s="8">
@@ -11998,13 +12001,13 @@
         <v>26</v>
       </c>
       <c r="N181" s="9" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O181" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P181" s="9" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q181" s="9"/>
       <c r="R181" s="9"/>
@@ -12014,7 +12017,7 @@
     </row>
     <row r="182" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B182" s="5">
         <v>46128.56708731482</v>
@@ -12026,16 +12029,16 @@
         <v>46194.70209015046</v>
       </c>
       <c r="E182" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F182" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G182" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H182" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I182" s="6"/>
       <c r="J182" s="5">
@@ -12051,13 +12054,13 @@
         <v>26</v>
       </c>
       <c r="N182" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O182" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P182" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q182" s="6"/>
       <c r="R182" s="6"/>
@@ -12067,7 +12070,7 @@
     </row>
     <row r="183" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A183" s="7" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B183" s="8">
         <v>46128.567094432874</v>
@@ -12079,16 +12082,16 @@
         <v>46194.702090729166</v>
       </c>
       <c r="E183" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F183" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G183" s="9" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H183" s="9" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I183" s="9"/>
       <c r="J183" s="8">
@@ -12104,13 +12107,13 @@
         <v>26</v>
       </c>
       <c r="N183" s="9" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O183" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P183" s="9" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q183" s="9"/>
       <c r="R183" s="9"/>
@@ -12120,7 +12123,7 @@
     </row>
     <row r="184" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B184" s="5">
         <v>46128.56710209491</v>
@@ -12132,16 +12135,16 @@
         <v>46194.702091354164</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F184" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G184" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H184" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I184" s="6"/>
       <c r="J184" s="5">
@@ -12157,13 +12160,13 @@
         <v>26</v>
       </c>
       <c r="N184" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O184" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P184" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q184" s="6"/>
       <c r="R184" s="6"/>
@@ -12173,7 +12176,7 @@
     </row>
     <row r="185" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A185" s="7" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B185" s="8">
         <v>46128.56710883102</v>
@@ -12185,16 +12188,16 @@
         <v>46194.70209196759</v>
       </c>
       <c r="E185" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F185" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G185" s="9" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H185" s="9" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I185" s="9"/>
       <c r="J185" s="8">
@@ -12210,13 +12213,13 @@
         <v>26</v>
       </c>
       <c r="N185" s="9" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O185" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P185" s="9" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q185" s="9"/>
       <c r="R185" s="9"/>
@@ -12226,7 +12229,7 @@
     </row>
     <row r="186" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B186" s="5">
         <v>46128.56711633102</v>
@@ -12238,16 +12241,16 @@
         <v>46194.7020958912</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F186" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G186" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H186" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I186" s="6"/>
       <c r="J186" s="5">
@@ -12263,13 +12266,13 @@
         <v>26</v>
       </c>
       <c r="N186" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O186" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P186" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q186" s="6"/>
       <c r="R186" s="6"/>
@@ -12279,7 +12282,7 @@
     </row>
     <row r="187" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A187" s="7" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B187" s="8">
         <v>46128.56712334491</v>
@@ -12291,16 +12294,16 @@
         <v>46194.70209655093</v>
       </c>
       <c r="E187" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F187" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G187" s="9" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H187" s="9" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I187" s="9"/>
       <c r="J187" s="8">
@@ -12316,13 +12319,13 @@
         <v>26</v>
       </c>
       <c r="N187" s="9" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O187" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P187" s="9" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q187" s="9"/>
       <c r="R187" s="9"/>
@@ -12332,7 +12335,7 @@
     </row>
     <row r="188" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B188" s="5">
         <v>46191.895071886574</v>
@@ -12344,16 +12347,16 @@
         <v>46194.702097546295</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F188" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G188" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H188" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I188" s="6"/>
       <c r="J188" s="5">
@@ -12369,7 +12372,7 @@
         <v>26</v>
       </c>
       <c r="N188" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O188" s="6" t="s">
         <v>26</v>
@@ -12385,7 +12388,7 @@
     </row>
     <row r="189" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A189" s="7" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B189" s="8">
         <v>46073.7678383912</v>
@@ -12397,7 +12400,7 @@
         <v>46223.83431805555</v>
       </c>
       <c r="E189" s="9" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F189" s="9" t="s">
         <v>26</v>
@@ -12406,7 +12409,7 @@
         <v>85</v>
       </c>
       <c r="H189" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I189" s="8">
         <v>46077</v>
@@ -12424,13 +12427,13 @@
         <v>26</v>
       </c>
       <c r="N189" s="9" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O189" s="9" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P189" s="9" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q189" s="8">
         <v>46077</v>
@@ -12445,12 +12448,12 @@
         <v>1</v>
       </c>
       <c r="U189" s="12" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="190" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B190" s="5">
         <v>46128.56718193287</v>
@@ -12462,7 +12465,7 @@
         <v>46223.81033344907</v>
       </c>
       <c r="E190" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F190" s="6" t="s">
         <v>26</v>
@@ -12471,7 +12474,7 @@
         <v>85</v>
       </c>
       <c r="H190" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I190" s="5">
         <v>46077</v>
@@ -12489,13 +12492,13 @@
         <v>26</v>
       </c>
       <c r="N190" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O190" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P190" s="6" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q190" s="6"/>
       <c r="R190" s="6"/>
@@ -12505,7 +12508,7 @@
     </row>
     <row r="191" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A191" s="7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B191" s="8">
         <v>46128.567190092595</v>
@@ -12517,7 +12520,7 @@
         <v>46223.810330196764</v>
       </c>
       <c r="E191" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F191" s="9" t="s">
         <v>26</v>
@@ -12526,7 +12529,7 @@
         <v>85</v>
       </c>
       <c r="H191" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I191" s="8">
         <v>46077</v>
@@ -12544,13 +12547,13 @@
         <v>26</v>
       </c>
       <c r="N191" s="9" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O191" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P191" s="9" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q191" s="9"/>
       <c r="R191" s="9"/>
@@ -12560,7 +12563,7 @@
     </row>
     <row r="192" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B192" s="5">
         <v>46128.567196550925</v>
@@ -12572,7 +12575,7 @@
         <v>46223.810326516206</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F192" s="6" t="s">
         <v>26</v>
@@ -12581,7 +12584,7 @@
         <v>85</v>
       </c>
       <c r="H192" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I192" s="5">
         <v>46077</v>
@@ -12599,13 +12602,13 @@
         <v>26</v>
       </c>
       <c r="N192" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O192" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P192" s="6" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q192" s="6"/>
       <c r="R192" s="6"/>
@@ -12615,7 +12618,7 @@
     </row>
     <row r="193" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A193" s="7" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B193" s="8">
         <v>46128.56720474537</v>
@@ -12627,7 +12630,7 @@
         <v>46223.81032321759</v>
       </c>
       <c r="E193" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F193" s="9" t="s">
         <v>26</v>
@@ -12636,7 +12639,7 @@
         <v>85</v>
       </c>
       <c r="H193" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I193" s="8">
         <v>46077</v>
@@ -12654,13 +12657,13 @@
         <v>26</v>
       </c>
       <c r="N193" s="9" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O193" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P193" s="9" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q193" s="9"/>
       <c r="R193" s="9"/>
@@ -12670,7 +12673,7 @@
     </row>
     <row r="194" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B194" s="5">
         <v>46128.56721146991</v>
@@ -12682,7 +12685,7 @@
         <v>46223.81031929398</v>
       </c>
       <c r="E194" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F194" s="6" t="s">
         <v>26</v>
@@ -12691,7 +12694,7 @@
         <v>85</v>
       </c>
       <c r="H194" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I194" s="5">
         <v>46077</v>
@@ -12709,13 +12712,13 @@
         <v>26</v>
       </c>
       <c r="N194" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O194" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P194" s="6" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q194" s="6"/>
       <c r="R194" s="6"/>
@@ -12725,7 +12728,7 @@
     </row>
     <row r="195" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A195" s="7" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B195" s="8">
         <v>46128.56721795139</v>
@@ -12737,7 +12740,7 @@
         <v>46223.81031556713</v>
       </c>
       <c r="E195" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F195" s="9" t="s">
         <v>26</v>
@@ -12746,7 +12749,7 @@
         <v>85</v>
       </c>
       <c r="H195" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I195" s="8">
         <v>46077</v>
@@ -12764,13 +12767,13 @@
         <v>26</v>
       </c>
       <c r="N195" s="9" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O195" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P195" s="9" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q195" s="9"/>
       <c r="R195" s="9"/>
@@ -12780,7 +12783,7 @@
     </row>
     <row r="196" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B196" s="5">
         <v>46128.56722548611</v>
@@ -12792,7 +12795,7 @@
         <v>46223.81031195602</v>
       </c>
       <c r="E196" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F196" s="6" t="s">
         <v>26</v>
@@ -12801,7 +12804,7 @@
         <v>85</v>
       </c>
       <c r="H196" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I196" s="5">
         <v>46077</v>
@@ -12819,13 +12822,13 @@
         <v>26</v>
       </c>
       <c r="N196" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O196" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P196" s="6" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q196" s="6"/>
       <c r="R196" s="6"/>
@@ -12835,7 +12838,7 @@
     </row>
     <row r="197" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A197" s="7" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B197" s="8">
         <v>46128.567233333335</v>
@@ -12847,7 +12850,7 @@
         <v>46223.81029607639</v>
       </c>
       <c r="E197" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F197" s="9" t="s">
         <v>26</v>
@@ -12856,7 +12859,7 @@
         <v>85</v>
       </c>
       <c r="H197" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I197" s="8">
         <v>46077</v>
@@ -12874,13 +12877,13 @@
         <v>26</v>
       </c>
       <c r="N197" s="9" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O197" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P197" s="9" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q197" s="9"/>
       <c r="R197" s="9"/>
@@ -12890,7 +12893,7 @@
     </row>
     <row r="198" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B198" s="5">
         <v>46128.56724010417</v>
@@ -12902,7 +12905,7 @@
         <v>46223.81029530092</v>
       </c>
       <c r="E198" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F198" s="6" t="s">
         <v>26</v>
@@ -12911,7 +12914,7 @@
         <v>85</v>
       </c>
       <c r="H198" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I198" s="5">
         <v>46077</v>
@@ -12929,10 +12932,10 @@
         <v>26</v>
       </c>
       <c r="N198" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O198" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P198" s="6" t="s">
         <v>26</v>
@@ -12945,7 +12948,7 @@
     </row>
     <row r="199" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A199" s="7" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B199" s="8">
         <v>46128.56724606482</v>
@@ -12957,7 +12960,7 @@
         <v>46223.810294537034</v>
       </c>
       <c r="E199" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F199" s="9" t="s">
         <v>26</v>
@@ -12966,7 +12969,7 @@
         <v>85</v>
       </c>
       <c r="H199" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I199" s="8">
         <v>46077</v>
@@ -12984,13 +12987,13 @@
         <v>26</v>
       </c>
       <c r="N199" s="9" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O199" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P199" s="9" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q199" s="9"/>
       <c r="R199" s="9"/>
@@ -13000,7 +13003,7 @@
     </row>
     <row r="200" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B200" s="5">
         <v>46128.56725237268</v>
@@ -13012,7 +13015,7 @@
         <v>46223.810293692135</v>
       </c>
       <c r="E200" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F200" s="6" t="s">
         <v>26</v>
@@ -13021,7 +13024,7 @@
         <v>85</v>
       </c>
       <c r="H200" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I200" s="5">
         <v>46077</v>
@@ -13039,13 +13042,13 @@
         <v>26</v>
       </c>
       <c r="N200" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O200" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P200" s="6" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q200" s="6"/>
       <c r="R200" s="6"/>
@@ -13055,7 +13058,7 @@
     </row>
     <row r="201" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A201" s="7" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B201" s="8">
         <v>46128.56725944445</v>
@@ -13067,7 +13070,7 @@
         <v>46223.810292905095</v>
       </c>
       <c r="E201" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F201" s="9" t="s">
         <v>26</v>
@@ -13076,7 +13079,7 @@
         <v>85</v>
       </c>
       <c r="H201" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I201" s="8">
         <v>46077</v>
@@ -13094,13 +13097,13 @@
         <v>26</v>
       </c>
       <c r="N201" s="9" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O201" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P201" s="9" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q201" s="9"/>
       <c r="R201" s="9"/>
@@ -13110,7 +13113,7 @@
     </row>
     <row r="202" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B202" s="5">
         <v>46073.76783868056</v>
@@ -13122,16 +13125,16 @@
         <v>46195.89050030093</v>
       </c>
       <c r="E202" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F202" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G202" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H202" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I202" s="6"/>
       <c r="J202" s="5">
@@ -13147,13 +13150,13 @@
         <v>26</v>
       </c>
       <c r="N202" s="6" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O202" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P202" s="6" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q202" s="5">
         <v>46078</v>
@@ -13168,12 +13171,12 @@
         <v>1</v>
       </c>
       <c r="U202" s="12" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="203" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A203" s="7" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B203" s="8">
         <v>46128.567313437496</v>
@@ -13185,16 +13188,16 @@
         <v>46195.88862107639</v>
       </c>
       <c r="E203" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F203" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G203" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H203" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I203" s="9"/>
       <c r="J203" s="8">
@@ -13210,13 +13213,13 @@
         <v>26</v>
       </c>
       <c r="N203" s="9" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O203" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P203" s="9" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q203" s="9"/>
       <c r="R203" s="9"/>
@@ -13226,7 +13229,7 @@
     </row>
     <row r="204" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B204" s="5">
         <v>46128.56732054398</v>
@@ -13238,16 +13241,16 @@
         <v>46195.88851415509</v>
       </c>
       <c r="E204" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F204" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G204" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H204" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I204" s="6"/>
       <c r="J204" s="5">
@@ -13263,13 +13266,13 @@
         <v>26</v>
       </c>
       <c r="N204" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O204" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P204" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q204" s="6"/>
       <c r="R204" s="6"/>
@@ -13279,7 +13282,7 @@
     </row>
     <row r="205" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A205" s="7" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B205" s="8">
         <v>46128.5673266088</v>
@@ -13291,16 +13294,16 @@
         <v>46195.88871565972</v>
       </c>
       <c r="E205" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F205" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G205" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H205" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I205" s="9"/>
       <c r="J205" s="8">
@@ -13316,13 +13319,13 @@
         <v>26</v>
       </c>
       <c r="N205" s="9" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O205" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P205" s="9" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q205" s="9"/>
       <c r="R205" s="9"/>
@@ -13332,7 +13335,7 @@
     </row>
     <row r="206" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B206" s="5">
         <v>46128.56733295139</v>
@@ -13344,16 +13347,16 @@
         <v>46195.89041287037</v>
       </c>
       <c r="E206" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F206" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G206" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H206" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I206" s="6"/>
       <c r="J206" s="5">
@@ -13369,13 +13372,13 @@
         <v>26</v>
       </c>
       <c r="N206" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O206" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P206" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q206" s="6"/>
       <c r="R206" s="6"/>
@@ -13385,7 +13388,7 @@
     </row>
     <row r="207" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A207" s="7" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B207" s="8">
         <v>46128.56733854167</v>
@@ -13397,16 +13400,16 @@
         <v>46195.89042275463</v>
       </c>
       <c r="E207" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F207" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G207" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H207" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I207" s="9"/>
       <c r="J207" s="8">
@@ -13422,13 +13425,13 @@
         <v>26</v>
       </c>
       <c r="N207" s="9" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O207" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P207" s="9" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q207" s="9"/>
       <c r="R207" s="9"/>
@@ -13438,7 +13441,7 @@
     </row>
     <row r="208" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B208" s="5">
         <v>46128.56734518518</v>
@@ -13450,16 +13453,16 @@
         <v>46195.89043167824</v>
       </c>
       <c r="E208" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F208" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G208" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H208" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I208" s="6"/>
       <c r="J208" s="5">
@@ -13475,13 +13478,13 @@
         <v>26</v>
       </c>
       <c r="N208" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O208" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P208" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q208" s="6"/>
       <c r="R208" s="6"/>
@@ -13491,7 +13494,7 @@
     </row>
     <row r="209" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A209" s="7" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B209" s="8">
         <v>46128.567351770835</v>
@@ -13503,16 +13506,16 @@
         <v>46195.89044037037</v>
       </c>
       <c r="E209" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F209" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G209" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H209" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I209" s="9"/>
       <c r="J209" s="8">
@@ -13528,13 +13531,13 @@
         <v>26</v>
       </c>
       <c r="N209" s="9" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O209" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P209" s="9" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q209" s="9"/>
       <c r="R209" s="9"/>
@@ -13544,7 +13547,7 @@
     </row>
     <row r="210" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B210" s="5">
         <v>46128.56735738426</v>
@@ -13556,16 +13559,16 @@
         <v>46195.890446805555</v>
       </c>
       <c r="E210" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F210" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G210" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H210" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I210" s="6"/>
       <c r="J210" s="5">
@@ -13581,13 +13584,13 @@
         <v>26</v>
       </c>
       <c r="N210" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O210" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P210" s="6" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q210" s="6"/>
       <c r="R210" s="6"/>
@@ -13597,7 +13600,7 @@
     </row>
     <row r="211" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A211" s="7" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B211" s="8">
         <v>46128.56736256945</v>
@@ -13609,16 +13612,16 @@
         <v>46195.89045333333</v>
       </c>
       <c r="E211" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F211" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G211" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H211" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I211" s="9"/>
       <c r="J211" s="8">
@@ -13634,13 +13637,13 @@
         <v>26</v>
       </c>
       <c r="N211" s="9" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O211" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P211" s="9" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q211" s="9"/>
       <c r="R211" s="9"/>
@@ -13650,7 +13653,7 @@
     </row>
     <row r="212" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B212" s="5">
         <v>46128.567368206015</v>
@@ -13662,16 +13665,16 @@
         <v>46195.890462361116</v>
       </c>
       <c r="E212" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F212" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G212" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H212" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I212" s="6"/>
       <c r="J212" s="5">
@@ -13687,13 +13690,13 @@
         <v>26</v>
       </c>
       <c r="N212" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O212" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P212" s="6" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q212" s="6"/>
       <c r="R212" s="6"/>
@@ -13703,7 +13706,7 @@
     </row>
     <row r="213" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A213" s="7" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B213" s="8">
         <v>46128.56737366898</v>
@@ -13715,16 +13718,16 @@
         <v>46195.89046699074</v>
       </c>
       <c r="E213" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F213" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G213" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H213" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I213" s="9"/>
       <c r="J213" s="8">
@@ -13740,13 +13743,13 @@
         <v>26</v>
       </c>
       <c r="N213" s="9" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O213" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P213" s="9" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q213" s="9"/>
       <c r="R213" s="9"/>
@@ -13756,7 +13759,7 @@
     </row>
     <row r="214" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B214" s="5">
         <v>46128.56737853009</v>
@@ -13768,16 +13771,16 @@
         <v>46195.89048138889</v>
       </c>
       <c r="E214" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F214" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G214" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H214" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I214" s="6"/>
       <c r="J214" s="5">
@@ -13793,13 +13796,13 @@
         <v>26</v>
       </c>
       <c r="N214" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O214" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P214" s="6" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q214" s="6"/>
       <c r="R214" s="6"/>
@@ -13809,7 +13812,7 @@
     </row>
     <row r="215" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A215" s="7" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B215" s="8">
         <v>46073.76783895833</v>
@@ -13821,16 +13824,16 @@
         <v>46195.890647175926</v>
       </c>
       <c r="E215" s="9" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F215" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G215" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H215" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I215" s="9"/>
       <c r="J215" s="8">
@@ -13846,13 +13849,13 @@
         <v>26</v>
       </c>
       <c r="N215" s="9" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O215" s="9" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P215" s="9" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Q215" s="8">
         <v>46079</v>
@@ -13867,12 +13870,12 @@
         <v>1</v>
       </c>
       <c r="U215" s="12" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="216" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B216" s="5">
         <v>46128.56746619213</v>
@@ -13884,16 +13887,16 @@
         <v>46195.890533206024</v>
       </c>
       <c r="E216" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F216" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G216" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H216" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I216" s="6"/>
       <c r="J216" s="5">
@@ -13909,13 +13912,13 @@
         <v>26</v>
       </c>
       <c r="N216" s="6" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O216" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P216" s="6" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q216" s="6"/>
       <c r="R216" s="6"/>
@@ -13925,7 +13928,7 @@
     </row>
     <row r="217" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A217" s="7" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B217" s="8">
         <v>46128.56747375</v>
@@ -13937,16 +13940,16 @@
         <v>46195.890539699074</v>
       </c>
       <c r="E217" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F217" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G217" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H217" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I217" s="9"/>
       <c r="J217" s="8">
@@ -13962,13 +13965,13 @@
         <v>26</v>
       </c>
       <c r="N217" s="9" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O217" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P217" s="9" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q217" s="9"/>
       <c r="R217" s="9"/>
@@ -13978,7 +13981,7 @@
     </row>
     <row r="218" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B218" s="5">
         <v>46128.567480833335</v>
@@ -13990,16 +13993,16 @@
         <v>46195.890547476854</v>
       </c>
       <c r="E218" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F218" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G218" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H218" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I218" s="6"/>
       <c r="J218" s="5">
@@ -14015,13 +14018,13 @@
         <v>26</v>
       </c>
       <c r="N218" s="6" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O218" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P218" s="6" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q218" s="6"/>
       <c r="R218" s="6"/>
@@ -14031,7 +14034,7 @@
     </row>
     <row r="219" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A219" s="7" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B219" s="8">
         <v>46128.56748863426</v>
@@ -14043,16 +14046,16 @@
         <v>46195.890552048615</v>
       </c>
       <c r="E219" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F219" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G219" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H219" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I219" s="9"/>
       <c r="J219" s="8">
@@ -14068,13 +14071,13 @@
         <v>26</v>
       </c>
       <c r="N219" s="9" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O219" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P219" s="9" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q219" s="9"/>
       <c r="R219" s="9"/>
@@ -14084,7 +14087,7 @@
     </row>
     <row r="220" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A220" s="4" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B220" s="5">
         <v>46128.5674962037</v>
@@ -14096,16 +14099,16 @@
         <v>46195.890559074076</v>
       </c>
       <c r="E220" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F220" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G220" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H220" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I220" s="6"/>
       <c r="J220" s="5">
@@ -14121,13 +14124,13 @@
         <v>26</v>
       </c>
       <c r="N220" s="6" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O220" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P220" s="6" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q220" s="6"/>
       <c r="R220" s="6"/>
@@ -14137,7 +14140,7 @@
     </row>
     <row r="221" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A221" s="7" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B221" s="8">
         <v>46128.567504074075</v>
@@ -14149,16 +14152,16 @@
         <v>46195.89058465278</v>
       </c>
       <c r="E221" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F221" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G221" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H221" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I221" s="9"/>
       <c r="J221" s="8">
@@ -14174,13 +14177,13 @@
         <v>26</v>
       </c>
       <c r="N221" s="9" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O221" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P221" s="9" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q221" s="9"/>
       <c r="R221" s="9"/>
@@ -14190,7 +14193,7 @@
     </row>
     <row r="222" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A222" s="4" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B222" s="5">
         <v>46128.56751277778</v>
@@ -14202,16 +14205,16 @@
         <v>46195.8905709838</v>
       </c>
       <c r="E222" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F222" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G222" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H222" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I222" s="6"/>
       <c r="J222" s="5">
@@ -14227,13 +14230,13 @@
         <v>26</v>
       </c>
       <c r="N222" s="6" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O222" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P222" s="6" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q222" s="6"/>
       <c r="R222" s="6"/>
@@ -14243,7 +14246,7 @@
     </row>
     <row r="223" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A223" s="7" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B223" s="8">
         <v>46128.56752138889</v>
@@ -14255,16 +14258,16 @@
         <v>46195.89059417824</v>
       </c>
       <c r="E223" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F223" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G223" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H223" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I223" s="9"/>
       <c r="J223" s="8">
@@ -14280,13 +14283,13 @@
         <v>26</v>
       </c>
       <c r="N223" s="9" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O223" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P223" s="9" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q223" s="9"/>
       <c r="R223" s="9"/>
@@ -14296,7 +14299,7 @@
     </row>
     <row r="224" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A224" s="4" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B224" s="5">
         <v>46128.56752835648</v>
@@ -14308,16 +14311,16 @@
         <v>46195.89060789352</v>
       </c>
       <c r="E224" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F224" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G224" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H224" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I224" s="6"/>
       <c r="J224" s="5">
@@ -14333,13 +14336,13 @@
         <v>26</v>
       </c>
       <c r="N224" s="6" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O224" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P224" s="6" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q224" s="6"/>
       <c r="R224" s="6"/>
@@ -14349,7 +14352,7 @@
     </row>
     <row r="225" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A225" s="7" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B225" s="8">
         <v>46128.567536284725</v>
@@ -14361,16 +14364,16 @@
         <v>46195.890617060184</v>
       </c>
       <c r="E225" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F225" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G225" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H225" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I225" s="9"/>
       <c r="J225" s="8">
@@ -14386,13 +14389,13 @@
         <v>26</v>
       </c>
       <c r="N225" s="9" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O225" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P225" s="9" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q225" s="9"/>
       <c r="R225" s="9"/>
@@ -14402,7 +14405,7 @@
     </row>
     <row r="226" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A226" s="4" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B226" s="5">
         <v>46128.56754392361</v>
@@ -14414,16 +14417,16 @@
         <v>46195.89062482639</v>
       </c>
       <c r="E226" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F226" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G226" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H226" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I226" s="6"/>
       <c r="J226" s="5">
@@ -14439,13 +14442,13 @@
         <v>26</v>
       </c>
       <c r="N226" s="6" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O226" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P226" s="6" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q226" s="6"/>
       <c r="R226" s="6"/>
@@ -14455,7 +14458,7 @@
     </row>
     <row r="227" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A227" s="7" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B227" s="8">
         <v>46128.567550949076</v>
@@ -14467,16 +14470,16 @@
         <v>46195.89063229167</v>
       </c>
       <c r="E227" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F227" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G227" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H227" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I227" s="9"/>
       <c r="J227" s="8">
@@ -14492,13 +14495,13 @@
         <v>26</v>
       </c>
       <c r="N227" s="9" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O227" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P227" s="9" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q227" s="9"/>
       <c r="R227" s="9"/>
@@ -14508,7 +14511,7 @@
     </row>
     <row r="228" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A228" s="4" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B228" s="5">
         <v>46073.76783957176</v>
@@ -14518,7 +14521,7 @@
         <v>46076.83478885417</v>
       </c>
       <c r="E228" s="6" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F228" s="6" t="s">
         <v>25</v>
@@ -14542,7 +14545,7 @@
         <v>26</v>
       </c>
       <c r="O228" s="6" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="P228" s="6" t="s">
         <v>26</v>
@@ -14555,7 +14558,7 @@
     </row>
     <row r="229" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A229" s="7" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B229" s="8">
         <v>46073.76783986111</v>
@@ -14565,16 +14568,16 @@
         <v>46191.79694986111</v>
       </c>
       <c r="E229" s="9" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F229" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G229" s="9" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H229" s="9" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="I229" s="8">
         <v>46080</v>
@@ -14592,13 +14595,13 @@
         <v>26</v>
       </c>
       <c r="N229" s="9" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O229" s="9" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="P229" s="9" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Q229" s="8">
         <v>46080</v>
@@ -14613,12 +14616,12 @@
         <v>0</v>
       </c>
       <c r="U229" s="12" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="230" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A230" s="4" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B230" s="5">
         <v>46073.767840127315</v>
@@ -14628,16 +14631,16 @@
         <v>46191.79695027778</v>
       </c>
       <c r="E230" s="6" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F230" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G230" s="6" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H230" s="6" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="I230" s="5">
         <v>46080</v>
@@ -14655,13 +14658,13 @@
         <v>26</v>
       </c>
       <c r="N230" s="6" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O230" s="6" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="P230" s="6" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Q230" s="5">
         <v>46080</v>
@@ -14676,12 +14679,12 @@
         <v>0</v>
       </c>
       <c r="U230" s="12" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="231" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A231" s="7" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B231" s="8">
         <v>46090.63839974537</v>
@@ -14691,7 +14694,7 @@
         <v>46091.862923043984</v>
       </c>
       <c r="E231" s="9" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F231" s="9" t="s">
         <v>25</v>
@@ -14715,7 +14718,7 @@
         <v>26</v>
       </c>
       <c r="O231" s="9" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="P231" s="9" t="s">
         <v>26</v>
@@ -14730,7 +14733,7 @@
     </row>
     <row r="232" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A232" s="4" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B232" s="5">
         <v>46090.638496851854</v>
@@ -14740,7 +14743,7 @@
         <v>46191.79695047454</v>
       </c>
       <c r="E232" s="6" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F232" s="6" t="s">
         <v>26</v>
@@ -14767,13 +14770,13 @@
         <v>26</v>
       </c>
       <c r="N232" s="6" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="O232" s="6" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="P232" s="6" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="Q232" s="5">
         <v>46080</v>
@@ -14788,12 +14791,12 @@
         <v>0</v>
       </c>
       <c r="U232" s="12" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="233" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A233" s="7" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B233" s="8">
         <v>46090.63872243055</v>
@@ -14803,7 +14806,7 @@
         <v>46100.13550428241</v>
       </c>
       <c r="E233" s="9" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F233" s="9" t="s">
         <v>26</v>
@@ -14830,13 +14833,13 @@
         <v>26</v>
       </c>
       <c r="N233" s="9" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="O233" s="9" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="P233" s="9" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="Q233" s="8">
         <v>46091</v>
@@ -14851,7 +14854,7 @@
         <v>0</v>
       </c>
       <c r="U233" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001501 - EQ MIN LA HACIENDA B.xlsx
+++ b/data/50001501 - EQ MIN LA HACIENDA B.xlsx
@@ -3241,7 +3241,7 @@
         <v>46191.89589885417</v>
       </c>
       <c r="D25" s="8">
-        <v>46191.89593702546</v>
+        <v>46229.259856944445</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>94</v>
@@ -4536,7 +4536,7 @@
         <v>46192.76206953704</v>
       </c>
       <c r="D46" s="5">
-        <v>46192.76208826389</v>
+        <v>46228.84693856481</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>164</v>
@@ -10192,7 +10192,7 @@
         <v>46191.795175555555</v>
       </c>
       <c r="D148" s="5">
-        <v>46223.80892216435</v>
+        <v>46229.044279050926</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>316</v>
@@ -12397,7 +12397,7 @@
         <v>46191.796778240736</v>
       </c>
       <c r="D189" s="8">
-        <v>46223.83431805555</v>
+        <v>46229.2514682176</v>
       </c>
       <c r="E189" s="9" t="s">
         <v>372</v>
@@ -13122,7 +13122,7 @@
         <v>46191.79687179398</v>
       </c>
       <c r="D202" s="5">
-        <v>46195.89050030093</v>
+        <v>46228.84701641204</v>
       </c>
       <c r="E202" s="6" t="s">
         <v>387</v>

--- a/data/50001501 - EQ MIN LA HACIENDA B.xlsx
+++ b/data/50001501 - EQ MIN LA HACIENDA B.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2669" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2670" uniqueCount="435">
   <si>
     <t>50001501 - EQ. MIN. LA HACIENDA</t>
   </si>
@@ -14516,9 +14516,11 @@
       <c r="B228" s="5">
         <v>46073.76783957176</v>
       </c>
-      <c r="C228" s="6"/>
+      <c r="C228" s="5">
+        <v>46232.662294340276</v>
+      </c>
       <c r="D228" s="5">
-        <v>46076.83478885417</v>
+        <v>46232.66230726852</v>
       </c>
       <c r="E228" s="6" t="s">
         <v>418</v>
@@ -14553,8 +14555,12 @@
       <c r="Q228" s="6"/>
       <c r="R228" s="6"/>
       <c r="S228" s="6"/>
-      <c r="T228" s="6"/>
-      <c r="U228" s="6"/>
+      <c r="T228" s="6">
+        <v>1</v>
+      </c>
+      <c r="U228" s="11" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="229" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A229" s="7" t="s">
@@ -14563,9 +14569,11 @@
       <c r="B229" s="8">
         <v>46073.76783986111</v>
       </c>
-      <c r="C229" s="9"/>
+      <c r="C229" s="8">
+        <v>46232.66227519676</v>
+      </c>
       <c r="D229" s="8">
-        <v>46191.79694986111</v>
+        <v>46232.6622944213</v>
       </c>
       <c r="E229" s="9" t="s">
         <v>421</v>
@@ -14613,10 +14621,10 @@
         <v>31</v>
       </c>
       <c r="T229" s="9">
-        <v>0</v>
-      </c>
-      <c r="U229" s="12" t="s">
-        <v>168</v>
+        <v>1</v>
+      </c>
+      <c r="U229" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="230" spans="1:21" x14ac:dyDescent="0.25">
@@ -14626,9 +14634,11 @@
       <c r="B230" s="5">
         <v>46073.767840127315</v>
       </c>
-      <c r="C230" s="6"/>
+      <c r="C230" s="5">
+        <v>46232.66228113426</v>
+      </c>
       <c r="D230" s="5">
-        <v>46191.79695027778</v>
+        <v>46232.66229778936</v>
       </c>
       <c r="E230" s="6" t="s">
         <v>425</v>
@@ -14676,10 +14686,10 @@
         <v>31</v>
       </c>
       <c r="T230" s="6">
-        <v>0</v>
-      </c>
-      <c r="U230" s="12" t="s">
-        <v>168</v>
+        <v>1</v>
+      </c>
+      <c r="U230" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="231" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001501 - EQ MIN LA HACIENDA B.xlsx
+++ b/data/50001501 - EQ MIN LA HACIENDA B.xlsx
@@ -2808,7 +2808,7 @@
         <v>46122.65802675926</v>
       </c>
       <c r="D18" s="5">
-        <v>46146.4968544213</v>
+        <v>46237.23478893518</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>72</v>
@@ -5536,7 +5536,7 @@
         <v>46146.89556576389</v>
       </c>
       <c r="D64" s="5">
-        <v>46158.97116490741</v>
+        <v>46237.51246947917</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>206</v>
@@ -5586,8 +5586,8 @@
       <c r="T64" s="6">
         <v>1</v>
       </c>
-      <c r="U64" s="12" t="s">
-        <v>168</v>
+      <c r="U64" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
@@ -7013,7 +7013,7 @@
         <v>46157.49932912037</v>
       </c>
       <c r="D91" s="8">
-        <v>46157.499330590275</v>
+        <v>46237.51271008102</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>242</v>
@@ -7061,8 +7061,8 @@
       <c r="T91" s="9">
         <v>0.2</v>
       </c>
-      <c r="U91" s="12" t="s">
-        <v>168</v>
+      <c r="U91" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
@@ -7141,7 +7141,7 @@
         <v>46157.499181701394</v>
       </c>
       <c r="D93" s="8">
-        <v>46157.49918305555</v>
+        <v>46237.51273736111</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>246</v>
@@ -7189,8 +7189,8 @@
       <c r="T93" s="9">
         <v>0</v>
       </c>
-      <c r="U93" s="12" t="s">
-        <v>168</v>
+      <c r="U93" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
@@ -8744,7 +8744,7 @@
         <v>46191.793681041665</v>
       </c>
       <c r="D122" s="5">
-        <v>46223.8093071412</v>
+        <v>46237.51276747685</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>285</v>
@@ -8794,8 +8794,8 @@
       <c r="T122" s="6">
         <v>1</v>
       </c>
-      <c r="U122" s="12" t="s">
-        <v>168</v>
+      <c r="U122" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
@@ -10192,7 +10192,7 @@
         <v>46191.795175555555</v>
       </c>
       <c r="D148" s="5">
-        <v>46229.044279050926</v>
+        <v>46237.512785115745</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>316</v>
@@ -10240,8 +10240,8 @@
       <c r="T148" s="6">
         <v>1</v>
       </c>
-      <c r="U148" s="12" t="s">
-        <v>168</v>
+      <c r="U148" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
@@ -10891,7 +10891,7 @@
         <v>46191.7954187963</v>
       </c>
       <c r="D161" s="8">
-        <v>46223.80891503472</v>
+        <v>46237.51280224537</v>
       </c>
       <c r="E161" s="9" t="s">
         <v>332</v>
@@ -10939,8 +10939,8 @@
       <c r="T161" s="9">
         <v>1</v>
       </c>
-      <c r="U161" s="12" t="s">
-        <v>168</v>
+      <c r="U161" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.25">
@@ -11590,7 +11590,7 @@
         <v>46193.560764988426</v>
       </c>
       <c r="D174" s="5">
-        <v>46193.561065925926</v>
+        <v>46237.51287908565</v>
       </c>
       <c r="E174" s="6" t="s">
         <v>348</v>
@@ -11628,8 +11628,8 @@
       <c r="T174" s="6">
         <v>1</v>
       </c>
-      <c r="U174" s="12" t="s">
-        <v>168</v>
+      <c r="U174" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="175" spans="1:21" x14ac:dyDescent="0.25">
@@ -11643,7 +11643,7 @@
         <v>46193.56105240741</v>
       </c>
       <c r="D175" s="8">
-        <v>46194.709360277775</v>
+        <v>46237.51289789352</v>
       </c>
       <c r="E175" s="9" t="s">
         <v>351</v>
@@ -11693,8 +11693,8 @@
       <c r="T175" s="9">
         <v>1</v>
       </c>
-      <c r="U175" s="12" t="s">
-        <v>168</v>
+      <c r="U175" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="176" spans="1:21" x14ac:dyDescent="0.25">
@@ -13122,7 +13122,7 @@
         <v>46191.79687179398</v>
       </c>
       <c r="D202" s="5">
-        <v>46228.84701641204</v>
+        <v>46237.512960023145</v>
       </c>
       <c r="E202" s="6" t="s">
         <v>387</v>
@@ -13170,8 +13170,8 @@
       <c r="T202" s="6">
         <v>1</v>
       </c>
-      <c r="U202" s="12" t="s">
-        <v>168</v>
+      <c r="U202" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="203" spans="1:21" x14ac:dyDescent="0.25">
@@ -13821,7 +13821,7 @@
         <v>46191.79693015046</v>
       </c>
       <c r="D215" s="8">
-        <v>46195.890647175926</v>
+        <v>46237.51300291667</v>
       </c>
       <c r="E215" s="9" t="s">
         <v>403</v>
@@ -13869,8 +13869,8 @@
       <c r="T215" s="9">
         <v>1</v>
       </c>
-      <c r="U215" s="12" t="s">
-        <v>168</v>
+      <c r="U215" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="216" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001501 - EQ MIN LA HACIENDA B.xlsx
+++ b/data/50001501 - EQ MIN LA HACIENDA B.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2670" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2634" uniqueCount="427">
   <si>
     <t>50001501 - EQ. MIN. LA HACIENDA</t>
   </si>
@@ -1225,7 +1225,7 @@
     <t>Despacho</t>
   </si>
   <si>
-    <t>Gestion,Costos,Logistica:,Instalación de componentes</t>
+    <t>Gestion,Costos,Logistica:</t>
   </si>
   <si>
     <t>1214075676500864</t>
@@ -1292,30 +1292,6 @@
   </si>
   <si>
     <t>Despacho,Analisis de costeo</t>
-  </si>
-  <si>
-    <t>1213575386156251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puesta en marcha Servicios </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Instalación de componentes,Pruebas de instalación de componentes </t>
-  </si>
-  <si>
-    <t>1213575386156253</t>
-  </si>
-  <si>
-    <t>Instalación de componentes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pruebas de instalación de componentes ,Puesta en marcha Servicios </t>
-  </si>
-  <si>
-    <t>1213575386156257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pruebas de instalación de componentes </t>
   </si>
 </sst>
 </file>
@@ -1839,7 +1815,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U233"/>
+  <dimension ref="A1:U230"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10.4" customWidth="1"/>
@@ -13821,7 +13797,7 @@
         <v>46191.79693015046</v>
       </c>
       <c r="D215" s="8">
-        <v>46237.51300291667</v>
+        <v>46240.71985862269</v>
       </c>
       <c r="E215" s="9" t="s">
         <v>403</v>
@@ -14690,181 +14666,6 @@
       </c>
       <c r="U230" s="11" t="s">
         <v>32</v>
-      </c>
-    </row>
-    <row r="231" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A231" s="7" t="s">
-        <v>427</v>
-      </c>
-      <c r="B231" s="8">
-        <v>46090.63839974537</v>
-      </c>
-      <c r="C231" s="9"/>
-      <c r="D231" s="8">
-        <v>46091.862923043984</v>
-      </c>
-      <c r="E231" s="9" t="s">
-        <v>428</v>
-      </c>
-      <c r="F231" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G231" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H231" s="9"/>
-      <c r="I231" s="9"/>
-      <c r="J231" s="9"/>
-      <c r="K231" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L231" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M231" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="N231" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="O231" s="9" t="s">
-        <v>429</v>
-      </c>
-      <c r="P231" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q231" s="9"/>
-      <c r="R231" s="9"/>
-      <c r="S231" s="9"/>
-      <c r="T231" s="9">
-        <v>0</v>
-      </c>
-      <c r="U231" s="9"/>
-    </row>
-    <row r="232" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A232" s="4" t="s">
-        <v>430</v>
-      </c>
-      <c r="B232" s="5">
-        <v>46090.638496851854</v>
-      </c>
-      <c r="C232" s="6"/>
-      <c r="D232" s="5">
-        <v>46191.79695047454</v>
-      </c>
-      <c r="E232" s="6" t="s">
-        <v>431</v>
-      </c>
-      <c r="F232" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G232" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="H232" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="I232" s="5">
-        <v>46080</v>
-      </c>
-      <c r="J232" s="5">
-        <v>46090</v>
-      </c>
-      <c r="K232" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L232" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M232" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N232" s="6" t="s">
-        <v>428</v>
-      </c>
-      <c r="O232" s="6" t="s">
-        <v>403</v>
-      </c>
-      <c r="P232" s="6" t="s">
-        <v>432</v>
-      </c>
-      <c r="Q232" s="5">
-        <v>46080</v>
-      </c>
-      <c r="R232" s="5">
-        <v>46090</v>
-      </c>
-      <c r="S232" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="T232" s="6">
-        <v>0</v>
-      </c>
-      <c r="U232" s="12" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="233" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A233" s="7" t="s">
-        <v>433</v>
-      </c>
-      <c r="B233" s="8">
-        <v>46090.63872243055</v>
-      </c>
-      <c r="C233" s="9"/>
-      <c r="D233" s="8">
-        <v>46100.13550428241</v>
-      </c>
-      <c r="E233" s="9" t="s">
-        <v>434</v>
-      </c>
-      <c r="F233" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G233" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="H233" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="I233" s="8">
-        <v>46091</v>
-      </c>
-      <c r="J233" s="8">
-        <v>46099</v>
-      </c>
-      <c r="K233" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L233" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M233" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N233" s="9" t="s">
-        <v>428</v>
-      </c>
-      <c r="O233" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="P233" s="9" t="s">
-        <v>428</v>
-      </c>
-      <c r="Q233" s="8">
-        <v>46091</v>
-      </c>
-      <c r="R233" s="8">
-        <v>46099</v>
-      </c>
-      <c r="S233" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="T233" s="9">
-        <v>0</v>
-      </c>
-      <c r="U233" s="10" t="s">
-        <v>105</v>
       </c>
     </row>
   </sheetData>
